--- a/Chronos_Vainqueurs.xlsx
+++ b/Chronos_Vainqueurs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$357</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$360</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E357"/>
+  <dimension ref="A1:E360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="C124" s="3" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>2:04:01</t>
+          <t>2:05:41</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:18:58</t>
         </is>
       </c>
     </row>
@@ -3599,16 +3599,16 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>2:04:39</t>
+          <t>2:04:01</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>2:17:26</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3624,16 +3624,16 @@
         </is>
       </c>
       <c r="C126" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>2:01:25</t>
+          <t>2:04:39</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>2:18:33</t>
+          <t>2:17:26</t>
         </is>
       </c>
     </row>
@@ -3649,16 +3649,16 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>2:04:01</t>
+          <t>2:01:25</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>2:16:16</t>
+          <t>2:18:33</t>
         </is>
       </c>
     </row>
@@ -3674,23 +3674,23 @@
         </is>
       </c>
       <c r="C128" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>2:02:27</t>
+          <t>2:04:01</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>2:15:50</t>
+          <t>2:16:16</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>TCS New York City Marathon</t>
+          <t>TCS London Marathon</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
@@ -3699,16 +3699,16 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>2:10:34</t>
+          <t>2:02:27</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>2:24:25</t>
+          <t>2:15:50</t>
         </is>
       </c>
     </row>
@@ -3724,16 +3724,16 @@
         </is>
       </c>
       <c r="C130" s="3" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>2:07:51</t>
+          <t>2:10:34</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>2:24:26</t>
+          <t>2:24:25</t>
         </is>
       </c>
     </row>
@@ -3749,16 +3749,16 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>2:10:53</t>
+          <t>2:07:51</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:24:26</t>
         </is>
       </c>
     </row>
@@ -3774,16 +3774,16 @@
         </is>
       </c>
       <c r="C132" s="3" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>2:05:59</t>
+          <t>2:10:53</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>2:22:48</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3799,16 +3799,16 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>2:08:13</t>
+          <t>2:05:59</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>2:22:38</t>
+          <t>2:22:48</t>
         </is>
       </c>
     </row>
@@ -3824,16 +3824,16 @@
         </is>
       </c>
       <c r="C134" s="3" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>2:08:22</t>
+          <t>2:08:13</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>2:22:39</t>
+          <t>2:22:38</t>
         </is>
       </c>
     </row>
@@ -3849,16 +3849,16 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>2:08:41</t>
+          <t>2:08:22</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>2:23:23</t>
+          <t>2:22:39</t>
         </is>
       </c>
     </row>
@@ -3874,16 +3874,16 @@
         </is>
       </c>
       <c r="C136" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>2:04:58</t>
+          <t>2:08:41</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>2:27:23</t>
+          <t>2:23:23</t>
         </is>
       </c>
     </row>
@@ -3899,16 +3899,16 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>2:07:39</t>
+          <t>2:04:58</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>2:24:35</t>
+          <t>2:27:23</t>
         </is>
       </c>
     </row>
@@ -3924,23 +3924,23 @@
         </is>
       </c>
       <c r="C138" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>2:08:09</t>
+          <t>2:07:39</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>2:19:51</t>
+          <t>2:24:35</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>TCS Sydney Marathon presented by ASICS</t>
+          <t>TCS New York City Marathon</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
@@ -3949,16 +3949,16 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>2:08:20</t>
+          <t>2:08:09</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>2:26:47</t>
+          <t>2:19:51</t>
         </is>
       </c>
     </row>
@@ -3974,16 +3974,16 @@
         </is>
       </c>
       <c r="C140" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>2:06:17</t>
+          <t>2:08:20</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>2:21:40</t>
+          <t>2:26:47</t>
         </is>
       </c>
     </row>
@@ -3999,23 +3999,23 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>2:06:06</t>
+          <t>2:06:17</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>2:18:22</t>
+          <t>2:21:40</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon</t>
+          <t>TCS Sydney Marathon presented by ASICS</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4024,16 +4024,16 @@
         </is>
       </c>
       <c r="C142" s="3" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>2:09:20</t>
+          <t>2:06:06</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>2:23:11</t>
+          <t>2:18:22</t>
         </is>
       </c>
     </row>
@@ -4049,16 +4049,16 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>2:07:16</t>
+          <t>2:09:20</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>2:20:44</t>
+          <t>2:23:11</t>
         </is>
       </c>
     </row>
@@ -4074,23 +4074,23 @@
         </is>
       </c>
       <c r="C144" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>2:08:05</t>
+          <t>2:07:16</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>2:21:04</t>
+          <t>2:20:44</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>Taipei Marathon</t>
+          <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
@@ -4099,16 +4099,16 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>2:11:05</t>
+          <t>2:08:05</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>2:27:14</t>
+          <t>2:21:04</t>
         </is>
       </c>
     </row>
@@ -4124,16 +4124,16 @@
         </is>
       </c>
       <c r="C146" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>2:11:41</t>
+          <t>2:11:05</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>2:32:47</t>
+          <t>2:27:14</t>
         </is>
       </c>
     </row>
@@ -4149,23 +4149,23 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:11:41</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:32:47</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon</t>
+          <t>Taipei Marathon</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4174,16 +4174,16 @@
         </is>
       </c>
       <c r="C148" s="3" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>2:07:32</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>2:24:15</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4199,16 +4199,16 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>2:07:50</t>
+          <t>2:07:32</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>2:26:06</t>
+          <t>2:24:15</t>
         </is>
       </c>
     </row>
@@ -4224,16 +4224,16 @@
         </is>
       </c>
       <c r="C150" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>2:11:44</t>
+          <t>2:07:50</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>2:24:56</t>
+          <t>2:26:06</t>
         </is>
       </c>
     </row>
@@ -4249,23 +4249,23 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>2:09:55</t>
+          <t>2:11:44</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>2:25:13</t>
+          <t>2:24:56</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Tokyo Marathon</t>
+          <t>Tata Mumbai Marathon</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4274,16 +4274,16 @@
         </is>
       </c>
       <c r="C152" s="3" t="n">
-        <v>2015</v>
+        <v>2026</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>2:06:00</t>
+          <t>2:09:55</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>2:23:15</t>
+          <t>2:25:13</t>
         </is>
       </c>
     </row>
@@ -4299,16 +4299,16 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>2:06:56</t>
+          <t>2:06:00</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>2:21:27</t>
+          <t>2:23:15</t>
         </is>
       </c>
     </row>
@@ -4324,16 +4324,16 @@
         </is>
       </c>
       <c r="C154" s="3" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>2:03:58</t>
+          <t>2:06:56</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:21:27</t>
         </is>
       </c>
     </row>
@@ -4349,16 +4349,16 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>2:05:30</t>
+          <t>2:03:58</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>2:19:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4374,16 +4374,16 @@
         </is>
       </c>
       <c r="C156" s="3" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>2:04:15</t>
+          <t>2:05:30</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:19:51</t>
         </is>
       </c>
     </row>
@@ -4399,16 +4399,16 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>2:02:40</t>
+          <t>2:04:15</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>2:16:02</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4424,16 +4424,16 @@
         </is>
       </c>
       <c r="C158" s="3" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>2:05:22</t>
+          <t>2:04:15</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>2:16:28</t>
+          <t>2:17:45</t>
         </is>
       </c>
     </row>
@@ -4449,16 +4449,16 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>2:02:16</t>
+          <t>2:02:40</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>2:15:55</t>
+          <t>2:16:02</t>
         </is>
       </c>
     </row>
@@ -4474,16 +4474,16 @@
         </is>
       </c>
       <c r="C160" s="3" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>2:03:23</t>
+          <t>2:05:22</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>2:16:31</t>
+          <t>2:16:28</t>
         </is>
       </c>
     </row>
@@ -4499,23 +4499,23 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>2:03:37</t>
+          <t>2:02:16</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>2:14:29</t>
+          <t>2:15:55</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
+          <t>Tokyo Marathon</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -4524,23 +4524,23 @@
         </is>
       </c>
       <c r="C162" s="3" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>2:06:13</t>
+          <t>2:03:23</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:16:31</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
+          <t>Tokyo Marathon</t>
         </is>
       </c>
       <c r="B163" s="5" t="inlineStr">
@@ -4549,16 +4549,16 @@
         </is>
       </c>
       <c r="C163" s="5" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>2:01:53</t>
+          <t>2:03:37</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>2:14:57</t>
+          <t>2:14:29</t>
         </is>
       </c>
     </row>
@@ -4574,16 +4574,16 @@
         </is>
       </c>
       <c r="C164" s="3" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>2:01:48</t>
+          <t>2:06:13</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>2:15:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4599,16 +4599,16 @@
         </is>
       </c>
       <c r="C165" s="5" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>2:02:05</t>
+          <t>2:03:00</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>2:16:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4624,23 +4624,23 @@
         </is>
       </c>
       <c r="C166" s="3" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>2:02:24</t>
+          <t>2:01:53</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>2:14:00</t>
+          <t>2:14:57</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Vienna City Marathon</t>
+          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
@@ -4649,23 +4649,23 @@
         </is>
       </c>
       <c r="C167" s="5" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>2:07:31</t>
+          <t>2:01:48</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>2:30:09</t>
+          <t>2:15:51</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Vienna City Marathon</t>
+          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -4674,23 +4674,23 @@
         </is>
       </c>
       <c r="C168" s="3" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>2:08:40</t>
+          <t>2:02:05</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>2:24:20</t>
+          <t>2:16:49</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>Vienna City Marathon</t>
+          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
@@ -4699,16 +4699,16 @@
         </is>
       </c>
       <c r="C169" s="5" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>2:06:56</t>
+          <t>2:02:24</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>2:22:12</t>
+          <t>2:14:00</t>
         </is>
       </c>
     </row>
@@ -4724,16 +4724,16 @@
         </is>
       </c>
       <c r="C170" s="3" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>2:09:25</t>
+          <t>2:07:31</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>2:24:29</t>
+          <t>2:30:09</t>
         </is>
       </c>
     </row>
@@ -4749,16 +4749,16 @@
         </is>
       </c>
       <c r="C171" s="5" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>2:06:53</t>
+          <t>2:08:40</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>2:20:59</t>
+          <t>2:24:20</t>
         </is>
       </c>
     </row>
@@ -4774,16 +4774,16 @@
         </is>
       </c>
       <c r="C172" s="3" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>2:05:08</t>
+          <t>2:06:56</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>2:24:12</t>
+          <t>2:22:12</t>
         </is>
       </c>
     </row>
@@ -4799,16 +4799,16 @@
         </is>
       </c>
       <c r="C173" s="5" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>2:06:35</t>
+          <t>2:09:25</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>2:24:08</t>
+          <t>2:24:29</t>
         </is>
       </c>
     </row>
@@ -4824,23 +4824,23 @@
         </is>
       </c>
       <c r="C174" s="3" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>2:08:28</t>
+          <t>2:06:53</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>2:24:14</t>
+          <t>2:20:59</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>Zurich Marató de Barcelona</t>
+          <t>Vienna City Marathon</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
@@ -4853,19 +4853,19 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>2:05:06</t>
+          <t>2:05:08</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>2:19:44</t>
+          <t>2:24:12</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Zurich Marató de Barcelona</t>
+          <t>Vienna City Marathon</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -4878,19 +4878,19 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>2:05:01</t>
+          <t>2:06:35</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>2:19:52</t>
+          <t>2:24:08</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>Zurich Marató de Barcelona</t>
+          <t>Vienna City Marathon</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>2:04:13</t>
+          <t>2:08:28</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>2:19:33</t>
+          <t>2:24:14</t>
         </is>
       </c>
     </row>
@@ -4924,23 +4924,23 @@
         </is>
       </c>
       <c r="C178" s="3" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>2:04:57</t>
+          <t>2:05:06</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>2:10:53</t>
+          <t>2:19:44</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>Zurich Maratón de Sevilla</t>
+          <t>Zurich Marató de Barcelona</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
@@ -4949,23 +4949,23 @@
         </is>
       </c>
       <c r="C179" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>2:04:59</t>
+          <t>2:05:01</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>2:20:29</t>
+          <t>2:19:52</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Zurich Maratón de Sevilla</t>
+          <t>Zurich Marató de Barcelona</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -4974,23 +4974,23 @@
         </is>
       </c>
       <c r="C180" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>2:03:27</t>
+          <t>2:04:13</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>2:22:13</t>
+          <t>2:19:33</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>Zurich Maratón de Sevilla</t>
+          <t>Zurich Marató de Barcelona</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
@@ -4999,16 +4999,16 @@
         </is>
       </c>
       <c r="C181" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>2:05:15</t>
+          <t>2:04:57</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>2:22:17</t>
+          <t>2:10:53</t>
         </is>
       </c>
     </row>
@@ -5024,23 +5024,23 @@
         </is>
       </c>
       <c r="C182" s="3" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>2:03:59</t>
+          <t>2:04:59</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>2:20:39</t>
+          <t>2:20:29</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
+          <t>Zurich Maratón de Sevilla</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
@@ -5049,23 +5049,23 @@
         </is>
       </c>
       <c r="C183" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>2:10:29</t>
+          <t>2:03:27</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>2:26:31</t>
+          <t>2:22:13</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
+          <t>Zurich Maratón de Sevilla</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5074,123 +5074,123 @@
         </is>
       </c>
       <c r="C184" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>2:08:05</t>
+          <t>2:05:15</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>2:26:19</t>
+          <t>2:22:17</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
+          <t>Zurich Maratón de Sevilla</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>42K</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>2:03:59</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>2:20:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
           <t>Zurich Rock 'n' Roll Running Series Madrid</t>
         </is>
       </c>
-      <c r="B185" s="5" t="inlineStr">
-        <is>
-          <t>42K</t>
-        </is>
-      </c>
-      <c r="C185" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D185" s="5" t="inlineStr">
-        <is>
-          <t>2:09:11</t>
-        </is>
-      </c>
-      <c r="E185" s="5" t="inlineStr">
-        <is>
-          <t>2:25:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>21K de Montréal</t>
-        </is>
-      </c>
-      <c r="B186" s="7" t="inlineStr">
-        <is>
-          <t>21K</t>
-        </is>
-      </c>
-      <c r="C186" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D186" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E186" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>42K</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>2:10:29</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>2:26:31</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Bristol Run</t>
+          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>21K</t>
+          <t>42K</t>
         </is>
       </c>
       <c r="C187" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:08:05</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:26:19</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>AJ Bell Great Manchester Run</t>
-        </is>
-      </c>
-      <c r="B188" s="7" t="inlineStr">
-        <is>
-          <t>21K</t>
-        </is>
-      </c>
-      <c r="C188" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D188" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E188" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>42K</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>2:09:11</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>2:25:55</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great North Run</t>
+          <t>21K de Montréal</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
@@ -5203,19 +5203,19 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>1:00:52</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>1:09:32</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>Aramco Houston Half Marathon</t>
+          <t>AJ Bell Great Bristol Run</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
@@ -5224,23 +5224,23 @@
         </is>
       </c>
       <c r="C190" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
-          <t>1:00:42</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E190" s="7" t="inlineStr">
         <is>
-          <t>1:04:37</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>Aramco Houston Half Marathon</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>0:59:17</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
@@ -5265,7 +5265,7 @@
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>Aramco Houston Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -5274,23 +5274,23 @@
         </is>
       </c>
       <c r="C192" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D192" s="7" t="inlineStr">
         <is>
-          <t>0:59:01</t>
+          <t>1:00:52</t>
         </is>
       </c>
       <c r="E192" s="7" t="inlineStr">
         <is>
-          <t>1:04:49</t>
+          <t>1:09:32</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>Asics Run Melbourne</t>
+          <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
@@ -5299,23 +5299,23 @@
         </is>
       </c>
       <c r="C193" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:42</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:37</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>Bangsaen21</t>
+          <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
@@ -5324,11 +5324,11 @@
         </is>
       </c>
       <c r="C194" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:17</t>
         </is>
       </c>
       <c r="E194" s="7" t="inlineStr">
@@ -5340,7 +5340,7 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen21</t>
+          <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
@@ -5349,23 +5349,23 @@
         </is>
       </c>
       <c r="C195" s="5" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:01</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:49</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>Bangsaen21</t>
+          <t>Asics Run Melbourne</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>Brølløbet - The Bridge Run</t>
+          <t>Bangsaen21</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="C197" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>Burj2Burj Half Marathon</t>
+          <t>Bangsaen21</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -5440,7 +5440,7 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>Burj2Burj Half Marathon</t>
+          <t>Bangsaen21</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
@@ -5465,7 +5465,7 @@
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>Burj2Burj Half Marathon</t>
+          <t>Brølløbet - The Bridge Run</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -5474,23 +5474,23 @@
         </is>
       </c>
       <c r="C200" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
-          <t>0:59:26</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E200" s="7" t="inlineStr">
         <is>
-          <t>1:06:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>Cardiff Half Marathon</t>
+          <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="C201" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>Coelmo Napoli City Half Marathon</t>
+          <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -5540,7 +5540,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>Coelmo Napoli City Half Marathon</t>
+          <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
@@ -5553,19 +5553,19 @@
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:26</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:57</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>Copenhagen Half Marathon</t>
+          <t>Cardiff Half Marathon</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
@@ -5574,23 +5574,23 @@
         </is>
       </c>
       <c r="C204" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D204" s="7" t="inlineStr">
         <is>
-          <t>0:59:11</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E204" s="7" t="inlineStr">
         <is>
-          <t>1:05:53</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen Half Marathon</t>
+          <t>Coelmo Napoli City Half Marathon</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
@@ -5599,23 +5599,23 @@
         </is>
       </c>
       <c r="C205" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>0:58:05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
         <is>
-          <t>1:05:11</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>Copenhagen Half Marathon</t>
+          <t>Coelmo Napoli City Half Marathon</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
@@ -5624,23 +5624,23 @@
         </is>
       </c>
       <c r="C206" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D206" s="7" t="inlineStr">
         <is>
-          <t>0:58:23</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E206" s="7" t="inlineStr">
         <is>
-          <t>1:04:44</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>Disney Princess Half Marathon</t>
+          <t>Copenhagen Half Marathon</t>
         </is>
       </c>
       <c r="B207" s="5" t="inlineStr">
@@ -5649,23 +5649,23 @@
         </is>
       </c>
       <c r="C207" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:11</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:53</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>Disney Princess Half Marathon</t>
+          <t>Copenhagen Half Marathon</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -5674,23 +5674,23 @@
         </is>
       </c>
       <c r="C208" s="7" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D208" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:05</t>
         </is>
       </c>
       <c r="E208" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:11</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>EDP Lisboa Meia Maratona</t>
+          <t>Copenhagen Half Marathon</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
@@ -5699,23 +5699,23 @@
         </is>
       </c>
       <c r="C209" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:23</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:44</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>EDP Lisboa Meia Maratona</t>
+          <t>Disney Princess Half Marathon</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -5740,7 +5740,7 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>EDP Lisboa Meia Maratona</t>
+          <t>Disney Princess Half Marathon</t>
         </is>
       </c>
       <c r="B211" s="5" t="inlineStr">
@@ -5765,7 +5765,7 @@
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>Eurospin RomaOstia Half Marathon</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
@@ -5774,23 +5774,23 @@
         </is>
       </c>
       <c r="C212" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D212" s="7" t="inlineStr">
         <is>
-          <t>0:59:17</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E212" s="7" t="inlineStr">
         <is>
-          <t>1:06:21</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>Eurospin RomaOstia Half Marathon</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B213" s="5" t="inlineStr">
@@ -5799,23 +5799,23 @@
         </is>
       </c>
       <c r="C213" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>1:01:10</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
         <is>
-          <t>1:07:38</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
         <is>
-          <t>Eurospin RomaOstia Half Marathon</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
@@ -5824,16 +5824,16 @@
         </is>
       </c>
       <c r="C214" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D214" s="7" t="inlineStr">
         <is>
-          <t>0:58:49</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E214" s="7" t="inlineStr">
         <is>
-          <t>1:08:20</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -5849,23 +5849,23 @@
         </is>
       </c>
       <c r="C215" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>0:58:00</t>
+          <t>0:59:17</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:21</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
         <is>
-          <t>Generali Berlin Half Marathon</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B216" s="7" t="inlineStr">
@@ -5874,23 +5874,23 @@
         </is>
       </c>
       <c r="C216" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D216" s="7" t="inlineStr">
         <is>
-          <t>0:59:01</t>
+          <t>1:01:10</t>
         </is>
       </c>
       <c r="E216" s="7" t="inlineStr">
         <is>
-          <t>1:05:43</t>
+          <t>1:07:38</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>Generali Berlin Half Marathon</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B217" s="5" t="inlineStr">
@@ -5899,23 +5899,23 @@
         </is>
       </c>
       <c r="C217" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>0:58:49</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>1:06:53</t>
+          <t>1:08:20</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>Generali Berlin Half Marathon</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
@@ -5924,23 +5924,23 @@
         </is>
       </c>
       <c r="C218" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D218" s="7" t="inlineStr">
         <is>
-          <t>0:58:43</t>
+          <t>0:58:00</t>
         </is>
       </c>
       <c r="E218" s="7" t="inlineStr">
         <is>
-          <t>1:03:35</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>Generali Prague Half Marathon</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B219" s="5" t="inlineStr">
@@ -5953,19 +5953,19 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>0:59:43</t>
+          <t>0:59:01</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>1:06:00</t>
+          <t>1:05:43</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>Generali Prague Half Marathon</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
@@ -5978,19 +5978,19 @@
       </c>
       <c r="D220" s="7" t="inlineStr">
         <is>
-          <t>0:58:24</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E220" s="7" t="inlineStr">
         <is>
-          <t>1:08:10</t>
+          <t>1:06:53</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>Generali Prague Half Marathon</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
@@ -6003,19 +6003,19 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>0:58:54</t>
+          <t>0:58:43</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>1:05:27</t>
+          <t>1:03:35</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
         <is>
-          <t>GetPro Bath Half</t>
+          <t>Generali Prague Half Marathon</t>
         </is>
       </c>
       <c r="B222" s="7" t="inlineStr">
@@ -6024,23 +6024,23 @@
         </is>
       </c>
       <c r="C222" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D222" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:43</t>
         </is>
       </c>
       <c r="E222" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:00</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>GetPro Bath Half</t>
+          <t>Generali Prague Half Marathon</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
@@ -6049,23 +6049,23 @@
         </is>
       </c>
       <c r="C223" s="5" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:24</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:10</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>Göteborgsvarvet</t>
+          <t>Generali Prague Half Marathon</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -6074,23 +6074,23 @@
         </is>
       </c>
       <c r="C224" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D224" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:54</t>
         </is>
       </c>
       <c r="E224" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:27</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>Göteborgsvarvet</t>
+          <t>GetPro Bath Half</t>
         </is>
       </c>
       <c r="B225" s="5" t="inlineStr">
@@ -6115,7 +6115,7 @@
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>HOKA Semi de Paris</t>
+          <t>GetPro Bath Half</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
@@ -6124,23 +6124,23 @@
         </is>
       </c>
       <c r="C226" s="7" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D226" s="7" t="inlineStr">
         <is>
-          <t>0:59:38</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E226" s="7" t="inlineStr">
         <is>
-          <t>1:06:01</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>HOKA Semi de Paris</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B227" s="5" t="inlineStr">
@@ -6153,19 +6153,19 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>1:00:45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
         <is>
-          <t>1:06:58</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
         <is>
-          <t>HOKA Semi de Paris</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
@@ -6178,12 +6178,12 @@
       </c>
       <c r="D228" s="7" t="inlineStr">
         <is>
-          <t>1:00:16</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E228" s="7" t="inlineStr">
         <is>
-          <t>1:07:14</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -6199,23 +6199,23 @@
         </is>
       </c>
       <c r="C229" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>1:00:11</t>
+          <t>0:59:38</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
         <is>
-          <t>1:05:12</t>
+          <t>1:06:01</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
         <is>
-          <t>Half Marathon Munchen by Brooks</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B230" s="7" t="inlineStr">
@@ -6224,23 +6224,23 @@
         </is>
       </c>
       <c r="C230" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D230" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:45</t>
         </is>
       </c>
       <c r="E230" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:58</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>Hoka Runaway Sydney Half Marathon</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B231" s="5" t="inlineStr">
@@ -6253,19 +6253,19 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:16</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:14</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
         <is>
-          <t>Hyundai Meia Maratona</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
@@ -6274,23 +6274,23 @@
         </is>
       </c>
       <c r="C232" s="7" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D232" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:11</t>
         </is>
       </c>
       <c r="E232" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:12</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>Hyundai Meia Maratona</t>
+          <t>Half Marathon Munchen by Brooks</t>
         </is>
       </c>
       <c r="B233" s="5" t="inlineStr">
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="C233" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
         <is>
-          <t>Hyundai Meia Maratona</t>
+          <t>Hoka Runaway Sydney Half Marathon</t>
         </is>
       </c>
       <c r="B234" s="7" t="inlineStr">
@@ -6340,7 +6340,7 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>IU Health 500 Festival Mini-Marathon</t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="B235" s="5" t="inlineStr">
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="C235" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
         <is>
-          <t>Kagawa Marugame International Half Marathon</t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="B236" s="7" t="inlineStr">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="C236" s="7" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D236" s="7" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>Life Time Chicago Half Marathon &amp; 5K</t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="B237" s="5" t="inlineStr">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="C237" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>Life Time Chicago Half Marathon &amp; 5K</t>
+          <t>IU Health 500 Festival Mini-Marathon</t>
         </is>
       </c>
       <c r="B238" s="7" t="inlineStr">
@@ -6440,7 +6440,7 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>London Landmarks Half Marathon</t>
+          <t>Kagawa Marugame International Half Marathon</t>
         </is>
       </c>
       <c r="B239" s="5" t="inlineStr">
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="C239" s="5" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>London Landmarks Half Marathon</t>
+          <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
       <c r="B240" s="7" t="inlineStr">
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="C240" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D240" s="7" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>Manchester Half Marathon</t>
+          <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
       <c r="B241" s="5" t="inlineStr">
@@ -6515,7 +6515,7 @@
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>Media Maraton de Bogota</t>
+          <t>London Landmarks Half Marathon</t>
         </is>
       </c>
       <c r="B242" s="7" t="inlineStr">
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="C242" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D242" s="7" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>Medio Maraton de Sevilla</t>
+          <t>London Landmarks Half Marathon</t>
         </is>
       </c>
       <c r="B243" s="5" t="inlineStr">
@@ -6549,23 +6549,23 @@
         </is>
       </c>
       <c r="C243" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>0:59:21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
         <is>
-          <t>1:07:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
         <is>
-          <t>Medio Maraton de Sevilla</t>
+          <t>Manchester Half Marathon</t>
         </is>
       </c>
       <c r="B244" s="7" t="inlineStr">
@@ -6578,19 +6578,19 @@
       </c>
       <c r="D244" s="7" t="inlineStr">
         <is>
-          <t>0:59:33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E244" s="7" t="inlineStr">
         <is>
-          <t>1:07:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>Medio Maraton de Sevilla</t>
+          <t>Media Maraton de Bogota</t>
         </is>
       </c>
       <c r="B245" s="5" t="inlineStr">
@@ -6599,23 +6599,23 @@
         </is>
       </c>
       <c r="C245" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>1:00:24</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
         <is>
-          <t>Mitja Marato Barcelona by Brooks</t>
+          <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
       <c r="B246" s="7" t="inlineStr">
@@ -6624,23 +6624,23 @@
         </is>
       </c>
       <c r="C246" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D246" s="7" t="inlineStr">
         <is>
-          <t>0:58:53</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E246" s="7" t="inlineStr">
         <is>
-          <t>1:04:37</t>
+          <t>1:07:59</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>Mitja Marato Barcelona by Brooks</t>
+          <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
       <c r="B247" s="5" t="inlineStr">
@@ -6649,23 +6649,23 @@
         </is>
       </c>
       <c r="C247" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>0:59:21</t>
+          <t>0:59:33</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>1:04:28</t>
+          <t>1:07:18</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>Mitja Marato Barcelona by Brooks</t>
+          <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
       <c r="B248" s="7" t="inlineStr">
@@ -6674,16 +6674,16 @@
         </is>
       </c>
       <c r="C248" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D248" s="7" t="inlineStr">
         <is>
-          <t>0:56:42</t>
+          <t>1:00:24</t>
         </is>
       </c>
       <c r="E248" s="7" t="inlineStr">
         <is>
-          <t>1:04:11</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
@@ -6699,23 +6699,23 @@
         </is>
       </c>
       <c r="C249" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:53</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>1:04:00</t>
+          <t>1:04:37</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>Movistar Madrid Medio Maraton</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B250" s="7" t="inlineStr">
@@ -6724,23 +6724,23 @@
         </is>
       </c>
       <c r="C250" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D250" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E250" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:28</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - Half Marathon</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
@@ -6753,19 +6753,19 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:56:42</t>
         </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:11</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - Half Marathon</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B252" s="7" t="inlineStr">
@@ -6783,14 +6783,14 @@
       </c>
       <c r="E252" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:00</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>NYCRUNS Brooklyn Experience Half Marathon</t>
+          <t>Movistar Madrid Medio Maraton</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
@@ -6815,7 +6815,7 @@
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>NYRR RBC Brooklyn Half</t>
+          <t>NN CPC Loop Den Haag - Half Marathon</t>
         </is>
       </c>
       <c r="B254" s="7" t="inlineStr">
@@ -6840,7 +6840,7 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>Nike Melbourne Marathon Festival</t>
+          <t>NN CPC Loop Den Haag - Half Marathon</t>
         </is>
       </c>
       <c r="B255" s="5" t="inlineStr">
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="C255" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>NYCRUNS Brooklyn Experience Half Marathon</t>
         </is>
       </c>
       <c r="B256" s="7" t="inlineStr">
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="C256" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D256" s="7" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="C257" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>Nike Melbourne Marathon Festival</t>
         </is>
       </c>
       <c r="B258" s="7" t="inlineStr">
@@ -6949,7 +6949,7 @@
         </is>
       </c>
       <c r="C259" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="C260" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D260" s="7" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B261" s="5" t="inlineStr">
@@ -6999,7 +6999,7 @@
         </is>
       </c>
       <c r="C261" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
     <row r="262">
       <c r="A262" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B262" s="7" t="inlineStr">
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="C262" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D262" s="7" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="C263" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Mexico City</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -7074,7 +7074,7 @@
         </is>
       </c>
       <c r="C264" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D264" s="7" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series San Diego</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B265" s="5" t="inlineStr">
@@ -7115,7 +7115,7 @@
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>Royal Parks Half Marathon</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="C266" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D266" s="7" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Rock 'n' Roll Running Series Mexico City</t>
         </is>
       </c>
       <c r="B267" s="5" t="inlineStr">
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="C267" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Rock 'n' Roll Running Series San Diego</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
@@ -7174,23 +7174,23 @@
         </is>
       </c>
       <c r="C268" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D268" s="7" t="inlineStr">
         <is>
-          <t>1:05:44</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E268" s="7" t="inlineStr">
         <is>
-          <t>1:18:34</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Royal Parks Half Marathon</t>
         </is>
       </c>
       <c r="B269" s="5" t="inlineStr">
@@ -7215,7 +7215,7 @@
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>Semi-Marathon de Boulogne-Billancourt</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="C270" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D270" s="7" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B271" s="5" t="inlineStr">
@@ -7249,23 +7249,23 @@
         </is>
       </c>
       <c r="C271" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:44</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:18:34</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Series Nashville</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -7290,7 +7290,7 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>Semi-Marathon de Boulogne-Billancourt</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
@@ -7315,7 +7315,7 @@
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>Standard Chartered Singapore Half Marathon</t>
+          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -7340,7 +7340,7 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>TCS Mizuno Half Marathon</t>
+          <t>St. Jude Rock 'n' Roll Series Nashville</t>
         </is>
       </c>
       <c r="B275" s="5" t="inlineStr">
@@ -7365,7 +7365,7 @@
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
@@ -7374,7 +7374,7 @@
         </is>
       </c>
       <c r="C276" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D276" s="7" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>Standard Chartered Singapore Half Marathon</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="C277" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -7440,7 +7440,7 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
@@ -7465,7 +7465,7 @@
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -7490,7 +7490,7 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
@@ -7515,7 +7515,7 @@
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon (Half)</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="C282" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D282" s="7" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon (Half)</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="C283" s="5" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>The Big Half</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -7590,7 +7590,7 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Legacy Half Marathon</t>
+          <t>Tata Mumbai Marathon (Half)</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
@@ -7615,7 +7615,7 @@
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>Tata Mumbai Marathon (Half)</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -7624,23 +7624,23 @@
         </is>
       </c>
       <c r="C286" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D286" s="7" t="inlineStr">
         <is>
-          <t>1:01:31</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E286" s="7" t="inlineStr">
         <is>
-          <t>1:07:04</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>The Big Half</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
@@ -7649,23 +7649,23 @@
         </is>
       </c>
       <c r="C287" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
+          <t>Tokyo Legacy Half Marathon</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -7678,19 +7678,19 @@
       </c>
       <c r="D288" s="7" t="inlineStr">
         <is>
-          <t>0:58:02</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E288" s="7" t="inlineStr">
         <is>
-          <t>1:03:08</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>Vedanta Delhi Half Marathon</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
@@ -7703,19 +7703,19 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>0:59:50</t>
+          <t>1:01:31</t>
         </is>
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>1:07:20</t>
+          <t>1:07:04</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>Vienna City Half Marathon</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -7724,23 +7724,23 @@
         </is>
       </c>
       <c r="C290" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D290" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E290" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>Walt Disney World Marathon Weekend</t>
+          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
@@ -7753,19 +7753,19 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:02</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:08</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>Walt Disney World Marathon Weekend</t>
+          <t>Vedanta Delhi Half Marathon</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -7774,23 +7774,23 @@
         </is>
       </c>
       <c r="C292" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D292" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:50</t>
         </is>
       </c>
       <c r="E292" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:20</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>Warsaw Half Marathon</t>
+          <t>Vienna City Half Marathon</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="C293" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>Warsaw Half Marathon</t>
+          <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -7840,7 +7840,7 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>Wizz Air Rome Half Marathon by Brooks</t>
+          <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
       <c r="B295" s="5" t="inlineStr">
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="C295" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Warsaw Half Marathon</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -7874,7 +7874,7 @@
         </is>
       </c>
       <c r="C296" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D296" s="7" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Warsaw Half Marathon</t>
         </is>
       </c>
       <c r="B297" s="5" t="inlineStr">
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="C297" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Wizz Air Rome Half Marathon by Brooks</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -7940,16 +7940,16 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>10K Montmartre</t>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
         </is>
       </c>
       <c r="B299" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C299" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
@@ -7963,43 +7963,43 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="8" t="inlineStr">
-        <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
-        </is>
-      </c>
-      <c r="B300" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C300" s="9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D300" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E300" s="9" t="inlineStr">
-        <is>
-          <t>0:29:19</t>
+      <c r="A300" s="6" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+        </is>
+      </c>
+      <c r="B300" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C300" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D300" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E300" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
         </is>
       </c>
       <c r="B301" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C301" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
@@ -8008,14 +8008,14 @@
       </c>
       <c r="E301" s="5" t="inlineStr">
         <is>
-          <t>0:28:45</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="8" t="inlineStr">
         <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
+          <t>10K Montmartre</t>
         </is>
       </c>
       <c r="B302" s="9" t="inlineStr">
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="C302" s="9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
@@ -8049,23 +8049,23 @@
         </is>
       </c>
       <c r="C303" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>0:26:45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E303" s="5" t="inlineStr">
         <is>
-          <t>0:29:25</t>
+          <t>0:29:19</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B304" s="9" t="inlineStr">
@@ -8083,14 +8083,14 @@
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:45</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B305" s="5" t="inlineStr">
@@ -8115,7 +8115,7 @@
     <row r="306">
       <c r="A306" s="8" t="inlineStr">
         <is>
-          <t>ASICS LDNX</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B306" s="9" t="inlineStr">
@@ -8124,23 +8124,23 @@
         </is>
       </c>
       <c r="C306" s="9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:26:45</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:25</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B307" s="5" t="inlineStr">
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="C307" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
     <row r="308">
       <c r="A308" s="8" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B308" s="9" t="inlineStr">
@@ -8174,23 +8174,23 @@
         </is>
       </c>
       <c r="C308" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>0:29:37</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>0:32:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>ASICS LDNX</t>
         </is>
       </c>
       <c r="B309" s="5" t="inlineStr">
@@ -8215,7 +8215,7 @@
     <row r="310">
       <c r="A310" s="8" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B310" s="9" t="inlineStr">
@@ -8228,19 +8228,19 @@
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>0:30:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B311" s="5" t="inlineStr">
@@ -8253,19 +8253,19 @@
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>0:29:37</t>
         </is>
       </c>
       <c r="E311" s="5" t="inlineStr">
         <is>
-          <t>0:31:12</t>
+          <t>0:32:18</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="8" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B312" s="9" t="inlineStr">
@@ -8283,14 +8283,14 @@
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>0:31:29</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B313" s="5" t="inlineStr">
@@ -8303,19 +8303,19 @@
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>0:29:08</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
-          <t>0:33:25</t>
+          <t>0:30:43</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="8" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B314" s="9" t="inlineStr">
@@ -8328,19 +8328,19 @@
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>0:29:13</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>0:32:45</t>
+          <t>0:31:12</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B315" s="5" t="inlineStr">
@@ -8358,14 +8358,14 @@
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:29</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="8" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B316" s="9" t="inlineStr">
@@ -8378,19 +8378,19 @@
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:08</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:33:25</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B317" s="5" t="inlineStr">
@@ -8403,19 +8403,19 @@
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:13</t>
         </is>
       </c>
       <c r="E317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:45</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="8" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B318" s="9" t="inlineStr">
@@ -8440,7 +8440,7 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B319" s="5" t="inlineStr">
@@ -8453,19 +8453,19 @@
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>0:28:52</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
-          <t>0:31:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="8" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B320" s="9" t="inlineStr">
@@ -8478,19 +8478,19 @@
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>0:28:46</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>0:32:33</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B321" s="5" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>0:29:22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>0:34:32</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -8524,23 +8524,23 @@
         </is>
       </c>
       <c r="C322" s="9" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:52</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:59</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B323" s="5" t="inlineStr">
@@ -8549,23 +8549,23 @@
         </is>
       </c>
       <c r="C323" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:46</t>
         </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:33</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="8" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B324" s="9" t="inlineStr">
@@ -8574,23 +8574,23 @@
         </is>
       </c>
       <c r="C324" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:22</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:34:32</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B325" s="5" t="inlineStr">
@@ -8599,23 +8599,23 @@
         </is>
       </c>
       <c r="C325" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>0:28:27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E325" s="5" t="inlineStr">
         <is>
-          <t>0:31:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="8" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B326" s="9" t="inlineStr">
@@ -8640,7 +8640,7 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B327" s="5" t="inlineStr">
@@ -8665,7 +8665,7 @@
     <row r="328">
       <c r="A328" s="8" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B328" s="9" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:27</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:49</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="C329" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
     <row r="330">
       <c r="A330" s="8" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B330" s="9" t="inlineStr">
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="C330" s="9" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B331" s="5" t="inlineStr">
@@ -8749,7 +8749,7 @@
         </is>
       </c>
       <c r="C331" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
     <row r="332">
       <c r="A332" s="8" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B332" s="9" t="inlineStr">
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="C332" s="9" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D332" s="9" t="inlineStr">
         <is>
@@ -8783,14 +8783,14 @@
       </c>
       <c r="E332" s="9" t="inlineStr">
         <is>
-          <t>0:31:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
         </is>
       </c>
       <c r="B333" s="5" t="inlineStr">
@@ -8799,23 +8799,23 @@
         </is>
       </c>
       <c r="C333" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E333" s="5" t="inlineStr">
         <is>
-          <t>0:31:11</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="8" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B334" s="9" t="inlineStr">
@@ -8840,7 +8840,7 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B335" s="5" t="inlineStr">
@@ -8858,14 +8858,14 @@
       </c>
       <c r="E335" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:18</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="8" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B336" s="9" t="inlineStr">
@@ -8878,19 +8878,19 @@
       </c>
       <c r="D336" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E336" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:11</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B337" s="5" t="inlineStr">
@@ -8915,7 +8915,7 @@
     <row r="338">
       <c r="A338" s="8" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -8940,7 +8940,7 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B339" s="5" t="inlineStr">
@@ -8965,7 +8965,7 @@
     <row r="340">
       <c r="A340" s="8" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -8990,7 +8990,7 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B341" s="5" t="inlineStr">
@@ -9003,19 +9003,19 @@
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>0:29:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>0:32:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="8" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>0:29:33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E342" s="9" t="inlineStr">
@@ -9040,7 +9040,7 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B343" s="5" t="inlineStr">
@@ -9065,7 +9065,7 @@
     <row r="344">
       <c r="A344" s="8" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -9078,19 +9078,19 @@
       </c>
       <c r="D344" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:41</t>
         </is>
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:51</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B345" s="5" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:33</t>
         </is>
       </c>
       <c r="E345" s="5" t="inlineStr">
@@ -9115,7 +9115,7 @@
     <row r="346">
       <c r="A346" s="8" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -9140,7 +9140,7 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B347" s="5" t="inlineStr">
@@ -9165,7 +9165,7 @@
     <row r="348">
       <c r="A348" s="8" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -9190,7 +9190,7 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B349" s="5" t="inlineStr">
@@ -9215,7 +9215,7 @@
     <row r="350">
       <c r="A350" s="8" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -9240,7 +9240,7 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B351" s="5" t="inlineStr">
@@ -9265,7 +9265,7 @@
     <row r="352">
       <c r="A352" s="8" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -9290,7 +9290,7 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B353" s="5" t="inlineStr">
@@ -9315,7 +9315,7 @@
     <row r="354">
       <c r="A354" s="8" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -9328,19 +9328,19 @@
       </c>
       <c r="D354" s="9" t="inlineStr">
         <is>
-          <t>0:28:09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E354" s="9" t="inlineStr">
         <is>
-          <t>0:32:54</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Vancouver Sun Run</t>
         </is>
       </c>
       <c r="B355" s="5" t="inlineStr">
@@ -9365,7 +9365,7 @@
     <row r="356">
       <c r="A356" s="8" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Vancouver Sun Run</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -9378,42 +9378,117 @@
       </c>
       <c r="D356" s="9" t="inlineStr">
         <is>
-          <t>0:29:14</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E356" s="9" t="inlineStr">
         <is>
-          <t>0:31:36</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
+          <t>Vancouver Sun Run</t>
+        </is>
+      </c>
+      <c r="B357" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C357" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D357" s="5" t="inlineStr">
+        <is>
+          <t>0:28:09</t>
+        </is>
+      </c>
+      <c r="E357" s="5" t="inlineStr">
+        <is>
+          <t>0:32:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="8" t="inlineStr">
+        <is>
           <t>Vitality London 10,000</t>
         </is>
       </c>
-      <c r="B357" s="5" t="inlineStr">
+      <c r="B358" s="9" t="inlineStr">
         <is>
           <t>10K</t>
         </is>
       </c>
-      <c r="C357" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D357" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E357" s="5" t="inlineStr">
+      <c r="C358" s="9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D358" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E358" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="4" t="inlineStr">
+        <is>
+          <t>Vitality London 10,000</t>
+        </is>
+      </c>
+      <c r="B359" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C359" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D359" s="5" t="inlineStr">
+        <is>
+          <t>0:29:14</t>
+        </is>
+      </c>
+      <c r="E359" s="5" t="inlineStr">
+        <is>
+          <t>0:31:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="8" t="inlineStr">
+        <is>
+          <t>Vitality London 10,000</t>
+        </is>
+      </c>
+      <c r="B360" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C360" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D360" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E360" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E357"/>
+  <autoFilter ref="A1:E360"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Chronos_Vainqueurs.xlsx
+++ b/Chronos_Vainqueurs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$360</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$366</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E360"/>
+  <dimension ref="A1:E366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3165,7 +3165,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Standard Chartered Singapore Marathon</t>
+          <t>Standard Chartered Hong Kong Marathon</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3174,23 +3174,23 @@
         </is>
       </c>
       <c r="C108" s="3" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>2:16:06</t>
+          <t>2:09:20</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>2:39:04</t>
+          <t>2:26:13</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Singapore Marathon</t>
+          <t>Standard Chartered Hong Kong Marathon</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -3199,23 +3199,23 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>2:15:40</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>2:41:24</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TCS Amsterdam Marathon</t>
+          <t>Standard Chartered KL Marathon</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3224,23 +3224,23 @@
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>2:06:19</t>
+          <t>2:17:28</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>2:24:11</t>
+          <t>2:41:36</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>TCS Amsterdam Marathon</t>
+          <t>Standard Chartered Singapore Marathon</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -3249,23 +3249,23 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>2:05:20</t>
+          <t>2:16:06</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>2:23:20</t>
+          <t>2:39:04</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TCS Amsterdam Marathon</t>
+          <t>Standard Chartered Singapore Marathon</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3274,16 +3274,16 @@
         </is>
       </c>
       <c r="C112" s="3" t="n">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>2:05:09</t>
+          <t>2:15:40</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>2:21:53</t>
+          <t>2:41:24</t>
         </is>
       </c>
     </row>
@@ -3299,16 +3299,16 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>2:04:06</t>
+          <t>2:06:19</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:24:11</t>
         </is>
       </c>
     </row>
@@ -3324,16 +3324,16 @@
         </is>
       </c>
       <c r="C114" s="3" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>2:03:38</t>
+          <t>2:05:20</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>2:17:57</t>
+          <t>2:23:20</t>
         </is>
       </c>
     </row>
@@ -3349,16 +3349,16 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:05:09</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>2:17:20</t>
+          <t>2:21:53</t>
         </is>
       </c>
     </row>
@@ -3374,16 +3374,16 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>2:04:18</t>
+          <t>2:04:06</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>2:18:21</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3399,16 +3399,16 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>2:05:38</t>
+          <t>2:03:38</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>2:16:52</t>
+          <t>2:17:57</t>
         </is>
       </c>
     </row>
@@ -3424,23 +3424,23 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>2:03:31</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>2:17:37</t>
+          <t>2:17:20</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>TCS London Marathon</t>
+          <t>TCS Amsterdam Marathon</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
@@ -3449,23 +3449,23 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>2:04:42</t>
+          <t>2:04:18</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:18:21</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>TCS London Marathon</t>
+          <t>TCS Amsterdam Marathon</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3474,23 +3474,23 @@
         </is>
       </c>
       <c r="C120" s="3" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>2:03:05</t>
+          <t>2:05:38</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:16:52</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>TCS London Marathon</t>
+          <t>TCS Amsterdam Marathon</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -3499,16 +3499,16 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>2:05:48</t>
+          <t>2:03:31</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>2:17:01</t>
+          <t>2:17:37</t>
         </is>
       </c>
     </row>
@@ -3524,16 +3524,16 @@
         </is>
       </c>
       <c r="C122" s="3" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>2:04:17</t>
+          <t>2:04:42</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>2:18:31</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3549,11 +3549,11 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>2:02:37</t>
+          <t>2:03:05</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="C124" s="3" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>2:05:41</t>
+          <t>2:05:48</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>2:18:58</t>
+          <t>2:17:01</t>
         </is>
       </c>
     </row>
@@ -3599,16 +3599,16 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>2:04:01</t>
+          <t>2:04:17</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:18:31</t>
         </is>
       </c>
     </row>
@@ -3624,16 +3624,16 @@
         </is>
       </c>
       <c r="C126" s="3" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>2:04:39</t>
+          <t>2:02:37</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>2:17:26</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3649,16 +3649,16 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>2:01:25</t>
+          <t>2:05:41</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>2:18:33</t>
+          <t>2:18:58</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="C128" s="3" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>2:16:16</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3699,23 +3699,23 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>2:02:27</t>
+          <t>2:04:39</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>2:15:50</t>
+          <t>2:17:26</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>TCS New York City Marathon</t>
+          <t>TCS London Marathon</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -3724,23 +3724,23 @@
         </is>
       </c>
       <c r="C130" s="3" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>2:10:34</t>
+          <t>2:01:25</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>2:24:25</t>
+          <t>2:18:33</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>TCS New York City Marathon</t>
+          <t>TCS London Marathon</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
@@ -3749,23 +3749,23 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>2:07:51</t>
+          <t>2:04:01</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>2:24:26</t>
+          <t>2:16:16</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>TCS New York City Marathon</t>
+          <t>TCS London Marathon</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -3774,16 +3774,16 @@
         </is>
       </c>
       <c r="C132" s="3" t="n">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>2:10:53</t>
+          <t>2:02:27</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:15:50</t>
         </is>
       </c>
     </row>
@@ -3799,16 +3799,16 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>2:05:59</t>
+          <t>2:10:34</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>2:22:48</t>
+          <t>2:24:25</t>
         </is>
       </c>
     </row>
@@ -3824,16 +3824,16 @@
         </is>
       </c>
       <c r="C134" s="3" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>2:08:13</t>
+          <t>2:07:51</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>2:22:38</t>
+          <t>2:24:26</t>
         </is>
       </c>
     </row>
@@ -3849,16 +3849,16 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>2:08:22</t>
+          <t>2:10:53</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>2:22:39</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3874,16 +3874,16 @@
         </is>
       </c>
       <c r="C136" s="3" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>2:08:41</t>
+          <t>2:05:59</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>2:23:23</t>
+          <t>2:22:48</t>
         </is>
       </c>
     </row>
@@ -3899,16 +3899,16 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>2:04:58</t>
+          <t>2:08:13</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>2:27:23</t>
+          <t>2:22:38</t>
         </is>
       </c>
     </row>
@@ -3924,16 +3924,16 @@
         </is>
       </c>
       <c r="C138" s="3" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>2:07:39</t>
+          <t>2:08:22</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>2:24:35</t>
+          <t>2:22:39</t>
         </is>
       </c>
     </row>
@@ -3949,23 +3949,23 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>2:08:09</t>
+          <t>2:08:41</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>2:19:51</t>
+          <t>2:23:23</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>TCS Sydney Marathon presented by ASICS</t>
+          <t>TCS New York City Marathon</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -3978,19 +3978,19 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>2:08:20</t>
+          <t>2:04:58</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>2:26:47</t>
+          <t>2:27:23</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>TCS Sydney Marathon presented by ASICS</t>
+          <t>TCS New York City Marathon</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
@@ -4003,19 +4003,19 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>2:06:17</t>
+          <t>2:07:39</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>2:21:40</t>
+          <t>2:24:35</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>TCS Sydney Marathon presented by ASICS</t>
+          <t>TCS New York City Marathon</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4028,19 +4028,19 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>2:06:06</t>
+          <t>2:08:09</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>2:18:22</t>
+          <t>2:19:51</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon</t>
+          <t>TCS Sydney Marathon presented by ASICS</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
@@ -4053,19 +4053,19 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>2:09:20</t>
+          <t>2:08:20</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>2:23:11</t>
+          <t>2:26:47</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon</t>
+          <t>TCS Sydney Marathon presented by ASICS</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4078,19 +4078,19 @@
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>2:07:16</t>
+          <t>2:06:17</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>2:20:44</t>
+          <t>2:21:40</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon</t>
+          <t>TCS Sydney Marathon presented by ASICS</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
@@ -4103,19 +4103,19 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>2:08:05</t>
+          <t>2:06:06</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>2:21:04</t>
+          <t>2:18:22</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Taipei Marathon</t>
+          <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4128,19 +4128,19 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>2:11:05</t>
+          <t>2:09:20</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>2:27:14</t>
+          <t>2:23:11</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>Taipei Marathon</t>
+          <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
@@ -4153,19 +4153,19 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>2:11:41</t>
+          <t>2:07:16</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>2:32:47</t>
+          <t>2:20:44</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Taipei Marathon</t>
+          <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4178,19 +4178,19 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:08:05</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:21:04</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon</t>
+          <t>Taipei Marathon</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
@@ -4203,19 +4203,19 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>2:07:32</t>
+          <t>2:11:05</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>2:24:15</t>
+          <t>2:27:14</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon</t>
+          <t>Taipei Marathon</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4228,19 +4228,19 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>2:07:50</t>
+          <t>2:11:41</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>2:26:06</t>
+          <t>2:32:47</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon</t>
+          <t>Taipei Marathon</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>2:11:44</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>2:24:56</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4274,23 +4274,23 @@
         </is>
       </c>
       <c r="C152" s="3" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>2:09:55</t>
+          <t>2:07:32</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>2:25:13</t>
+          <t>2:24:15</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Marathon</t>
+          <t>Tata Mumbai Marathon</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
@@ -4299,23 +4299,23 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>2:06:00</t>
+          <t>2:07:50</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>2:23:15</t>
+          <t>2:26:06</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Tokyo Marathon</t>
+          <t>Tata Mumbai Marathon</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4324,23 +4324,23 @@
         </is>
       </c>
       <c r="C154" s="3" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>2:06:56</t>
+          <t>2:11:44</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>2:21:27</t>
+          <t>2:24:56</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Marathon</t>
+          <t>Tata Mumbai Marathon</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
@@ -4349,16 +4349,16 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>2017</v>
+        <v>2026</v>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>2:03:58</t>
+          <t>2:09:55</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:25:13</t>
         </is>
       </c>
     </row>
@@ -4374,16 +4374,16 @@
         </is>
       </c>
       <c r="C156" s="3" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>2:05:30</t>
+          <t>2:06:00</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>2:19:51</t>
+          <t>2:23:15</t>
         </is>
       </c>
     </row>
@@ -4399,16 +4399,16 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>2:04:15</t>
+          <t>2:06:56</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:21:27</t>
         </is>
       </c>
     </row>
@@ -4424,16 +4424,16 @@
         </is>
       </c>
       <c r="C158" s="3" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>2:04:15</t>
+          <t>2:03:58</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>2:17:45</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4449,16 +4449,16 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>2:02:40</t>
+          <t>2:05:30</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>2:16:02</t>
+          <t>2:19:51</t>
         </is>
       </c>
     </row>
@@ -4474,16 +4474,16 @@
         </is>
       </c>
       <c r="C160" s="3" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>2:05:22</t>
+          <t>2:04:15</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>2:16:28</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4499,16 +4499,16 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>2:02:16</t>
+          <t>2:04:15</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>2:15:55</t>
+          <t>2:17:45</t>
         </is>
       </c>
     </row>
@@ -4524,16 +4524,16 @@
         </is>
       </c>
       <c r="C162" s="3" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>2:03:23</t>
+          <t>2:02:40</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>2:16:31</t>
+          <t>2:16:02</t>
         </is>
       </c>
     </row>
@@ -4549,23 +4549,23 @@
         </is>
       </c>
       <c r="C163" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>2:03:37</t>
+          <t>2:05:22</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>2:14:29</t>
+          <t>2:16:28</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
+          <t>Tokyo Marathon</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -4574,23 +4574,23 @@
         </is>
       </c>
       <c r="C164" s="3" t="n">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>2:06:13</t>
+          <t>2:02:16</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:15:55</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
+          <t>Tokyo Marathon</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
@@ -4599,23 +4599,23 @@
         </is>
       </c>
       <c r="C165" s="5" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>2:03:00</t>
+          <t>2:03:23</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:16:31</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
+          <t>Tokyo Marathon</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -4624,16 +4624,16 @@
         </is>
       </c>
       <c r="C166" s="3" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>2:01:53</t>
+          <t>2:03:37</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>2:14:57</t>
+          <t>2:14:29</t>
         </is>
       </c>
     </row>
@@ -4649,16 +4649,16 @@
         </is>
       </c>
       <c r="C167" s="5" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>2:01:48</t>
+          <t>2:06:13</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>2:15:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4674,16 +4674,16 @@
         </is>
       </c>
       <c r="C168" s="3" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>2:02:05</t>
+          <t>2:03:00</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>2:16:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4699,23 +4699,23 @@
         </is>
       </c>
       <c r="C169" s="5" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>2:02:24</t>
+          <t>2:01:53</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>2:14:00</t>
+          <t>2:14:57</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Vienna City Marathon</t>
+          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -4724,23 +4724,23 @@
         </is>
       </c>
       <c r="C170" s="3" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>2:07:31</t>
+          <t>2:01:48</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>2:30:09</t>
+          <t>2:15:51</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>Vienna City Marathon</t>
+          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
@@ -4749,23 +4749,23 @@
         </is>
       </c>
       <c r="C171" s="5" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>2:08:40</t>
+          <t>2:02:05</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>2:24:20</t>
+          <t>2:16:49</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Vienna City Marathon</t>
+          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -4774,16 +4774,16 @@
         </is>
       </c>
       <c r="C172" s="3" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>2:06:56</t>
+          <t>2:02:24</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>2:22:12</t>
+          <t>2:14:00</t>
         </is>
       </c>
     </row>
@@ -4799,16 +4799,16 @@
         </is>
       </c>
       <c r="C173" s="5" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>2:09:25</t>
+          <t>2:07:31</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>2:24:29</t>
+          <t>2:30:09</t>
         </is>
       </c>
     </row>
@@ -4824,16 +4824,16 @@
         </is>
       </c>
       <c r="C174" s="3" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>2:06:53</t>
+          <t>2:08:40</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>2:20:59</t>
+          <t>2:24:20</t>
         </is>
       </c>
     </row>
@@ -4849,16 +4849,16 @@
         </is>
       </c>
       <c r="C175" s="5" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>2:05:08</t>
+          <t>2:06:56</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>2:24:12</t>
+          <t>2:22:12</t>
         </is>
       </c>
     </row>
@@ -4874,16 +4874,16 @@
         </is>
       </c>
       <c r="C176" s="3" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>2:06:35</t>
+          <t>2:09:25</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>2:24:08</t>
+          <t>2:24:29</t>
         </is>
       </c>
     </row>
@@ -4899,23 +4899,23 @@
         </is>
       </c>
       <c r="C177" s="5" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>2:08:28</t>
+          <t>2:06:53</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>2:24:14</t>
+          <t>2:20:59</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Zurich Marató de Barcelona</t>
+          <t>Vienna City Marathon</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -4928,19 +4928,19 @@
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>2:05:06</t>
+          <t>2:05:08</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>2:19:44</t>
+          <t>2:24:12</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>Zurich Marató de Barcelona</t>
+          <t>Vienna City Marathon</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
@@ -4953,19 +4953,19 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>2:05:01</t>
+          <t>2:06:35</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>2:19:52</t>
+          <t>2:24:08</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Zurich Marató de Barcelona</t>
+          <t>Vienna City Marathon</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>2:04:13</t>
+          <t>2:08:28</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>2:19:33</t>
+          <t>2:24:14</t>
         </is>
       </c>
     </row>
@@ -4999,23 +4999,23 @@
         </is>
       </c>
       <c r="C181" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>2:04:57</t>
+          <t>2:05:06</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>2:10:53</t>
+          <t>2:19:44</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Zurich Maratón de Sevilla</t>
+          <t>Zurich Marató de Barcelona</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5024,23 +5024,23 @@
         </is>
       </c>
       <c r="C182" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>2:04:59</t>
+          <t>2:05:01</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>2:20:29</t>
+          <t>2:19:52</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>Zurich Maratón de Sevilla</t>
+          <t>Zurich Marató de Barcelona</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
@@ -5049,23 +5049,23 @@
         </is>
       </c>
       <c r="C183" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>2:03:27</t>
+          <t>2:04:13</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>2:22:13</t>
+          <t>2:19:33</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Zurich Maratón de Sevilla</t>
+          <t>Zurich Marató de Barcelona</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5074,16 +5074,16 @@
         </is>
       </c>
       <c r="C184" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>2:05:15</t>
+          <t>2:04:57</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>2:22:17</t>
+          <t>2:10:53</t>
         </is>
       </c>
     </row>
@@ -5099,23 +5099,23 @@
         </is>
       </c>
       <c r="C185" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>2:03:59</t>
+          <t>2:04:59</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>2:20:39</t>
+          <t>2:20:29</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
+          <t>Zurich Maratón de Sevilla</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5124,23 +5124,23 @@
         </is>
       </c>
       <c r="C186" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>2:10:29</t>
+          <t>2:03:27</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>2:26:31</t>
+          <t>2:22:13</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
+          <t>Zurich Maratón de Sevilla</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
@@ -5149,23 +5149,23 @@
         </is>
       </c>
       <c r="C187" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>2:08:05</t>
+          <t>2:05:15</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>2:26:19</t>
+          <t>2:22:17</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
+          <t>Zurich Maratón de Sevilla</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5174,78 +5174,78 @@
         </is>
       </c>
       <c r="C188" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>2:09:11</t>
+          <t>2:03:59</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>2:25:55</t>
+          <t>2:20:39</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>21K de Montréal</t>
+          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>21K</t>
+          <t>42K</t>
         </is>
       </c>
       <c r="C189" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:10:29</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:26:31</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>AJ Bell Great Bristol Run</t>
-        </is>
-      </c>
-      <c r="B190" s="7" t="inlineStr">
-        <is>
-          <t>21K</t>
-        </is>
-      </c>
-      <c r="C190" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D190" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E190" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>42K</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>2:08:05</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>2:26:19</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run</t>
+          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>21K</t>
+          <t>42K</t>
         </is>
       </c>
       <c r="C191" s="5" t="n">
@@ -5253,19 +5253,19 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:09:11</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:25:55</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>AJ Bell Great North Run</t>
+          <t>21K de Montréal</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -5278,19 +5278,19 @@
       </c>
       <c r="D192" s="7" t="inlineStr">
         <is>
-          <t>1:00:52</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E192" s="7" t="inlineStr">
         <is>
-          <t>1:09:32</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>Aramco Houston Half Marathon</t>
+          <t>AJ Bell Great Bristol Run</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
@@ -5299,23 +5299,23 @@
         </is>
       </c>
       <c r="C193" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>1:00:42</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>1:04:37</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>Aramco Houston Half Marathon</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
-          <t>0:59:17</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E194" s="7" t="inlineStr">
@@ -5340,7 +5340,7 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>Aramco Houston Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
@@ -5349,23 +5349,23 @@
         </is>
       </c>
       <c r="C195" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>0:59:01</t>
+          <t>1:00:52</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>1:04:49</t>
+          <t>1:09:32</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>Asics Run Melbourne</t>
+          <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -5374,23 +5374,23 @@
         </is>
       </c>
       <c r="C196" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D196" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:42</t>
         </is>
       </c>
       <c r="E196" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:37</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen21</t>
+          <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
@@ -5399,11 +5399,11 @@
         </is>
       </c>
       <c r="C197" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:17</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
@@ -5415,7 +5415,7 @@
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>Bangsaen21</t>
+          <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -5424,23 +5424,23 @@
         </is>
       </c>
       <c r="C198" s="7" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D198" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:01</t>
         </is>
       </c>
       <c r="E198" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:49</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen21</t>
+          <t>Asics Run Melbourne</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
@@ -5465,7 +5465,7 @@
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>Brølløbet - The Bridge Run</t>
+          <t>Bangsaen21</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="C200" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>Burj2Burj Half Marathon</t>
+          <t>Bangsaen21</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
@@ -5515,7 +5515,7 @@
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>Burj2Burj Half Marathon</t>
+          <t>Bangsaen21</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -5540,7 +5540,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>Burj2Burj Half Marathon</t>
+          <t>Brølløbet - The Bridge Run</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
@@ -5549,23 +5549,23 @@
         </is>
       </c>
       <c r="C203" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>0:59:26</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>1:06:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>Cardiff Half Marathon</t>
+          <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="C204" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D204" s="7" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>Coelmo Napoli City Half Marathon</t>
+          <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>Coelmo Napoli City Half Marathon</t>
+          <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
@@ -5628,19 +5628,19 @@
       </c>
       <c r="D206" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:26</t>
         </is>
       </c>
       <c r="E206" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:57</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen Half Marathon</t>
+          <t>Cardiff Half Marathon</t>
         </is>
       </c>
       <c r="B207" s="5" t="inlineStr">
@@ -5649,23 +5649,23 @@
         </is>
       </c>
       <c r="C207" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>0:59:11</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
         <is>
-          <t>1:05:53</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>Copenhagen Half Marathon</t>
+          <t>Coelmo Napoli City Half Marathon</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -5674,23 +5674,23 @@
         </is>
       </c>
       <c r="C208" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D208" s="7" t="inlineStr">
         <is>
-          <t>0:58:05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E208" s="7" t="inlineStr">
         <is>
-          <t>1:05:11</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen Half Marathon</t>
+          <t>Coelmo Napoli City Half Marathon</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
@@ -5699,23 +5699,23 @@
         </is>
       </c>
       <c r="C209" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>0:58:23</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
         <is>
-          <t>1:04:44</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>Disney Princess Half Marathon</t>
+          <t>Copenhagen Half Marathon</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -5724,23 +5724,23 @@
         </is>
       </c>
       <c r="C210" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D210" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:11</t>
         </is>
       </c>
       <c r="E210" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:53</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>Disney Princess Half Marathon</t>
+          <t>Copenhagen Half Marathon</t>
         </is>
       </c>
       <c r="B211" s="5" t="inlineStr">
@@ -5749,23 +5749,23 @@
         </is>
       </c>
       <c r="C211" s="5" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:05</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:11</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>EDP Lisboa Meia Maratona</t>
+          <t>Copenhagen Half Marathon</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
@@ -5774,23 +5774,23 @@
         </is>
       </c>
       <c r="C212" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D212" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:23</t>
         </is>
       </c>
       <c r="E212" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:44</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>EDP Lisboa Meia Maratona</t>
+          <t>Disney Princess Half Marathon</t>
         </is>
       </c>
       <c r="B213" s="5" t="inlineStr">
@@ -5815,7 +5815,7 @@
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
         <is>
-          <t>EDP Lisboa Meia Maratona</t>
+          <t>Disney Princess Half Marathon</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
@@ -5840,7 +5840,7 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>Eurospin RomaOstia Half Marathon</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B215" s="5" t="inlineStr">
@@ -5849,23 +5849,23 @@
         </is>
       </c>
       <c r="C215" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>0:59:17</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>1:06:21</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
         <is>
-          <t>Eurospin RomaOstia Half Marathon</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B216" s="7" t="inlineStr">
@@ -5874,23 +5874,23 @@
         </is>
       </c>
       <c r="C216" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D216" s="7" t="inlineStr">
         <is>
-          <t>1:01:10</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E216" s="7" t="inlineStr">
         <is>
-          <t>1:07:38</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>Eurospin RomaOstia Half Marathon</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B217" s="5" t="inlineStr">
@@ -5899,16 +5899,16 @@
         </is>
       </c>
       <c r="C217" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>0:58:49</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>1:08:20</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -5924,23 +5924,23 @@
         </is>
       </c>
       <c r="C218" s="7" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D218" s="7" t="inlineStr">
         <is>
-          <t>0:58:00</t>
+          <t>0:59:17</t>
         </is>
       </c>
       <c r="E218" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:21</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>Generali Berlin Half Marathon</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B219" s="5" t="inlineStr">
@@ -5949,23 +5949,23 @@
         </is>
       </c>
       <c r="C219" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>0:59:01</t>
+          <t>1:01:10</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>1:05:43</t>
+          <t>1:07:38</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>Generali Berlin Half Marathon</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
@@ -5974,23 +5974,23 @@
         </is>
       </c>
       <c r="C220" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D220" s="7" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>0:58:49</t>
         </is>
       </c>
       <c r="E220" s="7" t="inlineStr">
         <is>
-          <t>1:06:53</t>
+          <t>1:08:20</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>Generali Berlin Half Marathon</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
@@ -5999,23 +5999,23 @@
         </is>
       </c>
       <c r="C221" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>0:58:43</t>
+          <t>0:58:00</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>1:03:35</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
         <is>
-          <t>Generali Prague Half Marathon</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B222" s="7" t="inlineStr">
@@ -6028,19 +6028,19 @@
       </c>
       <c r="D222" s="7" t="inlineStr">
         <is>
-          <t>0:59:43</t>
+          <t>0:59:01</t>
         </is>
       </c>
       <c r="E222" s="7" t="inlineStr">
         <is>
-          <t>1:06:00</t>
+          <t>1:05:43</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>Generali Prague Half Marathon</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
@@ -6053,19 +6053,19 @@
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>0:58:24</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>1:08:10</t>
+          <t>1:06:53</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>Generali Prague Half Marathon</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -6078,19 +6078,19 @@
       </c>
       <c r="D224" s="7" t="inlineStr">
         <is>
-          <t>0:58:54</t>
+          <t>0:58:43</t>
         </is>
       </c>
       <c r="E224" s="7" t="inlineStr">
         <is>
-          <t>1:05:27</t>
+          <t>1:03:35</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>GetPro Bath Half</t>
+          <t>Generali Prague Half Marathon</t>
         </is>
       </c>
       <c r="B225" s="5" t="inlineStr">
@@ -6099,23 +6099,23 @@
         </is>
       </c>
       <c r="C225" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:43</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:00</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>GetPro Bath Half</t>
+          <t>Generali Prague Half Marathon</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
@@ -6124,23 +6124,23 @@
         </is>
       </c>
       <c r="C226" s="7" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D226" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:24</t>
         </is>
       </c>
       <c r="E226" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:10</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>Göteborgsvarvet</t>
+          <t>Generali Prague Half Marathon</t>
         </is>
       </c>
       <c r="B227" s="5" t="inlineStr">
@@ -6149,23 +6149,23 @@
         </is>
       </c>
       <c r="C227" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:54</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:27</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
         <is>
-          <t>Göteborgsvarvet</t>
+          <t>GetPro Bath Half</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
@@ -6190,7 +6190,7 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>HOKA Semi de Paris</t>
+          <t>GetPro Bath Half</t>
         </is>
       </c>
       <c r="B229" s="5" t="inlineStr">
@@ -6199,23 +6199,23 @@
         </is>
       </c>
       <c r="C229" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>0:59:38</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
         <is>
-          <t>1:06:01</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
         <is>
-          <t>HOKA Semi de Paris</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B230" s="7" t="inlineStr">
@@ -6228,19 +6228,19 @@
       </c>
       <c r="D230" s="7" t="inlineStr">
         <is>
-          <t>1:00:45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E230" s="7" t="inlineStr">
         <is>
-          <t>1:06:58</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>HOKA Semi de Paris</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B231" s="5" t="inlineStr">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>1:00:16</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>1:07:14</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -6274,23 +6274,23 @@
         </is>
       </c>
       <c r="C232" s="7" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D232" s="7" t="inlineStr">
         <is>
-          <t>1:00:11</t>
+          <t>0:59:38</t>
         </is>
       </c>
       <c r="E232" s="7" t="inlineStr">
         <is>
-          <t>1:05:12</t>
+          <t>1:06:01</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>Half Marathon Munchen by Brooks</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B233" s="5" t="inlineStr">
@@ -6299,23 +6299,23 @@
         </is>
       </c>
       <c r="C233" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:45</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:58</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
         <is>
-          <t>Hoka Runaway Sydney Half Marathon</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B234" s="7" t="inlineStr">
@@ -6328,19 +6328,19 @@
       </c>
       <c r="D234" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:16</t>
         </is>
       </c>
       <c r="E234" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:14</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>Hyundai Meia Maratona</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B235" s="5" t="inlineStr">
@@ -6349,23 +6349,23 @@
         </is>
       </c>
       <c r="C235" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:11</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:12</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
         <is>
-          <t>Hyundai Meia Maratona</t>
+          <t>Half Marathon Munchen by Brooks</t>
         </is>
       </c>
       <c r="B236" s="7" t="inlineStr">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="C236" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D236" s="7" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>Hyundai Meia Maratona</t>
+          <t>Hoka Runaway Sydney Half Marathon</t>
         </is>
       </c>
       <c r="B237" s="5" t="inlineStr">
@@ -6415,7 +6415,7 @@
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>IU Health 500 Festival Mini-Marathon</t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="B238" s="7" t="inlineStr">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="C238" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D238" s="7" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>Kagawa Marugame International Half Marathon</t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="B239" s="5" t="inlineStr">
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="C239" s="5" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>Life Time Chicago Half Marathon &amp; 5K</t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="B240" s="7" t="inlineStr">
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="C240" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D240" s="7" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>Life Time Chicago Half Marathon &amp; 5K</t>
+          <t>IU Health 500 Festival Mini-Marathon</t>
         </is>
       </c>
       <c r="B241" s="5" t="inlineStr">
@@ -6515,7 +6515,7 @@
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>London Landmarks Half Marathon</t>
+          <t>Kagawa Marugame International Half Marathon</t>
         </is>
       </c>
       <c r="B242" s="7" t="inlineStr">
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="C242" s="7" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D242" s="7" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>London Landmarks Half Marathon</t>
+          <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
       <c r="B243" s="5" t="inlineStr">
@@ -6549,7 +6549,7 @@
         </is>
       </c>
       <c r="C243" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
         <is>
-          <t>Manchester Half Marathon</t>
+          <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
       <c r="B244" s="7" t="inlineStr">
@@ -6590,7 +6590,7 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>Media Maraton de Bogota</t>
+          <t>London Landmarks Half Marathon</t>
         </is>
       </c>
       <c r="B245" s="5" t="inlineStr">
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="C245" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
         <is>
-          <t>Medio Maraton de Sevilla</t>
+          <t>London Landmarks Half Marathon</t>
         </is>
       </c>
       <c r="B246" s="7" t="inlineStr">
@@ -6624,23 +6624,23 @@
         </is>
       </c>
       <c r="C246" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D246" s="7" t="inlineStr">
         <is>
-          <t>0:59:21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E246" s="7" t="inlineStr">
         <is>
-          <t>1:07:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>Medio Maraton de Sevilla</t>
+          <t>Manchester Half Marathon</t>
         </is>
       </c>
       <c r="B247" s="5" t="inlineStr">
@@ -6653,19 +6653,19 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>0:59:33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>1:07:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>Medio Maraton de Sevilla</t>
+          <t>Media Maraton de Bogota</t>
         </is>
       </c>
       <c r="B248" s="7" t="inlineStr">
@@ -6674,23 +6674,23 @@
         </is>
       </c>
       <c r="C248" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D248" s="7" t="inlineStr">
         <is>
-          <t>1:00:24</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E248" s="7" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>Mitja Marato Barcelona by Brooks</t>
+          <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
       <c r="B249" s="5" t="inlineStr">
@@ -6699,23 +6699,23 @@
         </is>
       </c>
       <c r="C249" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>0:58:53</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>1:04:37</t>
+          <t>1:07:59</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>Mitja Marato Barcelona by Brooks</t>
+          <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
       <c r="B250" s="7" t="inlineStr">
@@ -6724,23 +6724,23 @@
         </is>
       </c>
       <c r="C250" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D250" s="7" t="inlineStr">
         <is>
-          <t>0:59:21</t>
+          <t>0:59:33</t>
         </is>
       </c>
       <c r="E250" s="7" t="inlineStr">
         <is>
-          <t>1:04:28</t>
+          <t>1:07:18</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>Mitja Marato Barcelona by Brooks</t>
+          <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
@@ -6749,16 +6749,16 @@
         </is>
       </c>
       <c r="C251" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>0:56:42</t>
+          <t>1:00:24</t>
         </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>1:04:11</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
@@ -6774,23 +6774,23 @@
         </is>
       </c>
       <c r="C252" s="7" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D252" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:53</t>
         </is>
       </c>
       <c r="E252" s="7" t="inlineStr">
         <is>
-          <t>1:04:00</t>
+          <t>1:04:37</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>Movistar Madrid Medio Maraton</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
@@ -6799,23 +6799,23 @@
         </is>
       </c>
       <c r="C253" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:28</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - Half Marathon</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B254" s="7" t="inlineStr">
@@ -6828,19 +6828,19 @@
       </c>
       <c r="D254" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:56:42</t>
         </is>
       </c>
       <c r="E254" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:11</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - Half Marathon</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B255" s="5" t="inlineStr">
@@ -6858,14 +6858,14 @@
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:00</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>NYCRUNS Brooklyn Experience Half Marathon</t>
+          <t>Movistar Madrid Medio Maraton</t>
         </is>
       </c>
       <c r="B256" s="7" t="inlineStr">
@@ -6890,7 +6890,7 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>NYRR RBC Brooklyn Half</t>
+          <t>NN CPC Loop Den Haag - Half Marathon</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
@@ -6915,7 +6915,7 @@
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>Nike Melbourne Marathon Festival</t>
+          <t>NN CPC Loop Den Haag - Half Marathon</t>
         </is>
       </c>
       <c r="B258" s="7" t="inlineStr">
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C258" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D258" s="7" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>NYCRUNS Brooklyn Experience Half Marathon</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
@@ -6949,7 +6949,7 @@
         </is>
       </c>
       <c r="C259" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="C260" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D260" s="7" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>Nike Melbourne Marathon Festival</t>
         </is>
       </c>
       <c r="B261" s="5" t="inlineStr">
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="C262" s="7" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D262" s="7" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B263" s="5" t="inlineStr">
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="C263" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -7074,7 +7074,7 @@
         </is>
       </c>
       <c r="C264" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D264" s="7" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B265" s="5" t="inlineStr">
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="C265" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="C266" s="7" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D266" s="7" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Mexico City</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B267" s="5" t="inlineStr">
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="C267" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series San Diego</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
@@ -7190,7 +7190,7 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>Royal Parks Half Marathon</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B269" s="5" t="inlineStr">
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="C269" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Rock 'n' Roll Running Series Mexico City</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="C270" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D270" s="7" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Rock 'n' Roll Running Series San Diego</t>
         </is>
       </c>
       <c r="B271" s="5" t="inlineStr">
@@ -7249,23 +7249,23 @@
         </is>
       </c>
       <c r="C271" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>1:05:44</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>1:18:34</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Royal Parks Half Marathon</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -7290,7 +7290,7 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>Semi-Marathon de Boulogne-Billancourt</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="C273" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -7324,23 +7324,23 @@
         </is>
       </c>
       <c r="C274" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D274" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:44</t>
         </is>
       </c>
       <c r="E274" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:18:34</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Series Nashville</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B275" s="5" t="inlineStr">
@@ -7365,7 +7365,7 @@
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>Semi-Marathon de Boulogne-Billancourt</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
@@ -7390,7 +7390,7 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Singapore Half Marathon</t>
+          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
@@ -7415,7 +7415,7 @@
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>TCS Mizuno Half Marathon</t>
+          <t>St. Jude Rock 'n' Roll Series Nashville</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -7440,7 +7440,7 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
@@ -7449,23 +7449,23 @@
         </is>
       </c>
       <c r="C279" s="5" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:13</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:09:28</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="C280" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D280" s="7" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="C281" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>Standard Chartered KL Half Marathon</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -7524,23 +7524,23 @@
         </is>
       </c>
       <c r="C282" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D282" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:11:08</t>
         </is>
       </c>
       <c r="E282" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:23:55</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>Standard Chartered Singapore Half Marathon</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="C283" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -7590,7 +7590,7 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon (Half)</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="C285" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon (Half)</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -7624,7 +7624,7 @@
         </is>
       </c>
       <c r="C286" s="7" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D286" s="7" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>The Big Half</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
@@ -7665,7 +7665,7 @@
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>Tokyo Legacy Half Marathon</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -7674,7 +7674,7 @@
         </is>
       </c>
       <c r="C288" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D288" s="7" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
@@ -7699,23 +7699,23 @@
         </is>
       </c>
       <c r="C289" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>1:01:31</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>1:07:04</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -7724,23 +7724,23 @@
         </is>
       </c>
       <c r="C290" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D290" s="7" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E290" s="7" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
+          <t>Tata Mumbai Marathon (Half)</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
@@ -7753,19 +7753,19 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>0:58:02</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>1:03:08</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>Vedanta Delhi Half Marathon</t>
+          <t>Tata Mumbai Marathon (Half)</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -7774,23 +7774,23 @@
         </is>
       </c>
       <c r="C292" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D292" s="7" t="inlineStr">
         <is>
-          <t>0:59:50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E292" s="7" t="inlineStr">
         <is>
-          <t>1:07:20</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>Vienna City Half Marathon</t>
+          <t>The Big Half</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
@@ -7815,7 +7815,7 @@
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>Walt Disney World Marathon Weekend</t>
+          <t>Tokyo Legacy Half Marathon</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -7840,7 +7840,7 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>Walt Disney World Marathon Weekend</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B295" s="5" t="inlineStr">
@@ -7849,23 +7849,23 @@
         </is>
       </c>
       <c r="C295" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:31</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:04</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>Warsaw Half Marathon</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -7874,23 +7874,23 @@
         </is>
       </c>
       <c r="C296" s="7" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D296" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E296" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>Warsaw Half Marathon</t>
+          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B297" s="5" t="inlineStr">
@@ -7903,19 +7903,19 @@
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:02</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:08</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>Wizz Air Rome Half Marathon by Brooks</t>
+          <t>Vedanta Delhi Half Marathon</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -7928,19 +7928,19 @@
       </c>
       <c r="D298" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:50</t>
         </is>
       </c>
       <c r="E298" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:20</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Vienna City Half Marathon</t>
         </is>
       </c>
       <c r="B299" s="5" t="inlineStr">
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="C299" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
@@ -7974,7 +7974,7 @@
         </is>
       </c>
       <c r="C300" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D300" s="7" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
       <c r="B301" s="5" t="inlineStr">
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="C301" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
@@ -8013,25 +8013,25 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="8" t="inlineStr">
-        <is>
-          <t>10K Montmartre</t>
-        </is>
-      </c>
-      <c r="B302" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C302" s="9" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D302" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E302" s="9" t="inlineStr">
+      <c r="A302" s="6" t="inlineStr">
+        <is>
+          <t>Warsaw Half Marathon</t>
+        </is>
+      </c>
+      <c r="B302" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C302" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D302" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E302" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8040,16 +8040,16 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
+          <t>Warsaw Half Marathon</t>
         </is>
       </c>
       <c r="B303" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C303" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
@@ -8058,48 +8058,48 @@
       </c>
       <c r="E303" s="5" t="inlineStr">
         <is>
-          <t>0:29:19</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="8" t="inlineStr">
-        <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
-        </is>
-      </c>
-      <c r="B304" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C304" s="9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D304" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E304" s="9" t="inlineStr">
-        <is>
-          <t>0:28:45</t>
+      <c r="A304" s="6" t="inlineStr">
+        <is>
+          <t>Wizz Air Rome Half Marathon by Brooks</t>
+        </is>
+      </c>
+      <c r="B304" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C304" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D304" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E304" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
         </is>
       </c>
       <c r="B305" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C305" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
@@ -8113,43 +8113,43 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="8" t="inlineStr">
-        <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
-        </is>
-      </c>
-      <c r="B306" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C306" s="9" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D306" s="9" t="inlineStr">
-        <is>
-          <t>0:26:45</t>
-        </is>
-      </c>
-      <c r="E306" s="9" t="inlineStr">
-        <is>
-          <t>0:29:25</t>
+      <c r="A306" s="6" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+        </is>
+      </c>
+      <c r="B306" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C306" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D306" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E306" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
         </is>
       </c>
       <c r="B307" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C307" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
     <row r="308">
       <c r="A308" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>10K Montmartre</t>
         </is>
       </c>
       <c r="B308" s="9" t="inlineStr">
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="C308" s="9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>ASICS LDNX</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B309" s="5" t="inlineStr">
@@ -8199,7 +8199,7 @@
         </is>
       </c>
       <c r="C309" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="E309" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:19</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="8" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B310" s="9" t="inlineStr">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C310" s="9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
@@ -8233,14 +8233,14 @@
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:45</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B311" s="5" t="inlineStr">
@@ -8249,23 +8249,23 @@
         </is>
       </c>
       <c r="C311" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>0:29:37</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E311" s="5" t="inlineStr">
         <is>
-          <t>0:32:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="8" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B312" s="9" t="inlineStr">
@@ -8274,23 +8274,23 @@
         </is>
       </c>
       <c r="C312" s="9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:26:45</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:25</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B313" s="5" t="inlineStr">
@@ -8299,23 +8299,23 @@
         </is>
       </c>
       <c r="C313" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
-          <t>0:30:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="8" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B314" s="9" t="inlineStr">
@@ -8324,23 +8324,23 @@
         </is>
       </c>
       <c r="C314" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>0:31:12</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>ASICS LDNX</t>
         </is>
       </c>
       <c r="B315" s="5" t="inlineStr">
@@ -8358,14 +8358,14 @@
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>0:31:29</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="8" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B316" s="9" t="inlineStr">
@@ -8378,19 +8378,19 @@
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>0:29:08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>0:33:25</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B317" s="5" t="inlineStr">
@@ -8403,19 +8403,19 @@
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>0:29:13</t>
+          <t>0:29:37</t>
         </is>
       </c>
       <c r="E317" s="5" t="inlineStr">
         <is>
-          <t>0:32:45</t>
+          <t>0:32:18</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="8" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B318" s="9" t="inlineStr">
@@ -8440,7 +8440,7 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B319" s="5" t="inlineStr">
@@ -8453,19 +8453,19 @@
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:30:43</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="8" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B320" s="9" t="inlineStr">
@@ -8478,19 +8478,19 @@
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:12</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B321" s="5" t="inlineStr">
@@ -8508,14 +8508,14 @@
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:29</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="8" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B322" s="9" t="inlineStr">
@@ -8528,19 +8528,19 @@
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>0:28:52</t>
+          <t>0:29:08</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>0:31:59</t>
+          <t>0:33:25</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B323" s="5" t="inlineStr">
@@ -8553,19 +8553,19 @@
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>0:28:46</t>
+          <t>0:29:13</t>
         </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
         <is>
-          <t>0:32:33</t>
+          <t>0:32:45</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="8" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B324" s="9" t="inlineStr">
@@ -8578,19 +8578,19 @@
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>0:29:22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>0:34:32</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B325" s="5" t="inlineStr">
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="C325" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
     <row r="326">
       <c r="A326" s="8" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B326" s="9" t="inlineStr">
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="C326" s="9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B327" s="5" t="inlineStr">
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="C327" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D327" s="5" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
     <row r="328">
       <c r="A328" s="8" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B328" s="9" t="inlineStr">
@@ -8674,23 +8674,23 @@
         </is>
       </c>
       <c r="C328" s="9" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>0:28:27</t>
+          <t>0:28:52</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>0:31:49</t>
+          <t>0:31:59</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B329" s="5" t="inlineStr">
@@ -8699,23 +8699,23 @@
         </is>
       </c>
       <c r="C329" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:46</t>
         </is>
       </c>
       <c r="E329" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:33</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="8" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B330" s="9" t="inlineStr">
@@ -8724,23 +8724,23 @@
         </is>
       </c>
       <c r="C330" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:22</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:34:32</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B331" s="5" t="inlineStr">
@@ -8749,7 +8749,7 @@
         </is>
       </c>
       <c r="C331" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
     <row r="332">
       <c r="A332" s="8" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B332" s="9" t="inlineStr">
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="C332" s="9" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D332" s="9" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B333" s="5" t="inlineStr">
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="C333" s="5" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
     <row r="334">
       <c r="A334" s="8" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B334" s="9" t="inlineStr">
@@ -8824,23 +8824,23 @@
         </is>
       </c>
       <c r="C334" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D334" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:27</t>
         </is>
       </c>
       <c r="E334" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:49</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B335" s="5" t="inlineStr">
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="C335" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
@@ -8858,14 +8858,14 @@
       </c>
       <c r="E335" s="5" t="inlineStr">
         <is>
-          <t>0:31:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="8" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B336" s="9" t="inlineStr">
@@ -8874,23 +8874,23 @@
         </is>
       </c>
       <c r="C336" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D336" s="9" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E336" s="9" t="inlineStr">
         <is>
-          <t>0:31:11</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B337" s="5" t="inlineStr">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="C337" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
     <row r="338">
       <c r="A338" s="8" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="C338" s="9" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D338" s="9" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
         </is>
       </c>
       <c r="B339" s="5" t="inlineStr">
@@ -8949,7 +8949,7 @@
         </is>
       </c>
       <c r="C339" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
     <row r="340">
       <c r="A340" s="8" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -8990,7 +8990,7 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B341" s="5" t="inlineStr">
@@ -9008,14 +9008,14 @@
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:18</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="8" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -9028,19 +9028,19 @@
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E342" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:11</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B343" s="5" t="inlineStr">
@@ -9065,7 +9065,7 @@
     <row r="344">
       <c r="A344" s="8" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -9078,19 +9078,19 @@
       </c>
       <c r="D344" s="9" t="inlineStr">
         <is>
-          <t>0:29:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>0:32:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B345" s="5" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>0:29:33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E345" s="5" t="inlineStr">
@@ -9115,7 +9115,7 @@
     <row r="346">
       <c r="A346" s="8" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -9140,7 +9140,7 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B347" s="5" t="inlineStr">
@@ -9165,7 +9165,7 @@
     <row r="348">
       <c r="A348" s="8" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -9190,7 +9190,7 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B349" s="5" t="inlineStr">
@@ -9215,7 +9215,7 @@
     <row r="350">
       <c r="A350" s="8" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -9228,19 +9228,19 @@
       </c>
       <c r="D350" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:41</t>
         </is>
       </c>
       <c r="E350" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:51</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B351" s="5" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:33</t>
         </is>
       </c>
       <c r="E351" s="5" t="inlineStr">
@@ -9265,7 +9265,7 @@
     <row r="352">
       <c r="A352" s="8" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -9290,7 +9290,7 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B353" s="5" t="inlineStr">
@@ -9315,7 +9315,7 @@
     <row r="354">
       <c r="A354" s="8" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -9340,7 +9340,7 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B355" s="5" t="inlineStr">
@@ -9365,7 +9365,7 @@
     <row r="356">
       <c r="A356" s="8" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -9390,7 +9390,7 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B357" s="5" t="inlineStr">
@@ -9403,19 +9403,19 @@
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
-          <t>0:28:09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E357" s="5" t="inlineStr">
         <is>
-          <t>0:32:54</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="8" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -9440,7 +9440,7 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B359" s="5" t="inlineStr">
@@ -9453,42 +9453,192 @@
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>0:29:14</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E359" s="5" t="inlineStr">
         <is>
-          <t>0:31:36</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="8" t="inlineStr">
         <is>
+          <t>Ukrop's Monument Avenue 10K</t>
+        </is>
+      </c>
+      <c r="B360" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C360" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D360" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E360" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="4" t="inlineStr">
+        <is>
+          <t>Vancouver Sun Run</t>
+        </is>
+      </c>
+      <c r="B361" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C361" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D361" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E361" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="8" t="inlineStr">
+        <is>
+          <t>Vancouver Sun Run</t>
+        </is>
+      </c>
+      <c r="B362" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C362" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D362" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E362" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="4" t="inlineStr">
+        <is>
+          <t>Vancouver Sun Run</t>
+        </is>
+      </c>
+      <c r="B363" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C363" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D363" s="5" t="inlineStr">
+        <is>
+          <t>0:28:09</t>
+        </is>
+      </c>
+      <c r="E363" s="5" t="inlineStr">
+        <is>
+          <t>0:32:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="8" t="inlineStr">
+        <is>
           <t>Vitality London 10,000</t>
         </is>
       </c>
-      <c r="B360" s="9" t="inlineStr">
+      <c r="B364" s="9" t="inlineStr">
         <is>
           <t>10K</t>
         </is>
       </c>
-      <c r="C360" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D360" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E360" s="9" t="inlineStr">
+      <c r="C364" s="9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D364" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E364" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="4" t="inlineStr">
+        <is>
+          <t>Vitality London 10,000</t>
+        </is>
+      </c>
+      <c r="B365" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C365" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D365" s="5" t="inlineStr">
+        <is>
+          <t>0:29:14</t>
+        </is>
+      </c>
+      <c r="E365" s="5" t="inlineStr">
+        <is>
+          <t>0:31:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="8" t="inlineStr">
+        <is>
+          <t>Vitality London 10,000</t>
+        </is>
+      </c>
+      <c r="B366" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C366" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D366" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E366" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E360"/>
+  <autoFilter ref="A1:E366"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Chronos_Vainqueurs.xlsx
+++ b/Chronos_Vainqueurs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$366</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$391</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E366"/>
+  <dimension ref="A1:E391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -8290,7 +8290,7 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>AJ Bell Great Birmingham Run 10K</t>
         </is>
       </c>
       <c r="B313" s="5" t="inlineStr">
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="C313" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
     <row r="314">
       <c r="A314" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>AJ Bell Great Bristol Run 10K</t>
         </is>
       </c>
       <c r="B314" s="9" t="inlineStr">
@@ -8340,7 +8340,7 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>ASICS LDNX</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B315" s="5" t="inlineStr">
@@ -8365,7 +8365,7 @@
     <row r="316">
       <c r="A316" s="8" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B316" s="9" t="inlineStr">
@@ -8374,7 +8374,7 @@
         </is>
       </c>
       <c r="C316" s="9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B317" s="5" t="inlineStr">
@@ -8399,23 +8399,23 @@
         </is>
       </c>
       <c r="C317" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>0:29:37</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E317" s="5" t="inlineStr">
         <is>
-          <t>0:32:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="8" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>AJ Bell Great North 10K</t>
         </is>
       </c>
       <c r="B318" s="9" t="inlineStr">
@@ -8440,7 +8440,7 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>ASICS LDNX</t>
         </is>
       </c>
       <c r="B319" s="5" t="inlineStr">
@@ -8449,23 +8449,23 @@
         </is>
       </c>
       <c r="C319" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
-          <t>0:30:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="8" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B320" s="9" t="inlineStr">
@@ -8474,23 +8474,23 @@
         </is>
       </c>
       <c r="C320" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>0:31:12</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B321" s="5" t="inlineStr">
@@ -8499,23 +8499,23 @@
         </is>
       </c>
       <c r="C321" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:37</t>
         </is>
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>0:31:29</t>
+          <t>0:32:18</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="8" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B322" s="9" t="inlineStr">
@@ -8524,23 +8524,23 @@
         </is>
       </c>
       <c r="C322" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>0:29:08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>0:33:25</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B323" s="5" t="inlineStr">
@@ -8549,23 +8549,23 @@
         </is>
       </c>
       <c r="C323" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>0:29:13</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
         <is>
-          <t>0:32:45</t>
+          <t>0:30:43</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="8" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B324" s="9" t="inlineStr">
@@ -8574,23 +8574,23 @@
         </is>
       </c>
       <c r="C324" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:12</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B325" s="5" t="inlineStr">
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="C325" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
@@ -8608,14 +8608,14 @@
       </c>
       <c r="E325" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:29</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="8" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B326" s="9" t="inlineStr">
@@ -8624,23 +8624,23 @@
         </is>
       </c>
       <c r="C326" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:08</t>
         </is>
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:33:25</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B327" s="5" t="inlineStr">
@@ -8649,23 +8649,23 @@
         </is>
       </c>
       <c r="C327" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D327" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:13</t>
         </is>
       </c>
       <c r="E327" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:45</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="8" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B328" s="9" t="inlineStr">
@@ -8674,23 +8674,23 @@
         </is>
       </c>
       <c r="C328" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>0:28:52</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>0:31:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B329" s="5" t="inlineStr">
@@ -8699,23 +8699,23 @@
         </is>
       </c>
       <c r="C329" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t>0:28:46</t>
+          <t>0:28:36</t>
         </is>
       </c>
       <c r="E329" s="5" t="inlineStr">
         <is>
-          <t>0:32:33</t>
+          <t>0:31:51</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="8" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B330" s="9" t="inlineStr">
@@ -8724,23 +8724,23 @@
         </is>
       </c>
       <c r="C330" s="9" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>0:29:22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>0:34:32</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B331" s="5" t="inlineStr">
@@ -8749,7 +8749,7 @@
         </is>
       </c>
       <c r="C331" s="5" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
     <row r="332">
       <c r="A332" s="8" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B332" s="9" t="inlineStr">
@@ -8774,7 +8774,7 @@
         </is>
       </c>
       <c r="C332" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D332" s="9" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B333" s="5" t="inlineStr">
@@ -8799,23 +8799,23 @@
         </is>
       </c>
       <c r="C333" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:52</t>
         </is>
       </c>
       <c r="E333" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:59</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="8" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B334" s="9" t="inlineStr">
@@ -8824,23 +8824,23 @@
         </is>
       </c>
       <c r="C334" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D334" s="9" t="inlineStr">
         <is>
-          <t>0:28:27</t>
+          <t>0:28:46</t>
         </is>
       </c>
       <c r="E334" s="9" t="inlineStr">
         <is>
-          <t>0:31:49</t>
+          <t>0:32:33</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B335" s="5" t="inlineStr">
@@ -8849,23 +8849,23 @@
         </is>
       </c>
       <c r="C335" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:22</t>
         </is>
       </c>
       <c r="E335" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:34:32</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="8" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B336" s="9" t="inlineStr">
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="C336" s="9" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D336" s="9" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B337" s="5" t="inlineStr">
@@ -8899,7 +8899,7 @@
         </is>
       </c>
       <c r="C337" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
     <row r="338">
       <c r="A338" s="8" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="C338" s="9" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D338" s="9" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B339" s="5" t="inlineStr">
@@ -8949,23 +8949,23 @@
         </is>
       </c>
       <c r="C339" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:27</t>
         </is>
       </c>
       <c r="E339" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:49</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="8" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -8974,7 +8974,7 @@
         </is>
       </c>
       <c r="C340" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D340" s="9" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B341" s="5" t="inlineStr">
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="C341" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
@@ -9008,14 +9008,14 @@
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>0:31:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="8" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -9024,23 +9024,23 @@
         </is>
       </c>
       <c r="C342" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E342" s="9" t="inlineStr">
         <is>
-          <t>0:31:11</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B343" s="5" t="inlineStr">
@@ -9049,7 +9049,7 @@
         </is>
       </c>
       <c r="C343" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
     <row r="344">
       <c r="A344" s="8" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -9074,7 +9074,7 @@
         </is>
       </c>
       <c r="C344" s="9" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D344" s="9" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>Great Scottish Run 10K</t>
         </is>
       </c>
       <c r="B345" s="5" t="inlineStr">
@@ -9115,7 +9115,7 @@
     <row r="346">
       <c r="A346" s="8" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="C346" s="9" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D346" s="9" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B347" s="5" t="inlineStr">
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="C347" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
     <row r="348">
       <c r="A348" s="8" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="C348" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D348" s="9" t="inlineStr">
         <is>
@@ -9183,14 +9183,14 @@
       </c>
       <c r="E348" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:18</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B349" s="5" t="inlineStr">
@@ -9199,23 +9199,23 @@
         </is>
       </c>
       <c r="C349" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:11</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="8" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -9224,23 +9224,23 @@
         </is>
       </c>
       <c r="C350" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D350" s="9" t="inlineStr">
         <is>
-          <t>0:29:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E350" s="9" t="inlineStr">
         <is>
-          <t>0:32:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B351" s="5" t="inlineStr">
@@ -9249,11 +9249,11 @@
         </is>
       </c>
       <c r="C351" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>0:29:33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E351" s="5" t="inlineStr">
@@ -9265,7 +9265,7 @@
     <row r="352">
       <c r="A352" s="8" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="C352" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D352" s="9" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Run in Lyon</t>
         </is>
       </c>
       <c r="B353" s="5" t="inlineStr">
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="C353" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D353" s="5" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
     <row r="354">
       <c r="A354" s="8" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="C354" s="9" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D354" s="9" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B355" s="5" t="inlineStr">
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="C355" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
     <row r="356">
       <c r="A356" s="8" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -9374,7 +9374,7 @@
         </is>
       </c>
       <c r="C356" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D356" s="9" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B357" s="5" t="inlineStr">
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="C357" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
     <row r="358">
       <c r="A358" s="8" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -9424,23 +9424,23 @@
         </is>
       </c>
       <c r="C358" s="9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D358" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:41</t>
         </is>
       </c>
       <c r="E358" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:51</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B359" s="5" t="inlineStr">
@@ -9449,11 +9449,11 @@
         </is>
       </c>
       <c r="C359" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:33</t>
         </is>
       </c>
       <c r="E359" s="5" t="inlineStr">
@@ -9465,7 +9465,7 @@
     <row r="360">
       <c r="A360" s="8" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Standard Chartered KL 10K</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -9478,19 +9478,19 @@
       </c>
       <c r="D360" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:26</t>
         </is>
       </c>
       <c r="E360" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:39:23</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B361" s="5" t="inlineStr">
@@ -9515,7 +9515,7 @@
     <row r="362">
       <c r="A362" s="8" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -9540,7 +9540,7 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B363" s="5" t="inlineStr">
@@ -9553,19 +9553,19 @@
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
-          <t>0:28:09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E363" s="5" t="inlineStr">
         <is>
-          <t>0:32:54</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="8" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -9590,7 +9590,7 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B365" s="5" t="inlineStr">
@@ -9603,42 +9603,667 @@
       </c>
       <c r="D365" s="5" t="inlineStr">
         <is>
-          <t>0:29:14</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E365" s="5" t="inlineStr">
         <is>
-          <t>0:31:36</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="8" t="inlineStr">
         <is>
+          <t>Transurban Bridge to Brisbane</t>
+        </is>
+      </c>
+      <c r="B366" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C366" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D366" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E366" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="4" t="inlineStr">
+        <is>
+          <t>Ukrop's Monument Avenue 10K</t>
+        </is>
+      </c>
+      <c r="B367" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C367" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D367" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E367" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="8" t="inlineStr">
+        <is>
+          <t>Ukrop's Monument Avenue 10K</t>
+        </is>
+      </c>
+      <c r="B368" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C368" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D368" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E368" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="4" t="inlineStr">
+        <is>
+          <t>Ukrop's Monument Avenue 10K</t>
+        </is>
+      </c>
+      <c r="B369" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C369" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D369" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E369" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="8" t="inlineStr">
+        <is>
+          <t>Vancouver Sun Run</t>
+        </is>
+      </c>
+      <c r="B370" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C370" s="9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D370" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E370" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="4" t="inlineStr">
+        <is>
+          <t>Vancouver Sun Run</t>
+        </is>
+      </c>
+      <c r="B371" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C371" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D371" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E371" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="8" t="inlineStr">
+        <is>
+          <t>Vancouver Sun Run</t>
+        </is>
+      </c>
+      <c r="B372" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C372" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D372" s="9" t="inlineStr">
+        <is>
+          <t>0:28:09</t>
+        </is>
+      </c>
+      <c r="E372" s="9" t="inlineStr">
+        <is>
+          <t>0:32:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="4" t="inlineStr">
+        <is>
           <t>Vitality London 10,000</t>
         </is>
       </c>
-      <c r="B366" s="9" t="inlineStr">
+      <c r="B373" s="5" t="inlineStr">
         <is>
           <t>10K</t>
         </is>
       </c>
-      <c r="C366" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D366" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E366" s="9" t="inlineStr">
+      <c r="C373" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D373" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E373" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="8" t="inlineStr">
+        <is>
+          <t>Vitality London 10,000</t>
+        </is>
+      </c>
+      <c r="B374" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C374" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D374" s="9" t="inlineStr">
+        <is>
+          <t>0:29:14</t>
+        </is>
+      </c>
+      <c r="E374" s="9" t="inlineStr">
+        <is>
+          <t>0:31:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="4" t="inlineStr">
+        <is>
+          <t>Vitality London 10,000</t>
+        </is>
+      </c>
+      <c r="B375" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C375" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D375" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E375" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="8" t="inlineStr">
+        <is>
+          <t>AJ Bell Great Birmingham Run</t>
+        </is>
+      </c>
+      <c r="B376" s="9" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="C376" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D376" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E376" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="4" t="inlineStr">
+        <is>
+          <t>AJ Bell Great South Run</t>
+        </is>
+      </c>
+      <c r="B377" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C377" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D377" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E377" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="8" t="inlineStr">
+        <is>
+          <t>Army Ten Miler</t>
+        </is>
+      </c>
+      <c r="B378" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C378" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D378" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E378" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="4" t="inlineStr">
+        <is>
+          <t>Bay to Breakers</t>
+        </is>
+      </c>
+      <c r="B379" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C379" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D379" s="5" t="inlineStr">
+        <is>
+          <t>0:35:01</t>
+        </is>
+      </c>
+      <c r="E379" s="5" t="inlineStr">
+        <is>
+          <t>0:39:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="8" t="inlineStr">
+        <is>
+          <t>Bay to Breakers</t>
+        </is>
+      </c>
+      <c r="B380" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C380" s="9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D380" s="9" t="inlineStr">
+        <is>
+          <t>0:36:10</t>
+        </is>
+      </c>
+      <c r="E380" s="9" t="inlineStr">
+        <is>
+          <t>0:42:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="4" t="inlineStr">
+        <is>
+          <t>Bay to Breakers</t>
+        </is>
+      </c>
+      <c r="B381" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C381" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D381" s="5" t="inlineStr">
+        <is>
+          <t>0:37:02</t>
+        </is>
+      </c>
+      <c r="E381" s="5" t="inlineStr">
+        <is>
+          <t>0:43:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="8" t="inlineStr">
+        <is>
+          <t>Boilermaker Road Race</t>
+        </is>
+      </c>
+      <c r="B382" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C382" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D382" s="9" t="inlineStr">
+        <is>
+          <t>0:42:44</t>
+        </is>
+      </c>
+      <c r="E382" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="4" t="inlineStr">
+        <is>
+          <t>Broad Street Run</t>
+        </is>
+      </c>
+      <c r="B383" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C383" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D383" s="5" t="inlineStr">
+        <is>
+          <t>0:46:13</t>
+        </is>
+      </c>
+      <c r="E383" s="5" t="inlineStr">
+        <is>
+          <t>0:54:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="8" t="inlineStr">
+        <is>
+          <t>City2Surf</t>
+        </is>
+      </c>
+      <c r="B384" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C384" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D384" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E384" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B385" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C385" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D385" s="5" t="inlineStr">
+        <is>
+          <t>0:45:15</t>
+        </is>
+      </c>
+      <c r="E385" s="5" t="inlineStr">
+        <is>
+          <t>0:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B386" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C386" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D386" s="9" t="inlineStr">
+        <is>
+          <t>0:44:51</t>
+        </is>
+      </c>
+      <c r="E386" s="9" t="inlineStr">
+        <is>
+          <t>0:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B387" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C387" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D387" s="5" t="inlineStr">
+        <is>
+          <t>0:46:07</t>
+        </is>
+      </c>
+      <c r="E387" s="5" t="inlineStr">
+        <is>
+          <t>0:50:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="8" t="inlineStr">
+        <is>
+          <t>Falmouth Road Race</t>
+        </is>
+      </c>
+      <c r="B388" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C388" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D388" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E388" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="4" t="inlineStr">
+        <is>
+          <t>Great Scottish Run</t>
+        </is>
+      </c>
+      <c r="B389" s="5" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="C389" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D389" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E389" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="8" t="inlineStr">
+        <is>
+          <t>Lilac Bloomsday Run</t>
+        </is>
+      </c>
+      <c r="B390" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C390" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D390" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E390" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="4" t="inlineStr">
+        <is>
+          <t>Manchester Road Race</t>
+        </is>
+      </c>
+      <c r="B391" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C391" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D391" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E391" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E366"/>
+  <autoFilter ref="A1:E391"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Chronos_Vainqueurs.xlsx
+++ b/Chronos_Vainqueurs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$818</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$890</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E818"/>
+  <dimension ref="A1:E890"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -16024,23 +16024,23 @@
         </is>
       </c>
       <c r="C622" s="7" t="n">
-        <v>2025</v>
+        <v>2000</v>
       </c>
       <c r="D622" s="7" t="inlineStr">
         <is>
-          <t>1:00:52</t>
+          <t>1:01:57</t>
         </is>
       </c>
       <c r="E622" s="7" t="inlineStr">
         <is>
-          <t>1:09:32</t>
+          <t>1:08:49</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="4" t="inlineStr">
         <is>
-          <t>Aramco Houston Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B623" s="5" t="inlineStr">
@@ -16049,23 +16049,23 @@
         </is>
       </c>
       <c r="C623" s="5" t="n">
-        <v>2024</v>
+        <v>2001</v>
       </c>
       <c r="D623" s="5" t="inlineStr">
         <is>
-          <t>1:00:42</t>
+          <t>1:00:30</t>
         </is>
       </c>
       <c r="E623" s="5" t="inlineStr">
         <is>
-          <t>1:04:37</t>
+          <t>1:08:40</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="6" t="inlineStr">
         <is>
-          <t>Aramco Houston Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B624" s="7" t="inlineStr">
@@ -16074,11 +16074,11 @@
         </is>
       </c>
       <c r="C624" s="7" t="n">
-        <v>2025</v>
+        <v>2002</v>
       </c>
       <c r="D624" s="7" t="inlineStr">
         <is>
-          <t>0:59:17</t>
+          <t>0:59:58</t>
         </is>
       </c>
       <c r="E624" s="7" t="inlineStr">
@@ -16090,7 +16090,7 @@
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
         <is>
-          <t>Aramco Houston Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B625" s="5" t="inlineStr">
@@ -16099,23 +16099,23 @@
         </is>
       </c>
       <c r="C625" s="5" t="n">
-        <v>2026</v>
+        <v>2003</v>
       </c>
       <c r="D625" s="5" t="inlineStr">
         <is>
-          <t>0:59:01</t>
+          <t>1:00:01</t>
         </is>
       </c>
       <c r="E625" s="5" t="inlineStr">
         <is>
-          <t>1:04:49</t>
+          <t>1:05:40</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="6" t="inlineStr">
         <is>
-          <t>Asics Run Melbourne</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B626" s="7" t="inlineStr">
@@ -16124,11 +16124,11 @@
         </is>
       </c>
       <c r="C626" s="7" t="n">
-        <v>2025</v>
+        <v>2004</v>
       </c>
       <c r="D626" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:37</t>
         </is>
       </c>
       <c r="E626" s="7" t="inlineStr">
@@ -16140,7 +16140,7 @@
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen21</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B627" s="5" t="inlineStr">
@@ -16149,11 +16149,11 @@
         </is>
       </c>
       <c r="C627" s="5" t="n">
-        <v>2023</v>
+        <v>2005</v>
       </c>
       <c r="D627" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:05</t>
         </is>
       </c>
       <c r="E627" s="5" t="inlineStr">
@@ -16165,7 +16165,7 @@
     <row r="628">
       <c r="A628" s="6" t="inlineStr">
         <is>
-          <t>Bangsaen21</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B628" s="7" t="inlineStr">
@@ -16174,11 +16174,11 @@
         </is>
       </c>
       <c r="C628" s="7" t="n">
-        <v>2024</v>
+        <v>2006</v>
       </c>
       <c r="D628" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:04</t>
         </is>
       </c>
       <c r="E628" s="7" t="inlineStr">
@@ -16190,7 +16190,7 @@
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen21</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B629" s="5" t="inlineStr">
@@ -16199,23 +16199,23 @@
         </is>
       </c>
       <c r="C629" s="5" t="n">
-        <v>2025</v>
+        <v>2007</v>
       </c>
       <c r="D629" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:08</t>
         </is>
       </c>
       <c r="E629" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:57</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="6" t="inlineStr">
         <is>
-          <t>Brølløbet - The Bridge Run</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B630" s="7" t="inlineStr">
@@ -16224,11 +16224,11 @@
         </is>
       </c>
       <c r="C630" s="7" t="n">
-        <v>2025</v>
+        <v>2008</v>
       </c>
       <c r="D630" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:45</t>
         </is>
       </c>
       <c r="E630" s="7" t="inlineStr">
@@ -16240,7 +16240,7 @@
     <row r="631">
       <c r="A631" s="4" t="inlineStr">
         <is>
-          <t>Burj2Burj Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B631" s="5" t="inlineStr">
@@ -16249,11 +16249,11 @@
         </is>
       </c>
       <c r="C631" s="5" t="n">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="D631" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:32</t>
         </is>
       </c>
       <c r="E631" s="5" t="inlineStr">
@@ -16265,7 +16265,7 @@
     <row r="632">
       <c r="A632" s="6" t="inlineStr">
         <is>
-          <t>Burj2Burj Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B632" s="7" t="inlineStr">
@@ -16274,11 +16274,11 @@
         </is>
       </c>
       <c r="C632" s="7" t="n">
-        <v>2025</v>
+        <v>2010</v>
       </c>
       <c r="D632" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:33</t>
         </is>
       </c>
       <c r="E632" s="7" t="inlineStr">
@@ -16290,7 +16290,7 @@
     <row r="633">
       <c r="A633" s="4" t="inlineStr">
         <is>
-          <t>Burj2Burj Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B633" s="5" t="inlineStr">
@@ -16299,23 +16299,23 @@
         </is>
       </c>
       <c r="C633" s="5" t="n">
-        <v>2026</v>
+        <v>2011</v>
       </c>
       <c r="D633" s="5" t="inlineStr">
         <is>
-          <t>0:59:26</t>
+          <t>0:58:56</t>
         </is>
       </c>
       <c r="E633" s="5" t="inlineStr">
         <is>
-          <t>1:06:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" s="6" t="inlineStr">
         <is>
-          <t>Cardiff Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B634" s="7" t="inlineStr">
@@ -16324,11 +16324,11 @@
         </is>
       </c>
       <c r="C634" s="7" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="D634" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:06</t>
         </is>
       </c>
       <c r="E634" s="7" t="inlineStr">
@@ -16340,7 +16340,7 @@
     <row r="635">
       <c r="A635" s="4" t="inlineStr">
         <is>
-          <t>Coelmo Napoli City Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B635" s="5" t="inlineStr">
@@ -16349,23 +16349,23 @@
         </is>
       </c>
       <c r="C635" s="5" t="n">
-        <v>2025</v>
+        <v>2013</v>
       </c>
       <c r="D635" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:09</t>
         </is>
       </c>
       <c r="E635" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:29</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" s="6" t="inlineStr">
         <is>
-          <t>Coelmo Napoli City Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B636" s="7" t="inlineStr">
@@ -16374,23 +16374,23 @@
         </is>
       </c>
       <c r="C636" s="7" t="n">
-        <v>2026</v>
+        <v>2014</v>
       </c>
       <c r="D636" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:00</t>
         </is>
       </c>
       <c r="E636" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:39</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B637" s="5" t="inlineStr">
@@ -16399,23 +16399,23 @@
         </is>
       </c>
       <c r="C637" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D637" s="5" t="inlineStr">
         <is>
-          <t>0:59:11</t>
+          <t>1:00:52</t>
         </is>
       </c>
       <c r="E637" s="5" t="inlineStr">
         <is>
-          <t>1:05:53</t>
+          <t>1:09:32</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" s="6" t="inlineStr">
         <is>
-          <t>Copenhagen Half Marathon</t>
+          <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
       <c r="B638" s="7" t="inlineStr">
@@ -16428,19 +16428,19 @@
       </c>
       <c r="D638" s="7" t="inlineStr">
         <is>
-          <t>0:58:05</t>
+          <t>1:00:42</t>
         </is>
       </c>
       <c r="E638" s="7" t="inlineStr">
         <is>
-          <t>1:05:11</t>
+          <t>1:04:37</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen Half Marathon</t>
+          <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
       <c r="B639" s="5" t="inlineStr">
@@ -16453,19 +16453,19 @@
       </c>
       <c r="D639" s="5" t="inlineStr">
         <is>
-          <t>0:58:23</t>
+          <t>0:59:17</t>
         </is>
       </c>
       <c r="E639" s="5" t="inlineStr">
         <is>
-          <t>1:04:44</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" s="6" t="inlineStr">
         <is>
-          <t>Disney Princess Half Marathon</t>
+          <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
       <c r="B640" s="7" t="inlineStr">
@@ -16474,23 +16474,23 @@
         </is>
       </c>
       <c r="C640" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D640" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:01</t>
         </is>
       </c>
       <c r="E640" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:49</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" s="4" t="inlineStr">
         <is>
-          <t>Disney Princess Half Marathon</t>
+          <t>Asics Run Melbourne</t>
         </is>
       </c>
       <c r="B641" s="5" t="inlineStr">
@@ -16499,7 +16499,7 @@
         </is>
       </c>
       <c r="C641" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D641" s="5" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
     <row r="642">
       <c r="A642" s="6" t="inlineStr">
         <is>
-          <t>EDP Lisboa Meia Maratona</t>
+          <t>Bangsaen21</t>
         </is>
       </c>
       <c r="B642" s="7" t="inlineStr">
@@ -16524,7 +16524,7 @@
         </is>
       </c>
       <c r="C642" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D642" s="7" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
     <row r="643">
       <c r="A643" s="4" t="inlineStr">
         <is>
-          <t>EDP Lisboa Meia Maratona</t>
+          <t>Bangsaen21</t>
         </is>
       </c>
       <c r="B643" s="5" t="inlineStr">
@@ -16549,7 +16549,7 @@
         </is>
       </c>
       <c r="C643" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D643" s="5" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
     <row r="644">
       <c r="A644" s="6" t="inlineStr">
         <is>
-          <t>EDP Lisboa Meia Maratona</t>
+          <t>Bangsaen21</t>
         </is>
       </c>
       <c r="B644" s="7" t="inlineStr">
@@ -16574,7 +16574,7 @@
         </is>
       </c>
       <c r="C644" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D644" s="7" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
     <row r="645">
       <c r="A645" s="4" t="inlineStr">
         <is>
-          <t>Eurospin RomaOstia Half Marathon</t>
+          <t>Brølløbet - The Bridge Run</t>
         </is>
       </c>
       <c r="B645" s="5" t="inlineStr">
@@ -16599,23 +16599,23 @@
         </is>
       </c>
       <c r="C645" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D645" s="5" t="inlineStr">
         <is>
-          <t>0:59:17</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E645" s="5" t="inlineStr">
         <is>
-          <t>1:06:21</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" s="6" t="inlineStr">
         <is>
-          <t>Eurospin RomaOstia Half Marathon</t>
+          <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
       <c r="B646" s="7" t="inlineStr">
@@ -16628,19 +16628,19 @@
       </c>
       <c r="D646" s="7" t="inlineStr">
         <is>
-          <t>1:01:10</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E646" s="7" t="inlineStr">
         <is>
-          <t>1:07:38</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" s="4" t="inlineStr">
         <is>
-          <t>Eurospin RomaOstia Half Marathon</t>
+          <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
       <c r="B647" s="5" t="inlineStr">
@@ -16653,19 +16653,19 @@
       </c>
       <c r="D647" s="5" t="inlineStr">
         <is>
-          <t>0:58:49</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E647" s="5" t="inlineStr">
         <is>
-          <t>1:08:20</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" s="6" t="inlineStr">
         <is>
-          <t>Eurospin RomaOstia Half Marathon</t>
+          <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
       <c r="B648" s="7" t="inlineStr">
@@ -16678,19 +16678,19 @@
       </c>
       <c r="D648" s="7" t="inlineStr">
         <is>
-          <t>0:58:00</t>
+          <t>0:59:26</t>
         </is>
       </c>
       <c r="E648" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:57</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" s="4" t="inlineStr">
         <is>
-          <t>Generali Berlin Half Marathon</t>
+          <t>Cardiff Half Marathon</t>
         </is>
       </c>
       <c r="B649" s="5" t="inlineStr">
@@ -16699,23 +16699,23 @@
         </is>
       </c>
       <c r="C649" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D649" s="5" t="inlineStr">
         <is>
-          <t>0:59:01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E649" s="5" t="inlineStr">
         <is>
-          <t>1:05:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" s="6" t="inlineStr">
         <is>
-          <t>Generali Berlin Half Marathon</t>
+          <t>Coelmo Napoli City Half Marathon</t>
         </is>
       </c>
       <c r="B650" s="7" t="inlineStr">
@@ -16724,23 +16724,23 @@
         </is>
       </c>
       <c r="C650" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D650" s="7" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E650" s="7" t="inlineStr">
         <is>
-          <t>1:06:53</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" s="4" t="inlineStr">
         <is>
-          <t>Generali Berlin Half Marathon</t>
+          <t>Coelmo Napoli City Half Marathon</t>
         </is>
       </c>
       <c r="B651" s="5" t="inlineStr">
@@ -16749,23 +16749,23 @@
         </is>
       </c>
       <c r="C651" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D651" s="5" t="inlineStr">
         <is>
-          <t>0:58:43</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E651" s="5" t="inlineStr">
         <is>
-          <t>1:03:35</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" s="6" t="inlineStr">
         <is>
-          <t>Generali Prague Half Marathon</t>
+          <t>Copenhagen Half Marathon</t>
         </is>
       </c>
       <c r="B652" s="7" t="inlineStr">
@@ -16778,19 +16778,19 @@
       </c>
       <c r="D652" s="7" t="inlineStr">
         <is>
-          <t>0:59:43</t>
+          <t>0:59:11</t>
         </is>
       </c>
       <c r="E652" s="7" t="inlineStr">
         <is>
-          <t>1:06:00</t>
+          <t>1:05:53</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="4" t="inlineStr">
         <is>
-          <t>Generali Prague Half Marathon</t>
+          <t>Copenhagen Half Marathon</t>
         </is>
       </c>
       <c r="B653" s="5" t="inlineStr">
@@ -16803,19 +16803,19 @@
       </c>
       <c r="D653" s="5" t="inlineStr">
         <is>
-          <t>0:58:24</t>
+          <t>0:58:05</t>
         </is>
       </c>
       <c r="E653" s="5" t="inlineStr">
         <is>
-          <t>1:08:10</t>
+          <t>1:05:11</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" s="6" t="inlineStr">
         <is>
-          <t>Generali Prague Half Marathon</t>
+          <t>Copenhagen Half Marathon</t>
         </is>
       </c>
       <c r="B654" s="7" t="inlineStr">
@@ -16828,19 +16828,19 @@
       </c>
       <c r="D654" s="7" t="inlineStr">
         <is>
-          <t>0:58:54</t>
+          <t>0:58:23</t>
         </is>
       </c>
       <c r="E654" s="7" t="inlineStr">
         <is>
-          <t>1:05:27</t>
+          <t>1:04:44</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" s="4" t="inlineStr">
         <is>
-          <t>GetPro Bath Half</t>
+          <t>Disney Princess Half Marathon</t>
         </is>
       </c>
       <c r="B655" s="5" t="inlineStr">
@@ -16865,7 +16865,7 @@
     <row r="656">
       <c r="A656" s="6" t="inlineStr">
         <is>
-          <t>GetPro Bath Half</t>
+          <t>Disney Princess Half Marathon</t>
         </is>
       </c>
       <c r="B656" s="7" t="inlineStr">
@@ -16890,7 +16890,7 @@
     <row r="657">
       <c r="A657" s="4" t="inlineStr">
         <is>
-          <t>Göteborgsvarvet</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B657" s="5" t="inlineStr">
@@ -16899,11 +16899,11 @@
         </is>
       </c>
       <c r="C657" s="5" t="n">
-        <v>2024</v>
+        <v>2000</v>
       </c>
       <c r="D657" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:06</t>
         </is>
       </c>
       <c r="E657" s="5" t="inlineStr">
@@ -16915,7 +16915,7 @@
     <row r="658">
       <c r="A658" s="6" t="inlineStr">
         <is>
-          <t>Göteborgsvarvet</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B658" s="7" t="inlineStr">
@@ -16924,23 +16924,23 @@
         </is>
       </c>
       <c r="C658" s="7" t="n">
-        <v>2025</v>
+        <v>2001</v>
       </c>
       <c r="D658" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:26</t>
         </is>
       </c>
       <c r="E658" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:44</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="4" t="inlineStr">
         <is>
-          <t>HOKA Semi de Paris</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B659" s="5" t="inlineStr">
@@ -16949,23 +16949,23 @@
         </is>
       </c>
       <c r="C659" s="5" t="n">
-        <v>2023</v>
+        <v>2003</v>
       </c>
       <c r="D659" s="5" t="inlineStr">
         <is>
-          <t>0:59:38</t>
+          <t>1:00:10</t>
         </is>
       </c>
       <c r="E659" s="5" t="inlineStr">
         <is>
-          <t>1:06:01</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" s="6" t="inlineStr">
         <is>
-          <t>HOKA Semi de Paris</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B660" s="7" t="inlineStr">
@@ -16974,23 +16974,23 @@
         </is>
       </c>
       <c r="C660" s="7" t="n">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="D660" s="7" t="inlineStr">
         <is>
-          <t>1:00:45</t>
+          <t>0:58:23</t>
         </is>
       </c>
       <c r="E660" s="7" t="inlineStr">
         <is>
-          <t>1:06:58</t>
+          <t>1:08:38</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="4" t="inlineStr">
         <is>
-          <t>HOKA Semi de Paris</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B661" s="5" t="inlineStr">
@@ -16999,23 +16999,23 @@
         </is>
       </c>
       <c r="C661" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D661" s="5" t="inlineStr">
         <is>
-          <t>1:00:16</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E661" s="5" t="inlineStr">
         <is>
-          <t>1:07:14</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" s="6" t="inlineStr">
         <is>
-          <t>HOKA Semi de Paris</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B662" s="7" t="inlineStr">
@@ -17024,23 +17024,23 @@
         </is>
       </c>
       <c r="C662" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D662" s="7" t="inlineStr">
         <is>
-          <t>1:00:11</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E662" s="7" t="inlineStr">
         <is>
-          <t>1:05:12</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" s="4" t="inlineStr">
         <is>
-          <t>Half Marathon Munchen by Brooks</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B663" s="5" t="inlineStr">
@@ -17049,7 +17049,7 @@
         </is>
       </c>
       <c r="C663" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D663" s="5" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
     <row r="664">
       <c r="A664" s="6" t="inlineStr">
         <is>
-          <t>Hoka Runaway Sydney Half Marathon</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B664" s="7" t="inlineStr">
@@ -17074,7 +17074,7 @@
         </is>
       </c>
       <c r="C664" s="7" t="n">
-        <v>2025</v>
+        <v>2004</v>
       </c>
       <c r="D664" s="7" t="inlineStr">
         <is>
@@ -17083,14 +17083,14 @@
       </c>
       <c r="E664" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:39</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" s="4" t="inlineStr">
         <is>
-          <t>Hyundai Meia Maratona</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B665" s="5" t="inlineStr">
@@ -17099,23 +17099,23 @@
         </is>
       </c>
       <c r="C665" s="5" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="D665" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:32</t>
         </is>
       </c>
       <c r="E665" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:38</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" s="6" t="inlineStr">
         <is>
-          <t>Hyundai Meia Maratona</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B666" s="7" t="inlineStr">
@@ -17124,23 +17124,23 @@
         </is>
       </c>
       <c r="C666" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D666" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:17</t>
         </is>
       </c>
       <c r="E666" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:21</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" s="4" t="inlineStr">
         <is>
-          <t>Hyundai Meia Maratona</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B667" s="5" t="inlineStr">
@@ -17149,23 +17149,23 @@
         </is>
       </c>
       <c r="C667" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D667" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:10</t>
         </is>
       </c>
       <c r="E667" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:38</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" s="6" t="inlineStr">
         <is>
-          <t>IU Health 500 Festival Mini-Marathon</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B668" s="7" t="inlineStr">
@@ -17178,19 +17178,19 @@
       </c>
       <c r="D668" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:49</t>
         </is>
       </c>
       <c r="E668" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:20</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" s="4" t="inlineStr">
         <is>
-          <t>Kagawa Marugame International Half Marathon</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B669" s="5" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="D669" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:00</t>
         </is>
       </c>
       <c r="E669" s="5" t="inlineStr">
@@ -17215,7 +17215,7 @@
     <row r="670">
       <c r="A670" s="6" t="inlineStr">
         <is>
-          <t>Life Time Chicago Half Marathon &amp; 5K</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B670" s="7" t="inlineStr">
@@ -17224,7 +17224,7 @@
         </is>
       </c>
       <c r="C670" s="7" t="n">
-        <v>2024</v>
+        <v>2006</v>
       </c>
       <c r="D670" s="7" t="inlineStr">
         <is>
@@ -17233,14 +17233,14 @@
       </c>
       <c r="E670" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:16</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" s="4" t="inlineStr">
         <is>
-          <t>Life Time Chicago Half Marathon &amp; 5K</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B671" s="5" t="inlineStr">
@@ -17249,11 +17249,11 @@
         </is>
       </c>
       <c r="C671" s="5" t="n">
-        <v>2025</v>
+        <v>2007</v>
       </c>
       <c r="D671" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:56</t>
         </is>
       </c>
       <c r="E671" s="5" t="inlineStr">
@@ -17265,7 +17265,7 @@
     <row r="672">
       <c r="A672" s="6" t="inlineStr">
         <is>
-          <t>London Landmarks Half Marathon</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B672" s="7" t="inlineStr">
@@ -17274,23 +17274,23 @@
         </is>
       </c>
       <c r="C672" s="7" t="n">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="D672" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:16</t>
         </is>
       </c>
       <c r="E672" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:09:43</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" s="4" t="inlineStr">
         <is>
-          <t>London Landmarks Half Marathon</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B673" s="5" t="inlineStr">
@@ -17299,11 +17299,11 @@
         </is>
       </c>
       <c r="C673" s="5" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="D673" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:14</t>
         </is>
       </c>
       <c r="E673" s="5" t="inlineStr">
@@ -17315,7 +17315,7 @@
     <row r="674">
       <c r="A674" s="6" t="inlineStr">
         <is>
-          <t>Manchester Half Marathon</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B674" s="7" t="inlineStr">
@@ -17324,23 +17324,23 @@
         </is>
       </c>
       <c r="C674" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D674" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:01</t>
         </is>
       </c>
       <c r="E674" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:43</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" s="4" t="inlineStr">
         <is>
-          <t>Media Maraton de Bogota</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B675" s="5" t="inlineStr">
@@ -17349,23 +17349,23 @@
         </is>
       </c>
       <c r="C675" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D675" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E675" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:53</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" s="6" t="inlineStr">
         <is>
-          <t>Medio Maraton de Sevilla</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B676" s="7" t="inlineStr">
@@ -17374,23 +17374,23 @@
         </is>
       </c>
       <c r="C676" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D676" s="7" t="inlineStr">
         <is>
-          <t>0:59:21</t>
+          <t>0:58:43</t>
         </is>
       </c>
       <c r="E676" s="7" t="inlineStr">
         <is>
-          <t>1:07:59</t>
+          <t>1:03:35</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" s="4" t="inlineStr">
         <is>
-          <t>Medio Maraton de Sevilla</t>
+          <t>Generali Prague Half Marathon</t>
         </is>
       </c>
       <c r="B677" s="5" t="inlineStr">
@@ -17399,23 +17399,23 @@
         </is>
       </c>
       <c r="C677" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D677" s="5" t="inlineStr">
         <is>
-          <t>0:59:33</t>
+          <t>0:59:43</t>
         </is>
       </c>
       <c r="E677" s="5" t="inlineStr">
         <is>
-          <t>1:07:18</t>
+          <t>1:06:00</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" s="6" t="inlineStr">
         <is>
-          <t>Medio Maraton de Sevilla</t>
+          <t>Generali Prague Half Marathon</t>
         </is>
       </c>
       <c r="B678" s="7" t="inlineStr">
@@ -17424,23 +17424,23 @@
         </is>
       </c>
       <c r="C678" s="7" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D678" s="7" t="inlineStr">
         <is>
-          <t>1:00:24</t>
+          <t>0:58:24</t>
         </is>
       </c>
       <c r="E678" s="7" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>1:08:10</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" s="4" t="inlineStr">
         <is>
-          <t>Mitja Marato Barcelona by Brooks</t>
+          <t>Generali Prague Half Marathon</t>
         </is>
       </c>
       <c r="B679" s="5" t="inlineStr">
@@ -17449,23 +17449,23 @@
         </is>
       </c>
       <c r="C679" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D679" s="5" t="inlineStr">
         <is>
-          <t>0:58:53</t>
+          <t>0:58:54</t>
         </is>
       </c>
       <c r="E679" s="5" t="inlineStr">
         <is>
-          <t>1:04:37</t>
+          <t>1:05:27</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" s="6" t="inlineStr">
         <is>
-          <t>Mitja Marato Barcelona by Brooks</t>
+          <t>GetPro Bath Half</t>
         </is>
       </c>
       <c r="B680" s="7" t="inlineStr">
@@ -17474,23 +17474,23 @@
         </is>
       </c>
       <c r="C680" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D680" s="7" t="inlineStr">
         <is>
-          <t>0:59:21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E680" s="7" t="inlineStr">
         <is>
-          <t>1:04:28</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" s="4" t="inlineStr">
         <is>
-          <t>Mitja Marato Barcelona by Brooks</t>
+          <t>GetPro Bath Half</t>
         </is>
       </c>
       <c r="B681" s="5" t="inlineStr">
@@ -17499,23 +17499,23 @@
         </is>
       </c>
       <c r="C681" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D681" s="5" t="inlineStr">
         <is>
-          <t>0:56:42</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E681" s="5" t="inlineStr">
         <is>
-          <t>1:04:11</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" s="6" t="inlineStr">
         <is>
-          <t>Mitja Marato Barcelona by Brooks</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B682" s="7" t="inlineStr">
@@ -17524,23 +17524,23 @@
         </is>
       </c>
       <c r="C682" s="7" t="n">
-        <v>2026</v>
+        <v>2000</v>
       </c>
       <c r="D682" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:02:42</t>
         </is>
       </c>
       <c r="E682" s="7" t="inlineStr">
         <is>
-          <t>1:04:00</t>
+          <t>1:09:28</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" s="4" t="inlineStr">
         <is>
-          <t>Movistar Madrid Medio Maraton</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B683" s="5" t="inlineStr">
@@ -17549,23 +17549,23 @@
         </is>
       </c>
       <c r="C683" s="5" t="n">
-        <v>2025</v>
+        <v>2001</v>
       </c>
       <c r="D683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:00</t>
         </is>
       </c>
       <c r="E683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:11:07</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" s="6" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - Half Marathon</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B684" s="7" t="inlineStr">
@@ -17574,23 +17574,23 @@
         </is>
       </c>
       <c r="C684" s="7" t="n">
-        <v>2025</v>
+        <v>2002</v>
       </c>
       <c r="D684" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:35</t>
         </is>
       </c>
       <c r="E684" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:13:03</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" s="4" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - Half Marathon</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B685" s="5" t="inlineStr">
@@ -17599,23 +17599,23 @@
         </is>
       </c>
       <c r="C685" s="5" t="n">
-        <v>2026</v>
+        <v>2003</v>
       </c>
       <c r="D685" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:43</t>
         </is>
       </c>
       <c r="E685" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:13:27</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" s="6" t="inlineStr">
         <is>
-          <t>NYCRUNS Brooklyn Experience Half Marathon</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B686" s="7" t="inlineStr">
@@ -17624,23 +17624,23 @@
         </is>
       </c>
       <c r="C686" s="7" t="n">
-        <v>2025</v>
+        <v>2004</v>
       </c>
       <c r="D686" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:03</t>
         </is>
       </c>
       <c r="E686" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:18:06</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" s="4" t="inlineStr">
         <is>
-          <t>NYRR RBC Brooklyn Half</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B687" s="5" t="inlineStr">
@@ -17649,23 +17649,23 @@
         </is>
       </c>
       <c r="C687" s="5" t="n">
-        <v>2025</v>
+        <v>2005</v>
       </c>
       <c r="D687" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:19</t>
         </is>
       </c>
       <c r="E687" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:12:34</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" s="6" t="inlineStr">
         <is>
-          <t>Nike Melbourne Marathon Festival</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B688" s="7" t="inlineStr">
@@ -17674,23 +17674,23 @@
         </is>
       </c>
       <c r="C688" s="7" t="n">
-        <v>2025</v>
+        <v>2006</v>
       </c>
       <c r="D688" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:02:14</t>
         </is>
       </c>
       <c r="E688" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:12:34</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" s="4" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B689" s="5" t="inlineStr">
@@ -17699,23 +17699,23 @@
         </is>
       </c>
       <c r="C689" s="5" t="n">
-        <v>2023</v>
+        <v>2007</v>
       </c>
       <c r="D689" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:03</t>
         </is>
       </c>
       <c r="E689" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:12:38</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" s="6" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B690" s="7" t="inlineStr">
@@ -17724,23 +17724,23 @@
         </is>
       </c>
       <c r="C690" s="7" t="n">
-        <v>2024</v>
+        <v>2008</v>
       </c>
       <c r="D690" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:21</t>
         </is>
       </c>
       <c r="E690" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:19</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" s="4" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B691" s="5" t="inlineStr">
@@ -17749,23 +17749,23 @@
         </is>
       </c>
       <c r="C691" s="5" t="n">
-        <v>2025</v>
+        <v>2009</v>
       </c>
       <c r="D691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:55</t>
         </is>
       </c>
       <c r="E691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:11:27</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" s="6" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B692" s="7" t="inlineStr">
@@ -17774,23 +17774,23 @@
         </is>
       </c>
       <c r="C692" s="7" t="n">
-        <v>2026</v>
+        <v>2010</v>
       </c>
       <c r="D692" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:10</t>
         </is>
       </c>
       <c r="E692" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:11:40</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B693" s="5" t="inlineStr">
@@ -17799,23 +17799,23 @@
         </is>
       </c>
       <c r="C693" s="5" t="n">
-        <v>2023</v>
+        <v>2011</v>
       </c>
       <c r="D693" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:52</t>
         </is>
       </c>
       <c r="E693" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:09:04</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B694" s="7" t="inlineStr">
@@ -17824,23 +17824,23 @@
         </is>
       </c>
       <c r="C694" s="7" t="n">
-        <v>2024</v>
+        <v>2012</v>
       </c>
       <c r="D694" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:25</t>
         </is>
       </c>
       <c r="E694" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:09:27</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B695" s="5" t="inlineStr">
@@ -17849,23 +17849,23 @@
         </is>
       </c>
       <c r="C695" s="5" t="n">
-        <v>2025</v>
+        <v>2013</v>
       </c>
       <c r="D695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:13</t>
         </is>
       </c>
       <c r="E695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:11:29</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B696" s="7" t="inlineStr">
@@ -17874,23 +17874,23 @@
         </is>
       </c>
       <c r="C696" s="7" t="n">
-        <v>2026</v>
+        <v>2014</v>
       </c>
       <c r="D696" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:36</t>
         </is>
       </c>
       <c r="E696" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:12</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Mexico City</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B697" s="5" t="inlineStr">
@@ -17899,7 +17899,7 @@
         </is>
       </c>
       <c r="C697" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D697" s="5" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
     <row r="698">
       <c r="A698" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series San Diego</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B698" s="7" t="inlineStr">
@@ -17940,7 +17940,7 @@
     <row r="699">
       <c r="A699" s="4" t="inlineStr">
         <is>
-          <t>Royal Parks Half Marathon</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B699" s="5" t="inlineStr">
@@ -17949,23 +17949,23 @@
         </is>
       </c>
       <c r="C699" s="5" t="n">
-        <v>2025</v>
+        <v>2002</v>
       </c>
       <c r="D699" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:33</t>
         </is>
       </c>
       <c r="E699" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:11:07</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" s="6" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B700" s="7" t="inlineStr">
@@ -17974,23 +17974,23 @@
         </is>
       </c>
       <c r="C700" s="7" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="D700" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:44</t>
         </is>
       </c>
       <c r="E700" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:55</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B701" s="5" t="inlineStr">
@@ -17999,23 +17999,23 @@
         </is>
       </c>
       <c r="C701" s="5" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="D701" s="5" t="inlineStr">
         <is>
-          <t>1:05:44</t>
+          <t>1:00:08</t>
         </is>
       </c>
       <c r="E701" s="5" t="inlineStr">
         <is>
-          <t>1:18:34</t>
+          <t>1:09:23</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" s="6" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B702" s="7" t="inlineStr">
@@ -18024,23 +18024,23 @@
         </is>
       </c>
       <c r="C702" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D702" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:38</t>
         </is>
       </c>
       <c r="E702" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:01</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="A703" s="4" t="inlineStr">
         <is>
-          <t>Semi-Marathon de Boulogne-Billancourt</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B703" s="5" t="inlineStr">
@@ -18049,23 +18049,23 @@
         </is>
       </c>
       <c r="C703" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D703" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:45</t>
         </is>
       </c>
       <c r="E703" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:58</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" s="6" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B704" s="7" t="inlineStr">
@@ -18078,19 +18078,19 @@
       </c>
       <c r="D704" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:16</t>
         </is>
       </c>
       <c r="E704" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:14</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="A705" s="4" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Series Nashville</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B705" s="5" t="inlineStr">
@@ -18099,23 +18099,23 @@
         </is>
       </c>
       <c r="C705" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D705" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:11</t>
         </is>
       </c>
       <c r="E705" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:12</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="A706" s="6" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>Half Marathon Munchen by Brooks</t>
         </is>
       </c>
       <c r="B706" s="7" t="inlineStr">
@@ -18124,23 +18124,23 @@
         </is>
       </c>
       <c r="C706" s="7" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D706" s="7" t="inlineStr">
         <is>
-          <t>1:01:13</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E706" s="7" t="inlineStr">
         <is>
-          <t>1:09:28</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>Hoka Runaway Sydney Half Marathon</t>
         </is>
       </c>
       <c r="B707" s="5" t="inlineStr">
@@ -18165,7 +18165,7 @@
     <row r="708">
       <c r="A708" s="6" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="B708" s="7" t="inlineStr">
@@ -18174,7 +18174,7 @@
         </is>
       </c>
       <c r="C708" s="7" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D708" s="7" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
     <row r="709">
       <c r="A709" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered KL Half Marathon</t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="B709" s="5" t="inlineStr">
@@ -18199,23 +18199,23 @@
         </is>
       </c>
       <c r="C709" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D709" s="5" t="inlineStr">
         <is>
-          <t>1:11:08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E709" s="5" t="inlineStr">
         <is>
-          <t>1:23:55</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" s="6" t="inlineStr">
         <is>
-          <t>Standard Chartered Singapore Half Marathon</t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="B710" s="7" t="inlineStr">
@@ -18240,7 +18240,7 @@
     <row r="711">
       <c r="A711" s="4" t="inlineStr">
         <is>
-          <t>TCS Mizuno Half Marathon</t>
+          <t>IU Health 500 Festival Mini-Marathon</t>
         </is>
       </c>
       <c r="B711" s="5" t="inlineStr">
@@ -18265,7 +18265,7 @@
     <row r="712">
       <c r="A712" s="6" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>Kagawa Marugame International Half Marathon</t>
         </is>
       </c>
       <c r="B712" s="7" t="inlineStr">
@@ -18274,7 +18274,7 @@
         </is>
       </c>
       <c r="C712" s="7" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D712" s="7" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
     <row r="713">
       <c r="A713" s="4" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
       <c r="B713" s="5" t="inlineStr">
@@ -18315,7 +18315,7 @@
     <row r="714">
       <c r="A714" s="6" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
       <c r="B714" s="7" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="715">
       <c r="A715" s="4" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>London Landmarks Half Marathon</t>
         </is>
       </c>
       <c r="B715" s="5" t="inlineStr">
@@ -18349,7 +18349,7 @@
         </is>
       </c>
       <c r="C715" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D715" s="5" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
     <row r="716">
       <c r="A716" s="6" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>London Landmarks Half Marathon</t>
         </is>
       </c>
       <c r="B716" s="7" t="inlineStr">
@@ -18374,7 +18374,7 @@
         </is>
       </c>
       <c r="C716" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D716" s="7" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
     <row r="717">
       <c r="A717" s="4" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>Manchester Half Marathon</t>
         </is>
       </c>
       <c r="B717" s="5" t="inlineStr">
@@ -18415,7 +18415,7 @@
     <row r="718">
       <c r="A718" s="6" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon (Half)</t>
+          <t>Media Maraton de Bogota</t>
         </is>
       </c>
       <c r="B718" s="7" t="inlineStr">
@@ -18440,7 +18440,7 @@
     <row r="719">
       <c r="A719" s="4" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon (Half)</t>
+          <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
       <c r="B719" s="5" t="inlineStr">
@@ -18449,23 +18449,23 @@
         </is>
       </c>
       <c r="C719" s="5" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D719" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E719" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:59</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" s="6" t="inlineStr">
         <is>
-          <t>The Big Half</t>
+          <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
       <c r="B720" s="7" t="inlineStr">
@@ -18478,19 +18478,19 @@
       </c>
       <c r="D720" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:33</t>
         </is>
       </c>
       <c r="E720" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:18</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Legacy Half Marathon</t>
+          <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
       <c r="B721" s="5" t="inlineStr">
@@ -18499,23 +18499,23 @@
         </is>
       </c>
       <c r="C721" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D721" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:24</t>
         </is>
       </c>
       <c r="E721" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" s="6" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B722" s="7" t="inlineStr">
@@ -18524,23 +18524,23 @@
         </is>
       </c>
       <c r="C722" s="7" t="n">
-        <v>2025</v>
+        <v>2005</v>
       </c>
       <c r="D722" s="7" t="inlineStr">
         <is>
-          <t>1:01:31</t>
+          <t>1:03:29</t>
         </is>
       </c>
       <c r="E722" s="7" t="inlineStr">
         <is>
-          <t>1:07:04</t>
+          <t>1:09:34</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" s="4" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B723" s="5" t="inlineStr">
@@ -18549,23 +18549,23 @@
         </is>
       </c>
       <c r="C723" s="5" t="n">
-        <v>2026</v>
+        <v>2006</v>
       </c>
       <c r="D723" s="5" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>1:02:25</t>
         </is>
       </c>
       <c r="E723" s="5" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>1:09:26</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" s="6" t="inlineStr">
         <is>
-          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B724" s="7" t="inlineStr">
@@ -18574,23 +18574,23 @@
         </is>
       </c>
       <c r="C724" s="7" t="n">
-        <v>2025</v>
+        <v>2007</v>
       </c>
       <c r="D724" s="7" t="inlineStr">
         <is>
-          <t>0:58:02</t>
+          <t>1:03:02</t>
         </is>
       </c>
       <c r="E724" s="7" t="inlineStr">
         <is>
-          <t>1:03:08</t>
+          <t>1:09:05</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" s="4" t="inlineStr">
         <is>
-          <t>Vedanta Delhi Half Marathon</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B725" s="5" t="inlineStr">
@@ -18599,23 +18599,23 @@
         </is>
       </c>
       <c r="C725" s="5" t="n">
-        <v>2025</v>
+        <v>2008</v>
       </c>
       <c r="D725" s="5" t="inlineStr">
         <is>
-          <t>0:59:50</t>
+          <t>1:02:39</t>
         </is>
       </c>
       <c r="E725" s="5" t="inlineStr">
         <is>
-          <t>1:07:20</t>
+          <t>1:09:15</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" s="6" t="inlineStr">
         <is>
-          <t>Vienna City Half Marathon</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B726" s="7" t="inlineStr">
@@ -18624,23 +18624,23 @@
         </is>
       </c>
       <c r="C726" s="7" t="n">
-        <v>2025</v>
+        <v>2009</v>
       </c>
       <c r="D726" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:45</t>
         </is>
       </c>
       <c r="E726" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:09:34</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" s="4" t="inlineStr">
         <is>
-          <t>Walt Disney World Marathon Weekend</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B727" s="5" t="inlineStr">
@@ -18649,23 +18649,23 @@
         </is>
       </c>
       <c r="C727" s="5" t="n">
-        <v>2025</v>
+        <v>2010</v>
       </c>
       <c r="D727" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:00</t>
         </is>
       </c>
       <c r="E727" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:52</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" s="6" t="inlineStr">
         <is>
-          <t>Walt Disney World Marathon Weekend</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B728" s="7" t="inlineStr">
@@ -18674,23 +18674,23 @@
         </is>
       </c>
       <c r="C728" s="7" t="n">
-        <v>2026</v>
+        <v>2011</v>
       </c>
       <c r="D728" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:06</t>
         </is>
       </c>
       <c r="E728" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:13</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" s="4" t="inlineStr">
         <is>
-          <t>Warsaw Half Marathon</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B729" s="5" t="inlineStr">
@@ -18699,23 +18699,23 @@
         </is>
       </c>
       <c r="C729" s="5" t="n">
-        <v>2024</v>
+        <v>2012</v>
       </c>
       <c r="D729" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:02:54</t>
         </is>
       </c>
       <c r="E729" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:51</t>
         </is>
       </c>
     </row>
     <row r="730">
       <c r="A730" s="6" t="inlineStr">
         <is>
-          <t>Warsaw Half Marathon</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B730" s="7" t="inlineStr">
@@ -18724,23 +18724,23 @@
         </is>
       </c>
       <c r="C730" s="7" t="n">
-        <v>2025</v>
+        <v>2013</v>
       </c>
       <c r="D730" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:44</t>
         </is>
       </c>
       <c r="E730" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:28</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" s="4" t="inlineStr">
         <is>
-          <t>Wizz Air Rome Half Marathon by Brooks</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B731" s="5" t="inlineStr">
@@ -18749,23 +18749,23 @@
         </is>
       </c>
       <c r="C731" s="5" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D731" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:02:55</t>
         </is>
       </c>
       <c r="E731" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:35</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" s="6" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B732" s="7" t="inlineStr">
@@ -18778,19 +18778,19 @@
       </c>
       <c r="D732" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:53</t>
         </is>
       </c>
       <c r="E732" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:37</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B733" s="5" t="inlineStr">
@@ -18803,19 +18803,19 @@
       </c>
       <c r="D733" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E733" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:28</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" s="6" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B734" s="7" t="inlineStr">
@@ -18828,24 +18828,24 @@
       </c>
       <c r="D734" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:56:42</t>
         </is>
       </c>
       <c r="E734" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:11</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" s="4" t="inlineStr">
         <is>
-          <t>10K Montmartre</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B735" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C735" s="5" t="n">
@@ -18858,48 +18858,48 @@
       </c>
       <c r="E735" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:00</t>
         </is>
       </c>
     </row>
     <row r="736">
-      <c r="A736" s="8" t="inlineStr">
-        <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
-        </is>
-      </c>
-      <c r="B736" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C736" s="9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D736" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E736" s="9" t="inlineStr">
-        <is>
-          <t>0:29:19</t>
+      <c r="A736" s="6" t="inlineStr">
+        <is>
+          <t>Movistar Madrid Medio Maraton</t>
+        </is>
+      </c>
+      <c r="B736" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C736" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D736" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E736" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" s="4" t="inlineStr">
         <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
+          <t>NN CPC Loop Den Haag - Half Marathon</t>
         </is>
       </c>
       <c r="B737" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C737" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D737" s="5" t="inlineStr">
         <is>
@@ -18908,30 +18908,30 @@
       </c>
       <c r="E737" s="5" t="inlineStr">
         <is>
-          <t>0:28:45</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="738">
-      <c r="A738" s="8" t="inlineStr">
-        <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
-        </is>
-      </c>
-      <c r="B738" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C738" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D738" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E738" s="9" t="inlineStr">
+      <c r="A738" s="6" t="inlineStr">
+        <is>
+          <t>NN CPC Loop Den Haag - Half Marathon</t>
+        </is>
+      </c>
+      <c r="B738" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C738" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D738" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E738" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18940,48 +18940,48 @@
     <row r="739">
       <c r="A739" s="4" t="inlineStr">
         <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
+          <t>NYCRUNS Brooklyn Experience Half Marathon</t>
         </is>
       </c>
       <c r="B739" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C739" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D739" s="5" t="inlineStr">
         <is>
-          <t>0:26:45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E739" s="5" t="inlineStr">
         <is>
-          <t>0:29:25</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="740">
-      <c r="A740" s="8" t="inlineStr">
-        <is>
-          <t>AJ Bell Great Birmingham Run 10K</t>
-        </is>
-      </c>
-      <c r="B740" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C740" s="9" t="n">
+      <c r="A740" s="6" t="inlineStr">
+        <is>
+          <t>NYRR RBC Brooklyn Half</t>
+        </is>
+      </c>
+      <c r="B740" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C740" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="D740" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E740" s="9" t="inlineStr">
+      <c r="D740" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E740" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -18990,12 +18990,12 @@
     <row r="741">
       <c r="A741" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Bristol Run 10K</t>
+          <t>Nike Melbourne Marathon Festival</t>
         </is>
       </c>
       <c r="B741" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C741" s="5" t="n">
@@ -19013,25 +19013,25 @@
       </c>
     </row>
     <row r="742">
-      <c r="A742" s="8" t="inlineStr">
-        <is>
-          <t>AJ Bell Great Manchester Run</t>
-        </is>
-      </c>
-      <c r="B742" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C742" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D742" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E742" s="9" t="inlineStr">
+      <c r="A742" s="6" t="inlineStr">
+        <is>
+          <t>Riyadh Marathon (Half)</t>
+        </is>
+      </c>
+      <c r="B742" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C742" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D742" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E742" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19040,12 +19040,12 @@
     <row r="743">
       <c r="A743" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B743" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C743" s="5" t="n">
@@ -19063,25 +19063,25 @@
       </c>
     </row>
     <row r="744">
-      <c r="A744" s="8" t="inlineStr">
-        <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
-        </is>
-      </c>
-      <c r="B744" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C744" s="9" t="n">
+      <c r="A744" s="6" t="inlineStr">
+        <is>
+          <t>Riyadh Marathon (Half)</t>
+        </is>
+      </c>
+      <c r="B744" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C744" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="D744" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E744" s="9" t="inlineStr">
+      <c r="D744" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E744" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19090,16 +19090,16 @@
     <row r="745">
       <c r="A745" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great North 10K</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B745" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C745" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D745" s="5" t="inlineStr">
         <is>
@@ -19113,25 +19113,25 @@
       </c>
     </row>
     <row r="746">
-      <c r="A746" s="8" t="inlineStr">
-        <is>
-          <t>ASICS LDNX</t>
-        </is>
-      </c>
-      <c r="B746" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C746" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D746" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E746" s="9" t="inlineStr">
+      <c r="A746" s="6" t="inlineStr">
+        <is>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
+        </is>
+      </c>
+      <c r="B746" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C746" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D746" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E746" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19140,16 +19140,16 @@
     <row r="747">
       <c r="A747" s="4" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B747" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C747" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D747" s="5" t="inlineStr">
         <is>
@@ -19163,139 +19163,139 @@
       </c>
     </row>
     <row r="748">
-      <c r="A748" s="8" t="inlineStr">
-        <is>
-          <t>Adidas 10K Paris</t>
-        </is>
-      </c>
-      <c r="B748" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C748" s="9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D748" s="9" t="inlineStr">
-        <is>
-          <t>0:29:37</t>
-        </is>
-      </c>
-      <c r="E748" s="9" t="inlineStr">
-        <is>
-          <t>0:32:18</t>
+      <c r="A748" s="6" t="inlineStr">
+        <is>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
+        </is>
+      </c>
+      <c r="B748" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C748" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D748" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E748" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" s="4" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B749" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C749" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D749" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E749" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="6" t="inlineStr">
+        <is>
+          <t>Rock 'n' Roll Running Series Mexico City</t>
+        </is>
+      </c>
+      <c r="B750" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C750" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="D749" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E749" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" s="8" t="inlineStr">
-        <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
-        </is>
-      </c>
-      <c r="B750" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C750" s="9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D750" s="9" t="inlineStr">
-        <is>
-          <t>0:27:41</t>
-        </is>
-      </c>
-      <c r="E750" s="9" t="inlineStr">
-        <is>
-          <t>0:30:43</t>
+      <c r="D750" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E750" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" s="4" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Rock 'n' Roll Running Series San Diego</t>
         </is>
       </c>
       <c r="B751" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C751" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D751" s="5" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E751" s="5" t="inlineStr">
         <is>
-          <t>0:31:12</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="752">
-      <c r="A752" s="8" t="inlineStr">
-        <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
-        </is>
-      </c>
-      <c r="B752" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C752" s="9" t="n">
+      <c r="A752" s="6" t="inlineStr">
+        <is>
+          <t>Royal Parks Half Marathon</t>
+        </is>
+      </c>
+      <c r="B752" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C752" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="D752" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E752" s="9" t="inlineStr">
-        <is>
-          <t>0:31:29</t>
+      <c r="D752" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E752" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" s="4" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B753" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C753" s="5" t="n">
@@ -19303,49 +19303,49 @@
       </c>
       <c r="D753" s="5" t="inlineStr">
         <is>
-          <t>0:29:08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E753" s="5" t="inlineStr">
         <is>
-          <t>0:33:25</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="754">
-      <c r="A754" s="8" t="inlineStr">
-        <is>
-          <t>BOLDERBoulder 10K</t>
-        </is>
-      </c>
-      <c r="B754" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C754" s="9" t="n">
+      <c r="A754" s="6" t="inlineStr">
+        <is>
+          <t>Run in Lyon (Semi)</t>
+        </is>
+      </c>
+      <c r="B754" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C754" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="D754" s="9" t="inlineStr">
-        <is>
-          <t>0:29:13</t>
-        </is>
-      </c>
-      <c r="E754" s="9" t="inlineStr">
-        <is>
-          <t>0:32:45</t>
+      <c r="D754" s="7" t="inlineStr">
+        <is>
+          <t>1:05:44</t>
+        </is>
+      </c>
+      <c r="E754" s="7" t="inlineStr">
+        <is>
+          <t>1:18:34</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" s="4" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B755" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C755" s="5" t="n">
@@ -19363,43 +19363,43 @@
       </c>
     </row>
     <row r="756">
-      <c r="A756" s="8" t="inlineStr">
-        <is>
-          <t>BOLDERBoulder 10K</t>
-        </is>
-      </c>
-      <c r="B756" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C756" s="9" t="n">
+      <c r="A756" s="6" t="inlineStr">
+        <is>
+          <t>Semi-Marathon de Boulogne-Billancourt</t>
+        </is>
+      </c>
+      <c r="B756" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C756" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="D756" s="9" t="inlineStr">
-        <is>
-          <t>0:28:36</t>
-        </is>
-      </c>
-      <c r="E756" s="9" t="inlineStr">
-        <is>
-          <t>0:31:51</t>
+      <c r="D756" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E756" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
         </is>
       </c>
       <c r="B757" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C757" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D757" s="5" t="inlineStr">
         <is>
@@ -19413,25 +19413,25 @@
       </c>
     </row>
     <row r="758">
-      <c r="A758" s="8" t="inlineStr">
-        <is>
-          <t>Bangsaen10</t>
-        </is>
-      </c>
-      <c r="B758" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C758" s="9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D758" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E758" s="9" t="inlineStr">
+      <c r="A758" s="6" t="inlineStr">
+        <is>
+          <t>St. Jude Rock 'n' Roll Series Nashville</t>
+        </is>
+      </c>
+      <c r="B758" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C758" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D758" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E758" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19440,116 +19440,116 @@
     <row r="759">
       <c r="A759" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B759" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C759" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D759" s="5" t="inlineStr">
+        <is>
+          <t>1:01:13</t>
+        </is>
+      </c>
+      <c r="E759" s="5" t="inlineStr">
+        <is>
+          <t>1:09:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="6" t="inlineStr">
+        <is>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
+        </is>
+      </c>
+      <c r="B760" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C760" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="D759" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E759" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="760">
-      <c r="A760" s="8" t="inlineStr">
-        <is>
-          <t>Cancer Research UK London Winter Run</t>
-        </is>
-      </c>
-      <c r="B760" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C760" s="9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D760" s="9" t="inlineStr">
-        <is>
-          <t>0:28:52</t>
-        </is>
-      </c>
-      <c r="E760" s="9" t="inlineStr">
-        <is>
-          <t>0:31:59</t>
+      <c r="D760" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E760" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" s="4" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B761" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C761" s="5" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D761" s="5" t="inlineStr">
         <is>
-          <t>0:28:46</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E761" s="5" t="inlineStr">
         <is>
-          <t>0:32:33</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="762">
-      <c r="A762" s="8" t="inlineStr">
-        <is>
-          <t>Cancer Research UK London Winter Run</t>
-        </is>
-      </c>
-      <c r="B762" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C762" s="9" t="n">
+      <c r="A762" s="6" t="inlineStr">
+        <is>
+          <t>Standard Chartered KL Half Marathon</t>
+        </is>
+      </c>
+      <c r="B762" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C762" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="D762" s="9" t="inlineStr">
-        <is>
-          <t>0:29:22</t>
-        </is>
-      </c>
-      <c r="E762" s="9" t="inlineStr">
-        <is>
-          <t>0:34:32</t>
+      <c r="D762" s="7" t="inlineStr">
+        <is>
+          <t>1:11:08</t>
+        </is>
+      </c>
+      <c r="E762" s="7" t="inlineStr">
+        <is>
+          <t>1:23:55</t>
         </is>
       </c>
     </row>
     <row r="763">
       <c r="A763" s="4" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Standard Chartered Singapore Half Marathon</t>
         </is>
       </c>
       <c r="B763" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C763" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D763" s="5" t="inlineStr">
         <is>
@@ -19563,25 +19563,25 @@
       </c>
     </row>
     <row r="764">
-      <c r="A764" s="8" t="inlineStr">
-        <is>
-          <t>Cooper River Bridge Run</t>
-        </is>
-      </c>
-      <c r="B764" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C764" s="9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D764" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E764" s="9" t="inlineStr">
+      <c r="A764" s="6" t="inlineStr">
+        <is>
+          <t>TCS Mizuno Half Marathon</t>
+        </is>
+      </c>
+      <c r="B764" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C764" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D764" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E764" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19590,62 +19590,62 @@
     <row r="765">
       <c r="A765" s="4" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B765" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C765" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D765" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E765" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="6" t="inlineStr">
+        <is>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
+        </is>
+      </c>
+      <c r="B766" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C766" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="D765" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E765" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="766">
-      <c r="A766" s="8" t="inlineStr">
-        <is>
-          <t>Cooper River Bridge Run</t>
-        </is>
-      </c>
-      <c r="B766" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C766" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D766" s="9" t="inlineStr">
-        <is>
-          <t>0:28:27</t>
-        </is>
-      </c>
-      <c r="E766" s="9" t="inlineStr">
-        <is>
-          <t>0:31:49</t>
+      <c r="D766" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E766" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" s="4" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B767" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C767" s="5" t="n">
@@ -19663,25 +19663,25 @@
       </c>
     </row>
     <row r="768">
-      <c r="A768" s="8" t="inlineStr">
-        <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
-        </is>
-      </c>
-      <c r="B768" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C768" s="9" t="n">
+      <c r="A768" s="6" t="inlineStr">
+        <is>
+          <t>Taipei Half Marathon</t>
+        </is>
+      </c>
+      <c r="B768" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C768" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="D768" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E768" s="9" t="inlineStr">
+      <c r="D768" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E768" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19690,12 +19690,12 @@
     <row r="769">
       <c r="A769" s="4" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B769" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C769" s="5" t="n">
@@ -19713,25 +19713,25 @@
       </c>
     </row>
     <row r="770">
-      <c r="A770" s="8" t="inlineStr">
-        <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
-        </is>
-      </c>
-      <c r="B770" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C770" s="9" t="n">
+      <c r="A770" s="6" t="inlineStr">
+        <is>
+          <t>Taipei Half Marathon</t>
+        </is>
+      </c>
+      <c r="B770" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C770" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="D770" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E770" s="9" t="inlineStr">
+      <c r="D770" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E770" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19740,48 +19740,48 @@
     <row r="771">
       <c r="A771" s="4" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Tata Mumbai Marathon (Half)</t>
         </is>
       </c>
       <c r="B771" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C771" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D771" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E771" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="6" t="inlineStr">
+        <is>
+          <t>Tata Mumbai Marathon (Half)</t>
+        </is>
+      </c>
+      <c r="B772" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C772" s="7" t="n">
         <v>2026</v>
       </c>
-      <c r="D771" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E771" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="772">
-      <c r="A772" s="8" t="inlineStr">
-        <is>
-          <t>Great Scottish Run 10K</t>
-        </is>
-      </c>
-      <c r="B772" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C772" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D772" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E772" s="9" t="inlineStr">
+      <c r="D772" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E772" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19790,16 +19790,16 @@
     <row r="773">
       <c r="A773" s="4" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
+          <t>The Big Half</t>
         </is>
       </c>
       <c r="B773" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C773" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D773" s="5" t="inlineStr">
         <is>
@@ -19813,25 +19813,25 @@
       </c>
     </row>
     <row r="774">
-      <c r="A774" s="8" t="inlineStr">
-        <is>
-          <t>NN San Silvestre Vallecana</t>
-        </is>
-      </c>
-      <c r="B774" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C774" s="9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D774" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E774" s="9" t="inlineStr">
+      <c r="A774" s="6" t="inlineStr">
+        <is>
+          <t>Tokyo Legacy Half Marathon</t>
+        </is>
+      </c>
+      <c r="B774" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C774" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D774" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E774" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -19840,312 +19840,312 @@
     <row r="775">
       <c r="A775" s="4" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B775" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C775" s="5" t="n">
-        <v>2024</v>
+        <v>2006</v>
       </c>
       <c r="D775" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:22</t>
         </is>
       </c>
       <c r="E775" s="5" t="inlineStr">
         <is>
-          <t>0:31:18</t>
+          <t>1:09:43</t>
         </is>
       </c>
     </row>
     <row r="776">
-      <c r="A776" s="8" t="inlineStr">
-        <is>
-          <t>NN San Silvestre Vallecana</t>
-        </is>
-      </c>
-      <c r="B776" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C776" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D776" s="9" t="inlineStr">
-        <is>
-          <t>0:27:41</t>
-        </is>
-      </c>
-      <c r="E776" s="9" t="inlineStr">
-        <is>
-          <t>0:31:11</t>
+      <c r="A776" s="6" t="inlineStr">
+        <is>
+          <t>United Airlines NYC Half</t>
+        </is>
+      </c>
+      <c r="B776" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C776" s="7" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D776" s="7" t="inlineStr">
+        <is>
+          <t>0:59:24</t>
+        </is>
+      </c>
+      <c r="E776" s="7" t="inlineStr">
+        <is>
+          <t>1:10:32</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" s="4" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B777" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C777" s="5" t="n">
-        <v>2023</v>
+        <v>2008</v>
       </c>
       <c r="D777" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:58</t>
         </is>
       </c>
       <c r="E777" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:19</t>
         </is>
       </c>
     </row>
     <row r="778">
-      <c r="A778" s="8" t="inlineStr">
-        <is>
-          <t>Royal Run</t>
-        </is>
-      </c>
-      <c r="B778" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C778" s="9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D778" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E778" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="A778" s="6" t="inlineStr">
+        <is>
+          <t>United Airlines NYC Half</t>
+        </is>
+      </c>
+      <c r="B778" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C778" s="7" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D778" s="7" t="inlineStr">
+        <is>
+          <t>1:01:06</t>
+        </is>
+      </c>
+      <c r="E778" s="7" t="inlineStr">
+        <is>
+          <t>1:09:32</t>
         </is>
       </c>
     </row>
     <row r="779">
       <c r="A779" s="4" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B779" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C779" s="5" t="n">
-        <v>2025</v>
+        <v>2010</v>
       </c>
       <c r="D779" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:52</t>
         </is>
       </c>
       <c r="E779" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:09:25</t>
         </is>
       </c>
     </row>
     <row r="780">
-      <c r="A780" s="8" t="inlineStr">
-        <is>
-          <t>Run in Lyon</t>
-        </is>
-      </c>
-      <c r="B780" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C780" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D780" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E780" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="A780" s="6" t="inlineStr">
+        <is>
+          <t>United Airlines NYC Half</t>
+        </is>
+      </c>
+      <c r="B780" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C780" s="7" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D780" s="7" t="inlineStr">
+        <is>
+          <t>1:00:23</t>
+        </is>
+      </c>
+      <c r="E780" s="7" t="inlineStr">
+        <is>
+          <t>1:08:52</t>
         </is>
       </c>
     </row>
     <row r="781">
       <c r="A781" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B781" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C781" s="5" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="D781" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:39</t>
         </is>
       </c>
       <c r="E781" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:35</t>
         </is>
       </c>
     </row>
     <row r="782">
-      <c r="A782" s="8" t="inlineStr">
-        <is>
-          <t>Run in Lyon (10K)</t>
-        </is>
-      </c>
-      <c r="B782" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C782" s="9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D782" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E782" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="A782" s="6" t="inlineStr">
+        <is>
+          <t>United Airlines NYC Half</t>
+        </is>
+      </c>
+      <c r="B782" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C782" s="7" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D782" s="7" t="inlineStr">
+        <is>
+          <t>1:01:02</t>
+        </is>
+      </c>
+      <c r="E782" s="7" t="inlineStr">
+        <is>
+          <t>1:09:09</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B783" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C783" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D783" s="5" t="inlineStr">
+        <is>
+          <t>1:00:50</t>
+        </is>
+      </c>
+      <c r="E783" s="5" t="inlineStr">
+        <is>
+          <t>1:08:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="6" t="inlineStr">
+        <is>
+          <t>United Airlines NYC Half</t>
+        </is>
+      </c>
+      <c r="B784" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C784" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="D783" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E783" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="784">
-      <c r="A784" s="8" t="inlineStr">
-        <is>
-          <t>Saucony London 10K</t>
-        </is>
-      </c>
-      <c r="B784" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C784" s="9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D784" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E784" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D784" s="7" t="inlineStr">
+        <is>
+          <t>1:01:31</t>
+        </is>
+      </c>
+      <c r="E784" s="7" t="inlineStr">
+        <is>
+          <t>1:07:04</t>
         </is>
       </c>
     </row>
     <row r="785">
       <c r="A785" s="4" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B785" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C785" s="5" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D785" s="5" t="inlineStr">
         <is>
-          <t>0:29:41</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E785" s="5" t="inlineStr">
         <is>
-          <t>0:32:51</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
     <row r="786">
-      <c r="A786" s="8" t="inlineStr">
-        <is>
-          <t>Saucony London 10K</t>
-        </is>
-      </c>
-      <c r="B786" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C786" s="9" t="n">
+      <c r="A786" s="6" t="inlineStr">
+        <is>
+          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
+        </is>
+      </c>
+      <c r="B786" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C786" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="D786" s="9" t="inlineStr">
-        <is>
-          <t>0:29:33</t>
-        </is>
-      </c>
-      <c r="E786" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D786" s="7" t="inlineStr">
+        <is>
+          <t>0:58:02</t>
+        </is>
+      </c>
+      <c r="E786" s="7" t="inlineStr">
+        <is>
+          <t>1:03:08</t>
         </is>
       </c>
     </row>
     <row r="787">
       <c r="A787" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered KL 10K</t>
+          <t>Vedanta Delhi Half Marathon</t>
         </is>
       </c>
       <c r="B787" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C787" s="5" t="n">
@@ -20153,35 +20153,35 @@
       </c>
       <c r="D787" s="5" t="inlineStr">
         <is>
-          <t>0:32:26</t>
+          <t>0:59:50</t>
         </is>
       </c>
       <c r="E787" s="5" t="inlineStr">
         <is>
-          <t>0:39:23</t>
+          <t>1:07:20</t>
         </is>
       </c>
     </row>
     <row r="788">
-      <c r="A788" s="8" t="inlineStr">
-        <is>
-          <t>Statesman Capitol 10K</t>
-        </is>
-      </c>
-      <c r="B788" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C788" s="9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D788" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E788" s="9" t="inlineStr">
+      <c r="A788" s="6" t="inlineStr">
+        <is>
+          <t>Vienna City Half Marathon</t>
+        </is>
+      </c>
+      <c r="B788" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C788" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D788" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E788" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20190,16 +20190,16 @@
     <row r="789">
       <c r="A789" s="4" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
       <c r="B789" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C789" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D789" s="5" t="inlineStr">
         <is>
@@ -20213,25 +20213,25 @@
       </c>
     </row>
     <row r="790">
-      <c r="A790" s="8" t="inlineStr">
-        <is>
-          <t>Statesman Capitol 10K</t>
-        </is>
-      </c>
-      <c r="B790" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C790" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D790" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E790" s="9" t="inlineStr">
+      <c r="A790" s="6" t="inlineStr">
+        <is>
+          <t>Walt Disney World Marathon Weekend</t>
+        </is>
+      </c>
+      <c r="B790" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C790" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D790" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E790" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20240,16 +20240,16 @@
     <row r="791">
       <c r="A791" s="4" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Warsaw Half Marathon</t>
         </is>
       </c>
       <c r="B791" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C791" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D791" s="5" t="inlineStr">
         <is>
@@ -20263,25 +20263,25 @@
       </c>
     </row>
     <row r="792">
-      <c r="A792" s="8" t="inlineStr">
-        <is>
-          <t>Transurban Bridge to Brisbane</t>
-        </is>
-      </c>
-      <c r="B792" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C792" s="9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D792" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E792" s="9" t="inlineStr">
+      <c r="A792" s="6" t="inlineStr">
+        <is>
+          <t>Warsaw Half Marathon</t>
+        </is>
+      </c>
+      <c r="B792" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C792" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D792" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E792" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20290,12 +20290,12 @@
     <row r="793">
       <c r="A793" s="4" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Wizz Air Rome Half Marathon by Brooks</t>
         </is>
       </c>
       <c r="B793" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C793" s="5" t="n">
@@ -20313,25 +20313,25 @@
       </c>
     </row>
     <row r="794">
-      <c r="A794" s="8" t="inlineStr">
-        <is>
-          <t>Ukrop's Monument Avenue 10K</t>
-        </is>
-      </c>
-      <c r="B794" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C794" s="9" t="n">
+      <c r="A794" s="6" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+        </is>
+      </c>
+      <c r="B794" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C794" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="D794" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E794" s="9" t="inlineStr">
+      <c r="D794" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E794" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20340,12 +20340,12 @@
     <row r="795">
       <c r="A795" s="4" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
         </is>
       </c>
       <c r="B795" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C795" s="5" t="n">
@@ -20363,25 +20363,25 @@
       </c>
     </row>
     <row r="796">
-      <c r="A796" s="8" t="inlineStr">
-        <is>
-          <t>Ukrop's Monument Avenue 10K</t>
-        </is>
-      </c>
-      <c r="B796" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C796" s="9" t="n">
+      <c r="A796" s="6" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+        </is>
+      </c>
+      <c r="B796" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C796" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="D796" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E796" s="9" t="inlineStr">
+      <c r="D796" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E796" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20390,7 +20390,7 @@
     <row r="797">
       <c r="A797" s="4" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>10K Montmartre</t>
         </is>
       </c>
       <c r="B797" s="5" t="inlineStr">
@@ -20399,7 +20399,7 @@
         </is>
       </c>
       <c r="C797" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D797" s="5" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
     <row r="798">
       <c r="A798" s="8" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B798" s="9" t="inlineStr">
@@ -20424,7 +20424,7 @@
         </is>
       </c>
       <c r="C798" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D798" s="9" t="inlineStr">
         <is>
@@ -20433,14 +20433,14 @@
       </c>
       <c r="E798" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:19</t>
         </is>
       </c>
     </row>
     <row r="799">
       <c r="A799" s="4" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B799" s="5" t="inlineStr">
@@ -20449,23 +20449,23 @@
         </is>
       </c>
       <c r="C799" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D799" s="5" t="inlineStr">
         <is>
-          <t>0:28:09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E799" s="5" t="inlineStr">
         <is>
-          <t>0:32:54</t>
+          <t>0:28:45</t>
         </is>
       </c>
     </row>
     <row r="800">
       <c r="A800" s="8" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B800" s="9" t="inlineStr">
@@ -20474,7 +20474,7 @@
         </is>
       </c>
       <c r="C800" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D800" s="9" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
     <row r="801">
       <c r="A801" s="4" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B801" s="5" t="inlineStr">
@@ -20499,23 +20499,23 @@
         </is>
       </c>
       <c r="C801" s="5" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D801" s="5" t="inlineStr">
         <is>
-          <t>0:29:14</t>
+          <t>0:26:45</t>
         </is>
       </c>
       <c r="E801" s="5" t="inlineStr">
         <is>
-          <t>0:31:36</t>
+          <t>0:29:25</t>
         </is>
       </c>
     </row>
     <row r="802">
       <c r="A802" s="8" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>AJ Bell Great Birmingham Run 10K</t>
         </is>
       </c>
       <c r="B802" s="9" t="inlineStr">
@@ -20540,12 +20540,12 @@
     <row r="803">
       <c r="A803" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Birmingham Run</t>
+          <t>AJ Bell Great Bristol Run 10K</t>
         </is>
       </c>
       <c r="B803" s="5" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C803" s="5" t="n">
@@ -20565,12 +20565,12 @@
     <row r="804">
       <c r="A804" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great South Run</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B804" s="9" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C804" s="9" t="n">
@@ -20590,16 +20590,16 @@
     <row r="805">
       <c r="A805" s="4" t="inlineStr">
         <is>
-          <t>Army Ten Miler</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B805" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C805" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D805" s="5" t="inlineStr">
         <is>
@@ -20615,95 +20615,95 @@
     <row r="806">
       <c r="A806" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B806" s="9" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C806" s="9" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D806" s="9" t="inlineStr">
         <is>
-          <t>0:35:01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E806" s="9" t="inlineStr">
         <is>
-          <t>0:39:28</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="807">
       <c r="A807" s="4" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>AJ Bell Great North 10K</t>
         </is>
       </c>
       <c r="B807" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C807" s="5" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D807" s="5" t="inlineStr">
         <is>
-          <t>0:36:10</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E807" s="5" t="inlineStr">
         <is>
-          <t>0:42:05</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="A808" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>ASICS LDNX</t>
         </is>
       </c>
       <c r="B808" s="9" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C808" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D808" s="9" t="inlineStr">
         <is>
-          <t>0:37:02</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E808" s="9" t="inlineStr">
         <is>
-          <t>0:43:48</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="809">
       <c r="A809" s="4" t="inlineStr">
         <is>
-          <t>Boilermaker Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B809" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C809" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D809" s="5" t="inlineStr">
         <is>
-          <t>0:42:44</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E809" s="5" t="inlineStr">
@@ -20715,41 +20715,41 @@
     <row r="810">
       <c r="A810" s="8" t="inlineStr">
         <is>
-          <t>Broad Street Run</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B810" s="9" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C810" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D810" s="9" t="inlineStr">
         <is>
-          <t>0:46:13</t>
+          <t>0:29:37</t>
         </is>
       </c>
       <c r="E810" s="9" t="inlineStr">
         <is>
-          <t>0:54:01</t>
+          <t>0:32:18</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" s="4" t="inlineStr">
         <is>
-          <t>City2Surf</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B811" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C811" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D811" s="5" t="inlineStr">
         <is>
@@ -20765,37 +20765,37 @@
     <row r="812">
       <c r="A812" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B812" s="9" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C812" s="9" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="D812" s="9" t="inlineStr">
         <is>
-          <t>0:45:15</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E812" s="9" t="inlineStr">
         <is>
-          <t>0:50:45</t>
+          <t>0:30:43</t>
         </is>
       </c>
     </row>
     <row r="813">
       <c r="A813" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B813" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C813" s="5" t="n">
@@ -20803,24 +20803,24 @@
       </c>
       <c r="D813" s="5" t="inlineStr">
         <is>
-          <t>0:44:51</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E813" s="5" t="inlineStr">
         <is>
-          <t>0:51:15</t>
+          <t>0:31:12</t>
         </is>
       </c>
     </row>
     <row r="814">
       <c r="A814" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B814" s="9" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C814" s="9" t="n">
@@ -20828,74 +20828,74 @@
       </c>
       <c r="D814" s="9" t="inlineStr">
         <is>
-          <t>0:46:07</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E814" s="9" t="inlineStr">
         <is>
-          <t>0:50:51</t>
+          <t>0:31:29</t>
         </is>
       </c>
     </row>
     <row r="815">
       <c r="A815" s="4" t="inlineStr">
         <is>
-          <t>Falmouth Road Race</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B815" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C815" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D815" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:08</t>
         </is>
       </c>
       <c r="E815" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:33:25</t>
         </is>
       </c>
     </row>
     <row r="816">
       <c r="A816" s="8" t="inlineStr">
         <is>
-          <t>Great Scottish Run</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B816" s="9" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C816" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D816" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:13</t>
         </is>
       </c>
       <c r="E816" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:45</t>
         </is>
       </c>
     </row>
     <row r="817">
       <c r="A817" s="4" t="inlineStr">
         <is>
-          <t>Lilac Bloomsday Run</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B817" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C817" s="5" t="n">
@@ -20915,30 +20915,1830 @@
     <row r="818">
       <c r="A818" s="8" t="inlineStr">
         <is>
+          <t>BOLDERBoulder 10K</t>
+        </is>
+      </c>
+      <c r="B818" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C818" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D818" s="9" t="inlineStr">
+        <is>
+          <t>0:28:36</t>
+        </is>
+      </c>
+      <c r="E818" s="9" t="inlineStr">
+        <is>
+          <t>0:31:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="4" t="inlineStr">
+        <is>
+          <t>Bangsaen10</t>
+        </is>
+      </c>
+      <c r="B819" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C819" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D819" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E819" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="8" t="inlineStr">
+        <is>
+          <t>Bangsaen10</t>
+        </is>
+      </c>
+      <c r="B820" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C820" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D820" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E820" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="4" t="inlineStr">
+        <is>
+          <t>Bangsaen10</t>
+        </is>
+      </c>
+      <c r="B821" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C821" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D821" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E821" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="8" t="inlineStr">
+        <is>
+          <t>Cancer Research UK London Winter Run</t>
+        </is>
+      </c>
+      <c r="B822" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C822" s="9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D822" s="9" t="inlineStr">
+        <is>
+          <t>0:28:52</t>
+        </is>
+      </c>
+      <c r="E822" s="9" t="inlineStr">
+        <is>
+          <t>0:31:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="4" t="inlineStr">
+        <is>
+          <t>Cancer Research UK London Winter Run</t>
+        </is>
+      </c>
+      <c r="B823" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C823" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D823" s="5" t="inlineStr">
+        <is>
+          <t>0:28:46</t>
+        </is>
+      </c>
+      <c r="E823" s="5" t="inlineStr">
+        <is>
+          <t>0:32:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="8" t="inlineStr">
+        <is>
+          <t>Cancer Research UK London Winter Run</t>
+        </is>
+      </c>
+      <c r="B824" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C824" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D824" s="9" t="inlineStr">
+        <is>
+          <t>0:29:22</t>
+        </is>
+      </c>
+      <c r="E824" s="9" t="inlineStr">
+        <is>
+          <t>0:34:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="4" t="inlineStr">
+        <is>
+          <t>Cancer Research UK London Winter Run</t>
+        </is>
+      </c>
+      <c r="B825" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C825" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D825" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E825" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="8" t="inlineStr">
+        <is>
+          <t>Cooper River Bridge Run</t>
+        </is>
+      </c>
+      <c r="B826" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C826" s="9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D826" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E826" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="4" t="inlineStr">
+        <is>
+          <t>Cooper River Bridge Run</t>
+        </is>
+      </c>
+      <c r="B827" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C827" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D827" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E827" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="8" t="inlineStr">
+        <is>
+          <t>Cooper River Bridge Run</t>
+        </is>
+      </c>
+      <c r="B828" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C828" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D828" s="9" t="inlineStr">
+        <is>
+          <t>0:28:27</t>
+        </is>
+      </c>
+      <c r="E828" s="9" t="inlineStr">
+        <is>
+          <t>0:31:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="4" t="inlineStr">
+        <is>
+          <t>Cooper River Bridge Run</t>
+        </is>
+      </c>
+      <c r="B829" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C829" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D829" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E829" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="8" t="inlineStr">
+        <is>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+        </is>
+      </c>
+      <c r="B830" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C830" s="9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D830" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E830" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="4" t="inlineStr">
+        <is>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+        </is>
+      </c>
+      <c r="B831" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C831" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D831" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E831" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="8" t="inlineStr">
+        <is>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+        </is>
+      </c>
+      <c r="B832" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C832" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D832" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E832" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="4" t="inlineStr">
+        <is>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+        </is>
+      </c>
+      <c r="B833" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C833" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D833" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E833" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="8" t="inlineStr">
+        <is>
+          <t>Great Scottish Run 10K</t>
+        </is>
+      </c>
+      <c r="B834" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C834" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D834" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E834" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="4" t="inlineStr">
+        <is>
+          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
+        </is>
+      </c>
+      <c r="B835" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C835" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D835" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E835" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="8" t="inlineStr">
+        <is>
+          <t>NN San Silvestre Vallecana</t>
+        </is>
+      </c>
+      <c r="B836" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C836" s="9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D836" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E836" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="4" t="inlineStr">
+        <is>
+          <t>NN San Silvestre Vallecana</t>
+        </is>
+      </c>
+      <c r="B837" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C837" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D837" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E837" s="5" t="inlineStr">
+        <is>
+          <t>0:31:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="8" t="inlineStr">
+        <is>
+          <t>NN San Silvestre Vallecana</t>
+        </is>
+      </c>
+      <c r="B838" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C838" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D838" s="9" t="inlineStr">
+        <is>
+          <t>0:27:41</t>
+        </is>
+      </c>
+      <c r="E838" s="9" t="inlineStr">
+        <is>
+          <t>0:31:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="4" t="inlineStr">
+        <is>
+          <t>Royal Run</t>
+        </is>
+      </c>
+      <c r="B839" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C839" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D839" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E839" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="8" t="inlineStr">
+        <is>
+          <t>Royal Run</t>
+        </is>
+      </c>
+      <c r="B840" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C840" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D840" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E840" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="4" t="inlineStr">
+        <is>
+          <t>Royal Run</t>
+        </is>
+      </c>
+      <c r="B841" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C841" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D841" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E841" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="8" t="inlineStr">
+        <is>
+          <t>Run in Lyon</t>
+        </is>
+      </c>
+      <c r="B842" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C842" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D842" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E842" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="4" t="inlineStr">
+        <is>
+          <t>Run in Lyon (10K)</t>
+        </is>
+      </c>
+      <c r="B843" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C843" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D843" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E843" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="8" t="inlineStr">
+        <is>
+          <t>Run in Lyon (10K)</t>
+        </is>
+      </c>
+      <c r="B844" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C844" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D844" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E844" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="4" t="inlineStr">
+        <is>
+          <t>Run in Lyon (10K)</t>
+        </is>
+      </c>
+      <c r="B845" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C845" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D845" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E845" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="8" t="inlineStr">
+        <is>
+          <t>Saucony London 10K</t>
+        </is>
+      </c>
+      <c r="B846" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C846" s="9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D846" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E846" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="4" t="inlineStr">
+        <is>
+          <t>Saucony London 10K</t>
+        </is>
+      </c>
+      <c r="B847" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C847" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D847" s="5" t="inlineStr">
+        <is>
+          <t>0:29:41</t>
+        </is>
+      </c>
+      <c r="E847" s="5" t="inlineStr">
+        <is>
+          <t>0:32:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="8" t="inlineStr">
+        <is>
+          <t>Saucony London 10K</t>
+        </is>
+      </c>
+      <c r="B848" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C848" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D848" s="9" t="inlineStr">
+        <is>
+          <t>0:29:33</t>
+        </is>
+      </c>
+      <c r="E848" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="4" t="inlineStr">
+        <is>
+          <t>Standard Chartered KL 10K</t>
+        </is>
+      </c>
+      <c r="B849" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C849" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D849" s="5" t="inlineStr">
+        <is>
+          <t>0:32:26</t>
+        </is>
+      </c>
+      <c r="E849" s="5" t="inlineStr">
+        <is>
+          <t>0:39:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="8" t="inlineStr">
+        <is>
+          <t>Statesman Capitol 10K</t>
+        </is>
+      </c>
+      <c r="B850" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C850" s="9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D850" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E850" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="4" t="inlineStr">
+        <is>
+          <t>Statesman Capitol 10K</t>
+        </is>
+      </c>
+      <c r="B851" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C851" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D851" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E851" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="8" t="inlineStr">
+        <is>
+          <t>Statesman Capitol 10K</t>
+        </is>
+      </c>
+      <c r="B852" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C852" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D852" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E852" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="4" t="inlineStr">
+        <is>
+          <t>Transurban Bridge to Brisbane</t>
+        </is>
+      </c>
+      <c r="B853" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C853" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D853" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E853" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="8" t="inlineStr">
+        <is>
+          <t>Transurban Bridge to Brisbane</t>
+        </is>
+      </c>
+      <c r="B854" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C854" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D854" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E854" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="4" t="inlineStr">
+        <is>
+          <t>Transurban Bridge to Brisbane</t>
+        </is>
+      </c>
+      <c r="B855" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C855" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D855" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E855" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="8" t="inlineStr">
+        <is>
+          <t>Ukrop's Monument Avenue 10K</t>
+        </is>
+      </c>
+      <c r="B856" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C856" s="9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D856" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E856" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="4" t="inlineStr">
+        <is>
+          <t>Ukrop's Monument Avenue 10K</t>
+        </is>
+      </c>
+      <c r="B857" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C857" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D857" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E857" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="8" t="inlineStr">
+        <is>
+          <t>Ukrop's Monument Avenue 10K</t>
+        </is>
+      </c>
+      <c r="B858" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C858" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D858" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E858" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="4" t="inlineStr">
+        <is>
+          <t>Vancouver Sun Run</t>
+        </is>
+      </c>
+      <c r="B859" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C859" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D859" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E859" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="8" t="inlineStr">
+        <is>
+          <t>Vancouver Sun Run</t>
+        </is>
+      </c>
+      <c r="B860" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C860" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D860" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E860" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="4" t="inlineStr">
+        <is>
+          <t>Vancouver Sun Run</t>
+        </is>
+      </c>
+      <c r="B861" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C861" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D861" s="5" t="inlineStr">
+        <is>
+          <t>0:28:09</t>
+        </is>
+      </c>
+      <c r="E861" s="5" t="inlineStr">
+        <is>
+          <t>0:32:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="8" t="inlineStr">
+        <is>
+          <t>Vitality London 10,000</t>
+        </is>
+      </c>
+      <c r="B862" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C862" s="9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D862" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E862" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="4" t="inlineStr">
+        <is>
+          <t>Vitality London 10,000</t>
+        </is>
+      </c>
+      <c r="B863" s="5" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C863" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D863" s="5" t="inlineStr">
+        <is>
+          <t>0:29:14</t>
+        </is>
+      </c>
+      <c r="E863" s="5" t="inlineStr">
+        <is>
+          <t>0:31:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="8" t="inlineStr">
+        <is>
+          <t>Vitality London 10,000</t>
+        </is>
+      </c>
+      <c r="B864" s="9" t="inlineStr">
+        <is>
+          <t>10K</t>
+        </is>
+      </c>
+      <c r="C864" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D864" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E864" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="4" t="inlineStr">
+        <is>
+          <t>AJ Bell Great Birmingham Run</t>
+        </is>
+      </c>
+      <c r="B865" s="5" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="C865" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D865" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E865" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="8" t="inlineStr">
+        <is>
+          <t>AJ Bell Great South Run</t>
+        </is>
+      </c>
+      <c r="B866" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C866" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D866" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E866" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="4" t="inlineStr">
+        <is>
+          <t>Army Ten Miler</t>
+        </is>
+      </c>
+      <c r="B867" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C867" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D867" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E867" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="8" t="inlineStr">
+        <is>
+          <t>Bay to Breakers</t>
+        </is>
+      </c>
+      <c r="B868" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C868" s="9" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D868" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E868" s="9" t="inlineStr">
+        <is>
+          <t>0:38:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="4" t="inlineStr">
+        <is>
+          <t>Bay to Breakers</t>
+        </is>
+      </c>
+      <c r="B869" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C869" s="5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D869" s="5" t="inlineStr">
+        <is>
+          <t>0:33:31</t>
+        </is>
+      </c>
+      <c r="E869" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="8" t="inlineStr">
+        <is>
+          <t>Bay to Breakers</t>
+        </is>
+      </c>
+      <c r="B870" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C870" s="9" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D870" s="9" t="inlineStr">
+        <is>
+          <t>0:34:15</t>
+        </is>
+      </c>
+      <c r="E870" s="9" t="inlineStr">
+        <is>
+          <t>0:38:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="4" t="inlineStr">
+        <is>
+          <t>Bay to Breakers</t>
+        </is>
+      </c>
+      <c r="B871" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C871" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D871" s="5" t="inlineStr">
+        <is>
+          <t>0:34:40</t>
+        </is>
+      </c>
+      <c r="E871" s="5" t="inlineStr">
+        <is>
+          <t>0:39:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="8" t="inlineStr">
+        <is>
+          <t>Bay to Breakers</t>
+        </is>
+      </c>
+      <c r="B872" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C872" s="9" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D872" s="9" t="inlineStr">
+        <is>
+          <t>0:35:01</t>
+        </is>
+      </c>
+      <c r="E872" s="9" t="inlineStr">
+        <is>
+          <t>0:39:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="4" t="inlineStr">
+        <is>
+          <t>Bay to Breakers</t>
+        </is>
+      </c>
+      <c r="B873" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C873" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D873" s="5" t="inlineStr">
+        <is>
+          <t>0:36:10</t>
+        </is>
+      </c>
+      <c r="E873" s="5" t="inlineStr">
+        <is>
+          <t>0:42:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="8" t="inlineStr">
+        <is>
+          <t>Bay to Breakers</t>
+        </is>
+      </c>
+      <c r="B874" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C874" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D874" s="9" t="inlineStr">
+        <is>
+          <t>0:37:02</t>
+        </is>
+      </c>
+      <c r="E874" s="9" t="inlineStr">
+        <is>
+          <t>0:43:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="4" t="inlineStr">
+        <is>
+          <t>Boilermaker Road Race</t>
+        </is>
+      </c>
+      <c r="B875" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C875" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D875" s="5" t="inlineStr">
+        <is>
+          <t>0:42:44</t>
+        </is>
+      </c>
+      <c r="E875" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="8" t="inlineStr">
+        <is>
+          <t>Broad Street Run</t>
+        </is>
+      </c>
+      <c r="B876" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C876" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D876" s="9" t="inlineStr">
+        <is>
+          <t>0:46:13</t>
+        </is>
+      </c>
+      <c r="E876" s="9" t="inlineStr">
+        <is>
+          <t>0:54:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="4" t="inlineStr">
+        <is>
+          <t>City2Surf</t>
+        </is>
+      </c>
+      <c r="B877" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C877" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D877" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E877" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B878" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C878" s="9" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D878" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E878" s="9" t="inlineStr">
+        <is>
+          <t>0:50:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B879" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C879" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D879" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E879" s="5" t="inlineStr">
+        <is>
+          <t>0:51:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B880" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C880" s="9" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D880" s="9" t="inlineStr">
+        <is>
+          <t>0:44:27</t>
+        </is>
+      </c>
+      <c r="E880" s="9" t="inlineStr">
+        <is>
+          <t>0:51:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B881" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C881" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D881" s="5" t="inlineStr">
+        <is>
+          <t>0:44:48</t>
+        </is>
+      </c>
+      <c r="E881" s="5" t="inlineStr">
+        <is>
+          <t>0:51:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B882" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C882" s="9" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D882" s="9" t="inlineStr">
+        <is>
+          <t>0:45:28</t>
+        </is>
+      </c>
+      <c r="E882" s="9" t="inlineStr">
+        <is>
+          <t>0:51:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B883" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C883" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D883" s="5" t="inlineStr">
+        <is>
+          <t>0:45:45</t>
+        </is>
+      </c>
+      <c r="E883" s="5" t="inlineStr">
+        <is>
+          <t>0:53:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B884" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C884" s="9" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D884" s="9" t="inlineStr">
+        <is>
+          <t>0:45:15</t>
+        </is>
+      </c>
+      <c r="E884" s="9" t="inlineStr">
+        <is>
+          <t>0:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B885" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C885" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D885" s="5" t="inlineStr">
+        <is>
+          <t>0:44:51</t>
+        </is>
+      </c>
+      <c r="E885" s="5" t="inlineStr">
+        <is>
+          <t>0:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B886" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C886" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D886" s="9" t="inlineStr">
+        <is>
+          <t>0:46:07</t>
+        </is>
+      </c>
+      <c r="E886" s="9" t="inlineStr">
+        <is>
+          <t>0:50:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="4" t="inlineStr">
+        <is>
+          <t>Falmouth Road Race</t>
+        </is>
+      </c>
+      <c r="B887" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C887" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D887" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E887" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="8" t="inlineStr">
+        <is>
+          <t>Great Scottish Run</t>
+        </is>
+      </c>
+      <c r="B888" s="9" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="C888" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D888" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E888" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="4" t="inlineStr">
+        <is>
+          <t>Lilac Bloomsday Run</t>
+        </is>
+      </c>
+      <c r="B889" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C889" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D889" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E889" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="8" t="inlineStr">
+        <is>
           <t>Manchester Road Race</t>
         </is>
       </c>
-      <c r="B818" s="9" t="inlineStr">
+      <c r="B890" s="9" t="inlineStr">
         <is>
           <t>AUTRE</t>
         </is>
       </c>
-      <c r="C818" s="9" t="n">
+      <c r="C890" s="9" t="n">
         <v>2024</v>
       </c>
-      <c r="D818" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E818" s="9" t="inlineStr">
+      <c r="D890" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E890" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E818"/>
+  <autoFilter ref="A1:E890"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Chronos_Vainqueurs.xlsx
+++ b/Chronos_Vainqueurs.xlsx
@@ -16178,12 +16178,12 @@
       </c>
       <c r="D628" s="7" t="inlineStr">
         <is>
-          <t>0:52:12</t>
+          <t>1:10:25</t>
         </is>
       </c>
       <c r="E628" s="7" t="inlineStr">
         <is>
-          <t>0:57:46</t>
+          <t>1:21:56</t>
         </is>
       </c>
     </row>

--- a/Chronos_Vainqueurs.xlsx
+++ b/Chronos_Vainqueurs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$907</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$908</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11128,7 +11128,7 @@
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>2:05:07</t>
+          <t>2:05:00</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
@@ -11215,7 +11215,7 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>Seoul Marathon</t>
+          <t>Schneider Electric Marathon de Paris</t>
         </is>
       </c>
       <c r="B430" s="3" t="inlineStr">
@@ -11224,16 +11224,16 @@
         </is>
       </c>
       <c r="C430" s="3" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>2:05:27</t>
+          <t>2:05:16</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>2:28:32</t>
+          <t>2:18:34</t>
         </is>
       </c>
     </row>
@@ -11249,16 +11249,16 @@
         </is>
       </c>
       <c r="C431" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>2:06:08</t>
+          <t>2:05:27</t>
         </is>
       </c>
       <c r="E431" s="5" t="inlineStr">
         <is>
-          <t>2:21:32</t>
+          <t>2:28:32</t>
         </is>
       </c>
     </row>
@@ -11274,23 +11274,23 @@
         </is>
       </c>
       <c r="C432" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>2:05:42</t>
+          <t>2:06:08</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>2:21:36</t>
+          <t>2:21:32</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>St. Jude Memphis Marathon</t>
+          <t>Seoul Marathon</t>
         </is>
       </c>
       <c r="B433" s="5" t="inlineStr">
@@ -11299,16 +11299,16 @@
         </is>
       </c>
       <c r="C433" s="5" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D433" s="5" t="inlineStr">
         <is>
-          <t>2:38:23</t>
+          <t>2:05:42</t>
         </is>
       </c>
       <c r="E433" s="5" t="inlineStr">
         <is>
-          <t>3:00:20</t>
+          <t>2:21:36</t>
         </is>
       </c>
     </row>
@@ -11324,16 +11324,16 @@
         </is>
       </c>
       <c r="C434" s="3" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="D434" s="3" t="inlineStr">
         <is>
-          <t>2:30:21</t>
+          <t>2:38:23</t>
         </is>
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>2:56:44</t>
+          <t>3:00:20</t>
         </is>
       </c>
     </row>
@@ -11349,16 +11349,16 @@
         </is>
       </c>
       <c r="C435" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
-          <t>2:34:18</t>
+          <t>2:30:21</t>
         </is>
       </c>
       <c r="E435" s="5" t="inlineStr">
         <is>
-          <t>2:54:45</t>
+          <t>2:56:44</t>
         </is>
       </c>
     </row>
@@ -11374,23 +11374,23 @@
         </is>
       </c>
       <c r="C436" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D436" s="3" t="inlineStr">
         <is>
-          <t>2:28:03</t>
+          <t>2:34:18</t>
         </is>
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>2:51:12</t>
+          <t>2:54:45</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Marathon</t>
+          <t>St. Jude Memphis Marathon</t>
         </is>
       </c>
       <c r="B437" s="5" t="inlineStr">
@@ -11399,16 +11399,16 @@
         </is>
       </c>
       <c r="C437" s="5" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
-          <t>2:09:20</t>
+          <t>2:28:03</t>
         </is>
       </c>
       <c r="E437" s="5" t="inlineStr">
         <is>
-          <t>2:26:13</t>
+          <t>2:51:12</t>
         </is>
       </c>
     </row>
@@ -11424,23 +11424,23 @@
         </is>
       </c>
       <c r="C438" s="3" t="n">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:09:20</t>
         </is>
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:26:13</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered KL Marathon</t>
+          <t>Standard Chartered Hong Kong Marathon</t>
         </is>
       </c>
       <c r="B439" s="5" t="inlineStr">
@@ -11449,23 +11449,23 @@
         </is>
       </c>
       <c r="C439" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D439" s="5" t="inlineStr">
         <is>
-          <t>2:17:28</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E439" s="5" t="inlineStr">
         <is>
-          <t>2:41:36</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>Standard Chartered Singapore Marathon</t>
+          <t>Standard Chartered KL Marathon</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
@@ -11474,16 +11474,16 @@
         </is>
       </c>
       <c r="C440" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>2:16:06</t>
+          <t>2:17:28</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>2:39:04</t>
+          <t>2:41:36</t>
         </is>
       </c>
     </row>
@@ -11499,23 +11499,23 @@
         </is>
       </c>
       <c r="C441" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D441" s="5" t="inlineStr">
         <is>
-          <t>2:15:40</t>
+          <t>2:16:06</t>
         </is>
       </c>
       <c r="E441" s="5" t="inlineStr">
         <is>
-          <t>2:41:24</t>
+          <t>2:39:04</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>Stockholm Marathon</t>
+          <t>Standard Chartered Singapore Marathon</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
@@ -11524,16 +11524,16 @@
         </is>
       </c>
       <c r="C442" s="3" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D442" s="3" t="inlineStr">
         <is>
-          <t>2:18:22</t>
+          <t>2:15:40</t>
         </is>
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>2:34:14</t>
+          <t>2:41:24</t>
         </is>
       </c>
     </row>
@@ -11549,16 +11549,16 @@
         </is>
       </c>
       <c r="C443" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D443" s="5" t="inlineStr">
         <is>
-          <t>2:10:58</t>
+          <t>2:18:22</t>
         </is>
       </c>
       <c r="E443" s="5" t="inlineStr">
         <is>
-          <t>2:31:46</t>
+          <t>2:34:14</t>
         </is>
       </c>
     </row>
@@ -11574,16 +11574,16 @@
         </is>
       </c>
       <c r="C444" s="3" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>2:11:36</t>
+          <t>2:10:58</t>
         </is>
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>2:35:45</t>
+          <t>2:31:46</t>
         </is>
       </c>
     </row>
@@ -11599,16 +11599,16 @@
         </is>
       </c>
       <c r="C445" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D445" s="5" t="inlineStr">
         <is>
-          <t>2:13:30</t>
+          <t>2:11:36</t>
         </is>
       </c>
       <c r="E445" s="5" t="inlineStr">
         <is>
-          <t>2:40:28</t>
+          <t>2:35:45</t>
         </is>
       </c>
     </row>
@@ -11624,16 +11624,16 @@
         </is>
       </c>
       <c r="C446" s="3" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>2:10:10</t>
+          <t>2:13:30</t>
         </is>
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>2:33:38</t>
+          <t>2:40:28</t>
         </is>
       </c>
     </row>
@@ -11649,16 +11649,16 @@
         </is>
       </c>
       <c r="C447" s="5" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D447" s="5" t="inlineStr">
         <is>
-          <t>2:12:24</t>
+          <t>2:10:10</t>
         </is>
       </c>
       <c r="E447" s="5" t="inlineStr">
         <is>
-          <t>2:29:03</t>
+          <t>2:33:38</t>
         </is>
       </c>
     </row>
@@ -11674,16 +11674,16 @@
         </is>
       </c>
       <c r="C448" s="3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>2:11:08</t>
+          <t>2:12:24</t>
         </is>
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>2:31:48</t>
+          <t>2:29:03</t>
         </is>
       </c>
     </row>
@@ -11699,16 +11699,16 @@
         </is>
       </c>
       <c r="C449" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D449" s="5" t="inlineStr">
         <is>
-          <t>2:10:32</t>
+          <t>2:11:08</t>
         </is>
       </c>
       <c r="E449" s="5" t="inlineStr">
         <is>
-          <t>2:30:44</t>
+          <t>2:31:48</t>
         </is>
       </c>
     </row>
@@ -11724,16 +11724,16 @@
         </is>
       </c>
       <c r="C450" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>2:14:17</t>
+          <t>2:10:32</t>
         </is>
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>2:31:46</t>
+          <t>2:30:44</t>
         </is>
       </c>
     </row>
@@ -11749,23 +11749,23 @@
         </is>
       </c>
       <c r="C451" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D451" s="5" t="inlineStr">
         <is>
-          <t>2:11:34</t>
+          <t>2:14:17</t>
         </is>
       </c>
       <c r="E451" s="5" t="inlineStr">
         <is>
-          <t>2:30:38</t>
+          <t>2:31:46</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>TCS Amsterdam Marathon</t>
+          <t>Stockholm Marathon</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
@@ -11774,16 +11774,16 @@
         </is>
       </c>
       <c r="C452" s="3" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D452" s="3" t="inlineStr">
         <is>
-          <t>2:08:47</t>
+          <t>2:11:34</t>
         </is>
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>2:28:42</t>
+          <t>2:30:38</t>
         </is>
       </c>
     </row>
@@ -11799,16 +11799,16 @@
         </is>
       </c>
       <c r="C453" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
-          <t>2:08:22</t>
+          <t>2:08:47</t>
         </is>
       </c>
       <c r="E453" s="5" t="inlineStr">
         <is>
-          <t>2:26:04</t>
+          <t>2:28:42</t>
         </is>
       </c>
     </row>
@@ -11824,16 +11824,16 @@
         </is>
       </c>
       <c r="C454" s="3" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D454" s="3" t="inlineStr">
         <is>
-          <t>2:07:45</t>
+          <t>2:08:22</t>
         </is>
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>2:23:54</t>
+          <t>2:26:04</t>
         </is>
       </c>
     </row>
@@ -11849,16 +11849,16 @@
         </is>
       </c>
       <c r="C455" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D455" s="5" t="inlineStr">
         <is>
-          <t>2:06:38</t>
+          <t>2:07:45</t>
         </is>
       </c>
       <c r="E455" s="5" t="inlineStr">
         <is>
-          <t>2:27:08</t>
+          <t>2:23:54</t>
         </is>
       </c>
     </row>
@@ -11874,16 +11874,16 @@
         </is>
       </c>
       <c r="C456" s="3" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D456" s="3" t="inlineStr">
         <is>
-          <t>2:06:20</t>
+          <t>2:06:38</t>
         </is>
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>2:28:39</t>
+          <t>2:27:08</t>
         </is>
       </c>
     </row>
@@ -11899,16 +11899,16 @@
         </is>
       </c>
       <c r="C457" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D457" s="5" t="inlineStr">
         <is>
-          <t>2:09:27</t>
+          <t>2:06:20</t>
         </is>
       </c>
       <c r="E457" s="5" t="inlineStr">
         <is>
-          <t>2:28:18</t>
+          <t>2:28:39</t>
         </is>
       </c>
     </row>
@@ -11924,16 +11924,16 @@
         </is>
       </c>
       <c r="C458" s="3" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D458" s="3" t="inlineStr">
         <is>
-          <t>2:08:41</t>
+          <t>2:09:27</t>
         </is>
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>2:27:37</t>
+          <t>2:28:18</t>
         </is>
       </c>
     </row>
@@ -11949,16 +11949,16 @@
         </is>
       </c>
       <c r="C459" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D459" s="5" t="inlineStr">
         <is>
-          <t>2:07:57</t>
+          <t>2:08:41</t>
         </is>
       </c>
       <c r="E459" s="5" t="inlineStr">
         <is>
-          <t>2:28:41</t>
+          <t>2:27:37</t>
         </is>
       </c>
     </row>
@@ -11974,16 +11974,16 @@
         </is>
       </c>
       <c r="C460" s="3" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D460" s="3" t="inlineStr">
         <is>
-          <t>2:06:13</t>
+          <t>2:07:57</t>
         </is>
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>2:29:02</t>
+          <t>2:28:41</t>
         </is>
       </c>
     </row>
@@ -11999,16 +11999,16 @@
         </is>
       </c>
       <c r="C461" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D461" s="5" t="inlineStr">
         <is>
-          <t>2:06:00</t>
+          <t>2:06:13</t>
         </is>
       </c>
       <c r="E461" s="5" t="inlineStr">
         <is>
-          <t>2:25:46</t>
+          <t>2:29:02</t>
         </is>
       </c>
     </row>
@@ -12024,16 +12024,16 @@
         </is>
       </c>
       <c r="C462" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D462" s="3" t="inlineStr">
         <is>
-          <t>2:05:44</t>
+          <t>2:06:00</t>
         </is>
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>2:28:28</t>
+          <t>2:25:46</t>
         </is>
       </c>
     </row>
@@ -12049,16 +12049,16 @@
         </is>
       </c>
       <c r="C463" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D463" s="5" t="inlineStr">
         <is>
-          <t>2:05:16</t>
+          <t>2:05:44</t>
         </is>
       </c>
       <c r="E463" s="5" t="inlineStr">
         <is>
-          <t>2:24:34</t>
+          <t>2:28:28</t>
         </is>
       </c>
     </row>
@@ -12074,16 +12074,16 @@
         </is>
       </c>
       <c r="C464" s="3" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D464" s="3" t="inlineStr">
         <is>
-          <t>2:05:36</t>
+          <t>2:05:16</t>
         </is>
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>2:21:09</t>
+          <t>2:24:34</t>
         </is>
       </c>
     </row>
@@ -12099,7 +12099,7 @@
         </is>
       </c>
       <c r="C465" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D465" s="5" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
       </c>
       <c r="E465" s="5" t="inlineStr">
         <is>
-          <t>2:24:27</t>
+          <t>2:21:09</t>
         </is>
       </c>
     </row>
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="C466" s="3" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D466" s="3" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
       </c>
       <c r="E466" s="3" t="inlineStr">
         <is>
-          <t>2:23:27</t>
+          <t>2:24:27</t>
         </is>
       </c>
     </row>
@@ -12149,16 +12149,16 @@
         </is>
       </c>
       <c r="C467" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D467" s="5" t="inlineStr">
         <is>
-          <t>2:06:19</t>
+          <t>2:05:36</t>
         </is>
       </c>
       <c r="E467" s="5" t="inlineStr">
         <is>
-          <t>2:24:11</t>
+          <t>2:23:27</t>
         </is>
       </c>
     </row>
@@ -12174,16 +12174,16 @@
         </is>
       </c>
       <c r="C468" s="3" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D468" s="3" t="inlineStr">
         <is>
-          <t>2:05:20</t>
+          <t>2:06:19</t>
         </is>
       </c>
       <c r="E468" s="3" t="inlineStr">
         <is>
-          <t>2:23:20</t>
+          <t>2:24:11</t>
         </is>
       </c>
     </row>
@@ -12199,16 +12199,16 @@
         </is>
       </c>
       <c r="C469" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D469" s="5" t="inlineStr">
         <is>
-          <t>2:05:09</t>
+          <t>2:05:20</t>
         </is>
       </c>
       <c r="E469" s="5" t="inlineStr">
         <is>
-          <t>2:21:53</t>
+          <t>2:23:20</t>
         </is>
       </c>
     </row>
@@ -12224,16 +12224,16 @@
         </is>
       </c>
       <c r="C470" s="3" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D470" s="3" t="inlineStr">
         <is>
-          <t>2:04:06</t>
+          <t>2:05:09</t>
         </is>
       </c>
       <c r="E470" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:21:53</t>
         </is>
       </c>
     </row>
@@ -12249,16 +12249,16 @@
         </is>
       </c>
       <c r="C471" s="5" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="D471" s="5" t="inlineStr">
         <is>
-          <t>2:03:38</t>
+          <t>2:04:06</t>
         </is>
       </c>
       <c r="E471" s="5" t="inlineStr">
         <is>
-          <t>2:17:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -12278,12 +12278,12 @@
       </c>
       <c r="D472" s="3" t="inlineStr">
         <is>
-          <t>2:03:36</t>
+          <t>2:03:38</t>
         </is>
       </c>
       <c r="E472" s="3" t="inlineStr">
         <is>
-          <t>2:17:55</t>
+          <t>2:17:57</t>
         </is>
       </c>
     </row>
@@ -12299,16 +12299,16 @@
         </is>
       </c>
       <c r="C473" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D473" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:03:36</t>
         </is>
       </c>
       <c r="E473" s="5" t="inlineStr">
         <is>
-          <t>2:17:20</t>
+          <t>2:17:55</t>
         </is>
       </c>
     </row>
@@ -12328,12 +12328,12 @@
       </c>
       <c r="D474" s="3" t="inlineStr">
         <is>
-          <t>2:04:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E474" s="3" t="inlineStr">
         <is>
-          <t>2:17:18</t>
+          <t>2:17:20</t>
         </is>
       </c>
     </row>
@@ -12349,16 +12349,16 @@
         </is>
       </c>
       <c r="C475" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D475" s="5" t="inlineStr">
         <is>
-          <t>2:04:18</t>
+          <t>2:04:48</t>
         </is>
       </c>
       <c r="E475" s="5" t="inlineStr">
         <is>
-          <t>2:18:21</t>
+          <t>2:17:18</t>
         </is>
       </c>
     </row>
@@ -12399,16 +12399,16 @@
         </is>
       </c>
       <c r="C477" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D477" s="5" t="inlineStr">
         <is>
-          <t>2:05:38</t>
+          <t>2:04:18</t>
         </is>
       </c>
       <c r="E477" s="5" t="inlineStr">
         <is>
-          <t>2:16:52</t>
+          <t>2:18:21</t>
         </is>
       </c>
     </row>
@@ -12428,12 +12428,12 @@
       </c>
       <c r="D478" s="3" t="inlineStr">
         <is>
-          <t>2:05:35</t>
+          <t>2:05:38</t>
         </is>
       </c>
       <c r="E478" s="3" t="inlineStr">
         <is>
-          <t>2:16:50</t>
+          <t>2:16:52</t>
         </is>
       </c>
     </row>
@@ -12449,16 +12449,16 @@
         </is>
       </c>
       <c r="C479" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D479" s="5" t="inlineStr">
         <is>
-          <t>2:03:31</t>
+          <t>2:05:35</t>
         </is>
       </c>
       <c r="E479" s="5" t="inlineStr">
         <is>
-          <t>2:17:37</t>
+          <t>2:16:50</t>
         </is>
       </c>
     </row>
@@ -12478,19 +12478,19 @@
       </c>
       <c r="D480" s="3" t="inlineStr">
         <is>
-          <t>2:07:59</t>
+          <t>2:03:31</t>
         </is>
       </c>
       <c r="E480" s="3" t="inlineStr">
         <is>
-          <t>2:28:27</t>
+          <t>2:17:37</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>TCS London Marathon</t>
+          <t>TCS Amsterdam Marathon</t>
         </is>
       </c>
       <c r="B481" s="5" t="inlineStr">
@@ -12499,16 +12499,16 @@
         </is>
       </c>
       <c r="C481" s="5" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D481" s="5" t="inlineStr">
         <is>
-          <t>2:06:36</t>
+          <t>2:07:59</t>
         </is>
       </c>
       <c r="E481" s="5" t="inlineStr">
         <is>
-          <t>2:24:33</t>
+          <t>2:28:27</t>
         </is>
       </c>
     </row>
@@ -12524,16 +12524,16 @@
         </is>
       </c>
       <c r="C482" s="3" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D482" s="3" t="inlineStr">
         <is>
-          <t>2:07:11</t>
+          <t>2:06:36</t>
         </is>
       </c>
       <c r="E482" s="3" t="inlineStr">
         <is>
-          <t>2:23:56</t>
+          <t>2:24:33</t>
         </is>
       </c>
     </row>
@@ -12549,16 +12549,16 @@
         </is>
       </c>
       <c r="C483" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D483" s="5" t="inlineStr">
         <is>
-          <t>2:05:38</t>
+          <t>2:07:11</t>
         </is>
       </c>
       <c r="E483" s="5" t="inlineStr">
         <is>
-          <t>2:18:56</t>
+          <t>2:23:56</t>
         </is>
       </c>
     </row>
@@ -12574,16 +12574,16 @@
         </is>
       </c>
       <c r="C484" s="3" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D484" s="3" t="inlineStr">
         <is>
-          <t>2:07:56</t>
+          <t>2:05:38</t>
         </is>
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>2:15:25</t>
+          <t>2:18:56</t>
         </is>
       </c>
     </row>
@@ -12599,16 +12599,16 @@
         </is>
       </c>
       <c r="C485" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D485" s="5" t="inlineStr">
         <is>
-          <t>2:06:18</t>
+          <t>2:07:56</t>
         </is>
       </c>
       <c r="E485" s="5" t="inlineStr">
         <is>
-          <t>2:22:35</t>
+          <t>2:15:25</t>
         </is>
       </c>
     </row>
@@ -12624,16 +12624,16 @@
         </is>
       </c>
       <c r="C486" s="3" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D486" s="3" t="inlineStr">
         <is>
-          <t>2:07:44</t>
+          <t>2:06:18</t>
         </is>
       </c>
       <c r="E486" s="3" t="inlineStr">
         <is>
-          <t>2:17:42</t>
+          <t>2:22:35</t>
         </is>
       </c>
     </row>
@@ -12649,16 +12649,16 @@
         </is>
       </c>
       <c r="C487" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D487" s="5" t="inlineStr">
         <is>
-          <t>2:06:39</t>
+          <t>2:07:44</t>
         </is>
       </c>
       <c r="E487" s="5" t="inlineStr">
         <is>
-          <t>2:20:04</t>
+          <t>2:17:42</t>
         </is>
       </c>
     </row>
@@ -12674,16 +12674,16 @@
         </is>
       </c>
       <c r="C488" s="3" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D488" s="3" t="inlineStr">
         <is>
-          <t>2:07:41</t>
+          <t>2:06:39</t>
         </is>
       </c>
       <c r="E488" s="3" t="inlineStr">
         <is>
-          <t>2:20:13</t>
+          <t>2:20:04</t>
         </is>
       </c>
     </row>
@@ -12699,16 +12699,16 @@
         </is>
       </c>
       <c r="C489" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D489" s="5" t="inlineStr">
         <is>
-          <t>2:05:15</t>
+          <t>2:07:41</t>
         </is>
       </c>
       <c r="E489" s="5" t="inlineStr">
         <is>
-          <t>2:24:14</t>
+          <t>2:20:13</t>
         </is>
       </c>
     </row>
@@ -12724,16 +12724,16 @@
         </is>
       </c>
       <c r="C490" s="3" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D490" s="3" t="inlineStr">
         <is>
-          <t>2:05:10</t>
+          <t>2:05:15</t>
         </is>
       </c>
       <c r="E490" s="3" t="inlineStr">
         <is>
-          <t>2:23:12</t>
+          <t>2:24:14</t>
         </is>
       </c>
     </row>
@@ -12749,16 +12749,16 @@
         </is>
       </c>
       <c r="C491" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D491" s="5" t="inlineStr">
         <is>
-          <t>2:05:19</t>
+          <t>2:05:10</t>
         </is>
       </c>
       <c r="E491" s="5" t="inlineStr">
         <is>
-          <t>2:22:00</t>
+          <t>2:23:12</t>
         </is>
       </c>
     </row>
@@ -12774,16 +12774,16 @@
         </is>
       </c>
       <c r="C492" s="3" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D492" s="3" t="inlineStr">
         <is>
-          <t>2:04:40</t>
+          <t>2:05:19</t>
         </is>
       </c>
       <c r="E492" s="3" t="inlineStr">
         <is>
-          <t>2:19:36</t>
+          <t>2:22:00</t>
         </is>
       </c>
     </row>
@@ -12799,16 +12799,16 @@
         </is>
       </c>
       <c r="C493" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D493" s="5" t="inlineStr">
         <is>
-          <t>2:04:44</t>
+          <t>2:04:40</t>
         </is>
       </c>
       <c r="E493" s="5" t="inlineStr">
         <is>
-          <t>2:18:37</t>
+          <t>2:19:36</t>
         </is>
       </c>
     </row>
@@ -12824,16 +12824,16 @@
         </is>
       </c>
       <c r="C494" s="3" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D494" s="3" t="inlineStr">
         <is>
-          <t>2:04:29</t>
+          <t>2:04:44</t>
         </is>
       </c>
       <c r="E494" s="3" t="inlineStr">
         <is>
-          <t>2:20:15</t>
+          <t>2:18:37</t>
         </is>
       </c>
     </row>
@@ -12849,7 +12849,7 @@
         </is>
       </c>
       <c r="C495" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D495" s="5" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="E495" s="5" t="inlineStr">
         <is>
-          <t>2:20:21</t>
+          <t>2:20:15</t>
         </is>
       </c>
     </row>
@@ -12874,16 +12874,16 @@
         </is>
       </c>
       <c r="C496" s="3" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D496" s="3" t="inlineStr">
         <is>
-          <t>2:04:42</t>
+          <t>2:04:29</t>
         </is>
       </c>
       <c r="E496" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:20:21</t>
         </is>
       </c>
     </row>
@@ -12899,11 +12899,11 @@
         </is>
       </c>
       <c r="C497" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D497" s="5" t="inlineStr">
         <is>
-          <t>2:03:05</t>
+          <t>2:04:42</t>
         </is>
       </c>
       <c r="E497" s="5" t="inlineStr">
@@ -12924,16 +12924,16 @@
         </is>
       </c>
       <c r="C498" s="3" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D498" s="3" t="inlineStr">
         <is>
-          <t>2:05:48</t>
+          <t>2:03:05</t>
         </is>
       </c>
       <c r="E498" s="3" t="inlineStr">
         <is>
-          <t>2:17:01</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -12949,16 +12949,16 @@
         </is>
       </c>
       <c r="C499" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D499" s="5" t="inlineStr">
         <is>
-          <t>2:04:17</t>
+          <t>2:05:48</t>
         </is>
       </c>
       <c r="E499" s="5" t="inlineStr">
         <is>
-          <t>2:18:31</t>
+          <t>2:17:01</t>
         </is>
       </c>
     </row>
@@ -12974,16 +12974,16 @@
         </is>
       </c>
       <c r="C500" s="3" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D500" s="3" t="inlineStr">
         <is>
-          <t>2:02:37</t>
+          <t>2:04:17</t>
         </is>
       </c>
       <c r="E500" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:18:31</t>
         </is>
       </c>
     </row>
@@ -12999,16 +12999,16 @@
         </is>
       </c>
       <c r="C501" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D501" s="5" t="inlineStr">
         <is>
-          <t>2:05:41</t>
+          <t>2:02:37</t>
         </is>
       </c>
       <c r="E501" s="5" t="inlineStr">
         <is>
-          <t>2:18:58</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -13024,16 +13024,16 @@
         </is>
       </c>
       <c r="C502" s="3" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D502" s="3" t="inlineStr">
         <is>
-          <t>2:04:01</t>
+          <t>2:05:41</t>
         </is>
       </c>
       <c r="E502" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:18:58</t>
         </is>
       </c>
     </row>
@@ -13049,16 +13049,16 @@
         </is>
       </c>
       <c r="C503" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D503" s="5" t="inlineStr">
         <is>
-          <t>2:04:39</t>
+          <t>2:04:01</t>
         </is>
       </c>
       <c r="E503" s="5" t="inlineStr">
         <is>
-          <t>2:17:26</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -13074,16 +13074,16 @@
         </is>
       </c>
       <c r="C504" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D504" s="3" t="inlineStr">
         <is>
-          <t>2:01:25</t>
+          <t>2:04:39</t>
         </is>
       </c>
       <c r="E504" s="3" t="inlineStr">
         <is>
-          <t>2:18:33</t>
+          <t>2:17:26</t>
         </is>
       </c>
     </row>
@@ -13099,16 +13099,16 @@
         </is>
       </c>
       <c r="C505" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D505" s="5" t="inlineStr">
         <is>
-          <t>2:04:01</t>
+          <t>2:01:25</t>
         </is>
       </c>
       <c r="E505" s="5" t="inlineStr">
         <is>
-          <t>2:16:16</t>
+          <t>2:18:33</t>
         </is>
       </c>
     </row>
@@ -13124,23 +13124,23 @@
         </is>
       </c>
       <c r="C506" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D506" s="3" t="inlineStr">
         <is>
-          <t>2:02:27</t>
+          <t>2:04:01</t>
         </is>
       </c>
       <c r="E506" s="3" t="inlineStr">
         <is>
-          <t>2:15:50</t>
+          <t>2:16:16</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>TCS New York City Marathon</t>
+          <t>TCS London Marathon</t>
         </is>
       </c>
       <c r="B507" s="5" t="inlineStr">
@@ -13149,16 +13149,16 @@
         </is>
       </c>
       <c r="C507" s="5" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D507" s="5" t="inlineStr">
         <is>
-          <t>2:10:09</t>
+          <t>2:02:27</t>
         </is>
       </c>
       <c r="E507" s="5" t="inlineStr">
         <is>
-          <t>2:25:45</t>
+          <t>2:15:50</t>
         </is>
       </c>
     </row>
@@ -13174,16 +13174,16 @@
         </is>
       </c>
       <c r="C508" s="3" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D508" s="3" t="inlineStr">
         <is>
-          <t>2:07:43</t>
+          <t>2:10:09</t>
         </is>
       </c>
       <c r="E508" s="3" t="inlineStr">
         <is>
-          <t>2:24:21</t>
+          <t>2:25:45</t>
         </is>
       </c>
     </row>
@@ -13199,16 +13199,16 @@
         </is>
       </c>
       <c r="C509" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D509" s="5" t="inlineStr">
         <is>
-          <t>2:08:07</t>
+          <t>2:07:43</t>
         </is>
       </c>
       <c r="E509" s="5" t="inlineStr">
         <is>
-          <t>2:22:31</t>
+          <t>2:24:21</t>
         </is>
       </c>
     </row>
@@ -13224,11 +13224,11 @@
         </is>
       </c>
       <c r="C510" s="3" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D510" s="3" t="inlineStr">
         <is>
-          <t>2:10:30</t>
+          <t>2:08:07</t>
         </is>
       </c>
       <c r="E510" s="3" t="inlineStr">
@@ -13249,16 +13249,16 @@
         </is>
       </c>
       <c r="C511" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D511" s="5" t="inlineStr">
         <is>
-          <t>2:09:28</t>
+          <t>2:10:30</t>
         </is>
       </c>
       <c r="E511" s="5" t="inlineStr">
         <is>
-          <t>2:23:10</t>
+          <t>2:22:31</t>
         </is>
       </c>
     </row>
@@ -13274,16 +13274,16 @@
         </is>
       </c>
       <c r="C512" s="3" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D512" s="3" t="inlineStr">
         <is>
-          <t>2:09:30</t>
+          <t>2:09:28</t>
         </is>
       </c>
       <c r="E512" s="3" t="inlineStr">
         <is>
-          <t>2:24:41</t>
+          <t>2:23:10</t>
         </is>
       </c>
     </row>
@@ -13299,16 +13299,16 @@
         </is>
       </c>
       <c r="C513" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D513" s="5" t="inlineStr">
         <is>
-          <t>2:09:58</t>
+          <t>2:09:30</t>
         </is>
       </c>
       <c r="E513" s="5" t="inlineStr">
         <is>
-          <t>2:25:05</t>
+          <t>2:24:41</t>
         </is>
       </c>
     </row>
@@ -13324,16 +13324,16 @@
         </is>
       </c>
       <c r="C514" s="3" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D514" s="3" t="inlineStr">
         <is>
-          <t>2:09:04</t>
+          <t>2:09:58</t>
         </is>
       </c>
       <c r="E514" s="3" t="inlineStr">
         <is>
-          <t>2:23:09</t>
+          <t>2:25:05</t>
         </is>
       </c>
     </row>
@@ -13349,16 +13349,16 @@
         </is>
       </c>
       <c r="C515" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D515" s="5" t="inlineStr">
         <is>
-          <t>2:08:43</t>
+          <t>2:09:04</t>
         </is>
       </c>
       <c r="E515" s="5" t="inlineStr">
         <is>
-          <t>2:23:56</t>
+          <t>2:23:09</t>
         </is>
       </c>
     </row>
@@ -13374,16 +13374,16 @@
         </is>
       </c>
       <c r="C516" s="3" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D516" s="3" t="inlineStr">
         <is>
-          <t>2:09:15</t>
+          <t>2:08:43</t>
         </is>
       </c>
       <c r="E516" s="3" t="inlineStr">
         <is>
-          <t>2:25:53</t>
+          <t>2:23:56</t>
         </is>
       </c>
     </row>
@@ -13399,16 +13399,16 @@
         </is>
       </c>
       <c r="C517" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D517" s="5" t="inlineStr">
         <is>
-          <t>2:08:14</t>
+          <t>2:09:15</t>
         </is>
       </c>
       <c r="E517" s="5" t="inlineStr">
         <is>
-          <t>2:28:20</t>
+          <t>2:25:53</t>
         </is>
       </c>
     </row>
@@ -13424,16 +13424,16 @@
         </is>
       </c>
       <c r="C518" s="3" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D518" s="3" t="inlineStr">
         <is>
-          <t>2:05:06</t>
+          <t>2:08:14</t>
         </is>
       </c>
       <c r="E518" s="3" t="inlineStr">
         <is>
-          <t>2:23:15</t>
+          <t>2:28:20</t>
         </is>
       </c>
     </row>
@@ -13449,16 +13449,16 @@
         </is>
       </c>
       <c r="C519" s="5" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="D519" s="5" t="inlineStr">
         <is>
-          <t>2:08:24</t>
+          <t>2:05:06</t>
         </is>
       </c>
       <c r="E519" s="5" t="inlineStr">
         <is>
-          <t>2:25:07</t>
+          <t>2:23:15</t>
         </is>
       </c>
     </row>
@@ -13474,11 +13474,11 @@
         </is>
       </c>
       <c r="C520" s="3" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D520" s="3" t="inlineStr">
         <is>
-          <t>2:10:59</t>
+          <t>2:08:24</t>
         </is>
       </c>
       <c r="E520" s="3" t="inlineStr">
@@ -13499,16 +13499,16 @@
         </is>
       </c>
       <c r="C521" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D521" s="5" t="inlineStr">
         <is>
-          <t>2:10:34</t>
+          <t>2:10:59</t>
         </is>
       </c>
       <c r="E521" s="5" t="inlineStr">
         <is>
-          <t>2:24:25</t>
+          <t>2:25:07</t>
         </is>
       </c>
     </row>
@@ -13524,16 +13524,16 @@
         </is>
       </c>
       <c r="C522" s="3" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D522" s="3" t="inlineStr">
         <is>
-          <t>2:07:51</t>
+          <t>2:10:34</t>
         </is>
       </c>
       <c r="E522" s="3" t="inlineStr">
         <is>
-          <t>2:24:26</t>
+          <t>2:24:25</t>
         </is>
       </c>
     </row>
@@ -13549,16 +13549,16 @@
         </is>
       </c>
       <c r="C523" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D523" s="5" t="inlineStr">
         <is>
-          <t>2:10:53</t>
+          <t>2:07:51</t>
         </is>
       </c>
       <c r="E523" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:24:26</t>
         </is>
       </c>
     </row>
@@ -13574,16 +13574,16 @@
         </is>
       </c>
       <c r="C524" s="3" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D524" s="3" t="inlineStr">
         <is>
-          <t>2:05:59</t>
+          <t>2:10:53</t>
         </is>
       </c>
       <c r="E524" s="3" t="inlineStr">
         <is>
-          <t>2:22:48</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -13599,16 +13599,16 @@
         </is>
       </c>
       <c r="C525" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D525" s="5" t="inlineStr">
         <is>
-          <t>2:08:13</t>
+          <t>2:05:59</t>
         </is>
       </c>
       <c r="E525" s="5" t="inlineStr">
         <is>
-          <t>2:22:38</t>
+          <t>2:22:48</t>
         </is>
       </c>
     </row>
@@ -13624,16 +13624,16 @@
         </is>
       </c>
       <c r="C526" s="3" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D526" s="3" t="inlineStr">
         <is>
-          <t>2:08:22</t>
+          <t>2:08:13</t>
         </is>
       </c>
       <c r="E526" s="3" t="inlineStr">
         <is>
-          <t>2:22:39</t>
+          <t>2:22:38</t>
         </is>
       </c>
     </row>
@@ -13649,16 +13649,16 @@
         </is>
       </c>
       <c r="C527" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D527" s="5" t="inlineStr">
         <is>
-          <t>2:08:41</t>
+          <t>2:08:22</t>
         </is>
       </c>
       <c r="E527" s="5" t="inlineStr">
         <is>
-          <t>2:23:23</t>
+          <t>2:22:39</t>
         </is>
       </c>
     </row>
@@ -13674,16 +13674,16 @@
         </is>
       </c>
       <c r="C528" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D528" s="3" t="inlineStr">
         <is>
-          <t>2:04:58</t>
+          <t>2:08:41</t>
         </is>
       </c>
       <c r="E528" s="3" t="inlineStr">
         <is>
-          <t>2:27:23</t>
+          <t>2:23:23</t>
         </is>
       </c>
     </row>
@@ -13699,16 +13699,16 @@
         </is>
       </c>
       <c r="C529" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
-          <t>2:07:39</t>
+          <t>2:04:58</t>
         </is>
       </c>
       <c r="E529" s="5" t="inlineStr">
         <is>
-          <t>2:24:35</t>
+          <t>2:27:23</t>
         </is>
       </c>
     </row>
@@ -13724,23 +13724,23 @@
         </is>
       </c>
       <c r="C530" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D530" s="3" t="inlineStr">
         <is>
-          <t>2:08:09</t>
+          <t>2:07:39</t>
         </is>
       </c>
       <c r="E530" s="3" t="inlineStr">
         <is>
-          <t>2:19:51</t>
+          <t>2:24:35</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>TCS Sydney Marathon presented by ASICS</t>
+          <t>TCS New York City Marathon</t>
         </is>
       </c>
       <c r="B531" s="5" t="inlineStr">
@@ -13749,16 +13749,16 @@
         </is>
       </c>
       <c r="C531" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D531" s="5" t="inlineStr">
         <is>
-          <t>2:08:20</t>
+          <t>2:08:09</t>
         </is>
       </c>
       <c r="E531" s="5" t="inlineStr">
         <is>
-          <t>2:26:47</t>
+          <t>2:19:51</t>
         </is>
       </c>
     </row>
@@ -13774,16 +13774,16 @@
         </is>
       </c>
       <c r="C532" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D532" s="3" t="inlineStr">
         <is>
-          <t>2:06:17</t>
+          <t>2:08:20</t>
         </is>
       </c>
       <c r="E532" s="3" t="inlineStr">
         <is>
-          <t>2:21:40</t>
+          <t>2:26:47</t>
         </is>
       </c>
     </row>
@@ -13799,23 +13799,23 @@
         </is>
       </c>
       <c r="C533" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D533" s="5" t="inlineStr">
         <is>
-          <t>2:06:06</t>
+          <t>2:06:17</t>
         </is>
       </c>
       <c r="E533" s="5" t="inlineStr">
         <is>
-          <t>2:18:22</t>
+          <t>2:21:40</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon</t>
+          <t>TCS Sydney Marathon presented by ASICS</t>
         </is>
       </c>
       <c r="B534" s="3" t="inlineStr">
@@ -13824,16 +13824,16 @@
         </is>
       </c>
       <c r="C534" s="3" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D534" s="3" t="inlineStr">
         <is>
-          <t>2:09:20</t>
+          <t>2:06:06</t>
         </is>
       </c>
       <c r="E534" s="3" t="inlineStr">
         <is>
-          <t>2:23:11</t>
+          <t>2:18:22</t>
         </is>
       </c>
     </row>
@@ -13849,16 +13849,16 @@
         </is>
       </c>
       <c r="C535" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D535" s="5" t="inlineStr">
         <is>
-          <t>2:07:16</t>
+          <t>2:09:20</t>
         </is>
       </c>
       <c r="E535" s="5" t="inlineStr">
         <is>
-          <t>2:20:44</t>
+          <t>2:23:11</t>
         </is>
       </c>
     </row>
@@ -13874,23 +13874,23 @@
         </is>
       </c>
       <c r="C536" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D536" s="3" t="inlineStr">
         <is>
-          <t>2:08:05</t>
+          <t>2:07:16</t>
         </is>
       </c>
       <c r="E536" s="3" t="inlineStr">
         <is>
-          <t>2:21:04</t>
+          <t>2:20:44</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>Taipei Marathon</t>
+          <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
       <c r="B537" s="5" t="inlineStr">
@@ -13899,16 +13899,16 @@
         </is>
       </c>
       <c r="C537" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D537" s="5" t="inlineStr">
         <is>
-          <t>2:11:05</t>
+          <t>2:08:05</t>
         </is>
       </c>
       <c r="E537" s="5" t="inlineStr">
         <is>
-          <t>2:27:14</t>
+          <t>2:21:04</t>
         </is>
       </c>
     </row>
@@ -13924,16 +13924,16 @@
         </is>
       </c>
       <c r="C538" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D538" s="3" t="inlineStr">
         <is>
-          <t>2:11:41</t>
+          <t>2:11:05</t>
         </is>
       </c>
       <c r="E538" s="3" t="inlineStr">
         <is>
-          <t>2:32:47</t>
+          <t>2:27:14</t>
         </is>
       </c>
     </row>
@@ -13949,23 +13949,23 @@
         </is>
       </c>
       <c r="C539" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D539" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:11:41</t>
         </is>
       </c>
       <c r="E539" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:32:47</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon</t>
+          <t>Taipei Marathon</t>
         </is>
       </c>
       <c r="B540" s="3" t="inlineStr">
@@ -13974,16 +13974,16 @@
         </is>
       </c>
       <c r="C540" s="3" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D540" s="3" t="inlineStr">
         <is>
-          <t>2:07:32</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E540" s="3" t="inlineStr">
         <is>
-          <t>2:24:15</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -13999,16 +13999,16 @@
         </is>
       </c>
       <c r="C541" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D541" s="5" t="inlineStr">
         <is>
-          <t>2:07:50</t>
+          <t>2:07:32</t>
         </is>
       </c>
       <c r="E541" s="5" t="inlineStr">
         <is>
-          <t>2:26:06</t>
+          <t>2:24:15</t>
         </is>
       </c>
     </row>
@@ -14024,16 +14024,16 @@
         </is>
       </c>
       <c r="C542" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D542" s="3" t="inlineStr">
         <is>
-          <t>2:11:44</t>
+          <t>2:07:50</t>
         </is>
       </c>
       <c r="E542" s="3" t="inlineStr">
         <is>
-          <t>2:24:56</t>
+          <t>2:26:06</t>
         </is>
       </c>
     </row>
@@ -14049,23 +14049,23 @@
         </is>
       </c>
       <c r="C543" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D543" s="5" t="inlineStr">
         <is>
-          <t>2:09:55</t>
+          <t>2:11:44</t>
         </is>
       </c>
       <c r="E543" s="5" t="inlineStr">
         <is>
-          <t>2:25:13</t>
+          <t>2:24:56</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>Tokyo Marathon</t>
+          <t>Tata Mumbai Marathon</t>
         </is>
       </c>
       <c r="B544" s="3" t="inlineStr">
@@ -14074,16 +14074,16 @@
         </is>
       </c>
       <c r="C544" s="3" t="n">
-        <v>2007</v>
+        <v>2026</v>
       </c>
       <c r="D544" s="3" t="inlineStr">
         <is>
-          <t>2:09:45</t>
+          <t>2:09:55</t>
         </is>
       </c>
       <c r="E544" s="3" t="inlineStr">
         <is>
-          <t>2:35:28</t>
+          <t>2:25:13</t>
         </is>
       </c>
     </row>
@@ -14099,16 +14099,16 @@
         </is>
       </c>
       <c r="C545" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D545" s="5" t="inlineStr">
         <is>
-          <t>2:10:57</t>
+          <t>2:09:45</t>
         </is>
       </c>
       <c r="E545" s="5" t="inlineStr">
         <is>
-          <t>2:25:51</t>
+          <t>2:35:28</t>
         </is>
       </c>
     </row>
@@ -14124,16 +14124,16 @@
         </is>
       </c>
       <c r="C546" s="3" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D546" s="3" t="inlineStr">
         <is>
-          <t>2:10:25</t>
+          <t>2:10:57</t>
         </is>
       </c>
       <c r="E546" s="3" t="inlineStr">
         <is>
-          <t>2:25:38</t>
+          <t>2:25:51</t>
         </is>
       </c>
     </row>
@@ -14149,16 +14149,16 @@
         </is>
       </c>
       <c r="C547" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D547" s="5" t="inlineStr">
         <is>
-          <t>2:08:12</t>
+          <t>2:10:25</t>
         </is>
       </c>
       <c r="E547" s="5" t="inlineStr">
         <is>
-          <t>2:25:27</t>
+          <t>2:25:38</t>
         </is>
       </c>
     </row>
@@ -14174,16 +14174,16 @@
         </is>
       </c>
       <c r="C548" s="3" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D548" s="3" t="inlineStr">
         <is>
-          <t>2:07:32</t>
+          <t>2:08:12</t>
         </is>
       </c>
       <c r="E548" s="3" t="inlineStr">
         <is>
-          <t>2:26:49</t>
+          <t>2:25:27</t>
         </is>
       </c>
     </row>
@@ -14199,16 +14199,16 @@
         </is>
       </c>
       <c r="C549" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D549" s="5" t="inlineStr">
         <is>
-          <t>2:07:37</t>
+          <t>2:07:32</t>
         </is>
       </c>
       <c r="E549" s="5" t="inlineStr">
         <is>
-          <t>2:25:28</t>
+          <t>2:26:49</t>
         </is>
       </c>
     </row>
@@ -14224,16 +14224,16 @@
         </is>
       </c>
       <c r="C550" s="3" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D550" s="3" t="inlineStr">
         <is>
-          <t>2:06:50</t>
+          <t>2:07:37</t>
         </is>
       </c>
       <c r="E550" s="3" t="inlineStr">
         <is>
-          <t>2:25:34</t>
+          <t>2:25:28</t>
         </is>
       </c>
     </row>
@@ -14249,16 +14249,16 @@
         </is>
       </c>
       <c r="C551" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D551" s="5" t="inlineStr">
         <is>
-          <t>2:05:42</t>
+          <t>2:06:50</t>
         </is>
       </c>
       <c r="E551" s="5" t="inlineStr">
         <is>
-          <t>2:22:23</t>
+          <t>2:25:34</t>
         </is>
       </c>
     </row>
@@ -14274,16 +14274,16 @@
         </is>
       </c>
       <c r="C552" s="3" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D552" s="3" t="inlineStr">
         <is>
-          <t>2:06:00</t>
+          <t>2:05:42</t>
         </is>
       </c>
       <c r="E552" s="3" t="inlineStr">
         <is>
-          <t>2:23:15</t>
+          <t>2:22:23</t>
         </is>
       </c>
     </row>
@@ -14299,16 +14299,16 @@
         </is>
       </c>
       <c r="C553" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D553" s="5" t="inlineStr">
         <is>
-          <t>2:06:56</t>
+          <t>2:06:00</t>
         </is>
       </c>
       <c r="E553" s="5" t="inlineStr">
         <is>
-          <t>2:21:27</t>
+          <t>2:23:15</t>
         </is>
       </c>
     </row>
@@ -14324,16 +14324,16 @@
         </is>
       </c>
       <c r="C554" s="3" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D554" s="3" t="inlineStr">
         <is>
-          <t>2:03:58</t>
+          <t>2:06:56</t>
         </is>
       </c>
       <c r="E554" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:21:27</t>
         </is>
       </c>
     </row>
@@ -14349,16 +14349,16 @@
         </is>
       </c>
       <c r="C555" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D555" s="5" t="inlineStr">
         <is>
-          <t>2:05:30</t>
+          <t>2:03:58</t>
         </is>
       </c>
       <c r="E555" s="5" t="inlineStr">
         <is>
-          <t>2:19:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -14374,16 +14374,16 @@
         </is>
       </c>
       <c r="C556" s="3" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D556" s="3" t="inlineStr">
         <is>
-          <t>2:04:15</t>
+          <t>2:05:30</t>
         </is>
       </c>
       <c r="E556" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:19:51</t>
         </is>
       </c>
     </row>
@@ -14399,7 +14399,7 @@
         </is>
       </c>
       <c r="C557" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D557" s="5" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="E557" s="5" t="inlineStr">
         <is>
-          <t>2:17:45</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -14424,16 +14424,16 @@
         </is>
       </c>
       <c r="C558" s="3" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D558" s="3" t="inlineStr">
         <is>
-          <t>2:02:40</t>
+          <t>2:04:15</t>
         </is>
       </c>
       <c r="E558" s="3" t="inlineStr">
         <is>
-          <t>2:16:02</t>
+          <t>2:17:45</t>
         </is>
       </c>
     </row>
@@ -14449,16 +14449,16 @@
         </is>
       </c>
       <c r="C559" s="5" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D559" s="5" t="inlineStr">
         <is>
-          <t>2:05:22</t>
+          <t>2:02:40</t>
         </is>
       </c>
       <c r="E559" s="5" t="inlineStr">
         <is>
-          <t>2:16:28</t>
+          <t>2:16:02</t>
         </is>
       </c>
     </row>
@@ -14474,16 +14474,16 @@
         </is>
       </c>
       <c r="C560" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D560" s="3" t="inlineStr">
         <is>
-          <t>2:02:16</t>
+          <t>2:05:22</t>
         </is>
       </c>
       <c r="E560" s="3" t="inlineStr">
         <is>
-          <t>2:15:55</t>
+          <t>2:16:28</t>
         </is>
       </c>
     </row>
@@ -14499,16 +14499,16 @@
         </is>
       </c>
       <c r="C561" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D561" s="5" t="inlineStr">
         <is>
-          <t>2:03:23</t>
+          <t>2:02:16</t>
         </is>
       </c>
       <c r="E561" s="5" t="inlineStr">
         <is>
-          <t>2:16:31</t>
+          <t>2:15:55</t>
         </is>
       </c>
     </row>
@@ -14524,23 +14524,23 @@
         </is>
       </c>
       <c r="C562" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D562" s="3" t="inlineStr">
         <is>
-          <t>2:03:37</t>
+          <t>2:03:23</t>
         </is>
       </c>
       <c r="E562" s="3" t="inlineStr">
         <is>
-          <t>2:14:29</t>
+          <t>2:16:31</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
+          <t>Tokyo Marathon</t>
         </is>
       </c>
       <c r="B563" s="5" t="inlineStr">
@@ -14549,16 +14549,16 @@
         </is>
       </c>
       <c r="C563" s="5" t="n">
-        <v>2008</v>
+        <v>2026</v>
       </c>
       <c r="D563" s="5" t="inlineStr">
         <is>
-          <t>2:12:27</t>
+          <t>2:03:37</t>
         </is>
       </c>
       <c r="E563" s="5" t="inlineStr">
         <is>
-          <t>2:36:27</t>
+          <t>2:14:29</t>
         </is>
       </c>
     </row>
@@ -14574,16 +14574,16 @@
         </is>
       </c>
       <c r="C564" s="3" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D564" s="3" t="inlineStr">
         <is>
-          <t>2:12:09</t>
+          <t>2:12:27</t>
         </is>
       </c>
       <c r="E564" s="3" t="inlineStr">
         <is>
-          <t>2:35:33</t>
+          <t>2:36:27</t>
         </is>
       </c>
     </row>
@@ -14599,16 +14599,16 @@
         </is>
       </c>
       <c r="C565" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D565" s="5" t="inlineStr">
         <is>
-          <t>2:09:52</t>
+          <t>2:12:09</t>
         </is>
       </c>
       <c r="E565" s="5" t="inlineStr">
         <is>
-          <t>2:33:08</t>
+          <t>2:35:33</t>
         </is>
       </c>
     </row>
@@ -14624,16 +14624,16 @@
         </is>
       </c>
       <c r="C566" s="3" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D566" s="3" t="inlineStr">
         <is>
-          <t>2:10:36</t>
+          <t>2:09:52</t>
         </is>
       </c>
       <c r="E566" s="3" t="inlineStr">
         <is>
-          <t>2:35:39</t>
+          <t>2:33:08</t>
         </is>
       </c>
     </row>
@@ -14649,16 +14649,16 @@
         </is>
       </c>
       <c r="C567" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D567" s="5" t="inlineStr">
         <is>
-          <t>2:09:09</t>
+          <t>2:10:36</t>
         </is>
       </c>
       <c r="E567" s="5" t="inlineStr">
         <is>
-          <t>2:31:35</t>
+          <t>2:35:39</t>
         </is>
       </c>
     </row>
@@ -14674,16 +14674,16 @@
         </is>
       </c>
       <c r="C568" s="3" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D568" s="3" t="inlineStr">
         <is>
-          <t>2:09:48</t>
+          <t>2:09:09</t>
         </is>
       </c>
       <c r="E568" s="3" t="inlineStr">
         <is>
-          <t>2:32:47</t>
+          <t>2:31:35</t>
         </is>
       </c>
     </row>
@@ -14699,16 +14699,16 @@
         </is>
       </c>
       <c r="C569" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D569" s="5" t="inlineStr">
         <is>
-          <t>2:10:42</t>
+          <t>2:09:48</t>
         </is>
       </c>
       <c r="E569" s="5" t="inlineStr">
         <is>
-          <t>2:30:54</t>
+          <t>2:32:47</t>
         </is>
       </c>
     </row>
@@ -14724,16 +14724,16 @@
         </is>
       </c>
       <c r="C570" s="3" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D570" s="3" t="inlineStr">
         <is>
-          <t>2:06:13</t>
+          <t>2:10:42</t>
         </is>
       </c>
       <c r="E570" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:30:54</t>
         </is>
       </c>
     </row>
@@ -14749,11 +14749,11 @@
         </is>
       </c>
       <c r="C571" s="5" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D571" s="5" t="inlineStr">
         <is>
-          <t>2:03:00</t>
+          <t>2:06:13</t>
         </is>
       </c>
       <c r="E571" s="5" t="inlineStr">
@@ -14774,16 +14774,16 @@
         </is>
       </c>
       <c r="C572" s="3" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D572" s="3" t="inlineStr">
         <is>
-          <t>2:01:53</t>
+          <t>2:03:00</t>
         </is>
       </c>
       <c r="E572" s="3" t="inlineStr">
         <is>
-          <t>2:14:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -14799,16 +14799,16 @@
         </is>
       </c>
       <c r="C573" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D573" s="5" t="inlineStr">
         <is>
-          <t>2:01:48</t>
+          <t>2:01:53</t>
         </is>
       </c>
       <c r="E573" s="5" t="inlineStr">
         <is>
-          <t>2:15:51</t>
+          <t>2:14:57</t>
         </is>
       </c>
     </row>
@@ -14824,16 +14824,16 @@
         </is>
       </c>
       <c r="C574" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D574" s="3" t="inlineStr">
         <is>
-          <t>2:02:05</t>
+          <t>2:01:48</t>
         </is>
       </c>
       <c r="E574" s="3" t="inlineStr">
         <is>
-          <t>2:16:49</t>
+          <t>2:15:51</t>
         </is>
       </c>
     </row>
@@ -14849,23 +14849,23 @@
         </is>
       </c>
       <c r="C575" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D575" s="5" t="inlineStr">
         <is>
-          <t>2:02:24</t>
+          <t>2:02:05</t>
         </is>
       </c>
       <c r="E575" s="5" t="inlineStr">
         <is>
-          <t>2:14:00</t>
+          <t>2:16:49</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>Vienna City Marathon</t>
+          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B576" s="3" t="inlineStr">
@@ -14874,16 +14874,16 @@
         </is>
       </c>
       <c r="C576" s="3" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D576" s="3" t="inlineStr">
         <is>
-          <t>2:10:24</t>
+          <t>2:02:24</t>
         </is>
       </c>
       <c r="E576" s="3" t="inlineStr">
         <is>
-          <t>2:23:47</t>
+          <t>2:14:00</t>
         </is>
       </c>
     </row>
@@ -14899,16 +14899,16 @@
         </is>
       </c>
       <c r="C577" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D577" s="5" t="inlineStr">
         <is>
-          <t>2:12:20</t>
+          <t>2:10:24</t>
         </is>
       </c>
       <c r="E577" s="5" t="inlineStr">
         <is>
-          <t>2:31:46</t>
+          <t>2:23:47</t>
         </is>
       </c>
     </row>
@@ -14924,16 +14924,16 @@
         </is>
       </c>
       <c r="C578" s="3" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D578" s="3" t="inlineStr">
         <is>
-          <t>2:10:18</t>
+          <t>2:12:20</t>
         </is>
       </c>
       <c r="E578" s="3" t="inlineStr">
         <is>
-          <t>2:30:41</t>
+          <t>2:31:46</t>
         </is>
       </c>
     </row>
@@ -14949,16 +14949,16 @@
         </is>
       </c>
       <c r="C579" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D579" s="5" t="inlineStr">
         <is>
-          <t>2:10:28</t>
+          <t>2:10:18</t>
         </is>
       </c>
       <c r="E579" s="5" t="inlineStr">
         <is>
-          <t>2:29:31</t>
+          <t>2:30:41</t>
         </is>
       </c>
     </row>
@@ -14974,16 +14974,16 @@
         </is>
       </c>
       <c r="C580" s="3" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D580" s="3" t="inlineStr">
         <is>
-          <t>2:10:41</t>
+          <t>2:10:28</t>
         </is>
       </c>
       <c r="E580" s="3" t="inlineStr">
         <is>
-          <t>2:29:24</t>
+          <t>2:29:31</t>
         </is>
       </c>
     </row>
@@ -14999,16 +14999,16 @@
         </is>
       </c>
       <c r="C581" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D581" s="5" t="inlineStr">
         <is>
-          <t>2:12:22</t>
+          <t>2:10:41</t>
         </is>
       </c>
       <c r="E581" s="5" t="inlineStr">
         <is>
-          <t>2:27:33</t>
+          <t>2:29:24</t>
         </is>
       </c>
     </row>
@@ -15024,16 +15024,16 @@
         </is>
       </c>
       <c r="C582" s="3" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D582" s="3" t="inlineStr">
         <is>
-          <t>2:12:09</t>
+          <t>2:12:22</t>
         </is>
       </c>
       <c r="E582" s="3" t="inlineStr">
         <is>
-          <t>2:29:19</t>
+          <t>2:27:33</t>
         </is>
       </c>
     </row>
@@ -15049,16 +15049,16 @@
         </is>
       </c>
       <c r="C583" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D583" s="5" t="inlineStr">
         <is>
-          <t>2:08:50</t>
+          <t>2:12:09</t>
         </is>
       </c>
       <c r="E583" s="5" t="inlineStr">
         <is>
-          <t>2:30:09</t>
+          <t>2:29:19</t>
         </is>
       </c>
     </row>
@@ -15074,16 +15074,16 @@
         </is>
       </c>
       <c r="C584" s="3" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D584" s="3" t="inlineStr">
         <is>
-          <t>2:07:38</t>
+          <t>2:08:50</t>
         </is>
       </c>
       <c r="E584" s="3" t="inlineStr">
         <is>
-          <t>2:25:47</t>
+          <t>2:30:09</t>
         </is>
       </c>
     </row>
@@ -15099,16 +15099,16 @@
         </is>
       </c>
       <c r="C585" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D585" s="5" t="inlineStr">
         <is>
-          <t>2:08:21</t>
+          <t>2:07:38</t>
         </is>
       </c>
       <c r="E585" s="5" t="inlineStr">
         <is>
-          <t>2:30:43</t>
+          <t>2:25:47</t>
         </is>
       </c>
     </row>
@@ -15124,16 +15124,16 @@
         </is>
       </c>
       <c r="C586" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D586" s="3" t="inlineStr">
         <is>
-          <t>2:08:40</t>
+          <t>2:08:21</t>
         </is>
       </c>
       <c r="E586" s="3" t="inlineStr">
         <is>
-          <t>2:31:08</t>
+          <t>2:30:43</t>
         </is>
       </c>
     </row>
@@ -15149,16 +15149,16 @@
         </is>
       </c>
       <c r="C587" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D587" s="5" t="inlineStr">
         <is>
-          <t>2:08:29</t>
+          <t>2:08:40</t>
         </is>
       </c>
       <c r="E587" s="5" t="inlineStr">
         <is>
-          <t>2:26:21</t>
+          <t>2:31:08</t>
         </is>
       </c>
     </row>
@@ -15174,16 +15174,16 @@
         </is>
       </c>
       <c r="C588" s="3" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D588" s="3" t="inlineStr">
         <is>
-          <t>2:06:58</t>
+          <t>2:08:29</t>
         </is>
       </c>
       <c r="E588" s="3" t="inlineStr">
         <is>
-          <t>2:26:39</t>
+          <t>2:26:21</t>
         </is>
       </c>
     </row>
@@ -15199,16 +15199,16 @@
         </is>
       </c>
       <c r="C589" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D589" s="5" t="inlineStr">
         <is>
-          <t>2:08:40</t>
+          <t>2:06:58</t>
         </is>
       </c>
       <c r="E589" s="5" t="inlineStr">
         <is>
-          <t>2:31:08</t>
+          <t>2:26:39</t>
         </is>
       </c>
     </row>
@@ -15224,16 +15224,16 @@
         </is>
       </c>
       <c r="C590" s="3" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D590" s="3" t="inlineStr">
         <is>
-          <t>2:05:41</t>
+          <t>2:08:40</t>
         </is>
       </c>
       <c r="E590" s="3" t="inlineStr">
         <is>
-          <t>2:28:59</t>
+          <t>2:31:08</t>
         </is>
       </c>
     </row>
@@ -15249,16 +15249,16 @@
         </is>
       </c>
       <c r="C591" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D591" s="5" t="inlineStr">
         <is>
-          <t>2:07:31</t>
+          <t>2:05:41</t>
         </is>
       </c>
       <c r="E591" s="5" t="inlineStr">
         <is>
-          <t>2:30:09</t>
+          <t>2:28:59</t>
         </is>
       </c>
     </row>
@@ -15274,16 +15274,16 @@
         </is>
       </c>
       <c r="C592" s="3" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="D592" s="3" t="inlineStr">
         <is>
-          <t>2:08:40</t>
+          <t>2:07:31</t>
         </is>
       </c>
       <c r="E592" s="3" t="inlineStr">
         <is>
-          <t>2:24:20</t>
+          <t>2:30:09</t>
         </is>
       </c>
     </row>
@@ -15299,16 +15299,16 @@
         </is>
       </c>
       <c r="C593" s="5" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="D593" s="5" t="inlineStr">
         <is>
-          <t>2:06:56</t>
+          <t>2:08:40</t>
         </is>
       </c>
       <c r="E593" s="5" t="inlineStr">
         <is>
-          <t>2:22:12</t>
+          <t>2:24:20</t>
         </is>
       </c>
     </row>
@@ -15324,16 +15324,16 @@
         </is>
       </c>
       <c r="C594" s="3" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D594" s="3" t="inlineStr">
         <is>
-          <t>2:09:25</t>
+          <t>2:06:56</t>
         </is>
       </c>
       <c r="E594" s="3" t="inlineStr">
         <is>
-          <t>2:24:29</t>
+          <t>2:22:12</t>
         </is>
       </c>
     </row>
@@ -15349,16 +15349,16 @@
         </is>
       </c>
       <c r="C595" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D595" s="5" t="inlineStr">
         <is>
-          <t>2:06:53</t>
+          <t>2:09:25</t>
         </is>
       </c>
       <c r="E595" s="5" t="inlineStr">
         <is>
-          <t>2:20:59</t>
+          <t>2:24:29</t>
         </is>
       </c>
     </row>
@@ -15374,16 +15374,16 @@
         </is>
       </c>
       <c r="C596" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D596" s="3" t="inlineStr">
         <is>
-          <t>2:05:08</t>
+          <t>2:06:53</t>
         </is>
       </c>
       <c r="E596" s="3" t="inlineStr">
         <is>
-          <t>2:24:12</t>
+          <t>2:20:59</t>
         </is>
       </c>
     </row>
@@ -15399,16 +15399,16 @@
         </is>
       </c>
       <c r="C597" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D597" s="5" t="inlineStr">
         <is>
-          <t>2:06:35</t>
+          <t>2:05:08</t>
         </is>
       </c>
       <c r="E597" s="5" t="inlineStr">
         <is>
-          <t>2:24:08</t>
+          <t>2:24:12</t>
         </is>
       </c>
     </row>
@@ -15424,23 +15424,23 @@
         </is>
       </c>
       <c r="C598" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D598" s="3" t="inlineStr">
         <is>
-          <t>2:08:28</t>
+          <t>2:06:35</t>
         </is>
       </c>
       <c r="E598" s="3" t="inlineStr">
         <is>
-          <t>2:24:14</t>
+          <t>2:24:08</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="4" t="inlineStr">
         <is>
-          <t>Zurich Marató de Barcelona</t>
+          <t>Vienna City Marathon</t>
         </is>
       </c>
       <c r="B599" s="5" t="inlineStr">
@@ -15449,16 +15449,16 @@
         </is>
       </c>
       <c r="C599" s="5" t="n">
-        <v>2006</v>
+        <v>2025</v>
       </c>
       <c r="D599" s="5" t="inlineStr">
         <is>
-          <t>2:11:44</t>
+          <t>2:08:28</t>
         </is>
       </c>
       <c r="E599" s="5" t="inlineStr">
         <is>
-          <t>2:36:04</t>
+          <t>2:24:14</t>
         </is>
       </c>
     </row>
@@ -15474,16 +15474,16 @@
         </is>
       </c>
       <c r="C600" s="3" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D600" s="3" t="inlineStr">
         <is>
-          <t>2:12:56</t>
+          <t>2:11:44</t>
         </is>
       </c>
       <c r="E600" s="3" t="inlineStr">
         <is>
-          <t>2:37:40</t>
+          <t>2:36:04</t>
         </is>
       </c>
     </row>
@@ -15499,16 +15499,16 @@
         </is>
       </c>
       <c r="C601" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D601" s="5" t="inlineStr">
         <is>
-          <t>2:10:55</t>
+          <t>2:12:56</t>
         </is>
       </c>
       <c r="E601" s="5" t="inlineStr">
         <is>
-          <t>2:34:03</t>
+          <t>2:37:40</t>
         </is>
       </c>
     </row>
@@ -15524,16 +15524,16 @@
         </is>
       </c>
       <c r="C602" s="3" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D602" s="3" t="inlineStr">
         <is>
-          <t>2:10:22</t>
+          <t>2:10:55</t>
         </is>
       </c>
       <c r="E602" s="3" t="inlineStr">
         <is>
-          <t>2:33:19</t>
+          <t>2:34:03</t>
         </is>
       </c>
     </row>
@@ -15549,16 +15549,16 @@
         </is>
       </c>
       <c r="C603" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D603" s="5" t="inlineStr">
         <is>
-          <t>2:07:30</t>
+          <t>2:10:22</t>
         </is>
       </c>
       <c r="E603" s="5" t="inlineStr">
         <is>
-          <t>2:31:51</t>
+          <t>2:33:19</t>
         </is>
       </c>
     </row>
@@ -15574,16 +15574,16 @@
         </is>
       </c>
       <c r="C604" s="3" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D604" s="3" t="inlineStr">
         <is>
-          <t>2:07:47</t>
+          <t>2:07:30</t>
         </is>
       </c>
       <c r="E604" s="3" t="inlineStr">
         <is>
-          <t>2:28:47</t>
+          <t>2:31:51</t>
         </is>
       </c>
     </row>
@@ -15599,16 +15599,16 @@
         </is>
       </c>
       <c r="C605" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D605" s="5" t="inlineStr">
         <is>
-          <t>2:10:06</t>
+          <t>2:07:47</t>
         </is>
       </c>
       <c r="E605" s="5" t="inlineStr">
         <is>
-          <t>2:33:10</t>
+          <t>2:28:47</t>
         </is>
       </c>
     </row>
@@ -15624,16 +15624,16 @@
         </is>
       </c>
       <c r="C606" s="3" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D606" s="3" t="inlineStr">
         <is>
-          <t>2:09:36</t>
+          <t>2:10:06</t>
         </is>
       </c>
       <c r="E606" s="3" t="inlineStr">
         <is>
-          <t>2:31:10</t>
+          <t>2:33:10</t>
         </is>
       </c>
     </row>
@@ -15649,16 +15649,16 @@
         </is>
       </c>
       <c r="C607" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D607" s="5" t="inlineStr">
         <is>
-          <t>2:09:41</t>
+          <t>2:09:36</t>
         </is>
       </c>
       <c r="E607" s="5" t="inlineStr">
         <is>
-          <t>2:29:10</t>
+          <t>2:31:10</t>
         </is>
       </c>
     </row>
@@ -15674,16 +15674,16 @@
         </is>
       </c>
       <c r="C608" s="3" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D608" s="3" t="inlineStr">
         <is>
-          <t>2:05:06</t>
+          <t>2:09:41</t>
         </is>
       </c>
       <c r="E608" s="3" t="inlineStr">
         <is>
-          <t>2:19:44</t>
+          <t>2:29:10</t>
         </is>
       </c>
     </row>
@@ -15699,16 +15699,16 @@
         </is>
       </c>
       <c r="C609" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D609" s="5" t="inlineStr">
         <is>
-          <t>2:05:01</t>
+          <t>2:05:06</t>
         </is>
       </c>
       <c r="E609" s="5" t="inlineStr">
         <is>
-          <t>2:19:52</t>
+          <t>2:19:44</t>
         </is>
       </c>
     </row>
@@ -15724,16 +15724,16 @@
         </is>
       </c>
       <c r="C610" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D610" s="3" t="inlineStr">
         <is>
-          <t>2:04:13</t>
+          <t>2:05:01</t>
         </is>
       </c>
       <c r="E610" s="3" t="inlineStr">
         <is>
-          <t>2:19:33</t>
+          <t>2:19:52</t>
         </is>
       </c>
     </row>
@@ -15749,23 +15749,23 @@
         </is>
       </c>
       <c r="C611" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D611" s="5" t="inlineStr">
         <is>
-          <t>2:04:57</t>
+          <t>2:04:13</t>
         </is>
       </c>
       <c r="E611" s="5" t="inlineStr">
         <is>
-          <t>2:10:53</t>
+          <t>2:19:33</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="inlineStr">
         <is>
-          <t>Zurich Maratón de Sevilla</t>
+          <t>Zurich Marató de Barcelona</t>
         </is>
       </c>
       <c r="B612" s="3" t="inlineStr">
@@ -15774,16 +15774,16 @@
         </is>
       </c>
       <c r="C612" s="3" t="n">
-        <v>2009</v>
+        <v>2026</v>
       </c>
       <c r="D612" s="3" t="inlineStr">
         <is>
-          <t>2:11:51</t>
+          <t>2:04:57</t>
         </is>
       </c>
       <c r="E612" s="3" t="inlineStr">
         <is>
-          <t>2:26:03</t>
+          <t>2:10:53</t>
         </is>
       </c>
     </row>
@@ -15799,16 +15799,16 @@
         </is>
       </c>
       <c r="C613" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D613" s="5" t="inlineStr">
         <is>
-          <t>2:09:53</t>
+          <t>2:11:51</t>
         </is>
       </c>
       <c r="E613" s="5" t="inlineStr">
         <is>
-          <t>2:30:55</t>
+          <t>2:26:03</t>
         </is>
       </c>
     </row>
@@ -15824,16 +15824,16 @@
         </is>
       </c>
       <c r="C614" s="3" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D614" s="3" t="inlineStr">
         <is>
-          <t>2:10:26</t>
+          <t>2:09:53</t>
         </is>
       </c>
       <c r="E614" s="3" t="inlineStr">
         <is>
-          <t>2:33:10</t>
+          <t>2:30:55</t>
         </is>
       </c>
     </row>
@@ -15849,16 +15849,16 @@
         </is>
       </c>
       <c r="C615" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D615" s="5" t="inlineStr">
         <is>
-          <t>2:10:19</t>
+          <t>2:10:26</t>
         </is>
       </c>
       <c r="E615" s="5" t="inlineStr">
         <is>
-          <t>2:33:41</t>
+          <t>2:33:10</t>
         </is>
       </c>
     </row>
@@ -15874,16 +15874,16 @@
         </is>
       </c>
       <c r="C616" s="3" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D616" s="3" t="inlineStr">
         <is>
-          <t>2:11:26</t>
+          <t>2:10:19</t>
         </is>
       </c>
       <c r="E616" s="3" t="inlineStr">
         <is>
-          <t>2:33:44</t>
+          <t>2:33:41</t>
         </is>
       </c>
     </row>
@@ -15899,16 +15899,16 @@
         </is>
       </c>
       <c r="C617" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D617" s="5" t="inlineStr">
         <is>
-          <t>2:08:33</t>
+          <t>2:11:26</t>
         </is>
       </c>
       <c r="E617" s="5" t="inlineStr">
         <is>
-          <t>2:28:39</t>
+          <t>2:33:44</t>
         </is>
       </c>
     </row>
@@ -15924,16 +15924,16 @@
         </is>
       </c>
       <c r="C618" s="3" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D618" s="3" t="inlineStr">
         <is>
-          <t>2:04:59</t>
+          <t>2:08:33</t>
         </is>
       </c>
       <c r="E618" s="3" t="inlineStr">
         <is>
-          <t>2:20:29</t>
+          <t>2:28:39</t>
         </is>
       </c>
     </row>
@@ -15949,16 +15949,16 @@
         </is>
       </c>
       <c r="C619" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D619" s="5" t="inlineStr">
         <is>
-          <t>2:03:27</t>
+          <t>2:04:59</t>
         </is>
       </c>
       <c r="E619" s="5" t="inlineStr">
         <is>
-          <t>2:22:13</t>
+          <t>2:20:29</t>
         </is>
       </c>
     </row>
@@ -15974,16 +15974,16 @@
         </is>
       </c>
       <c r="C620" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D620" s="3" t="inlineStr">
         <is>
-          <t>2:05:15</t>
+          <t>2:03:27</t>
         </is>
       </c>
       <c r="E620" s="3" t="inlineStr">
         <is>
-          <t>2:22:17</t>
+          <t>2:22:13</t>
         </is>
       </c>
     </row>
@@ -15999,23 +15999,23 @@
         </is>
       </c>
       <c r="C621" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D621" s="5" t="inlineStr">
         <is>
-          <t>2:03:59</t>
+          <t>2:05:15</t>
         </is>
       </c>
       <c r="E621" s="5" t="inlineStr">
         <is>
-          <t>2:20:39</t>
+          <t>2:22:17</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="2" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
+          <t>Zurich Maratón de Sevilla</t>
         </is>
       </c>
       <c r="B622" s="3" t="inlineStr">
@@ -16024,16 +16024,16 @@
         </is>
       </c>
       <c r="C622" s="3" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D622" s="3" t="inlineStr">
         <is>
-          <t>2:10:29</t>
+          <t>2:03:59</t>
         </is>
       </c>
       <c r="E622" s="3" t="inlineStr">
         <is>
-          <t>2:26:31</t>
+          <t>2:20:39</t>
         </is>
       </c>
     </row>
@@ -16049,16 +16049,16 @@
         </is>
       </c>
       <c r="C623" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D623" s="5" t="inlineStr">
         <is>
-          <t>2:08:05</t>
+          <t>2:10:29</t>
         </is>
       </c>
       <c r="E623" s="5" t="inlineStr">
         <is>
-          <t>2:26:19</t>
+          <t>2:26:31</t>
         </is>
       </c>
     </row>
@@ -16074,28 +16074,28 @@
         </is>
       </c>
       <c r="C624" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D624" s="3" t="inlineStr">
         <is>
-          <t>2:09:11</t>
+          <t>2:08:05</t>
         </is>
       </c>
       <c r="E624" s="3" t="inlineStr">
         <is>
-          <t>2:25:55</t>
+          <t>2:26:19</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
         <is>
-          <t>21K de Montréal</t>
+          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
         </is>
       </c>
       <c r="B625" s="5" t="inlineStr">
         <is>
-          <t>21K</t>
+          <t>42K</t>
         </is>
       </c>
       <c r="C625" s="5" t="n">
@@ -16103,19 +16103,19 @@
       </c>
       <c r="D625" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:09:11</t>
         </is>
       </c>
       <c r="E625" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:25:55</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="6" t="inlineStr">
         <is>
-          <t>AJ Bell Great Bristol Run</t>
+          <t>21K de Montréal</t>
         </is>
       </c>
       <c r="B626" s="7" t="inlineStr">
@@ -16124,16 +16124,16 @@
         </is>
       </c>
       <c r="C626" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D626" s="7" t="inlineStr">
         <is>
-          <t>1:07:50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E626" s="7" t="inlineStr">
         <is>
-          <t>1:18:15</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16149,23 +16149,23 @@
         </is>
       </c>
       <c r="C627" s="5" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D627" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:50</t>
         </is>
       </c>
       <c r="E627" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:18:15</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="6" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run</t>
+          <t>AJ Bell Great Bristol Run</t>
         </is>
       </c>
       <c r="B628" s="7" t="inlineStr">
@@ -16174,16 +16174,16 @@
         </is>
       </c>
       <c r="C628" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D628" s="7" t="inlineStr">
         <is>
-          <t>1:10:25</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E628" s="7" t="inlineStr">
         <is>
-          <t>1:21:56</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16199,23 +16199,23 @@
         </is>
       </c>
       <c r="C629" s="5" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D629" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:25</t>
         </is>
       </c>
       <c r="E629" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:21:56</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="6" t="inlineStr">
         <is>
-          <t>AJ Bell Great North Run</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B630" s="7" t="inlineStr">
@@ -16224,16 +16224,16 @@
         </is>
       </c>
       <c r="C630" s="7" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D630" s="7" t="inlineStr">
         <is>
-          <t>1:01:57</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E630" s="7" t="inlineStr">
         <is>
-          <t>1:08:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16249,16 +16249,16 @@
         </is>
       </c>
       <c r="C631" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D631" s="5" t="inlineStr">
         <is>
-          <t>1:00:30</t>
+          <t>1:01:57</t>
         </is>
       </c>
       <c r="E631" s="5" t="inlineStr">
         <is>
-          <t>1:08:40</t>
+          <t>1:08:49</t>
         </is>
       </c>
     </row>
@@ -16274,16 +16274,16 @@
         </is>
       </c>
       <c r="C632" s="7" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D632" s="7" t="inlineStr">
         <is>
-          <t>0:59:58</t>
+          <t>1:00:30</t>
         </is>
       </c>
       <c r="E632" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:40</t>
         </is>
       </c>
     </row>
@@ -16299,16 +16299,16 @@
         </is>
       </c>
       <c r="C633" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D633" s="5" t="inlineStr">
         <is>
-          <t>1:00:01</t>
+          <t>0:59:58</t>
         </is>
       </c>
       <c r="E633" s="5" t="inlineStr">
         <is>
-          <t>1:05:40</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16324,16 +16324,16 @@
         </is>
       </c>
       <c r="C634" s="7" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D634" s="7" t="inlineStr">
         <is>
-          <t>0:59:37</t>
+          <t>1:00:01</t>
         </is>
       </c>
       <c r="E634" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:40</t>
         </is>
       </c>
     </row>
@@ -16349,11 +16349,11 @@
         </is>
       </c>
       <c r="C635" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D635" s="5" t="inlineStr">
         <is>
-          <t>0:59:05</t>
+          <t>0:59:37</t>
         </is>
       </c>
       <c r="E635" s="5" t="inlineStr">
@@ -16374,11 +16374,11 @@
         </is>
       </c>
       <c r="C636" s="7" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D636" s="7" t="inlineStr">
         <is>
-          <t>1:01:04</t>
+          <t>0:59:05</t>
         </is>
       </c>
       <c r="E636" s="7" t="inlineStr">
@@ -16399,16 +16399,16 @@
         </is>
       </c>
       <c r="C637" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D637" s="5" t="inlineStr">
         <is>
-          <t>1:00:08</t>
+          <t>1:01:04</t>
         </is>
       </c>
       <c r="E637" s="5" t="inlineStr">
         <is>
-          <t>1:06:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16424,16 +16424,16 @@
         </is>
       </c>
       <c r="C638" s="7" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D638" s="7" t="inlineStr">
         <is>
-          <t>0:59:45</t>
+          <t>1:00:08</t>
         </is>
       </c>
       <c r="E638" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:57</t>
         </is>
       </c>
     </row>
@@ -16449,11 +16449,11 @@
         </is>
       </c>
       <c r="C639" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D639" s="5" t="inlineStr">
         <is>
-          <t>0:59:32</t>
+          <t>0:59:45</t>
         </is>
       </c>
       <c r="E639" s="5" t="inlineStr">
@@ -16474,11 +16474,11 @@
         </is>
       </c>
       <c r="C640" s="7" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D640" s="7" t="inlineStr">
         <is>
-          <t>0:59:33</t>
+          <t>0:59:32</t>
         </is>
       </c>
       <c r="E640" s="7" t="inlineStr">
@@ -16499,11 +16499,11 @@
         </is>
       </c>
       <c r="C641" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D641" s="5" t="inlineStr">
         <is>
-          <t>0:58:56</t>
+          <t>0:59:33</t>
         </is>
       </c>
       <c r="E641" s="5" t="inlineStr">
@@ -16524,11 +16524,11 @@
         </is>
       </c>
       <c r="C642" s="7" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D642" s="7" t="inlineStr">
         <is>
-          <t>0:59:06</t>
+          <t>0:58:56</t>
         </is>
       </c>
       <c r="E642" s="7" t="inlineStr">
@@ -16549,16 +16549,16 @@
         </is>
       </c>
       <c r="C643" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D643" s="5" t="inlineStr">
         <is>
-          <t>1:00:09</t>
+          <t>0:59:06</t>
         </is>
       </c>
       <c r="E643" s="5" t="inlineStr">
         <is>
-          <t>1:07:29</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16574,16 +16574,16 @@
         </is>
       </c>
       <c r="C644" s="7" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D644" s="7" t="inlineStr">
         <is>
-          <t>1:00:00</t>
+          <t>1:00:09</t>
         </is>
       </c>
       <c r="E644" s="7" t="inlineStr">
         <is>
-          <t>1:05:39</t>
+          <t>1:07:29</t>
         </is>
       </c>
     </row>
@@ -16599,16 +16599,16 @@
         </is>
       </c>
       <c r="C645" s="5" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="D645" s="5" t="inlineStr">
         <is>
-          <t>0:58:57</t>
+          <t>1:00:00</t>
         </is>
       </c>
       <c r="E645" s="5" t="inlineStr">
         <is>
-          <t>1:07:41</t>
+          <t>1:05:39</t>
         </is>
       </c>
     </row>
@@ -16624,23 +16624,23 @@
         </is>
       </c>
       <c r="C646" s="7" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D646" s="7" t="inlineStr">
         <is>
-          <t>1:00:52</t>
+          <t>0:58:57</t>
         </is>
       </c>
       <c r="E646" s="7" t="inlineStr">
         <is>
-          <t>1:09:32</t>
+          <t>1:07:41</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" s="4" t="inlineStr">
         <is>
-          <t>Aramco Houston Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B647" s="5" t="inlineStr">
@@ -16649,16 +16649,16 @@
         </is>
       </c>
       <c r="C647" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D647" s="5" t="inlineStr">
         <is>
-          <t>1:00:42</t>
+          <t>1:00:52</t>
         </is>
       </c>
       <c r="E647" s="5" t="inlineStr">
         <is>
-          <t>1:04:37</t>
+          <t>1:09:32</t>
         </is>
       </c>
     </row>
@@ -16674,16 +16674,16 @@
         </is>
       </c>
       <c r="C648" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D648" s="7" t="inlineStr">
         <is>
-          <t>0:59:17</t>
+          <t>1:00:42</t>
         </is>
       </c>
       <c r="E648" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:37</t>
         </is>
       </c>
     </row>
@@ -16699,23 +16699,23 @@
         </is>
       </c>
       <c r="C649" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D649" s="5" t="inlineStr">
         <is>
-          <t>0:59:01</t>
+          <t>0:59:17</t>
         </is>
       </c>
       <c r="E649" s="5" t="inlineStr">
         <is>
-          <t>1:04:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" s="6" t="inlineStr">
         <is>
-          <t>Asics Run Melbourne</t>
+          <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
       <c r="B650" s="7" t="inlineStr">
@@ -16724,23 +16724,23 @@
         </is>
       </c>
       <c r="C650" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D650" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:01</t>
         </is>
       </c>
       <c r="E650" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:49</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen21</t>
+          <t>Asics Run Melbourne</t>
         </is>
       </c>
       <c r="B651" s="5" t="inlineStr">
@@ -16749,7 +16749,7 @@
         </is>
       </c>
       <c r="C651" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D651" s="5" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         </is>
       </c>
       <c r="C652" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D652" s="7" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="C653" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D653" s="5" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
     <row r="654">
       <c r="A654" s="6" t="inlineStr">
         <is>
-          <t>Brølløbet - The Bridge Run</t>
+          <t>Bangsaen21</t>
         </is>
       </c>
       <c r="B654" s="7" t="inlineStr">
@@ -16840,7 +16840,7 @@
     <row r="655">
       <c r="A655" s="4" t="inlineStr">
         <is>
-          <t>Burj2Burj Half Marathon</t>
+          <t>Brølløbet - The Bridge Run</t>
         </is>
       </c>
       <c r="B655" s="5" t="inlineStr">
@@ -16849,7 +16849,7 @@
         </is>
       </c>
       <c r="C655" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D655" s="5" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         </is>
       </c>
       <c r="C656" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D656" s="7" t="inlineStr">
         <is>
@@ -16899,23 +16899,23 @@
         </is>
       </c>
       <c r="C657" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D657" s="5" t="inlineStr">
         <is>
-          <t>0:59:26</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E657" s="5" t="inlineStr">
         <is>
-          <t>1:06:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" s="6" t="inlineStr">
         <is>
-          <t>Cardiff Half Marathon</t>
+          <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
       <c r="B658" s="7" t="inlineStr">
@@ -16924,23 +16924,23 @@
         </is>
       </c>
       <c r="C658" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D658" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:26</t>
         </is>
       </c>
       <c r="E658" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:57</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="4" t="inlineStr">
         <is>
-          <t>Coelmo Napoli City Half Marathon</t>
+          <t>Cardiff Half Marathon</t>
         </is>
       </c>
       <c r="B659" s="5" t="inlineStr">
@@ -16974,7 +16974,7 @@
         </is>
       </c>
       <c r="C660" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D660" s="7" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
     <row r="661">
       <c r="A661" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen Half Marathon</t>
+          <t>Coelmo Napoli City Half Marathon</t>
         </is>
       </c>
       <c r="B661" s="5" t="inlineStr">
@@ -16999,16 +16999,16 @@
         </is>
       </c>
       <c r="C661" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D661" s="5" t="inlineStr">
         <is>
-          <t>0:59:11</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E661" s="5" t="inlineStr">
         <is>
-          <t>1:05:53</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17024,16 +17024,16 @@
         </is>
       </c>
       <c r="C662" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D662" s="7" t="inlineStr">
         <is>
-          <t>0:58:05</t>
+          <t>0:59:11</t>
         </is>
       </c>
       <c r="E662" s="7" t="inlineStr">
         <is>
-          <t>1:05:11</t>
+          <t>1:05:53</t>
         </is>
       </c>
     </row>
@@ -17049,23 +17049,23 @@
         </is>
       </c>
       <c r="C663" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D663" s="5" t="inlineStr">
         <is>
-          <t>0:58:23</t>
+          <t>0:58:05</t>
         </is>
       </c>
       <c r="E663" s="5" t="inlineStr">
         <is>
-          <t>1:04:44</t>
+          <t>1:05:11</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" s="6" t="inlineStr">
         <is>
-          <t>Disney Princess Half Marathon</t>
+          <t>Copenhagen Half Marathon</t>
         </is>
       </c>
       <c r="B664" s="7" t="inlineStr">
@@ -17078,12 +17078,12 @@
       </c>
       <c r="D664" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:23</t>
         </is>
       </c>
       <c r="E664" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:44</t>
         </is>
       </c>
     </row>
@@ -17099,7 +17099,7 @@
         </is>
       </c>
       <c r="C665" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D665" s="5" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
     <row r="666">
       <c r="A666" s="6" t="inlineStr">
         <is>
-          <t>EDP Lisboa Meia Maratona</t>
+          <t>Disney Princess Half Marathon</t>
         </is>
       </c>
       <c r="B666" s="7" t="inlineStr">
@@ -17124,11 +17124,11 @@
         </is>
       </c>
       <c r="C666" s="7" t="n">
-        <v>2000</v>
+        <v>2026</v>
       </c>
       <c r="D666" s="7" t="inlineStr">
         <is>
-          <t>0:59:06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E666" s="7" t="inlineStr">
@@ -17149,16 +17149,16 @@
         </is>
       </c>
       <c r="C667" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D667" s="5" t="inlineStr">
         <is>
-          <t>1:00:26</t>
+          <t>0:59:06</t>
         </is>
       </c>
       <c r="E667" s="5" t="inlineStr">
         <is>
-          <t>1:05:44</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17174,16 +17174,16 @@
         </is>
       </c>
       <c r="C668" s="7" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="D668" s="7" t="inlineStr">
         <is>
-          <t>1:00:10</t>
+          <t>1:00:26</t>
         </is>
       </c>
       <c r="E668" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:44</t>
         </is>
       </c>
     </row>
@@ -17199,16 +17199,16 @@
         </is>
       </c>
       <c r="C669" s="5" t="n">
-        <v>2010</v>
+        <v>2003</v>
       </c>
       <c r="D669" s="5" t="inlineStr">
         <is>
-          <t>0:58:23</t>
+          <t>1:00:10</t>
         </is>
       </c>
       <c r="E669" s="5" t="inlineStr">
         <is>
-          <t>1:08:38</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17224,16 +17224,16 @@
         </is>
       </c>
       <c r="C670" s="7" t="n">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="D670" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:23</t>
         </is>
       </c>
       <c r="E670" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:38</t>
         </is>
       </c>
     </row>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="C671" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D671" s="5" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         </is>
       </c>
       <c r="C672" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D672" s="7" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
     <row r="673">
       <c r="A673" s="4" t="inlineStr">
         <is>
-          <t>Eurospin RomaOstia Half Marathon</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B673" s="5" t="inlineStr">
@@ -17299,7 +17299,7 @@
         </is>
       </c>
       <c r="C673" s="5" t="n">
-        <v>2004</v>
+        <v>2026</v>
       </c>
       <c r="D673" s="5" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
       </c>
       <c r="E673" s="5" t="inlineStr">
         <is>
-          <t>1:10:39</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17324,16 +17324,16 @@
         </is>
       </c>
       <c r="C674" s="7" t="n">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="D674" s="7" t="inlineStr">
         <is>
-          <t>0:59:32</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E674" s="7" t="inlineStr">
         <is>
-          <t>1:06:38</t>
+          <t>1:10:39</t>
         </is>
       </c>
     </row>
@@ -17349,16 +17349,16 @@
         </is>
       </c>
       <c r="C675" s="5" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="D675" s="5" t="inlineStr">
         <is>
-          <t>0:59:17</t>
+          <t>0:59:32</t>
         </is>
       </c>
       <c r="E675" s="5" t="inlineStr">
         <is>
-          <t>1:06:21</t>
+          <t>1:06:38</t>
         </is>
       </c>
     </row>
@@ -17374,16 +17374,16 @@
         </is>
       </c>
       <c r="C676" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D676" s="7" t="inlineStr">
         <is>
-          <t>1:01:10</t>
+          <t>0:59:17</t>
         </is>
       </c>
       <c r="E676" s="7" t="inlineStr">
         <is>
-          <t>1:07:38</t>
+          <t>1:06:21</t>
         </is>
       </c>
     </row>
@@ -17399,16 +17399,16 @@
         </is>
       </c>
       <c r="C677" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D677" s="5" t="inlineStr">
         <is>
-          <t>0:58:49</t>
+          <t>1:01:10</t>
         </is>
       </c>
       <c r="E677" s="5" t="inlineStr">
         <is>
-          <t>1:08:20</t>
+          <t>1:07:38</t>
         </is>
       </c>
     </row>
@@ -17424,23 +17424,23 @@
         </is>
       </c>
       <c r="C678" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D678" s="7" t="inlineStr">
         <is>
-          <t>0:58:00</t>
+          <t>0:58:49</t>
         </is>
       </c>
       <c r="E678" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:20</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" s="4" t="inlineStr">
         <is>
-          <t>Generali Berlin Half Marathon</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B679" s="5" t="inlineStr">
@@ -17449,16 +17449,16 @@
         </is>
       </c>
       <c r="C679" s="5" t="n">
-        <v>2006</v>
+        <v>2026</v>
       </c>
       <c r="D679" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:00</t>
         </is>
       </c>
       <c r="E679" s="5" t="inlineStr">
         <is>
-          <t>1:07:16</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17474,16 +17474,16 @@
         </is>
       </c>
       <c r="C680" s="7" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D680" s="7" t="inlineStr">
         <is>
-          <t>0:58:56</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E680" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:16</t>
         </is>
       </c>
     </row>
@@ -17499,16 +17499,16 @@
         </is>
       </c>
       <c r="C681" s="5" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="D681" s="5" t="inlineStr">
         <is>
-          <t>1:00:16</t>
+          <t>0:58:56</t>
         </is>
       </c>
       <c r="E681" s="5" t="inlineStr">
         <is>
-          <t>1:09:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17524,16 +17524,16 @@
         </is>
       </c>
       <c r="C682" s="7" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="D682" s="7" t="inlineStr">
         <is>
-          <t>0:59:14</t>
+          <t>1:00:16</t>
         </is>
       </c>
       <c r="E682" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:09:43</t>
         </is>
       </c>
     </row>
@@ -17549,16 +17549,16 @@
         </is>
       </c>
       <c r="C683" s="5" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="D683" s="5" t="inlineStr">
         <is>
-          <t>0:59:01</t>
+          <t>0:59:14</t>
         </is>
       </c>
       <c r="E683" s="5" t="inlineStr">
         <is>
-          <t>1:05:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17574,16 +17574,16 @@
         </is>
       </c>
       <c r="C684" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D684" s="7" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>0:59:01</t>
         </is>
       </c>
       <c r="E684" s="7" t="inlineStr">
         <is>
-          <t>1:06:53</t>
+          <t>1:05:43</t>
         </is>
       </c>
     </row>
@@ -17599,23 +17599,23 @@
         </is>
       </c>
       <c r="C685" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D685" s="5" t="inlineStr">
         <is>
-          <t>0:58:43</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E685" s="5" t="inlineStr">
         <is>
-          <t>1:03:35</t>
+          <t>1:06:53</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" s="6" t="inlineStr">
         <is>
-          <t>Generali Prague Half Marathon</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B686" s="7" t="inlineStr">
@@ -17624,16 +17624,16 @@
         </is>
       </c>
       <c r="C686" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D686" s="7" t="inlineStr">
         <is>
-          <t>0:59:43</t>
+          <t>0:58:43</t>
         </is>
       </c>
       <c r="E686" s="7" t="inlineStr">
         <is>
-          <t>1:06:00</t>
+          <t>1:03:35</t>
         </is>
       </c>
     </row>
@@ -17649,16 +17649,16 @@
         </is>
       </c>
       <c r="C687" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D687" s="5" t="inlineStr">
         <is>
-          <t>0:58:24</t>
+          <t>0:59:43</t>
         </is>
       </c>
       <c r="E687" s="5" t="inlineStr">
         <is>
-          <t>1:08:10</t>
+          <t>1:06:00</t>
         </is>
       </c>
     </row>
@@ -17674,23 +17674,23 @@
         </is>
       </c>
       <c r="C688" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D688" s="7" t="inlineStr">
         <is>
-          <t>0:58:54</t>
+          <t>0:58:24</t>
         </is>
       </c>
       <c r="E688" s="7" t="inlineStr">
         <is>
-          <t>1:05:27</t>
+          <t>1:08:10</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" s="4" t="inlineStr">
         <is>
-          <t>GetPro Bath Half</t>
+          <t>Generali Prague Half Marathon</t>
         </is>
       </c>
       <c r="B689" s="5" t="inlineStr">
@@ -17703,12 +17703,12 @@
       </c>
       <c r="D689" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:54</t>
         </is>
       </c>
       <c r="E689" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:27</t>
         </is>
       </c>
     </row>
@@ -17724,7 +17724,7 @@
         </is>
       </c>
       <c r="C690" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D690" s="7" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
     <row r="691">
       <c r="A691" s="4" t="inlineStr">
         <is>
-          <t>Göteborgsvarvet</t>
+          <t>GetPro Bath Half</t>
         </is>
       </c>
       <c r="B691" s="5" t="inlineStr">
@@ -17749,16 +17749,16 @@
         </is>
       </c>
       <c r="C691" s="5" t="n">
-        <v>2000</v>
+        <v>2026</v>
       </c>
       <c r="D691" s="5" t="inlineStr">
         <is>
-          <t>1:02:42</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E691" s="5" t="inlineStr">
         <is>
-          <t>1:09:28</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17774,16 +17774,16 @@
         </is>
       </c>
       <c r="C692" s="7" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D692" s="7" t="inlineStr">
         <is>
-          <t>1:03:00</t>
+          <t>1:02:42</t>
         </is>
       </c>
       <c r="E692" s="7" t="inlineStr">
         <is>
-          <t>1:11:07</t>
+          <t>1:09:28</t>
         </is>
       </c>
     </row>
@@ -17799,16 +17799,16 @@
         </is>
       </c>
       <c r="C693" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D693" s="5" t="inlineStr">
         <is>
-          <t>1:03:35</t>
+          <t>1:03:00</t>
         </is>
       </c>
       <c r="E693" s="5" t="inlineStr">
         <is>
-          <t>1:13:03</t>
+          <t>1:11:07</t>
         </is>
       </c>
     </row>
@@ -17824,16 +17824,16 @@
         </is>
       </c>
       <c r="C694" s="7" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D694" s="7" t="inlineStr">
         <is>
-          <t>1:03:43</t>
+          <t>1:03:35</t>
         </is>
       </c>
       <c r="E694" s="7" t="inlineStr">
         <is>
-          <t>1:13:27</t>
+          <t>1:13:03</t>
         </is>
       </c>
     </row>
@@ -17849,16 +17849,16 @@
         </is>
       </c>
       <c r="C695" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D695" s="5" t="inlineStr">
         <is>
-          <t>1:04:03</t>
+          <t>1:03:43</t>
         </is>
       </c>
       <c r="E695" s="5" t="inlineStr">
         <is>
-          <t>1:18:06</t>
+          <t>1:13:27</t>
         </is>
       </c>
     </row>
@@ -17874,16 +17874,16 @@
         </is>
       </c>
       <c r="C696" s="7" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D696" s="7" t="inlineStr">
         <is>
-          <t>1:03:19</t>
+          <t>1:04:03</t>
         </is>
       </c>
       <c r="E696" s="7" t="inlineStr">
         <is>
-          <t>1:12:34</t>
+          <t>1:18:06</t>
         </is>
       </c>
     </row>
@@ -17899,11 +17899,11 @@
         </is>
       </c>
       <c r="C697" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D697" s="5" t="inlineStr">
         <is>
-          <t>1:02:14</t>
+          <t>1:03:19</t>
         </is>
       </c>
       <c r="E697" s="5" t="inlineStr">
@@ -17924,16 +17924,16 @@
         </is>
       </c>
       <c r="C698" s="7" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D698" s="7" t="inlineStr">
         <is>
-          <t>1:04:03</t>
+          <t>1:02:14</t>
         </is>
       </c>
       <c r="E698" s="7" t="inlineStr">
         <is>
-          <t>1:12:38</t>
+          <t>1:12:34</t>
         </is>
       </c>
     </row>
@@ -17949,16 +17949,16 @@
         </is>
       </c>
       <c r="C699" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D699" s="5" t="inlineStr">
         <is>
-          <t>1:01:21</t>
+          <t>1:04:03</t>
         </is>
       </c>
       <c r="E699" s="5" t="inlineStr">
         <is>
-          <t>1:10:19</t>
+          <t>1:12:38</t>
         </is>
       </c>
     </row>
@@ -17974,16 +17974,16 @@
         </is>
       </c>
       <c r="C700" s="7" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D700" s="7" t="inlineStr">
         <is>
-          <t>1:01:55</t>
+          <t>1:01:21</t>
         </is>
       </c>
       <c r="E700" s="7" t="inlineStr">
         <is>
-          <t>1:11:27</t>
+          <t>1:10:19</t>
         </is>
       </c>
     </row>
@@ -17999,16 +17999,16 @@
         </is>
       </c>
       <c r="C701" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D701" s="5" t="inlineStr">
         <is>
-          <t>1:01:10</t>
+          <t>1:01:55</t>
         </is>
       </c>
       <c r="E701" s="5" t="inlineStr">
         <is>
-          <t>1:11:40</t>
+          <t>1:11:27</t>
         </is>
       </c>
     </row>
@@ -18024,16 +18024,16 @@
         </is>
       </c>
       <c r="C702" s="7" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D702" s="7" t="inlineStr">
         <is>
-          <t>1:00:52</t>
+          <t>1:01:10</t>
         </is>
       </c>
       <c r="E702" s="7" t="inlineStr">
         <is>
-          <t>1:09:04</t>
+          <t>1:11:40</t>
         </is>
       </c>
     </row>
@@ -18049,16 +18049,16 @@
         </is>
       </c>
       <c r="C703" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D703" s="5" t="inlineStr">
         <is>
-          <t>1:00:25</t>
+          <t>1:00:52</t>
         </is>
       </c>
       <c r="E703" s="5" t="inlineStr">
         <is>
-          <t>1:09:27</t>
+          <t>1:09:04</t>
         </is>
       </c>
     </row>
@@ -18074,16 +18074,16 @@
         </is>
       </c>
       <c r="C704" s="7" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D704" s="7" t="inlineStr">
         <is>
-          <t>1:03:13</t>
+          <t>1:00:25</t>
         </is>
       </c>
       <c r="E704" s="7" t="inlineStr">
         <is>
-          <t>1:11:29</t>
+          <t>1:09:27</t>
         </is>
       </c>
     </row>
@@ -18099,16 +18099,16 @@
         </is>
       </c>
       <c r="C705" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D705" s="5" t="inlineStr">
         <is>
-          <t>1:00:36</t>
+          <t>1:03:13</t>
         </is>
       </c>
       <c r="E705" s="5" t="inlineStr">
         <is>
-          <t>1:10:12</t>
+          <t>1:11:29</t>
         </is>
       </c>
     </row>
@@ -18124,16 +18124,16 @@
         </is>
       </c>
       <c r="C706" s="7" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="D706" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:36</t>
         </is>
       </c>
       <c r="E706" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:12</t>
         </is>
       </c>
     </row>
@@ -18149,7 +18149,7 @@
         </is>
       </c>
       <c r="C707" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D707" s="5" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
     <row r="708">
       <c r="A708" s="6" t="inlineStr">
         <is>
-          <t>HOKA Semi de Paris</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B708" s="7" t="inlineStr">
@@ -18174,16 +18174,16 @@
         </is>
       </c>
       <c r="C708" s="7" t="n">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="D708" s="7" t="inlineStr">
         <is>
-          <t>1:01:33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E708" s="7" t="inlineStr">
         <is>
-          <t>1:11:07</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -18199,16 +18199,16 @@
         </is>
       </c>
       <c r="C709" s="5" t="n">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="D709" s="5" t="inlineStr">
         <is>
-          <t>0:59:44</t>
+          <t>1:01:33</t>
         </is>
       </c>
       <c r="E709" s="5" t="inlineStr">
         <is>
-          <t>1:07:55</t>
+          <t>1:11:07</t>
         </is>
       </c>
     </row>
@@ -18224,16 +18224,16 @@
         </is>
       </c>
       <c r="C710" s="7" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="D710" s="7" t="inlineStr">
         <is>
-          <t>1:00:08</t>
+          <t>0:59:44</t>
         </is>
       </c>
       <c r="E710" s="7" t="inlineStr">
         <is>
-          <t>1:09:23</t>
+          <t>1:07:55</t>
         </is>
       </c>
     </row>
@@ -18249,16 +18249,16 @@
         </is>
       </c>
       <c r="C711" s="5" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D711" s="5" t="inlineStr">
         <is>
-          <t>0:59:38</t>
+          <t>1:00:08</t>
         </is>
       </c>
       <c r="E711" s="5" t="inlineStr">
         <is>
-          <t>1:06:01</t>
+          <t>1:09:23</t>
         </is>
       </c>
     </row>
@@ -18274,16 +18274,16 @@
         </is>
       </c>
       <c r="C712" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D712" s="7" t="inlineStr">
         <is>
-          <t>1:00:45</t>
+          <t>0:59:38</t>
         </is>
       </c>
       <c r="E712" s="7" t="inlineStr">
         <is>
-          <t>1:06:58</t>
+          <t>1:06:01</t>
         </is>
       </c>
     </row>
@@ -18299,16 +18299,16 @@
         </is>
       </c>
       <c r="C713" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D713" s="5" t="inlineStr">
         <is>
-          <t>1:00:16</t>
+          <t>1:00:45</t>
         </is>
       </c>
       <c r="E713" s="5" t="inlineStr">
         <is>
-          <t>1:07:14</t>
+          <t>1:06:58</t>
         </is>
       </c>
     </row>
@@ -18324,23 +18324,23 @@
         </is>
       </c>
       <c r="C714" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D714" s="7" t="inlineStr">
         <is>
-          <t>1:00:11</t>
+          <t>1:00:16</t>
         </is>
       </c>
       <c r="E714" s="7" t="inlineStr">
         <is>
-          <t>1:05:12</t>
+          <t>1:07:14</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" s="4" t="inlineStr">
         <is>
-          <t>Half Marathon Munchen by Brooks</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B715" s="5" t="inlineStr">
@@ -18349,23 +18349,23 @@
         </is>
       </c>
       <c r="C715" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D715" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:11</t>
         </is>
       </c>
       <c r="E715" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:12</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" s="6" t="inlineStr">
         <is>
-          <t>Hoka Runaway Sydney Half Marathon</t>
+          <t>Half Marathon Munchen by Brooks</t>
         </is>
       </c>
       <c r="B716" s="7" t="inlineStr">
@@ -18390,7 +18390,7 @@
     <row r="717">
       <c r="A717" s="4" t="inlineStr">
         <is>
-          <t>Hyundai Meia Maratona</t>
+          <t>Hoka Runaway Sydney Half Marathon</t>
         </is>
       </c>
       <c r="B717" s="5" t="inlineStr">
@@ -18399,7 +18399,7 @@
         </is>
       </c>
       <c r="C717" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D717" s="5" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         </is>
       </c>
       <c r="C718" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D718" s="7" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         </is>
       </c>
       <c r="C719" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D719" s="5" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
     <row r="720">
       <c r="A720" s="6" t="inlineStr">
         <is>
-          <t>IU Health 500 Festival Mini-Marathon</t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="B720" s="7" t="inlineStr">
@@ -18490,7 +18490,7 @@
     <row r="721">
       <c r="A721" s="4" t="inlineStr">
         <is>
-          <t>Kagawa Marugame International Half Marathon</t>
+          <t>IU Health 500 Festival Mini-Marathon</t>
         </is>
       </c>
       <c r="B721" s="5" t="inlineStr">
@@ -18499,7 +18499,7 @@
         </is>
       </c>
       <c r="C721" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D721" s="5" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
     <row r="722">
       <c r="A722" s="6" t="inlineStr">
         <is>
-          <t>Life Time Chicago Half Marathon &amp; 5K</t>
+          <t>Kagawa Marugame International Half Marathon</t>
         </is>
       </c>
       <c r="B722" s="7" t="inlineStr">
@@ -18524,7 +18524,7 @@
         </is>
       </c>
       <c r="C722" s="7" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D722" s="7" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         </is>
       </c>
       <c r="C723" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D723" s="5" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
     <row r="724">
       <c r="A724" s="6" t="inlineStr">
         <is>
-          <t>London Landmarks Half Marathon</t>
+          <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
       <c r="B724" s="7" t="inlineStr">
@@ -18574,7 +18574,7 @@
         </is>
       </c>
       <c r="C724" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D724" s="7" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         </is>
       </c>
       <c r="C725" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D725" s="5" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
     <row r="726">
       <c r="A726" s="6" t="inlineStr">
         <is>
-          <t>Manchester Half Marathon</t>
+          <t>London Landmarks Half Marathon</t>
         </is>
       </c>
       <c r="B726" s="7" t="inlineStr">
@@ -18640,7 +18640,7 @@
     <row r="727">
       <c r="A727" s="4" t="inlineStr">
         <is>
-          <t>Media Maraton de Bogota</t>
+          <t>Manchester Half Marathon</t>
         </is>
       </c>
       <c r="B727" s="5" t="inlineStr">
@@ -18665,7 +18665,7 @@
     <row r="728">
       <c r="A728" s="6" t="inlineStr">
         <is>
-          <t>Medio Maraton de Sevilla</t>
+          <t>Media Maraton de Bogota</t>
         </is>
       </c>
       <c r="B728" s="7" t="inlineStr">
@@ -18674,16 +18674,16 @@
         </is>
       </c>
       <c r="C728" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D728" s="7" t="inlineStr">
         <is>
-          <t>0:59:21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E728" s="7" t="inlineStr">
         <is>
-          <t>1:07:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -18699,16 +18699,16 @@
         </is>
       </c>
       <c r="C729" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D729" s="5" t="inlineStr">
         <is>
-          <t>0:59:33</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E729" s="5" t="inlineStr">
         <is>
-          <t>1:07:18</t>
+          <t>1:07:59</t>
         </is>
       </c>
     </row>
@@ -18724,23 +18724,23 @@
         </is>
       </c>
       <c r="C730" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D730" s="7" t="inlineStr">
         <is>
-          <t>1:00:24</t>
+          <t>0:59:33</t>
         </is>
       </c>
       <c r="E730" s="7" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>1:07:18</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" s="4" t="inlineStr">
         <is>
-          <t>Mitja Marato Barcelona by Brooks</t>
+          <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
       <c r="B731" s="5" t="inlineStr">
@@ -18749,16 +18749,16 @@
         </is>
       </c>
       <c r="C731" s="5" t="n">
-        <v>2005</v>
+        <v>2026</v>
       </c>
       <c r="D731" s="5" t="inlineStr">
         <is>
-          <t>1:03:29</t>
+          <t>1:00:24</t>
         </is>
       </c>
       <c r="E731" s="5" t="inlineStr">
         <is>
-          <t>1:09:34</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
@@ -18774,16 +18774,16 @@
         </is>
       </c>
       <c r="C732" s="7" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D732" s="7" t="inlineStr">
         <is>
-          <t>1:02:25</t>
+          <t>1:03:29</t>
         </is>
       </c>
       <c r="E732" s="7" t="inlineStr">
         <is>
-          <t>1:09:26</t>
+          <t>1:09:34</t>
         </is>
       </c>
     </row>
@@ -18799,16 +18799,16 @@
         </is>
       </c>
       <c r="C733" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D733" s="5" t="inlineStr">
         <is>
-          <t>1:03:02</t>
+          <t>1:02:25</t>
         </is>
       </c>
       <c r="E733" s="5" t="inlineStr">
         <is>
-          <t>1:09:05</t>
+          <t>1:09:26</t>
         </is>
       </c>
     </row>
@@ -18824,16 +18824,16 @@
         </is>
       </c>
       <c r="C734" s="7" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D734" s="7" t="inlineStr">
         <is>
-          <t>1:02:39</t>
+          <t>1:03:02</t>
         </is>
       </c>
       <c r="E734" s="7" t="inlineStr">
         <is>
-          <t>1:09:15</t>
+          <t>1:09:05</t>
         </is>
       </c>
     </row>
@@ -18849,16 +18849,16 @@
         </is>
       </c>
       <c r="C735" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D735" s="5" t="inlineStr">
         <is>
-          <t>1:01:45</t>
+          <t>1:02:39</t>
         </is>
       </c>
       <c r="E735" s="5" t="inlineStr">
         <is>
-          <t>1:09:34</t>
+          <t>1:09:15</t>
         </is>
       </c>
     </row>
@@ -18874,16 +18874,16 @@
         </is>
       </c>
       <c r="C736" s="7" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D736" s="7" t="inlineStr">
         <is>
-          <t>1:03:00</t>
+          <t>1:01:45</t>
         </is>
       </c>
       <c r="E736" s="7" t="inlineStr">
         <is>
-          <t>1:08:52</t>
+          <t>1:09:34</t>
         </is>
       </c>
     </row>
@@ -18899,16 +18899,16 @@
         </is>
       </c>
       <c r="C737" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D737" s="5" t="inlineStr">
         <is>
-          <t>1:03:06</t>
+          <t>1:03:00</t>
         </is>
       </c>
       <c r="E737" s="5" t="inlineStr">
         <is>
-          <t>1:08:13</t>
+          <t>1:08:52</t>
         </is>
       </c>
     </row>
@@ -18924,16 +18924,16 @@
         </is>
       </c>
       <c r="C738" s="7" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D738" s="7" t="inlineStr">
         <is>
-          <t>1:02:54</t>
+          <t>1:03:06</t>
         </is>
       </c>
       <c r="E738" s="7" t="inlineStr">
         <is>
-          <t>1:10:51</t>
+          <t>1:08:13</t>
         </is>
       </c>
     </row>
@@ -18949,16 +18949,16 @@
         </is>
       </c>
       <c r="C739" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D739" s="5" t="inlineStr">
         <is>
-          <t>1:01:44</t>
+          <t>1:02:54</t>
         </is>
       </c>
       <c r="E739" s="5" t="inlineStr">
         <is>
-          <t>1:08:28</t>
+          <t>1:10:51</t>
         </is>
       </c>
     </row>
@@ -18974,16 +18974,16 @@
         </is>
       </c>
       <c r="C740" s="7" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D740" s="7" t="inlineStr">
         <is>
-          <t>1:02:55</t>
+          <t>1:01:44</t>
         </is>
       </c>
       <c r="E740" s="7" t="inlineStr">
         <is>
-          <t>1:08:35</t>
+          <t>1:08:28</t>
         </is>
       </c>
     </row>
@@ -18999,16 +18999,16 @@
         </is>
       </c>
       <c r="C741" s="5" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D741" s="5" t="inlineStr">
         <is>
-          <t>0:58:53</t>
+          <t>1:02:55</t>
         </is>
       </c>
       <c r="E741" s="5" t="inlineStr">
         <is>
-          <t>1:04:37</t>
+          <t>1:08:35</t>
         </is>
       </c>
     </row>
@@ -19024,16 +19024,16 @@
         </is>
       </c>
       <c r="C742" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D742" s="7" t="inlineStr">
         <is>
-          <t>0:59:21</t>
+          <t>0:58:53</t>
         </is>
       </c>
       <c r="E742" s="7" t="inlineStr">
         <is>
-          <t>1:04:28</t>
+          <t>1:04:37</t>
         </is>
       </c>
     </row>
@@ -19049,16 +19049,16 @@
         </is>
       </c>
       <c r="C743" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D743" s="5" t="inlineStr">
         <is>
-          <t>0:56:42</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E743" s="5" t="inlineStr">
         <is>
-          <t>1:04:11</t>
+          <t>1:04:28</t>
         </is>
       </c>
     </row>
@@ -19074,23 +19074,23 @@
         </is>
       </c>
       <c r="C744" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D744" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:56:42</t>
         </is>
       </c>
       <c r="E744" s="7" t="inlineStr">
         <is>
-          <t>1:04:00</t>
+          <t>1:04:11</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" s="4" t="inlineStr">
         <is>
-          <t>Movistar Madrid Medio Maraton</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B745" s="5" t="inlineStr">
@@ -19099,7 +19099,7 @@
         </is>
       </c>
       <c r="C745" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D745" s="5" t="inlineStr">
         <is>
@@ -19108,14 +19108,14 @@
       </c>
       <c r="E745" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:00</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" s="6" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - Half Marathon</t>
+          <t>Movistar Madrid Medio Maraton</t>
         </is>
       </c>
       <c r="B746" s="7" t="inlineStr">
@@ -19153,12 +19153,12 @@
       </c>
       <c r="D747" s="5" t="inlineStr">
         <is>
-          <t>0:59:36</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E747" s="5" t="inlineStr">
         <is>
-          <t>1:08:16</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19174,16 +19174,16 @@
         </is>
       </c>
       <c r="C748" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D748" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:36</t>
         </is>
       </c>
       <c r="E748" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:16</t>
         </is>
       </c>
     </row>
@@ -19203,19 +19203,19 @@
       </c>
       <c r="D749" s="5" t="inlineStr">
         <is>
-          <t>0:59:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E749" s="5" t="inlineStr">
         <is>
-          <t>1:07:34</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" s="6" t="inlineStr">
         <is>
-          <t>NYCRUNS Brooklyn Experience Half Marathon</t>
+          <t>NN CPC Loop Den Haag - Half Marathon</t>
         </is>
       </c>
       <c r="B750" s="7" t="inlineStr">
@@ -19224,23 +19224,23 @@
         </is>
       </c>
       <c r="C750" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D750" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:48</t>
         </is>
       </c>
       <c r="E750" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:34</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" s="4" t="inlineStr">
         <is>
-          <t>NYRR RBC Brooklyn Half</t>
+          <t>NYCRUNS Brooklyn Experience Half Marathon</t>
         </is>
       </c>
       <c r="B751" s="5" t="inlineStr">
@@ -19265,7 +19265,7 @@
     <row r="752">
       <c r="A752" s="6" t="inlineStr">
         <is>
-          <t>Nike Melbourne Marathon Festival</t>
+          <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
       <c r="B752" s="7" t="inlineStr">
@@ -19290,7 +19290,7 @@
     <row r="753">
       <c r="A753" s="4" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>Nike Melbourne Marathon Festival</t>
         </is>
       </c>
       <c r="B753" s="5" t="inlineStr">
@@ -19299,7 +19299,7 @@
         </is>
       </c>
       <c r="C753" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D753" s="5" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         </is>
       </c>
       <c r="C754" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D754" s="7" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         </is>
       </c>
       <c r="C755" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D755" s="5" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         </is>
       </c>
       <c r="C756" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D756" s="7" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
     <row r="757">
       <c r="A757" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B757" s="5" t="inlineStr">
@@ -19399,7 +19399,7 @@
         </is>
       </c>
       <c r="C757" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D757" s="5" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         </is>
       </c>
       <c r="C758" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D758" s="7" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         </is>
       </c>
       <c r="C759" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D759" s="5" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         </is>
       </c>
       <c r="C760" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D760" s="7" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
     <row r="761">
       <c r="A761" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Mexico City</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B761" s="5" t="inlineStr">
@@ -19499,7 +19499,7 @@
         </is>
       </c>
       <c r="C761" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D761" s="5" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
     <row r="762">
       <c r="A762" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series San Diego</t>
+          <t>Rock 'n' Roll Running Series Mexico City</t>
         </is>
       </c>
       <c r="B762" s="7" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="763">
       <c r="A763" s="4" t="inlineStr">
         <is>
-          <t>Royal Parks Half Marathon</t>
+          <t>Rock 'n' Roll Running Series San Diego</t>
         </is>
       </c>
       <c r="B763" s="5" t="inlineStr">
@@ -19565,7 +19565,7 @@
     <row r="764">
       <c r="A764" s="6" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Royal Parks Half Marathon</t>
         </is>
       </c>
       <c r="B764" s="7" t="inlineStr">
@@ -19574,7 +19574,7 @@
         </is>
       </c>
       <c r="C764" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D764" s="7" t="inlineStr">
         <is>
@@ -19599,16 +19599,16 @@
         </is>
       </c>
       <c r="C765" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D765" s="5" t="inlineStr">
         <is>
-          <t>1:05:44</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E765" s="5" t="inlineStr">
         <is>
-          <t>1:18:34</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19624,23 +19624,23 @@
         </is>
       </c>
       <c r="C766" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D766" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:44</t>
         </is>
       </c>
       <c r="E766" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:18:34</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" s="4" t="inlineStr">
         <is>
-          <t>Semi-Marathon de Boulogne-Billancourt</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B767" s="5" t="inlineStr">
@@ -19665,7 +19665,7 @@
     <row r="768">
       <c r="A768" s="6" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
+          <t>Semi-Marathon de Boulogne-Billancourt</t>
         </is>
       </c>
       <c r="B768" s="7" t="inlineStr">
@@ -19690,7 +19690,7 @@
     <row r="769">
       <c r="A769" s="4" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Series Nashville</t>
+          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
         </is>
       </c>
       <c r="B769" s="5" t="inlineStr">
@@ -19715,7 +19715,7 @@
     <row r="770">
       <c r="A770" s="6" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>St. Jude Rock 'n' Roll Series Nashville</t>
         </is>
       </c>
       <c r="B770" s="7" t="inlineStr">
@@ -19724,16 +19724,16 @@
         </is>
       </c>
       <c r="C770" s="7" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D770" s="7" t="inlineStr">
         <is>
-          <t>1:01:13</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E770" s="7" t="inlineStr">
         <is>
-          <t>1:09:28</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19749,16 +19749,16 @@
         </is>
       </c>
       <c r="C771" s="5" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D771" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:13</t>
         </is>
       </c>
       <c r="E771" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:09:28</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
         </is>
       </c>
       <c r="C772" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D772" s="7" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
     <row r="773">
       <c r="A773" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered KL Half Marathon</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B773" s="5" t="inlineStr">
@@ -19799,23 +19799,23 @@
         </is>
       </c>
       <c r="C773" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D773" s="5" t="inlineStr">
         <is>
-          <t>1:11:08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E773" s="5" t="inlineStr">
         <is>
-          <t>1:23:55</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" s="6" t="inlineStr">
         <is>
-          <t>Standard Chartered Singapore Half Marathon</t>
+          <t>Standard Chartered KL Half Marathon</t>
         </is>
       </c>
       <c r="B774" s="7" t="inlineStr">
@@ -19828,19 +19828,19 @@
       </c>
       <c r="D774" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:11:08</t>
         </is>
       </c>
       <c r="E774" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:23:55</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" s="4" t="inlineStr">
         <is>
-          <t>TCS Mizuno Half Marathon</t>
+          <t>Standard Chartered Singapore Half Marathon</t>
         </is>
       </c>
       <c r="B775" s="5" t="inlineStr">
@@ -19849,16 +19849,16 @@
         </is>
       </c>
       <c r="C775" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D775" s="5" t="inlineStr">
         <is>
-          <t>1:05:23</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E775" s="5" t="inlineStr">
         <is>
-          <t>1:13:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19874,16 +19874,16 @@
         </is>
       </c>
       <c r="C776" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D776" s="7" t="inlineStr">
         <is>
-          <t>1:06:28</t>
+          <t>1:05:23</t>
         </is>
       </c>
       <c r="E776" s="7" t="inlineStr">
         <is>
-          <t>1:17:54</t>
+          <t>1:13:59</t>
         </is>
       </c>
     </row>
@@ -19899,16 +19899,16 @@
         </is>
       </c>
       <c r="C777" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D777" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:28</t>
         </is>
       </c>
       <c r="E777" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:17:54</t>
         </is>
       </c>
     </row>
@@ -19928,19 +19928,19 @@
       </c>
       <c r="D778" s="7" t="inlineStr">
         <is>
-          <t>1:04:21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E778" s="7" t="inlineStr">
         <is>
-          <t>1:10:02</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="779">
       <c r="A779" s="4" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
       <c r="B779" s="5" t="inlineStr">
@@ -19949,16 +19949,16 @@
         </is>
       </c>
       <c r="C779" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D779" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:21</t>
         </is>
       </c>
       <c r="E779" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:02</t>
         </is>
       </c>
     </row>
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="C780" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D780" s="7" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         </is>
       </c>
       <c r="C781" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D781" s="5" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
     <row r="782">
       <c r="A782" s="6" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B782" s="7" t="inlineStr">
@@ -20024,7 +20024,7 @@
         </is>
       </c>
       <c r="C782" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D782" s="7" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         </is>
       </c>
       <c r="C783" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D783" s="5" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         </is>
       </c>
       <c r="C784" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D784" s="7" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
     <row r="785">
       <c r="A785" s="4" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon (Half)</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B785" s="5" t="inlineStr">
@@ -20124,7 +20124,7 @@
         </is>
       </c>
       <c r="C786" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D786" s="7" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
     <row r="787">
       <c r="A787" s="4" t="inlineStr">
         <is>
-          <t>The Big Half</t>
+          <t>Tata Mumbai Marathon (Half)</t>
         </is>
       </c>
       <c r="B787" s="5" t="inlineStr">
@@ -20149,7 +20149,7 @@
         </is>
       </c>
       <c r="C787" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D787" s="5" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
     <row r="788">
       <c r="A788" s="6" t="inlineStr">
         <is>
-          <t>Tokyo Legacy Half Marathon</t>
+          <t>The Big Half</t>
         </is>
       </c>
       <c r="B788" s="7" t="inlineStr">
@@ -20190,7 +20190,7 @@
     <row r="789">
       <c r="A789" s="4" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>Tokyo Legacy Half Marathon</t>
         </is>
       </c>
       <c r="B789" s="5" t="inlineStr">
@@ -20199,16 +20199,16 @@
         </is>
       </c>
       <c r="C789" s="5" t="n">
-        <v>2006</v>
+        <v>2025</v>
       </c>
       <c r="D789" s="5" t="inlineStr">
         <is>
-          <t>1:01:22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E789" s="5" t="inlineStr">
         <is>
-          <t>1:09:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20224,16 +20224,16 @@
         </is>
       </c>
       <c r="C790" s="7" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D790" s="7" t="inlineStr">
         <is>
-          <t>0:59:24</t>
+          <t>1:01:22</t>
         </is>
       </c>
       <c r="E790" s="7" t="inlineStr">
         <is>
-          <t>1:10:32</t>
+          <t>1:09:43</t>
         </is>
       </c>
     </row>
@@ -20249,16 +20249,16 @@
         </is>
       </c>
       <c r="C791" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D791" s="5" t="inlineStr">
         <is>
-          <t>1:00:58</t>
+          <t>0:59:24</t>
         </is>
       </c>
       <c r="E791" s="5" t="inlineStr">
         <is>
-          <t>1:10:19</t>
+          <t>1:10:32</t>
         </is>
       </c>
     </row>
@@ -20274,16 +20274,16 @@
         </is>
       </c>
       <c r="C792" s="7" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D792" s="7" t="inlineStr">
         <is>
-          <t>1:01:06</t>
+          <t>1:00:58</t>
         </is>
       </c>
       <c r="E792" s="7" t="inlineStr">
         <is>
-          <t>1:09:32</t>
+          <t>1:10:19</t>
         </is>
       </c>
     </row>
@@ -20299,16 +20299,16 @@
         </is>
       </c>
       <c r="C793" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D793" s="5" t="inlineStr">
         <is>
-          <t>0:59:52</t>
+          <t>1:01:06</t>
         </is>
       </c>
       <c r="E793" s="5" t="inlineStr">
         <is>
-          <t>1:09:25</t>
+          <t>1:09:32</t>
         </is>
       </c>
     </row>
@@ -20324,16 +20324,16 @@
         </is>
       </c>
       <c r="C794" s="7" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D794" s="7" t="inlineStr">
         <is>
-          <t>1:00:23</t>
+          <t>0:59:52</t>
         </is>
       </c>
       <c r="E794" s="7" t="inlineStr">
         <is>
-          <t>1:08:52</t>
+          <t>1:09:25</t>
         </is>
       </c>
     </row>
@@ -20349,16 +20349,16 @@
         </is>
       </c>
       <c r="C795" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D795" s="5" t="inlineStr">
         <is>
-          <t>0:59:39</t>
+          <t>1:00:23</t>
         </is>
       </c>
       <c r="E795" s="5" t="inlineStr">
         <is>
-          <t>1:08:35</t>
+          <t>1:08:52</t>
         </is>
       </c>
     </row>
@@ -20374,16 +20374,16 @@
         </is>
       </c>
       <c r="C796" s="7" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D796" s="7" t="inlineStr">
         <is>
-          <t>1:01:02</t>
+          <t>0:59:39</t>
         </is>
       </c>
       <c r="E796" s="7" t="inlineStr">
         <is>
-          <t>1:09:09</t>
+          <t>1:08:35</t>
         </is>
       </c>
     </row>
@@ -20399,16 +20399,16 @@
         </is>
       </c>
       <c r="C797" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D797" s="5" t="inlineStr">
         <is>
-          <t>1:00:50</t>
+          <t>1:01:02</t>
         </is>
       </c>
       <c r="E797" s="5" t="inlineStr">
         <is>
-          <t>1:08:31</t>
+          <t>1:09:09</t>
         </is>
       </c>
     </row>
@@ -20424,16 +20424,16 @@
         </is>
       </c>
       <c r="C798" s="7" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D798" s="7" t="inlineStr">
         <is>
-          <t>1:01:31</t>
+          <t>1:00:50</t>
         </is>
       </c>
       <c r="E798" s="7" t="inlineStr">
         <is>
-          <t>1:07:04</t>
+          <t>1:08:31</t>
         </is>
       </c>
     </row>
@@ -20449,23 +20449,23 @@
         </is>
       </c>
       <c r="C799" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D799" s="5" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>1:01:31</t>
         </is>
       </c>
       <c r="E799" s="5" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>1:07:04</t>
         </is>
       </c>
     </row>
     <row r="800">
       <c r="A800" s="6" t="inlineStr">
         <is>
-          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B800" s="7" t="inlineStr">
@@ -20474,23 +20474,23 @@
         </is>
       </c>
       <c r="C800" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D800" s="7" t="inlineStr">
         <is>
-          <t>0:58:02</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E800" s="7" t="inlineStr">
         <is>
-          <t>1:03:08</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
     <row r="801">
       <c r="A801" s="4" t="inlineStr">
         <is>
-          <t>Vedanta Delhi Half Marathon</t>
+          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B801" s="5" t="inlineStr">
@@ -20503,19 +20503,19 @@
       </c>
       <c r="D801" s="5" t="inlineStr">
         <is>
-          <t>0:59:50</t>
+          <t>0:58:02</t>
         </is>
       </c>
       <c r="E801" s="5" t="inlineStr">
         <is>
-          <t>1:07:20</t>
+          <t>1:03:08</t>
         </is>
       </c>
     </row>
     <row r="802">
       <c r="A802" s="6" t="inlineStr">
         <is>
-          <t>Vienna City Half Marathon</t>
+          <t>Vedanta Delhi Half Marathon</t>
         </is>
       </c>
       <c r="B802" s="7" t="inlineStr">
@@ -20528,19 +20528,19 @@
       </c>
       <c r="D802" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:50</t>
         </is>
       </c>
       <c r="E802" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:20</t>
         </is>
       </c>
     </row>
     <row r="803">
       <c r="A803" s="4" t="inlineStr">
         <is>
-          <t>Walt Disney World Marathon Weekend</t>
+          <t>Vienna City Half Marathon</t>
         </is>
       </c>
       <c r="B803" s="5" t="inlineStr">
@@ -20574,7 +20574,7 @@
         </is>
       </c>
       <c r="C804" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D804" s="7" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
     <row r="805">
       <c r="A805" s="4" t="inlineStr">
         <is>
-          <t>Warsaw Half Marathon</t>
+          <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
       <c r="B805" s="5" t="inlineStr">
@@ -20599,7 +20599,7 @@
         </is>
       </c>
       <c r="C805" s="5" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D805" s="5" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         </is>
       </c>
       <c r="C806" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D806" s="7" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
     <row r="807">
       <c r="A807" s="4" t="inlineStr">
         <is>
-          <t>Wizz Air Rome Half Marathon by Brooks</t>
+          <t>Warsaw Half Marathon</t>
         </is>
       </c>
       <c r="B807" s="5" t="inlineStr">
@@ -20665,7 +20665,7 @@
     <row r="808">
       <c r="A808" s="6" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Wizz Air Rome Half Marathon by Brooks</t>
         </is>
       </c>
       <c r="B808" s="7" t="inlineStr">
@@ -20674,7 +20674,7 @@
         </is>
       </c>
       <c r="C808" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D808" s="7" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="C809" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D809" s="5" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="C810" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D810" s="7" t="inlineStr">
         <is>
@@ -20740,16 +20740,16 @@
     <row r="811">
       <c r="A811" s="4" t="inlineStr">
         <is>
-          <t>10K Montmartre</t>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
         </is>
       </c>
       <c r="B811" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C811" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D811" s="5" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
     <row r="812">
       <c r="A812" s="8" t="inlineStr">
         <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
+          <t>10K Montmartre</t>
         </is>
       </c>
       <c r="B812" s="9" t="inlineStr">
@@ -20774,7 +20774,7 @@
         </is>
       </c>
       <c r="C812" s="9" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D812" s="9" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
       </c>
       <c r="E812" s="9" t="inlineStr">
         <is>
-          <t>0:29:19</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20799,7 +20799,7 @@
         </is>
       </c>
       <c r="C813" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D813" s="5" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="E813" s="5" t="inlineStr">
         <is>
-          <t>0:28:45</t>
+          <t>0:29:19</t>
         </is>
       </c>
     </row>
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="C814" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D814" s="9" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
       </c>
       <c r="E814" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:45</t>
         </is>
       </c>
     </row>
@@ -20849,23 +20849,23 @@
         </is>
       </c>
       <c r="C815" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D815" s="5" t="inlineStr">
         <is>
-          <t>0:26:45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E815" s="5" t="inlineStr">
         <is>
-          <t>0:29:25</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="816">
       <c r="A816" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Birmingham Run 10K</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B816" s="9" t="inlineStr">
@@ -20874,23 +20874,23 @@
         </is>
       </c>
       <c r="C816" s="9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D816" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:26:45</t>
         </is>
       </c>
       <c r="E816" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:25</t>
         </is>
       </c>
     </row>
     <row r="817">
       <c r="A817" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Bristol Run 10K</t>
+          <t>AJ Bell Great Birmingham Run 10K</t>
         </is>
       </c>
       <c r="B817" s="5" t="inlineStr">
@@ -20915,7 +20915,7 @@
     <row r="818">
       <c r="A818" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run</t>
+          <t>AJ Bell Great Bristol Run 10K</t>
         </is>
       </c>
       <c r="B818" s="9" t="inlineStr">
@@ -20924,16 +20924,16 @@
         </is>
       </c>
       <c r="C818" s="9" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D818" s="9" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E818" s="9" t="inlineStr">
         <is>
-          <t>0:30:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20949,23 +20949,23 @@
         </is>
       </c>
       <c r="C819" s="5" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D819" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E819" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:30:51</t>
         </is>
       </c>
     </row>
     <row r="820">
       <c r="A820" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B820" s="9" t="inlineStr">
@@ -20974,7 +20974,7 @@
         </is>
       </c>
       <c r="C820" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D820" s="9" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         </is>
       </c>
       <c r="C821" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D821" s="5" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
     <row r="822">
       <c r="A822" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great North 10K</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B822" s="9" t="inlineStr">
@@ -21040,7 +21040,7 @@
     <row r="823">
       <c r="A823" s="4" t="inlineStr">
         <is>
-          <t>ASICS LDNX</t>
+          <t>AJ Bell Great North 10K</t>
         </is>
       </c>
       <c r="B823" s="5" t="inlineStr">
@@ -21065,7 +21065,7 @@
     <row r="824">
       <c r="A824" s="8" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>ASICS LDNX</t>
         </is>
       </c>
       <c r="B824" s="9" t="inlineStr">
@@ -21074,7 +21074,7 @@
         </is>
       </c>
       <c r="C824" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D824" s="9" t="inlineStr">
         <is>
@@ -21099,16 +21099,16 @@
         </is>
       </c>
       <c r="C825" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D825" s="5" t="inlineStr">
         <is>
-          <t>0:29:37</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E825" s="5" t="inlineStr">
         <is>
-          <t>0:32:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21124,23 +21124,23 @@
         </is>
       </c>
       <c r="C826" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D826" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:37</t>
         </is>
       </c>
       <c r="E826" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:18</t>
         </is>
       </c>
     </row>
     <row r="827">
       <c r="A827" s="4" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B827" s="5" t="inlineStr">
@@ -21149,16 +21149,16 @@
         </is>
       </c>
       <c r="C827" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D827" s="5" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E827" s="5" t="inlineStr">
         <is>
-          <t>0:30:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21174,16 +21174,16 @@
         </is>
       </c>
       <c r="C828" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D828" s="9" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E828" s="9" t="inlineStr">
         <is>
-          <t>0:31:12</t>
+          <t>0:30:43</t>
         </is>
       </c>
     </row>
@@ -21199,23 +21199,23 @@
         </is>
       </c>
       <c r="C829" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D829" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E829" s="5" t="inlineStr">
         <is>
-          <t>0:31:29</t>
+          <t>0:31:12</t>
         </is>
       </c>
     </row>
     <row r="830">
       <c r="A830" s="8" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B830" s="9" t="inlineStr">
@@ -21224,16 +21224,16 @@
         </is>
       </c>
       <c r="C830" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D830" s="9" t="inlineStr">
         <is>
-          <t>0:29:08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E830" s="9" t="inlineStr">
         <is>
-          <t>0:33:25</t>
+          <t>0:31:29</t>
         </is>
       </c>
     </row>
@@ -21249,16 +21249,16 @@
         </is>
       </c>
       <c r="C831" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D831" s="5" t="inlineStr">
         <is>
-          <t>0:29:13</t>
+          <t>0:29:08</t>
         </is>
       </c>
       <c r="E831" s="5" t="inlineStr">
         <is>
-          <t>0:32:45</t>
+          <t>0:33:25</t>
         </is>
       </c>
     </row>
@@ -21274,16 +21274,16 @@
         </is>
       </c>
       <c r="C832" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D832" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:13</t>
         </is>
       </c>
       <c r="E832" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:45</t>
         </is>
       </c>
     </row>
@@ -21303,19 +21303,19 @@
       </c>
       <c r="D833" s="5" t="inlineStr">
         <is>
-          <t>0:28:36</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E833" s="5" t="inlineStr">
         <is>
-          <t>0:31:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" s="8" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B834" s="9" t="inlineStr">
@@ -21324,16 +21324,16 @@
         </is>
       </c>
       <c r="C834" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D834" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:36</t>
         </is>
       </c>
       <c r="E834" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:51</t>
         </is>
       </c>
     </row>
@@ -21349,7 +21349,7 @@
         </is>
       </c>
       <c r="C835" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D835" s="5" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="C836" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D836" s="9" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
     <row r="837">
       <c r="A837" s="4" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B837" s="5" t="inlineStr">
@@ -21399,16 +21399,16 @@
         </is>
       </c>
       <c r="C837" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D837" s="5" t="inlineStr">
         <is>
-          <t>0:28:52</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E837" s="5" t="inlineStr">
         <is>
-          <t>0:31:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21424,16 +21424,16 @@
         </is>
       </c>
       <c r="C838" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D838" s="9" t="inlineStr">
         <is>
-          <t>0:28:46</t>
+          <t>0:28:52</t>
         </is>
       </c>
       <c r="E838" s="9" t="inlineStr">
         <is>
-          <t>0:32:33</t>
+          <t>0:31:59</t>
         </is>
       </c>
     </row>
@@ -21449,16 +21449,16 @@
         </is>
       </c>
       <c r="C839" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D839" s="5" t="inlineStr">
         <is>
-          <t>0:29:22</t>
+          <t>0:28:46</t>
         </is>
       </c>
       <c r="E839" s="5" t="inlineStr">
         <is>
-          <t>0:34:32</t>
+          <t>0:32:33</t>
         </is>
       </c>
     </row>
@@ -21474,23 +21474,23 @@
         </is>
       </c>
       <c r="C840" s="9" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D840" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:22</t>
         </is>
       </c>
       <c r="E840" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:34:32</t>
         </is>
       </c>
     </row>
     <row r="841">
       <c r="A841" s="4" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B841" s="5" t="inlineStr">
@@ -21499,7 +21499,7 @@
         </is>
       </c>
       <c r="C841" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D841" s="5" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         </is>
       </c>
       <c r="C842" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D842" s="9" t="inlineStr">
         <is>
@@ -21549,16 +21549,16 @@
         </is>
       </c>
       <c r="C843" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D843" s="5" t="inlineStr">
         <is>
-          <t>0:28:27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E843" s="5" t="inlineStr">
         <is>
-          <t>0:31:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21578,19 +21578,19 @@
       </c>
       <c r="D844" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:27</t>
         </is>
       </c>
       <c r="E844" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:49</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" s="4" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B845" s="5" t="inlineStr">
@@ -21599,7 +21599,7 @@
         </is>
       </c>
       <c r="C845" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D845" s="5" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="C846" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D846" s="9" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         </is>
       </c>
       <c r="C847" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D847" s="5" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         </is>
       </c>
       <c r="C848" s="9" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D848" s="9" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
     <row r="849">
       <c r="A849" s="4" t="inlineStr">
         <is>
-          <t>Great Scottish Run 10K</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B849" s="5" t="inlineStr">
@@ -21699,7 +21699,7 @@
         </is>
       </c>
       <c r="C849" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D849" s="5" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
     <row r="850">
       <c r="A850" s="8" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
+          <t>Great Scottish Run 10K</t>
         </is>
       </c>
       <c r="B850" s="9" t="inlineStr">
@@ -21724,7 +21724,7 @@
         </is>
       </c>
       <c r="C850" s="9" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D850" s="9" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
     <row r="851">
       <c r="A851" s="4" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
         </is>
       </c>
       <c r="B851" s="5" t="inlineStr">
@@ -21749,7 +21749,7 @@
         </is>
       </c>
       <c r="C851" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D851" s="5" t="inlineStr">
         <is>
@@ -21774,7 +21774,7 @@
         </is>
       </c>
       <c r="C852" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D852" s="9" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
       </c>
       <c r="E852" s="9" t="inlineStr">
         <is>
-          <t>0:31:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21799,23 +21799,23 @@
         </is>
       </c>
       <c r="C853" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D853" s="5" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E853" s="5" t="inlineStr">
         <is>
-          <t>0:31:11</t>
+          <t>0:31:18</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" s="8" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B854" s="9" t="inlineStr">
@@ -21824,16 +21824,16 @@
         </is>
       </c>
       <c r="C854" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D854" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E854" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:11</t>
         </is>
       </c>
     </row>
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="C855" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D855" s="5" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         </is>
       </c>
       <c r="C856" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D856" s="9" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
     <row r="857">
       <c r="A857" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B857" s="5" t="inlineStr">
@@ -21915,7 +21915,7 @@
     <row r="858">
       <c r="A858" s="8" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>Run in Lyon</t>
         </is>
       </c>
       <c r="B858" s="9" t="inlineStr">
@@ -21924,7 +21924,7 @@
         </is>
       </c>
       <c r="C858" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D858" s="9" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         </is>
       </c>
       <c r="C859" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D859" s="5" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         </is>
       </c>
       <c r="C860" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D860" s="9" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
     <row r="861">
       <c r="A861" s="4" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B861" s="5" t="inlineStr">
@@ -21999,7 +21999,7 @@
         </is>
       </c>
       <c r="C861" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D861" s="5" t="inlineStr">
         <is>
@@ -22024,16 +22024,16 @@
         </is>
       </c>
       <c r="C862" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D862" s="9" t="inlineStr">
         <is>
-          <t>0:29:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E862" s="9" t="inlineStr">
         <is>
-          <t>0:32:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22049,23 +22049,23 @@
         </is>
       </c>
       <c r="C863" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D863" s="5" t="inlineStr">
         <is>
-          <t>0:29:33</t>
+          <t>0:29:41</t>
         </is>
       </c>
       <c r="E863" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:51</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" s="8" t="inlineStr">
         <is>
-          <t>Standard Chartered KL 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B864" s="9" t="inlineStr">
@@ -22078,19 +22078,19 @@
       </c>
       <c r="D864" s="9" t="inlineStr">
         <is>
-          <t>0:32:26</t>
+          <t>0:29:33</t>
         </is>
       </c>
       <c r="E864" s="9" t="inlineStr">
         <is>
-          <t>0:39:23</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" s="4" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Standard Chartered KL 10K</t>
         </is>
       </c>
       <c r="B865" s="5" t="inlineStr">
@@ -22099,16 +22099,16 @@
         </is>
       </c>
       <c r="C865" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D865" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:26</t>
         </is>
       </c>
       <c r="E865" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:39:23</t>
         </is>
       </c>
     </row>
@@ -22124,7 +22124,7 @@
         </is>
       </c>
       <c r="C866" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D866" s="9" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         </is>
       </c>
       <c r="C867" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D867" s="5" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
     <row r="868">
       <c r="A868" s="8" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B868" s="9" t="inlineStr">
@@ -22174,7 +22174,7 @@
         </is>
       </c>
       <c r="C868" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D868" s="9" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         </is>
       </c>
       <c r="C869" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D869" s="5" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="C870" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D870" s="9" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
     <row r="871">
       <c r="A871" s="4" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B871" s="5" t="inlineStr">
@@ -22249,7 +22249,7 @@
         </is>
       </c>
       <c r="C871" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D871" s="5" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         </is>
       </c>
       <c r="C872" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D872" s="9" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         </is>
       </c>
       <c r="C873" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D873" s="5" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
     <row r="874">
       <c r="A874" s="8" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B874" s="9" t="inlineStr">
@@ -22324,7 +22324,7 @@
         </is>
       </c>
       <c r="C874" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D874" s="9" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         </is>
       </c>
       <c r="C875" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D875" s="5" t="inlineStr">
         <is>
@@ -22374,23 +22374,23 @@
         </is>
       </c>
       <c r="C876" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D876" s="9" t="inlineStr">
         <is>
-          <t>0:28:09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E876" s="9" t="inlineStr">
         <is>
-          <t>0:32:54</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" s="4" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Vancouver Sun Run</t>
         </is>
       </c>
       <c r="B877" s="5" t="inlineStr">
@@ -22399,16 +22399,16 @@
         </is>
       </c>
       <c r="C877" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D877" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:09</t>
         </is>
       </c>
       <c r="E877" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:54</t>
         </is>
       </c>
     </row>
@@ -22424,16 +22424,16 @@
         </is>
       </c>
       <c r="C878" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D878" s="9" t="inlineStr">
         <is>
-          <t>0:29:14</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E878" s="9" t="inlineStr">
         <is>
-          <t>0:31:36</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22449,28 +22449,28 @@
         </is>
       </c>
       <c r="C879" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D879" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:14</t>
         </is>
       </c>
       <c r="E879" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:36</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Birmingham Run</t>
+          <t>Vitality London 10,000</t>
         </is>
       </c>
       <c r="B880" s="9" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C880" s="9" t="n">
@@ -22490,25 +22490,25 @@
     <row r="881">
       <c r="A881" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great South Run</t>
+          <t>AJ Bell Great Birmingham Run</t>
         </is>
       </c>
       <c r="B881" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>SEMI</t>
         </is>
       </c>
       <c r="C881" s="5" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D881" s="5" t="inlineStr">
         <is>
-          <t>0:47:19</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E881" s="5" t="inlineStr">
         <is>
-          <t>0:50:42</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22524,23 +22524,23 @@
         </is>
       </c>
       <c r="C882" s="9" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D882" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:47:19</t>
         </is>
       </c>
       <c r="E882" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:50:42</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" s="4" t="inlineStr">
         <is>
-          <t>Army Ten Miler</t>
+          <t>AJ Bell Great South Run</t>
         </is>
       </c>
       <c r="B883" s="5" t="inlineStr">
@@ -22565,7 +22565,7 @@
     <row r="884">
       <c r="A884" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>Army Ten Miler</t>
         </is>
       </c>
       <c r="B884" s="9" t="inlineStr">
@@ -22574,7 +22574,7 @@
         </is>
       </c>
       <c r="C884" s="9" t="n">
-        <v>2005</v>
+        <v>2025</v>
       </c>
       <c r="D884" s="9" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
       </c>
       <c r="E884" s="9" t="inlineStr">
         <is>
-          <t>0:38:22</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22599,16 +22599,16 @@
         </is>
       </c>
       <c r="C885" s="5" t="n">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="D885" s="5" t="inlineStr">
         <is>
-          <t>0:33:31</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E885" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:38:22</t>
         </is>
       </c>
     </row>
@@ -22624,16 +22624,16 @@
         </is>
       </c>
       <c r="C886" s="9" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D886" s="9" t="inlineStr">
         <is>
-          <t>0:34:15</t>
+          <t>0:33:31</t>
         </is>
       </c>
       <c r="E886" s="9" t="inlineStr">
         <is>
-          <t>0:38:07</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22649,16 +22649,16 @@
         </is>
       </c>
       <c r="C887" s="5" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="D887" s="5" t="inlineStr">
         <is>
-          <t>0:34:40</t>
+          <t>0:34:15</t>
         </is>
       </c>
       <c r="E887" s="5" t="inlineStr">
         <is>
-          <t>0:39:02</t>
+          <t>0:38:07</t>
         </is>
       </c>
     </row>
@@ -22674,16 +22674,16 @@
         </is>
       </c>
       <c r="C888" s="9" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="D888" s="9" t="inlineStr">
         <is>
-          <t>0:35:01</t>
+          <t>0:34:40</t>
         </is>
       </c>
       <c r="E888" s="9" t="inlineStr">
         <is>
-          <t>0:39:28</t>
+          <t>0:39:02</t>
         </is>
       </c>
     </row>
@@ -22699,16 +22699,16 @@
         </is>
       </c>
       <c r="C889" s="5" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D889" s="5" t="inlineStr">
         <is>
-          <t>0:36:10</t>
+          <t>0:35:01</t>
         </is>
       </c>
       <c r="E889" s="5" t="inlineStr">
         <is>
-          <t>0:42:05</t>
+          <t>0:39:28</t>
         </is>
       </c>
     </row>
@@ -22724,23 +22724,23 @@
         </is>
       </c>
       <c r="C890" s="9" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D890" s="9" t="inlineStr">
         <is>
-          <t>0:37:02</t>
+          <t>0:36:10</t>
         </is>
       </c>
       <c r="E890" s="9" t="inlineStr">
         <is>
-          <t>0:43:48</t>
+          <t>0:42:05</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" s="4" t="inlineStr">
         <is>
-          <t>Boilermaker Road Race</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B891" s="5" t="inlineStr">
@@ -22749,23 +22749,23 @@
         </is>
       </c>
       <c r="C891" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D891" s="5" t="inlineStr">
         <is>
-          <t>0:42:44</t>
+          <t>0:37:02</t>
         </is>
       </c>
       <c r="E891" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:43:48</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="8" t="inlineStr">
         <is>
-          <t>Broad Street Run</t>
+          <t>Boilermaker Road Race</t>
         </is>
       </c>
       <c r="B892" s="9" t="inlineStr">
@@ -22778,19 +22778,19 @@
       </c>
       <c r="D892" s="9" t="inlineStr">
         <is>
-          <t>0:46:13</t>
+          <t>0:42:44</t>
         </is>
       </c>
       <c r="E892" s="9" t="inlineStr">
         <is>
-          <t>0:54:01</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" s="4" t="inlineStr">
         <is>
-          <t>City2Surf</t>
+          <t>Broad Street Run</t>
         </is>
       </c>
       <c r="B893" s="5" t="inlineStr">
@@ -22799,23 +22799,23 @@
         </is>
       </c>
       <c r="C893" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D893" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:46:13</t>
         </is>
       </c>
       <c r="E893" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:54:01</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>City2Surf</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
@@ -22824,7 +22824,7 @@
         </is>
       </c>
       <c r="C894" s="9" t="n">
-        <v>2009</v>
+        <v>2024</v>
       </c>
       <c r="D894" s="9" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
       </c>
       <c r="E894" s="9" t="inlineStr">
         <is>
-          <t>0:50:39</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22849,7 +22849,7 @@
         </is>
       </c>
       <c r="C895" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D895" s="5" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
       </c>
       <c r="E895" s="5" t="inlineStr">
         <is>
-          <t>0:51:30</t>
+          <t>0:50:39</t>
         </is>
       </c>
     </row>
@@ -22874,16 +22874,16 @@
         </is>
       </c>
       <c r="C896" s="9" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D896" s="9" t="inlineStr">
         <is>
-          <t>0:44:27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E896" s="9" t="inlineStr">
         <is>
-          <t>0:51:57</t>
+          <t>0:51:30</t>
         </is>
       </c>
     </row>
@@ -22899,16 +22899,16 @@
         </is>
       </c>
       <c r="C897" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D897" s="5" t="inlineStr">
         <is>
-          <t>0:44:48</t>
+          <t>0:44:27</t>
         </is>
       </c>
       <c r="E897" s="5" t="inlineStr">
         <is>
-          <t>0:51:42</t>
+          <t>0:51:57</t>
         </is>
       </c>
     </row>
@@ -22924,16 +22924,16 @@
         </is>
       </c>
       <c r="C898" s="9" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D898" s="9" t="inlineStr">
         <is>
-          <t>0:45:28</t>
+          <t>0:44:48</t>
         </is>
       </c>
       <c r="E898" s="9" t="inlineStr">
         <is>
-          <t>0:51:33</t>
+          <t>0:51:42</t>
         </is>
       </c>
     </row>
@@ -22949,16 +22949,16 @@
         </is>
       </c>
       <c r="C899" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D899" s="5" t="inlineStr">
         <is>
-          <t>0:45:45</t>
+          <t>0:45:28</t>
         </is>
       </c>
       <c r="E899" s="5" t="inlineStr">
         <is>
-          <t>0:53:09</t>
+          <t>0:51:33</t>
         </is>
       </c>
     </row>
@@ -22974,16 +22974,16 @@
         </is>
       </c>
       <c r="C900" s="9" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D900" s="9" t="inlineStr">
         <is>
-          <t>0:45:15</t>
+          <t>0:45:45</t>
         </is>
       </c>
       <c r="E900" s="9" t="inlineStr">
         <is>
-          <t>0:50:45</t>
+          <t>0:53:09</t>
         </is>
       </c>
     </row>
@@ -22999,16 +22999,16 @@
         </is>
       </c>
       <c r="C901" s="5" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D901" s="5" t="inlineStr">
         <is>
-          <t>0:49:00</t>
+          <t>0:45:15</t>
         </is>
       </c>
       <c r="E901" s="5" t="inlineStr">
         <is>
-          <t>0:55:44</t>
+          <t>0:50:45</t>
         </is>
       </c>
     </row>
@@ -23024,16 +23024,16 @@
         </is>
       </c>
       <c r="C902" s="9" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D902" s="9" t="inlineStr">
         <is>
-          <t>0:44:51</t>
+          <t>0:49:00</t>
         </is>
       </c>
       <c r="E902" s="9" t="inlineStr">
         <is>
-          <t>0:51:15</t>
+          <t>0:55:44</t>
         </is>
       </c>
     </row>
@@ -23049,23 +23049,23 @@
         </is>
       </c>
       <c r="C903" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D903" s="5" t="inlineStr">
         <is>
-          <t>0:46:07</t>
+          <t>0:44:51</t>
         </is>
       </c>
       <c r="E903" s="5" t="inlineStr">
         <is>
-          <t>0:50:51</t>
+          <t>0:51:15</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" s="8" t="inlineStr">
         <is>
-          <t>Falmouth Road Race</t>
+          <t>Dam tot Damloop</t>
         </is>
       </c>
       <c r="B904" s="9" t="inlineStr">
@@ -23078,24 +23078,24 @@
       </c>
       <c r="D904" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:46:07</t>
         </is>
       </c>
       <c r="E904" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:50:51</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" s="4" t="inlineStr">
         <is>
-          <t>Great Scottish Run</t>
+          <t>Falmouth Road Race</t>
         </is>
       </c>
       <c r="B905" s="5" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="C905" s="5" t="n">
@@ -23115,12 +23115,12 @@
     <row r="906">
       <c r="A906" s="8" t="inlineStr">
         <is>
-          <t>Lilac Bloomsday Run</t>
+          <t>Great Scottish Run</t>
         </is>
       </c>
       <c r="B906" s="9" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>SEMI</t>
         </is>
       </c>
       <c r="C906" s="9" t="n">
@@ -23140,55 +23140,55 @@
     <row r="907">
       <c r="A907" s="4" t="inlineStr">
         <is>
+          <t>Lilac Bloomsday Run</t>
+        </is>
+      </c>
+      <c r="B907" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C907" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D907" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E907" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="8" t="inlineStr">
+        <is>
           <t>Manchester Road Race</t>
         </is>
       </c>
-      <c r="B907" s="5" t="inlineStr">
+      <c r="B908" s="9" t="inlineStr">
         <is>
           <t>AUTRE</t>
         </is>
       </c>
-      <c r="C907" s="5" t="n">
+      <c r="C908" s="9" t="n">
         <v>2024</v>
       </c>
-      <c r="D907" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E907" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="908">
-      <c r="A908" t="inlineStr">
-        <is>
-          <t>Schneider Electric Marathon de Paris</t>
-        </is>
-      </c>
-      <c r="B908" t="inlineStr">
-        <is>
-          <t>42K</t>
-        </is>
-      </c>
-      <c r="C908" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D908" t="inlineStr">
-        <is>
-          <t>2:04:21</t>
-        </is>
-      </c>
-      <c r="E908" t="inlineStr">
-        <is>
-          <t>2:26:11</t>
+      <c r="D908" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E908" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E907"/>
+  <autoFilter ref="A1:E908"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Chronos_Vainqueurs.xlsx
+++ b/Chronos_Vainqueurs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$908</definedName>
@@ -11228,12 +11228,12 @@
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>2:05:16</t>
+          <t>2:05:18</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>2:18:34</t>
+          <t>2:18:35</t>
         </is>
       </c>
     </row>

--- a/Chronos_Vainqueurs.xlsx
+++ b/Chronos_Vainqueurs.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$908</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$909</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E908"/>
+  <dimension ref="A1:E909"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -11124,16 +11124,16 @@
         </is>
       </c>
       <c r="C426" s="3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>2:05:00</t>
+          <t>2:04:21</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
         <is>
-          <t>2:19:48</t>
+          <t>2:26:11</t>
         </is>
       </c>
     </row>
@@ -11149,16 +11149,16 @@
         </is>
       </c>
       <c r="C427" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D427" s="5" t="inlineStr">
         <is>
-          <t>2:07:15</t>
+          <t>2:05:07</t>
         </is>
       </c>
       <c r="E427" s="5" t="inlineStr">
         <is>
-          <t>2:23:19</t>
+          <t>2:19:48</t>
         </is>
       </c>
     </row>
@@ -11174,16 +11174,16 @@
         </is>
       </c>
       <c r="C428" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>2:05:33</t>
+          <t>2:07:15</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>2:20:45</t>
+          <t>2:23:19</t>
         </is>
       </c>
     </row>
@@ -11199,11 +11199,11 @@
         </is>
       </c>
       <c r="C429" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D429" s="5" t="inlineStr">
         <is>
-          <t>2:05:25</t>
+          <t>2:05:33</t>
         </is>
       </c>
       <c r="E429" s="5" t="inlineStr">
@@ -11224,23 +11224,23 @@
         </is>
       </c>
       <c r="C430" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>2:05:18</t>
+          <t>2:05:25</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>2:18:35</t>
+          <t>2:20:45</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>Seoul Marathon</t>
+          <t>Schneider Electric Marathon de Paris</t>
         </is>
       </c>
       <c r="B431" s="5" t="inlineStr">
@@ -11249,16 +11249,16 @@
         </is>
       </c>
       <c r="C431" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>2:05:27</t>
+          <t>2:05:18</t>
         </is>
       </c>
       <c r="E431" s="5" t="inlineStr">
         <is>
-          <t>2:28:32</t>
+          <t>2:18:35</t>
         </is>
       </c>
     </row>
@@ -11274,16 +11274,16 @@
         </is>
       </c>
       <c r="C432" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>2:06:08</t>
+          <t>2:05:27</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>2:21:32</t>
+          <t>2:28:32</t>
         </is>
       </c>
     </row>
@@ -11299,23 +11299,23 @@
         </is>
       </c>
       <c r="C433" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D433" s="5" t="inlineStr">
         <is>
-          <t>2:05:42</t>
+          <t>2:06:08</t>
         </is>
       </c>
       <c r="E433" s="5" t="inlineStr">
         <is>
-          <t>2:21:36</t>
+          <t>2:21:32</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>St. Jude Memphis Marathon</t>
+          <t>Seoul Marathon</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
@@ -11324,16 +11324,16 @@
         </is>
       </c>
       <c r="C434" s="3" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D434" s="3" t="inlineStr">
         <is>
-          <t>2:38:23</t>
+          <t>2:05:42</t>
         </is>
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>3:00:20</t>
+          <t>2:21:36</t>
         </is>
       </c>
     </row>
@@ -11349,16 +11349,16 @@
         </is>
       </c>
       <c r="C435" s="5" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
-          <t>2:30:21</t>
+          <t>2:38:23</t>
         </is>
       </c>
       <c r="E435" s="5" t="inlineStr">
         <is>
-          <t>2:56:44</t>
+          <t>3:00:20</t>
         </is>
       </c>
     </row>
@@ -11374,16 +11374,16 @@
         </is>
       </c>
       <c r="C436" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D436" s="3" t="inlineStr">
         <is>
-          <t>2:34:18</t>
+          <t>2:30:21</t>
         </is>
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>2:54:45</t>
+          <t>2:56:44</t>
         </is>
       </c>
     </row>
@@ -11399,23 +11399,23 @@
         </is>
       </c>
       <c r="C437" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
-          <t>2:28:03</t>
+          <t>2:34:18</t>
         </is>
       </c>
       <c r="E437" s="5" t="inlineStr">
         <is>
-          <t>2:51:12</t>
+          <t>2:54:45</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Marathon</t>
+          <t>St. Jude Memphis Marathon</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
@@ -11424,16 +11424,16 @@
         </is>
       </c>
       <c r="C438" s="3" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>2:09:20</t>
+          <t>2:28:03</t>
         </is>
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>2:26:13</t>
+          <t>2:51:12</t>
         </is>
       </c>
     </row>
@@ -11449,23 +11449,23 @@
         </is>
       </c>
       <c r="C439" s="5" t="n">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="D439" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:09:20</t>
         </is>
       </c>
       <c r="E439" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:26:13</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>Standard Chartered KL Marathon</t>
+          <t>Standard Chartered Hong Kong Marathon</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
@@ -11474,23 +11474,23 @@
         </is>
       </c>
       <c r="C440" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>2:17:28</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>2:41:36</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Singapore Marathon</t>
+          <t>Standard Chartered KL Marathon</t>
         </is>
       </c>
       <c r="B441" s="5" t="inlineStr">
@@ -11499,16 +11499,16 @@
         </is>
       </c>
       <c r="C441" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D441" s="5" t="inlineStr">
         <is>
-          <t>2:16:06</t>
+          <t>2:17:28</t>
         </is>
       </c>
       <c r="E441" s="5" t="inlineStr">
         <is>
-          <t>2:39:04</t>
+          <t>2:41:36</t>
         </is>
       </c>
     </row>
@@ -11524,23 +11524,23 @@
         </is>
       </c>
       <c r="C442" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D442" s="3" t="inlineStr">
         <is>
-          <t>2:15:40</t>
+          <t>2:16:06</t>
         </is>
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>2:41:24</t>
+          <t>2:39:04</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="4" t="inlineStr">
         <is>
-          <t>Stockholm Marathon</t>
+          <t>Standard Chartered Singapore Marathon</t>
         </is>
       </c>
       <c r="B443" s="5" t="inlineStr">
@@ -11549,16 +11549,16 @@
         </is>
       </c>
       <c r="C443" s="5" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D443" s="5" t="inlineStr">
         <is>
-          <t>2:18:22</t>
+          <t>2:15:40</t>
         </is>
       </c>
       <c r="E443" s="5" t="inlineStr">
         <is>
-          <t>2:34:14</t>
+          <t>2:41:24</t>
         </is>
       </c>
     </row>
@@ -11574,16 +11574,16 @@
         </is>
       </c>
       <c r="C444" s="3" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>2:10:58</t>
+          <t>2:18:22</t>
         </is>
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>2:31:46</t>
+          <t>2:34:14</t>
         </is>
       </c>
     </row>
@@ -11599,16 +11599,16 @@
         </is>
       </c>
       <c r="C445" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D445" s="5" t="inlineStr">
         <is>
-          <t>2:11:36</t>
+          <t>2:10:58</t>
         </is>
       </c>
       <c r="E445" s="5" t="inlineStr">
         <is>
-          <t>2:35:45</t>
+          <t>2:31:46</t>
         </is>
       </c>
     </row>
@@ -11624,16 +11624,16 @@
         </is>
       </c>
       <c r="C446" s="3" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>2:13:30</t>
+          <t>2:11:36</t>
         </is>
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>2:40:28</t>
+          <t>2:35:45</t>
         </is>
       </c>
     </row>
@@ -11649,16 +11649,16 @@
         </is>
       </c>
       <c r="C447" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D447" s="5" t="inlineStr">
         <is>
-          <t>2:10:10</t>
+          <t>2:13:30</t>
         </is>
       </c>
       <c r="E447" s="5" t="inlineStr">
         <is>
-          <t>2:33:38</t>
+          <t>2:40:28</t>
         </is>
       </c>
     </row>
@@ -11674,16 +11674,16 @@
         </is>
       </c>
       <c r="C448" s="3" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>2:12:24</t>
+          <t>2:10:10</t>
         </is>
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>2:29:03</t>
+          <t>2:33:38</t>
         </is>
       </c>
     </row>
@@ -11699,16 +11699,16 @@
         </is>
       </c>
       <c r="C449" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D449" s="5" t="inlineStr">
         <is>
-          <t>2:11:08</t>
+          <t>2:12:24</t>
         </is>
       </c>
       <c r="E449" s="5" t="inlineStr">
         <is>
-          <t>2:31:48</t>
+          <t>2:29:03</t>
         </is>
       </c>
     </row>
@@ -11724,16 +11724,16 @@
         </is>
       </c>
       <c r="C450" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>2:10:32</t>
+          <t>2:11:08</t>
         </is>
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>2:30:44</t>
+          <t>2:31:48</t>
         </is>
       </c>
     </row>
@@ -11749,16 +11749,16 @@
         </is>
       </c>
       <c r="C451" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D451" s="5" t="inlineStr">
         <is>
-          <t>2:14:17</t>
+          <t>2:10:32</t>
         </is>
       </c>
       <c r="E451" s="5" t="inlineStr">
         <is>
-          <t>2:31:46</t>
+          <t>2:30:44</t>
         </is>
       </c>
     </row>
@@ -11774,23 +11774,23 @@
         </is>
       </c>
       <c r="C452" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D452" s="3" t="inlineStr">
         <is>
-          <t>2:11:34</t>
+          <t>2:14:17</t>
         </is>
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>2:30:38</t>
+          <t>2:31:46</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="4" t="inlineStr">
         <is>
-          <t>TCS Amsterdam Marathon</t>
+          <t>Stockholm Marathon</t>
         </is>
       </c>
       <c r="B453" s="5" t="inlineStr">
@@ -11799,16 +11799,16 @@
         </is>
       </c>
       <c r="C453" s="5" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
-          <t>2:08:47</t>
+          <t>2:11:34</t>
         </is>
       </c>
       <c r="E453" s="5" t="inlineStr">
         <is>
-          <t>2:28:42</t>
+          <t>2:30:38</t>
         </is>
       </c>
     </row>
@@ -11824,16 +11824,16 @@
         </is>
       </c>
       <c r="C454" s="3" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D454" s="3" t="inlineStr">
         <is>
-          <t>2:08:22</t>
+          <t>2:08:47</t>
         </is>
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>2:26:04</t>
+          <t>2:28:42</t>
         </is>
       </c>
     </row>
@@ -11849,16 +11849,16 @@
         </is>
       </c>
       <c r="C455" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D455" s="5" t="inlineStr">
         <is>
-          <t>2:07:45</t>
+          <t>2:08:22</t>
         </is>
       </c>
       <c r="E455" s="5" t="inlineStr">
         <is>
-          <t>2:23:54</t>
+          <t>2:26:04</t>
         </is>
       </c>
     </row>
@@ -11874,16 +11874,16 @@
         </is>
       </c>
       <c r="C456" s="3" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D456" s="3" t="inlineStr">
         <is>
-          <t>2:06:38</t>
+          <t>2:07:45</t>
         </is>
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>2:27:08</t>
+          <t>2:23:54</t>
         </is>
       </c>
     </row>
@@ -11899,16 +11899,16 @@
         </is>
       </c>
       <c r="C457" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D457" s="5" t="inlineStr">
         <is>
-          <t>2:06:20</t>
+          <t>2:06:38</t>
         </is>
       </c>
       <c r="E457" s="5" t="inlineStr">
         <is>
-          <t>2:28:39</t>
+          <t>2:27:08</t>
         </is>
       </c>
     </row>
@@ -11924,16 +11924,16 @@
         </is>
       </c>
       <c r="C458" s="3" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D458" s="3" t="inlineStr">
         <is>
-          <t>2:09:27</t>
+          <t>2:06:20</t>
         </is>
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>2:28:18</t>
+          <t>2:28:39</t>
         </is>
       </c>
     </row>
@@ -11949,16 +11949,16 @@
         </is>
       </c>
       <c r="C459" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D459" s="5" t="inlineStr">
         <is>
-          <t>2:08:41</t>
+          <t>2:09:27</t>
         </is>
       </c>
       <c r="E459" s="5" t="inlineStr">
         <is>
-          <t>2:27:37</t>
+          <t>2:28:18</t>
         </is>
       </c>
     </row>
@@ -11974,16 +11974,16 @@
         </is>
       </c>
       <c r="C460" s="3" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D460" s="3" t="inlineStr">
         <is>
-          <t>2:07:57</t>
+          <t>2:08:41</t>
         </is>
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>2:28:41</t>
+          <t>2:27:37</t>
         </is>
       </c>
     </row>
@@ -11999,16 +11999,16 @@
         </is>
       </c>
       <c r="C461" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D461" s="5" t="inlineStr">
         <is>
-          <t>2:06:13</t>
+          <t>2:07:57</t>
         </is>
       </c>
       <c r="E461" s="5" t="inlineStr">
         <is>
-          <t>2:29:02</t>
+          <t>2:28:41</t>
         </is>
       </c>
     </row>
@@ -12024,16 +12024,16 @@
         </is>
       </c>
       <c r="C462" s="3" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D462" s="3" t="inlineStr">
         <is>
-          <t>2:06:00</t>
+          <t>2:06:13</t>
         </is>
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>2:25:46</t>
+          <t>2:29:02</t>
         </is>
       </c>
     </row>
@@ -12049,16 +12049,16 @@
         </is>
       </c>
       <c r="C463" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D463" s="5" t="inlineStr">
         <is>
-          <t>2:05:44</t>
+          <t>2:06:00</t>
         </is>
       </c>
       <c r="E463" s="5" t="inlineStr">
         <is>
-          <t>2:28:28</t>
+          <t>2:25:46</t>
         </is>
       </c>
     </row>
@@ -12074,16 +12074,16 @@
         </is>
       </c>
       <c r="C464" s="3" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D464" s="3" t="inlineStr">
         <is>
-          <t>2:05:16</t>
+          <t>2:05:44</t>
         </is>
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>2:24:34</t>
+          <t>2:28:28</t>
         </is>
       </c>
     </row>
@@ -12099,16 +12099,16 @@
         </is>
       </c>
       <c r="C465" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D465" s="5" t="inlineStr">
         <is>
-          <t>2:05:36</t>
+          <t>2:05:16</t>
         </is>
       </c>
       <c r="E465" s="5" t="inlineStr">
         <is>
-          <t>2:21:09</t>
+          <t>2:24:34</t>
         </is>
       </c>
     </row>
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="C466" s="3" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D466" s="3" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
       </c>
       <c r="E466" s="3" t="inlineStr">
         <is>
-          <t>2:24:27</t>
+          <t>2:21:09</t>
         </is>
       </c>
     </row>
@@ -12149,7 +12149,7 @@
         </is>
       </c>
       <c r="C467" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D467" s="5" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="E467" s="5" t="inlineStr">
         <is>
-          <t>2:23:27</t>
+          <t>2:24:27</t>
         </is>
       </c>
     </row>
@@ -12174,16 +12174,16 @@
         </is>
       </c>
       <c r="C468" s="3" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D468" s="3" t="inlineStr">
         <is>
-          <t>2:06:19</t>
+          <t>2:05:36</t>
         </is>
       </c>
       <c r="E468" s="3" t="inlineStr">
         <is>
-          <t>2:24:11</t>
+          <t>2:23:27</t>
         </is>
       </c>
     </row>
@@ -12199,16 +12199,16 @@
         </is>
       </c>
       <c r="C469" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D469" s="5" t="inlineStr">
         <is>
-          <t>2:05:20</t>
+          <t>2:06:19</t>
         </is>
       </c>
       <c r="E469" s="5" t="inlineStr">
         <is>
-          <t>2:23:20</t>
+          <t>2:24:11</t>
         </is>
       </c>
     </row>
@@ -12224,16 +12224,16 @@
         </is>
       </c>
       <c r="C470" s="3" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D470" s="3" t="inlineStr">
         <is>
-          <t>2:05:09</t>
+          <t>2:05:20</t>
         </is>
       </c>
       <c r="E470" s="3" t="inlineStr">
         <is>
-          <t>2:21:53</t>
+          <t>2:23:20</t>
         </is>
       </c>
     </row>
@@ -12249,16 +12249,16 @@
         </is>
       </c>
       <c r="C471" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D471" s="5" t="inlineStr">
         <is>
-          <t>2:04:06</t>
+          <t>2:05:09</t>
         </is>
       </c>
       <c r="E471" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:21:53</t>
         </is>
       </c>
     </row>
@@ -12274,16 +12274,16 @@
         </is>
       </c>
       <c r="C472" s="3" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="D472" s="3" t="inlineStr">
         <is>
-          <t>2:03:38</t>
+          <t>2:04:06</t>
         </is>
       </c>
       <c r="E472" s="3" t="inlineStr">
         <is>
-          <t>2:17:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -12303,12 +12303,12 @@
       </c>
       <c r="D473" s="5" t="inlineStr">
         <is>
-          <t>2:03:36</t>
+          <t>2:03:38</t>
         </is>
       </c>
       <c r="E473" s="5" t="inlineStr">
         <is>
-          <t>2:17:55</t>
+          <t>2:17:57</t>
         </is>
       </c>
     </row>
@@ -12324,16 +12324,16 @@
         </is>
       </c>
       <c r="C474" s="3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D474" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:03:36</t>
         </is>
       </c>
       <c r="E474" s="3" t="inlineStr">
         <is>
-          <t>2:17:20</t>
+          <t>2:17:55</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="D475" s="5" t="inlineStr">
         <is>
-          <t>2:04:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E475" s="5" t="inlineStr">
         <is>
-          <t>2:17:18</t>
+          <t>2:17:20</t>
         </is>
       </c>
     </row>
@@ -12374,16 +12374,16 @@
         </is>
       </c>
       <c r="C476" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D476" s="3" t="inlineStr">
         <is>
-          <t>2:04:18</t>
+          <t>2:04:48</t>
         </is>
       </c>
       <c r="E476" s="3" t="inlineStr">
         <is>
-          <t>2:18:21</t>
+          <t>2:17:18</t>
         </is>
       </c>
     </row>
@@ -12424,16 +12424,16 @@
         </is>
       </c>
       <c r="C478" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D478" s="3" t="inlineStr">
         <is>
-          <t>2:05:38</t>
+          <t>2:04:18</t>
         </is>
       </c>
       <c r="E478" s="3" t="inlineStr">
         <is>
-          <t>2:16:52</t>
+          <t>2:18:21</t>
         </is>
       </c>
     </row>
@@ -12453,12 +12453,12 @@
       </c>
       <c r="D479" s="5" t="inlineStr">
         <is>
-          <t>2:05:35</t>
+          <t>2:05:38</t>
         </is>
       </c>
       <c r="E479" s="5" t="inlineStr">
         <is>
-          <t>2:16:50</t>
+          <t>2:16:52</t>
         </is>
       </c>
     </row>
@@ -12474,16 +12474,16 @@
         </is>
       </c>
       <c r="C480" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D480" s="3" t="inlineStr">
         <is>
-          <t>2:03:31</t>
+          <t>2:05:35</t>
         </is>
       </c>
       <c r="E480" s="3" t="inlineStr">
         <is>
-          <t>2:17:37</t>
+          <t>2:16:50</t>
         </is>
       </c>
     </row>
@@ -12503,19 +12503,19 @@
       </c>
       <c r="D481" s="5" t="inlineStr">
         <is>
-          <t>2:07:59</t>
+          <t>2:03:31</t>
         </is>
       </c>
       <c r="E481" s="5" t="inlineStr">
         <is>
-          <t>2:28:27</t>
+          <t>2:17:37</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>TCS London Marathon</t>
+          <t>TCS Amsterdam Marathon</t>
         </is>
       </c>
       <c r="B482" s="3" t="inlineStr">
@@ -12524,16 +12524,16 @@
         </is>
       </c>
       <c r="C482" s="3" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D482" s="3" t="inlineStr">
         <is>
-          <t>2:06:36</t>
+          <t>2:07:59</t>
         </is>
       </c>
       <c r="E482" s="3" t="inlineStr">
         <is>
-          <t>2:24:33</t>
+          <t>2:28:27</t>
         </is>
       </c>
     </row>
@@ -12549,16 +12549,16 @@
         </is>
       </c>
       <c r="C483" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D483" s="5" t="inlineStr">
         <is>
-          <t>2:07:11</t>
+          <t>2:06:36</t>
         </is>
       </c>
       <c r="E483" s="5" t="inlineStr">
         <is>
-          <t>2:23:56</t>
+          <t>2:24:33</t>
         </is>
       </c>
     </row>
@@ -12574,16 +12574,16 @@
         </is>
       </c>
       <c r="C484" s="3" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D484" s="3" t="inlineStr">
         <is>
-          <t>2:05:38</t>
+          <t>2:07:11</t>
         </is>
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>2:18:56</t>
+          <t>2:23:56</t>
         </is>
       </c>
     </row>
@@ -12599,16 +12599,16 @@
         </is>
       </c>
       <c r="C485" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D485" s="5" t="inlineStr">
         <is>
-          <t>2:07:56</t>
+          <t>2:05:38</t>
         </is>
       </c>
       <c r="E485" s="5" t="inlineStr">
         <is>
-          <t>2:15:25</t>
+          <t>2:18:56</t>
         </is>
       </c>
     </row>
@@ -12624,16 +12624,16 @@
         </is>
       </c>
       <c r="C486" s="3" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D486" s="3" t="inlineStr">
         <is>
-          <t>2:06:18</t>
+          <t>2:07:56</t>
         </is>
       </c>
       <c r="E486" s="3" t="inlineStr">
         <is>
-          <t>2:22:35</t>
+          <t>2:15:25</t>
         </is>
       </c>
     </row>
@@ -12649,16 +12649,16 @@
         </is>
       </c>
       <c r="C487" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D487" s="5" t="inlineStr">
         <is>
-          <t>2:07:44</t>
+          <t>2:06:18</t>
         </is>
       </c>
       <c r="E487" s="5" t="inlineStr">
         <is>
-          <t>2:17:42</t>
+          <t>2:22:35</t>
         </is>
       </c>
     </row>
@@ -12674,16 +12674,16 @@
         </is>
       </c>
       <c r="C488" s="3" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D488" s="3" t="inlineStr">
         <is>
-          <t>2:06:39</t>
+          <t>2:07:44</t>
         </is>
       </c>
       <c r="E488" s="3" t="inlineStr">
         <is>
-          <t>2:20:04</t>
+          <t>2:17:42</t>
         </is>
       </c>
     </row>
@@ -12699,16 +12699,16 @@
         </is>
       </c>
       <c r="C489" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D489" s="5" t="inlineStr">
         <is>
-          <t>2:07:41</t>
+          <t>2:06:39</t>
         </is>
       </c>
       <c r="E489" s="5" t="inlineStr">
         <is>
-          <t>2:20:13</t>
+          <t>2:20:04</t>
         </is>
       </c>
     </row>
@@ -12724,16 +12724,16 @@
         </is>
       </c>
       <c r="C490" s="3" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D490" s="3" t="inlineStr">
         <is>
-          <t>2:05:15</t>
+          <t>2:07:41</t>
         </is>
       </c>
       <c r="E490" s="3" t="inlineStr">
         <is>
-          <t>2:24:14</t>
+          <t>2:20:13</t>
         </is>
       </c>
     </row>
@@ -12749,16 +12749,16 @@
         </is>
       </c>
       <c r="C491" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D491" s="5" t="inlineStr">
         <is>
-          <t>2:05:10</t>
+          <t>2:05:15</t>
         </is>
       </c>
       <c r="E491" s="5" t="inlineStr">
         <is>
-          <t>2:23:12</t>
+          <t>2:24:14</t>
         </is>
       </c>
     </row>
@@ -12774,16 +12774,16 @@
         </is>
       </c>
       <c r="C492" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D492" s="3" t="inlineStr">
         <is>
-          <t>2:05:19</t>
+          <t>2:05:10</t>
         </is>
       </c>
       <c r="E492" s="3" t="inlineStr">
         <is>
-          <t>2:22:00</t>
+          <t>2:23:12</t>
         </is>
       </c>
     </row>
@@ -12799,16 +12799,16 @@
         </is>
       </c>
       <c r="C493" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D493" s="5" t="inlineStr">
         <is>
-          <t>2:04:40</t>
+          <t>2:05:19</t>
         </is>
       </c>
       <c r="E493" s="5" t="inlineStr">
         <is>
-          <t>2:19:36</t>
+          <t>2:22:00</t>
         </is>
       </c>
     </row>
@@ -12824,16 +12824,16 @@
         </is>
       </c>
       <c r="C494" s="3" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D494" s="3" t="inlineStr">
         <is>
-          <t>2:04:44</t>
+          <t>2:04:40</t>
         </is>
       </c>
       <c r="E494" s="3" t="inlineStr">
         <is>
-          <t>2:18:37</t>
+          <t>2:19:36</t>
         </is>
       </c>
     </row>
@@ -12849,16 +12849,16 @@
         </is>
       </c>
       <c r="C495" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D495" s="5" t="inlineStr">
         <is>
-          <t>2:04:29</t>
+          <t>2:04:44</t>
         </is>
       </c>
       <c r="E495" s="5" t="inlineStr">
         <is>
-          <t>2:20:15</t>
+          <t>2:18:37</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12874,7 @@
         </is>
       </c>
       <c r="C496" s="3" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D496" s="3" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="E496" s="3" t="inlineStr">
         <is>
-          <t>2:20:21</t>
+          <t>2:20:15</t>
         </is>
       </c>
     </row>
@@ -12899,16 +12899,16 @@
         </is>
       </c>
       <c r="C497" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D497" s="5" t="inlineStr">
         <is>
-          <t>2:04:42</t>
+          <t>2:04:29</t>
         </is>
       </c>
       <c r="E497" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:20:21</t>
         </is>
       </c>
     </row>
@@ -12924,11 +12924,11 @@
         </is>
       </c>
       <c r="C498" s="3" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D498" s="3" t="inlineStr">
         <is>
-          <t>2:03:05</t>
+          <t>2:04:42</t>
         </is>
       </c>
       <c r="E498" s="3" t="inlineStr">
@@ -12949,16 +12949,16 @@
         </is>
       </c>
       <c r="C499" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D499" s="5" t="inlineStr">
         <is>
-          <t>2:05:48</t>
+          <t>2:03:05</t>
         </is>
       </c>
       <c r="E499" s="5" t="inlineStr">
         <is>
-          <t>2:17:01</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -12974,16 +12974,16 @@
         </is>
       </c>
       <c r="C500" s="3" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D500" s="3" t="inlineStr">
         <is>
-          <t>2:04:17</t>
+          <t>2:05:48</t>
         </is>
       </c>
       <c r="E500" s="3" t="inlineStr">
         <is>
-          <t>2:18:31</t>
+          <t>2:17:01</t>
         </is>
       </c>
     </row>
@@ -12999,16 +12999,16 @@
         </is>
       </c>
       <c r="C501" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D501" s="5" t="inlineStr">
         <is>
-          <t>2:02:37</t>
+          <t>2:04:17</t>
         </is>
       </c>
       <c r="E501" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:18:31</t>
         </is>
       </c>
     </row>
@@ -13024,16 +13024,16 @@
         </is>
       </c>
       <c r="C502" s="3" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D502" s="3" t="inlineStr">
         <is>
-          <t>2:05:41</t>
+          <t>2:02:37</t>
         </is>
       </c>
       <c r="E502" s="3" t="inlineStr">
         <is>
-          <t>2:18:58</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -13049,16 +13049,16 @@
         </is>
       </c>
       <c r="C503" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D503" s="5" t="inlineStr">
         <is>
-          <t>2:04:01</t>
+          <t>2:05:41</t>
         </is>
       </c>
       <c r="E503" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:18:58</t>
         </is>
       </c>
     </row>
@@ -13074,16 +13074,16 @@
         </is>
       </c>
       <c r="C504" s="3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D504" s="3" t="inlineStr">
         <is>
-          <t>2:04:39</t>
+          <t>2:04:01</t>
         </is>
       </c>
       <c r="E504" s="3" t="inlineStr">
         <is>
-          <t>2:17:26</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -13099,16 +13099,16 @@
         </is>
       </c>
       <c r="C505" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D505" s="5" t="inlineStr">
         <is>
-          <t>2:01:25</t>
+          <t>2:04:39</t>
         </is>
       </c>
       <c r="E505" s="5" t="inlineStr">
         <is>
-          <t>2:18:33</t>
+          <t>2:17:26</t>
         </is>
       </c>
     </row>
@@ -13124,16 +13124,16 @@
         </is>
       </c>
       <c r="C506" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D506" s="3" t="inlineStr">
         <is>
-          <t>2:04:01</t>
+          <t>2:01:25</t>
         </is>
       </c>
       <c r="E506" s="3" t="inlineStr">
         <is>
-          <t>2:16:16</t>
+          <t>2:18:33</t>
         </is>
       </c>
     </row>
@@ -13149,23 +13149,23 @@
         </is>
       </c>
       <c r="C507" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D507" s="5" t="inlineStr">
         <is>
-          <t>2:02:27</t>
+          <t>2:04:01</t>
         </is>
       </c>
       <c r="E507" s="5" t="inlineStr">
         <is>
-          <t>2:15:50</t>
+          <t>2:16:16</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>TCS New York City Marathon</t>
+          <t>TCS London Marathon</t>
         </is>
       </c>
       <c r="B508" s="3" t="inlineStr">
@@ -13174,16 +13174,16 @@
         </is>
       </c>
       <c r="C508" s="3" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D508" s="3" t="inlineStr">
         <is>
-          <t>2:10:09</t>
+          <t>2:02:27</t>
         </is>
       </c>
       <c r="E508" s="3" t="inlineStr">
         <is>
-          <t>2:25:45</t>
+          <t>2:15:50</t>
         </is>
       </c>
     </row>
@@ -13199,16 +13199,16 @@
         </is>
       </c>
       <c r="C509" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D509" s="5" t="inlineStr">
         <is>
-          <t>2:07:43</t>
+          <t>2:10:09</t>
         </is>
       </c>
       <c r="E509" s="5" t="inlineStr">
         <is>
-          <t>2:24:21</t>
+          <t>2:25:45</t>
         </is>
       </c>
     </row>
@@ -13224,16 +13224,16 @@
         </is>
       </c>
       <c r="C510" s="3" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D510" s="3" t="inlineStr">
         <is>
-          <t>2:08:07</t>
+          <t>2:07:43</t>
         </is>
       </c>
       <c r="E510" s="3" t="inlineStr">
         <is>
-          <t>2:22:31</t>
+          <t>2:24:21</t>
         </is>
       </c>
     </row>
@@ -13249,11 +13249,11 @@
         </is>
       </c>
       <c r="C511" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D511" s="5" t="inlineStr">
         <is>
-          <t>2:10:30</t>
+          <t>2:08:07</t>
         </is>
       </c>
       <c r="E511" s="5" t="inlineStr">
@@ -13274,16 +13274,16 @@
         </is>
       </c>
       <c r="C512" s="3" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D512" s="3" t="inlineStr">
         <is>
-          <t>2:09:28</t>
+          <t>2:10:30</t>
         </is>
       </c>
       <c r="E512" s="3" t="inlineStr">
         <is>
-          <t>2:23:10</t>
+          <t>2:22:31</t>
         </is>
       </c>
     </row>
@@ -13299,16 +13299,16 @@
         </is>
       </c>
       <c r="C513" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D513" s="5" t="inlineStr">
         <is>
-          <t>2:09:30</t>
+          <t>2:09:28</t>
         </is>
       </c>
       <c r="E513" s="5" t="inlineStr">
         <is>
-          <t>2:24:41</t>
+          <t>2:23:10</t>
         </is>
       </c>
     </row>
@@ -13324,16 +13324,16 @@
         </is>
       </c>
       <c r="C514" s="3" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D514" s="3" t="inlineStr">
         <is>
-          <t>2:09:58</t>
+          <t>2:09:30</t>
         </is>
       </c>
       <c r="E514" s="3" t="inlineStr">
         <is>
-          <t>2:25:05</t>
+          <t>2:24:41</t>
         </is>
       </c>
     </row>
@@ -13349,16 +13349,16 @@
         </is>
       </c>
       <c r="C515" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D515" s="5" t="inlineStr">
         <is>
-          <t>2:09:04</t>
+          <t>2:09:58</t>
         </is>
       </c>
       <c r="E515" s="5" t="inlineStr">
         <is>
-          <t>2:23:09</t>
+          <t>2:25:05</t>
         </is>
       </c>
     </row>
@@ -13374,16 +13374,16 @@
         </is>
       </c>
       <c r="C516" s="3" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D516" s="3" t="inlineStr">
         <is>
-          <t>2:08:43</t>
+          <t>2:09:04</t>
         </is>
       </c>
       <c r="E516" s="3" t="inlineStr">
         <is>
-          <t>2:23:56</t>
+          <t>2:23:09</t>
         </is>
       </c>
     </row>
@@ -13399,16 +13399,16 @@
         </is>
       </c>
       <c r="C517" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D517" s="5" t="inlineStr">
         <is>
-          <t>2:09:15</t>
+          <t>2:08:43</t>
         </is>
       </c>
       <c r="E517" s="5" t="inlineStr">
         <is>
-          <t>2:25:53</t>
+          <t>2:23:56</t>
         </is>
       </c>
     </row>
@@ -13424,16 +13424,16 @@
         </is>
       </c>
       <c r="C518" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D518" s="3" t="inlineStr">
         <is>
-          <t>2:08:14</t>
+          <t>2:09:15</t>
         </is>
       </c>
       <c r="E518" s="3" t="inlineStr">
         <is>
-          <t>2:28:20</t>
+          <t>2:25:53</t>
         </is>
       </c>
     </row>
@@ -13449,16 +13449,16 @@
         </is>
       </c>
       <c r="C519" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D519" s="5" t="inlineStr">
         <is>
-          <t>2:05:06</t>
+          <t>2:08:14</t>
         </is>
       </c>
       <c r="E519" s="5" t="inlineStr">
         <is>
-          <t>2:23:15</t>
+          <t>2:28:20</t>
         </is>
       </c>
     </row>
@@ -13474,16 +13474,16 @@
         </is>
       </c>
       <c r="C520" s="3" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="D520" s="3" t="inlineStr">
         <is>
-          <t>2:08:24</t>
+          <t>2:05:06</t>
         </is>
       </c>
       <c r="E520" s="3" t="inlineStr">
         <is>
-          <t>2:25:07</t>
+          <t>2:23:15</t>
         </is>
       </c>
     </row>
@@ -13499,11 +13499,11 @@
         </is>
       </c>
       <c r="C521" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D521" s="5" t="inlineStr">
         <is>
-          <t>2:10:59</t>
+          <t>2:08:24</t>
         </is>
       </c>
       <c r="E521" s="5" t="inlineStr">
@@ -13524,16 +13524,16 @@
         </is>
       </c>
       <c r="C522" s="3" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D522" s="3" t="inlineStr">
         <is>
-          <t>2:10:34</t>
+          <t>2:10:59</t>
         </is>
       </c>
       <c r="E522" s="3" t="inlineStr">
         <is>
-          <t>2:24:25</t>
+          <t>2:25:07</t>
         </is>
       </c>
     </row>
@@ -13549,16 +13549,16 @@
         </is>
       </c>
       <c r="C523" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D523" s="5" t="inlineStr">
         <is>
-          <t>2:07:51</t>
+          <t>2:10:34</t>
         </is>
       </c>
       <c r="E523" s="5" t="inlineStr">
         <is>
-          <t>2:24:26</t>
+          <t>2:24:25</t>
         </is>
       </c>
     </row>
@@ -13574,16 +13574,16 @@
         </is>
       </c>
       <c r="C524" s="3" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D524" s="3" t="inlineStr">
         <is>
-          <t>2:10:53</t>
+          <t>2:07:51</t>
         </is>
       </c>
       <c r="E524" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:24:26</t>
         </is>
       </c>
     </row>
@@ -13599,16 +13599,16 @@
         </is>
       </c>
       <c r="C525" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D525" s="5" t="inlineStr">
         <is>
-          <t>2:05:59</t>
+          <t>2:10:53</t>
         </is>
       </c>
       <c r="E525" s="5" t="inlineStr">
         <is>
-          <t>2:22:48</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -13624,16 +13624,16 @@
         </is>
       </c>
       <c r="C526" s="3" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D526" s="3" t="inlineStr">
         <is>
-          <t>2:08:13</t>
+          <t>2:05:59</t>
         </is>
       </c>
       <c r="E526" s="3" t="inlineStr">
         <is>
-          <t>2:22:38</t>
+          <t>2:22:48</t>
         </is>
       </c>
     </row>
@@ -13649,16 +13649,16 @@
         </is>
       </c>
       <c r="C527" s="5" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D527" s="5" t="inlineStr">
         <is>
-          <t>2:08:22</t>
+          <t>2:08:13</t>
         </is>
       </c>
       <c r="E527" s="5" t="inlineStr">
         <is>
-          <t>2:22:39</t>
+          <t>2:22:38</t>
         </is>
       </c>
     </row>
@@ -13674,16 +13674,16 @@
         </is>
       </c>
       <c r="C528" s="3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D528" s="3" t="inlineStr">
         <is>
-          <t>2:08:41</t>
+          <t>2:08:22</t>
         </is>
       </c>
       <c r="E528" s="3" t="inlineStr">
         <is>
-          <t>2:23:23</t>
+          <t>2:22:39</t>
         </is>
       </c>
     </row>
@@ -13699,16 +13699,16 @@
         </is>
       </c>
       <c r="C529" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
-          <t>2:04:58</t>
+          <t>2:08:41</t>
         </is>
       </c>
       <c r="E529" s="5" t="inlineStr">
         <is>
-          <t>2:27:23</t>
+          <t>2:23:23</t>
         </is>
       </c>
     </row>
@@ -13724,16 +13724,16 @@
         </is>
       </c>
       <c r="C530" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D530" s="3" t="inlineStr">
         <is>
-          <t>2:07:39</t>
+          <t>2:04:58</t>
         </is>
       </c>
       <c r="E530" s="3" t="inlineStr">
         <is>
-          <t>2:24:35</t>
+          <t>2:27:23</t>
         </is>
       </c>
     </row>
@@ -13749,23 +13749,23 @@
         </is>
       </c>
       <c r="C531" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D531" s="5" t="inlineStr">
         <is>
-          <t>2:08:09</t>
+          <t>2:07:39</t>
         </is>
       </c>
       <c r="E531" s="5" t="inlineStr">
         <is>
-          <t>2:19:51</t>
+          <t>2:24:35</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>TCS Sydney Marathon presented by ASICS</t>
+          <t>TCS New York City Marathon</t>
         </is>
       </c>
       <c r="B532" s="3" t="inlineStr">
@@ -13774,16 +13774,16 @@
         </is>
       </c>
       <c r="C532" s="3" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D532" s="3" t="inlineStr">
         <is>
-          <t>2:08:20</t>
+          <t>2:08:09</t>
         </is>
       </c>
       <c r="E532" s="3" t="inlineStr">
         <is>
-          <t>2:26:47</t>
+          <t>2:19:51</t>
         </is>
       </c>
     </row>
@@ -13799,16 +13799,16 @@
         </is>
       </c>
       <c r="C533" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D533" s="5" t="inlineStr">
         <is>
-          <t>2:06:17</t>
+          <t>2:08:20</t>
         </is>
       </c>
       <c r="E533" s="5" t="inlineStr">
         <is>
-          <t>2:21:40</t>
+          <t>2:26:47</t>
         </is>
       </c>
     </row>
@@ -13824,23 +13824,23 @@
         </is>
       </c>
       <c r="C534" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D534" s="3" t="inlineStr">
         <is>
-          <t>2:06:06</t>
+          <t>2:06:17</t>
         </is>
       </c>
       <c r="E534" s="3" t="inlineStr">
         <is>
-          <t>2:18:22</t>
+          <t>2:21:40</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon</t>
+          <t>TCS Sydney Marathon presented by ASICS</t>
         </is>
       </c>
       <c r="B535" s="5" t="inlineStr">
@@ -13849,16 +13849,16 @@
         </is>
       </c>
       <c r="C535" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D535" s="5" t="inlineStr">
         <is>
-          <t>2:09:20</t>
+          <t>2:06:06</t>
         </is>
       </c>
       <c r="E535" s="5" t="inlineStr">
         <is>
-          <t>2:23:11</t>
+          <t>2:18:22</t>
         </is>
       </c>
     </row>
@@ -13874,16 +13874,16 @@
         </is>
       </c>
       <c r="C536" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D536" s="3" t="inlineStr">
         <is>
-          <t>2:07:16</t>
+          <t>2:09:20</t>
         </is>
       </c>
       <c r="E536" s="3" t="inlineStr">
         <is>
-          <t>2:20:44</t>
+          <t>2:23:11</t>
         </is>
       </c>
     </row>
@@ -13899,23 +13899,23 @@
         </is>
       </c>
       <c r="C537" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D537" s="5" t="inlineStr">
         <is>
-          <t>2:08:05</t>
+          <t>2:07:16</t>
         </is>
       </c>
       <c r="E537" s="5" t="inlineStr">
         <is>
-          <t>2:21:04</t>
+          <t>2:20:44</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>Taipei Marathon</t>
+          <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
       <c r="B538" s="3" t="inlineStr">
@@ -13924,16 +13924,16 @@
         </is>
       </c>
       <c r="C538" s="3" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D538" s="3" t="inlineStr">
         <is>
-          <t>2:11:05</t>
+          <t>2:08:05</t>
         </is>
       </c>
       <c r="E538" s="3" t="inlineStr">
         <is>
-          <t>2:27:14</t>
+          <t>2:21:04</t>
         </is>
       </c>
     </row>
@@ -13949,16 +13949,16 @@
         </is>
       </c>
       <c r="C539" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D539" s="5" t="inlineStr">
         <is>
-          <t>2:11:41</t>
+          <t>2:11:05</t>
         </is>
       </c>
       <c r="E539" s="5" t="inlineStr">
         <is>
-          <t>2:32:47</t>
+          <t>2:27:14</t>
         </is>
       </c>
     </row>
@@ -13974,23 +13974,23 @@
         </is>
       </c>
       <c r="C540" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D540" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:11:41</t>
         </is>
       </c>
       <c r="E540" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:32:47</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon</t>
+          <t>Taipei Marathon</t>
         </is>
       </c>
       <c r="B541" s="5" t="inlineStr">
@@ -13999,16 +13999,16 @@
         </is>
       </c>
       <c r="C541" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D541" s="5" t="inlineStr">
         <is>
-          <t>2:07:32</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E541" s="5" t="inlineStr">
         <is>
-          <t>2:24:15</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -14024,16 +14024,16 @@
         </is>
       </c>
       <c r="C542" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D542" s="3" t="inlineStr">
         <is>
-          <t>2:07:50</t>
+          <t>2:07:32</t>
         </is>
       </c>
       <c r="E542" s="3" t="inlineStr">
         <is>
-          <t>2:26:06</t>
+          <t>2:24:15</t>
         </is>
       </c>
     </row>
@@ -14049,16 +14049,16 @@
         </is>
       </c>
       <c r="C543" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D543" s="5" t="inlineStr">
         <is>
-          <t>2:11:44</t>
+          <t>2:07:50</t>
         </is>
       </c>
       <c r="E543" s="5" t="inlineStr">
         <is>
-          <t>2:24:56</t>
+          <t>2:26:06</t>
         </is>
       </c>
     </row>
@@ -14074,23 +14074,23 @@
         </is>
       </c>
       <c r="C544" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D544" s="3" t="inlineStr">
         <is>
-          <t>2:09:55</t>
+          <t>2:11:44</t>
         </is>
       </c>
       <c r="E544" s="3" t="inlineStr">
         <is>
-          <t>2:25:13</t>
+          <t>2:24:56</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Marathon</t>
+          <t>Tata Mumbai Marathon</t>
         </is>
       </c>
       <c r="B545" s="5" t="inlineStr">
@@ -14099,16 +14099,16 @@
         </is>
       </c>
       <c r="C545" s="5" t="n">
-        <v>2007</v>
+        <v>2026</v>
       </c>
       <c r="D545" s="5" t="inlineStr">
         <is>
-          <t>2:09:45</t>
+          <t>2:09:55</t>
         </is>
       </c>
       <c r="E545" s="5" t="inlineStr">
         <is>
-          <t>2:35:28</t>
+          <t>2:25:13</t>
         </is>
       </c>
     </row>
@@ -14124,16 +14124,16 @@
         </is>
       </c>
       <c r="C546" s="3" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D546" s="3" t="inlineStr">
         <is>
-          <t>2:10:57</t>
+          <t>2:09:45</t>
         </is>
       </c>
       <c r="E546" s="3" t="inlineStr">
         <is>
-          <t>2:25:51</t>
+          <t>2:35:28</t>
         </is>
       </c>
     </row>
@@ -14149,16 +14149,16 @@
         </is>
       </c>
       <c r="C547" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D547" s="5" t="inlineStr">
         <is>
-          <t>2:10:25</t>
+          <t>2:10:57</t>
         </is>
       </c>
       <c r="E547" s="5" t="inlineStr">
         <is>
-          <t>2:25:38</t>
+          <t>2:25:51</t>
         </is>
       </c>
     </row>
@@ -14174,16 +14174,16 @@
         </is>
       </c>
       <c r="C548" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D548" s="3" t="inlineStr">
         <is>
-          <t>2:08:12</t>
+          <t>2:10:25</t>
         </is>
       </c>
       <c r="E548" s="3" t="inlineStr">
         <is>
-          <t>2:25:27</t>
+          <t>2:25:38</t>
         </is>
       </c>
     </row>
@@ -14199,16 +14199,16 @@
         </is>
       </c>
       <c r="C549" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D549" s="5" t="inlineStr">
         <is>
-          <t>2:07:32</t>
+          <t>2:08:12</t>
         </is>
       </c>
       <c r="E549" s="5" t="inlineStr">
         <is>
-          <t>2:26:49</t>
+          <t>2:25:27</t>
         </is>
       </c>
     </row>
@@ -14224,16 +14224,16 @@
         </is>
       </c>
       <c r="C550" s="3" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D550" s="3" t="inlineStr">
         <is>
-          <t>2:07:37</t>
+          <t>2:07:32</t>
         </is>
       </c>
       <c r="E550" s="3" t="inlineStr">
         <is>
-          <t>2:25:28</t>
+          <t>2:26:49</t>
         </is>
       </c>
     </row>
@@ -14249,16 +14249,16 @@
         </is>
       </c>
       <c r="C551" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D551" s="5" t="inlineStr">
         <is>
-          <t>2:06:50</t>
+          <t>2:07:37</t>
         </is>
       </c>
       <c r="E551" s="5" t="inlineStr">
         <is>
-          <t>2:25:34</t>
+          <t>2:25:28</t>
         </is>
       </c>
     </row>
@@ -14274,16 +14274,16 @@
         </is>
       </c>
       <c r="C552" s="3" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D552" s="3" t="inlineStr">
         <is>
-          <t>2:05:42</t>
+          <t>2:06:50</t>
         </is>
       </c>
       <c r="E552" s="3" t="inlineStr">
         <is>
-          <t>2:22:23</t>
+          <t>2:25:34</t>
         </is>
       </c>
     </row>
@@ -14299,16 +14299,16 @@
         </is>
       </c>
       <c r="C553" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D553" s="5" t="inlineStr">
         <is>
-          <t>2:06:00</t>
+          <t>2:05:42</t>
         </is>
       </c>
       <c r="E553" s="5" t="inlineStr">
         <is>
-          <t>2:23:15</t>
+          <t>2:22:23</t>
         </is>
       </c>
     </row>
@@ -14324,16 +14324,16 @@
         </is>
       </c>
       <c r="C554" s="3" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D554" s="3" t="inlineStr">
         <is>
-          <t>2:06:56</t>
+          <t>2:06:00</t>
         </is>
       </c>
       <c r="E554" s="3" t="inlineStr">
         <is>
-          <t>2:21:27</t>
+          <t>2:23:15</t>
         </is>
       </c>
     </row>
@@ -14349,16 +14349,16 @@
         </is>
       </c>
       <c r="C555" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D555" s="5" t="inlineStr">
         <is>
-          <t>2:03:58</t>
+          <t>2:06:56</t>
         </is>
       </c>
       <c r="E555" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:21:27</t>
         </is>
       </c>
     </row>
@@ -14374,16 +14374,16 @@
         </is>
       </c>
       <c r="C556" s="3" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D556" s="3" t="inlineStr">
         <is>
-          <t>2:05:30</t>
+          <t>2:03:58</t>
         </is>
       </c>
       <c r="E556" s="3" t="inlineStr">
         <is>
-          <t>2:19:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -14399,16 +14399,16 @@
         </is>
       </c>
       <c r="C557" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D557" s="5" t="inlineStr">
         <is>
-          <t>2:04:15</t>
+          <t>2:05:30</t>
         </is>
       </c>
       <c r="E557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:19:51</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="C558" s="3" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D558" s="3" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
       </c>
       <c r="E558" s="3" t="inlineStr">
         <is>
-          <t>2:17:45</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -14449,16 +14449,16 @@
         </is>
       </c>
       <c r="C559" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D559" s="5" t="inlineStr">
         <is>
-          <t>2:02:40</t>
+          <t>2:04:15</t>
         </is>
       </c>
       <c r="E559" s="5" t="inlineStr">
         <is>
-          <t>2:16:02</t>
+          <t>2:17:45</t>
         </is>
       </c>
     </row>
@@ -14474,16 +14474,16 @@
         </is>
       </c>
       <c r="C560" s="3" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D560" s="3" t="inlineStr">
         <is>
-          <t>2:05:22</t>
+          <t>2:02:40</t>
         </is>
       </c>
       <c r="E560" s="3" t="inlineStr">
         <is>
-          <t>2:16:28</t>
+          <t>2:16:02</t>
         </is>
       </c>
     </row>
@@ -14499,16 +14499,16 @@
         </is>
       </c>
       <c r="C561" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D561" s="5" t="inlineStr">
         <is>
-          <t>2:02:16</t>
+          <t>2:05:22</t>
         </is>
       </c>
       <c r="E561" s="5" t="inlineStr">
         <is>
-          <t>2:15:55</t>
+          <t>2:16:28</t>
         </is>
       </c>
     </row>
@@ -14524,16 +14524,16 @@
         </is>
       </c>
       <c r="C562" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D562" s="3" t="inlineStr">
         <is>
-          <t>2:03:23</t>
+          <t>2:02:16</t>
         </is>
       </c>
       <c r="E562" s="3" t="inlineStr">
         <is>
-          <t>2:16:31</t>
+          <t>2:15:55</t>
         </is>
       </c>
     </row>
@@ -14549,23 +14549,23 @@
         </is>
       </c>
       <c r="C563" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D563" s="5" t="inlineStr">
         <is>
-          <t>2:03:37</t>
+          <t>2:03:23</t>
         </is>
       </c>
       <c r="E563" s="5" t="inlineStr">
         <is>
-          <t>2:14:29</t>
+          <t>2:16:31</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
+          <t>Tokyo Marathon</t>
         </is>
       </c>
       <c r="B564" s="3" t="inlineStr">
@@ -14574,16 +14574,16 @@
         </is>
       </c>
       <c r="C564" s="3" t="n">
-        <v>2008</v>
+        <v>2026</v>
       </c>
       <c r="D564" s="3" t="inlineStr">
         <is>
-          <t>2:12:27</t>
+          <t>2:03:37</t>
         </is>
       </c>
       <c r="E564" s="3" t="inlineStr">
         <is>
-          <t>2:36:27</t>
+          <t>2:14:29</t>
         </is>
       </c>
     </row>
@@ -14599,16 +14599,16 @@
         </is>
       </c>
       <c r="C565" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D565" s="5" t="inlineStr">
         <is>
-          <t>2:12:09</t>
+          <t>2:12:27</t>
         </is>
       </c>
       <c r="E565" s="5" t="inlineStr">
         <is>
-          <t>2:35:33</t>
+          <t>2:36:27</t>
         </is>
       </c>
     </row>
@@ -14624,16 +14624,16 @@
         </is>
       </c>
       <c r="C566" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D566" s="3" t="inlineStr">
         <is>
-          <t>2:09:52</t>
+          <t>2:12:09</t>
         </is>
       </c>
       <c r="E566" s="3" t="inlineStr">
         <is>
-          <t>2:33:08</t>
+          <t>2:35:33</t>
         </is>
       </c>
     </row>
@@ -14649,16 +14649,16 @@
         </is>
       </c>
       <c r="C567" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D567" s="5" t="inlineStr">
         <is>
-          <t>2:10:36</t>
+          <t>2:09:52</t>
         </is>
       </c>
       <c r="E567" s="5" t="inlineStr">
         <is>
-          <t>2:35:39</t>
+          <t>2:33:08</t>
         </is>
       </c>
     </row>
@@ -14674,16 +14674,16 @@
         </is>
       </c>
       <c r="C568" s="3" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D568" s="3" t="inlineStr">
         <is>
-          <t>2:09:09</t>
+          <t>2:10:36</t>
         </is>
       </c>
       <c r="E568" s="3" t="inlineStr">
         <is>
-          <t>2:31:35</t>
+          <t>2:35:39</t>
         </is>
       </c>
     </row>
@@ -14699,16 +14699,16 @@
         </is>
       </c>
       <c r="C569" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D569" s="5" t="inlineStr">
         <is>
-          <t>2:09:48</t>
+          <t>2:09:09</t>
         </is>
       </c>
       <c r="E569" s="5" t="inlineStr">
         <is>
-          <t>2:32:47</t>
+          <t>2:31:35</t>
         </is>
       </c>
     </row>
@@ -14724,16 +14724,16 @@
         </is>
       </c>
       <c r="C570" s="3" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D570" s="3" t="inlineStr">
         <is>
-          <t>2:10:42</t>
+          <t>2:09:48</t>
         </is>
       </c>
       <c r="E570" s="3" t="inlineStr">
         <is>
-          <t>2:30:54</t>
+          <t>2:32:47</t>
         </is>
       </c>
     </row>
@@ -14749,16 +14749,16 @@
         </is>
       </c>
       <c r="C571" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D571" s="5" t="inlineStr">
         <is>
-          <t>2:06:13</t>
+          <t>2:10:42</t>
         </is>
       </c>
       <c r="E571" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:30:54</t>
         </is>
       </c>
     </row>
@@ -14774,11 +14774,11 @@
         </is>
       </c>
       <c r="C572" s="3" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D572" s="3" t="inlineStr">
         <is>
-          <t>2:03:00</t>
+          <t>2:06:13</t>
         </is>
       </c>
       <c r="E572" s="3" t="inlineStr">
@@ -14799,16 +14799,16 @@
         </is>
       </c>
       <c r="C573" s="5" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D573" s="5" t="inlineStr">
         <is>
-          <t>2:01:53</t>
+          <t>2:03:00</t>
         </is>
       </c>
       <c r="E573" s="5" t="inlineStr">
         <is>
-          <t>2:14:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -14824,16 +14824,16 @@
         </is>
       </c>
       <c r="C574" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D574" s="3" t="inlineStr">
         <is>
-          <t>2:01:48</t>
+          <t>2:01:53</t>
         </is>
       </c>
       <c r="E574" s="3" t="inlineStr">
         <is>
-          <t>2:15:51</t>
+          <t>2:14:57</t>
         </is>
       </c>
     </row>
@@ -14849,16 +14849,16 @@
         </is>
       </c>
       <c r="C575" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D575" s="5" t="inlineStr">
         <is>
-          <t>2:02:05</t>
+          <t>2:01:48</t>
         </is>
       </c>
       <c r="E575" s="5" t="inlineStr">
         <is>
-          <t>2:16:49</t>
+          <t>2:15:51</t>
         </is>
       </c>
     </row>
@@ -14874,23 +14874,23 @@
         </is>
       </c>
       <c r="C576" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D576" s="3" t="inlineStr">
         <is>
-          <t>2:02:24</t>
+          <t>2:02:05</t>
         </is>
       </c>
       <c r="E576" s="3" t="inlineStr">
         <is>
-          <t>2:14:00</t>
+          <t>2:16:49</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>Vienna City Marathon</t>
+          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B577" s="5" t="inlineStr">
@@ -14899,16 +14899,16 @@
         </is>
       </c>
       <c r="C577" s="5" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D577" s="5" t="inlineStr">
         <is>
-          <t>2:10:24</t>
+          <t>2:02:24</t>
         </is>
       </c>
       <c r="E577" s="5" t="inlineStr">
         <is>
-          <t>2:23:47</t>
+          <t>2:14:00</t>
         </is>
       </c>
     </row>
@@ -14924,16 +14924,16 @@
         </is>
       </c>
       <c r="C578" s="3" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D578" s="3" t="inlineStr">
         <is>
-          <t>2:12:20</t>
+          <t>2:10:24</t>
         </is>
       </c>
       <c r="E578" s="3" t="inlineStr">
         <is>
-          <t>2:31:46</t>
+          <t>2:23:47</t>
         </is>
       </c>
     </row>
@@ -14949,16 +14949,16 @@
         </is>
       </c>
       <c r="C579" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D579" s="5" t="inlineStr">
         <is>
-          <t>2:10:18</t>
+          <t>2:12:20</t>
         </is>
       </c>
       <c r="E579" s="5" t="inlineStr">
         <is>
-          <t>2:30:41</t>
+          <t>2:31:46</t>
         </is>
       </c>
     </row>
@@ -14974,16 +14974,16 @@
         </is>
       </c>
       <c r="C580" s="3" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D580" s="3" t="inlineStr">
         <is>
-          <t>2:10:28</t>
+          <t>2:10:18</t>
         </is>
       </c>
       <c r="E580" s="3" t="inlineStr">
         <is>
-          <t>2:29:31</t>
+          <t>2:30:41</t>
         </is>
       </c>
     </row>
@@ -14999,16 +14999,16 @@
         </is>
       </c>
       <c r="C581" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D581" s="5" t="inlineStr">
         <is>
-          <t>2:10:41</t>
+          <t>2:10:28</t>
         </is>
       </c>
       <c r="E581" s="5" t="inlineStr">
         <is>
-          <t>2:29:24</t>
+          <t>2:29:31</t>
         </is>
       </c>
     </row>
@@ -15024,16 +15024,16 @@
         </is>
       </c>
       <c r="C582" s="3" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D582" s="3" t="inlineStr">
         <is>
-          <t>2:12:22</t>
+          <t>2:10:41</t>
         </is>
       </c>
       <c r="E582" s="3" t="inlineStr">
         <is>
-          <t>2:27:33</t>
+          <t>2:29:24</t>
         </is>
       </c>
     </row>
@@ -15049,16 +15049,16 @@
         </is>
       </c>
       <c r="C583" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D583" s="5" t="inlineStr">
         <is>
-          <t>2:12:09</t>
+          <t>2:12:22</t>
         </is>
       </c>
       <c r="E583" s="5" t="inlineStr">
         <is>
-          <t>2:29:19</t>
+          <t>2:27:33</t>
         </is>
       </c>
     </row>
@@ -15074,16 +15074,16 @@
         </is>
       </c>
       <c r="C584" s="3" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D584" s="3" t="inlineStr">
         <is>
-          <t>2:08:50</t>
+          <t>2:12:09</t>
         </is>
       </c>
       <c r="E584" s="3" t="inlineStr">
         <is>
-          <t>2:30:09</t>
+          <t>2:29:19</t>
         </is>
       </c>
     </row>
@@ -15099,16 +15099,16 @@
         </is>
       </c>
       <c r="C585" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D585" s="5" t="inlineStr">
         <is>
-          <t>2:07:38</t>
+          <t>2:08:50</t>
         </is>
       </c>
       <c r="E585" s="5" t="inlineStr">
         <is>
-          <t>2:25:47</t>
+          <t>2:30:09</t>
         </is>
       </c>
     </row>
@@ -15124,16 +15124,16 @@
         </is>
       </c>
       <c r="C586" s="3" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D586" s="3" t="inlineStr">
         <is>
-          <t>2:08:21</t>
+          <t>2:07:38</t>
         </is>
       </c>
       <c r="E586" s="3" t="inlineStr">
         <is>
-          <t>2:30:43</t>
+          <t>2:25:47</t>
         </is>
       </c>
     </row>
@@ -15149,16 +15149,16 @@
         </is>
       </c>
       <c r="C587" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D587" s="5" t="inlineStr">
         <is>
-          <t>2:08:40</t>
+          <t>2:08:21</t>
         </is>
       </c>
       <c r="E587" s="5" t="inlineStr">
         <is>
-          <t>2:31:08</t>
+          <t>2:30:43</t>
         </is>
       </c>
     </row>
@@ -15174,16 +15174,16 @@
         </is>
       </c>
       <c r="C588" s="3" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D588" s="3" t="inlineStr">
         <is>
-          <t>2:08:29</t>
+          <t>2:08:40</t>
         </is>
       </c>
       <c r="E588" s="3" t="inlineStr">
         <is>
-          <t>2:26:21</t>
+          <t>2:31:08</t>
         </is>
       </c>
     </row>
@@ -15199,16 +15199,16 @@
         </is>
       </c>
       <c r="C589" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D589" s="5" t="inlineStr">
         <is>
-          <t>2:06:58</t>
+          <t>2:08:29</t>
         </is>
       </c>
       <c r="E589" s="5" t="inlineStr">
         <is>
-          <t>2:26:39</t>
+          <t>2:26:21</t>
         </is>
       </c>
     </row>
@@ -15224,16 +15224,16 @@
         </is>
       </c>
       <c r="C590" s="3" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D590" s="3" t="inlineStr">
         <is>
-          <t>2:08:40</t>
+          <t>2:06:58</t>
         </is>
       </c>
       <c r="E590" s="3" t="inlineStr">
         <is>
-          <t>2:31:08</t>
+          <t>2:26:39</t>
         </is>
       </c>
     </row>
@@ -15249,16 +15249,16 @@
         </is>
       </c>
       <c r="C591" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D591" s="5" t="inlineStr">
         <is>
-          <t>2:05:41</t>
+          <t>2:08:40</t>
         </is>
       </c>
       <c r="E591" s="5" t="inlineStr">
         <is>
-          <t>2:28:59</t>
+          <t>2:31:08</t>
         </is>
       </c>
     </row>
@@ -15274,16 +15274,16 @@
         </is>
       </c>
       <c r="C592" s="3" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D592" s="3" t="inlineStr">
         <is>
-          <t>2:07:31</t>
+          <t>2:05:41</t>
         </is>
       </c>
       <c r="E592" s="3" t="inlineStr">
         <is>
-          <t>2:30:09</t>
+          <t>2:28:59</t>
         </is>
       </c>
     </row>
@@ -15299,16 +15299,16 @@
         </is>
       </c>
       <c r="C593" s="5" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="D593" s="5" t="inlineStr">
         <is>
-          <t>2:08:40</t>
+          <t>2:07:31</t>
         </is>
       </c>
       <c r="E593" s="5" t="inlineStr">
         <is>
-          <t>2:24:20</t>
+          <t>2:30:09</t>
         </is>
       </c>
     </row>
@@ -15324,16 +15324,16 @@
         </is>
       </c>
       <c r="C594" s="3" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="D594" s="3" t="inlineStr">
         <is>
-          <t>2:06:56</t>
+          <t>2:08:40</t>
         </is>
       </c>
       <c r="E594" s="3" t="inlineStr">
         <is>
-          <t>2:22:12</t>
+          <t>2:24:20</t>
         </is>
       </c>
     </row>
@@ -15349,16 +15349,16 @@
         </is>
       </c>
       <c r="C595" s="5" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D595" s="5" t="inlineStr">
         <is>
-          <t>2:09:25</t>
+          <t>2:06:56</t>
         </is>
       </c>
       <c r="E595" s="5" t="inlineStr">
         <is>
-          <t>2:24:29</t>
+          <t>2:22:12</t>
         </is>
       </c>
     </row>
@@ -15374,16 +15374,16 @@
         </is>
       </c>
       <c r="C596" s="3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D596" s="3" t="inlineStr">
         <is>
-          <t>2:06:53</t>
+          <t>2:09:25</t>
         </is>
       </c>
       <c r="E596" s="3" t="inlineStr">
         <is>
-          <t>2:20:59</t>
+          <t>2:24:29</t>
         </is>
       </c>
     </row>
@@ -15399,16 +15399,16 @@
         </is>
       </c>
       <c r="C597" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D597" s="5" t="inlineStr">
         <is>
-          <t>2:05:08</t>
+          <t>2:06:53</t>
         </is>
       </c>
       <c r="E597" s="5" t="inlineStr">
         <is>
-          <t>2:24:12</t>
+          <t>2:20:59</t>
         </is>
       </c>
     </row>
@@ -15424,16 +15424,16 @@
         </is>
       </c>
       <c r="C598" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D598" s="3" t="inlineStr">
         <is>
-          <t>2:06:35</t>
+          <t>2:05:08</t>
         </is>
       </c>
       <c r="E598" s="3" t="inlineStr">
         <is>
-          <t>2:24:08</t>
+          <t>2:24:12</t>
         </is>
       </c>
     </row>
@@ -15449,23 +15449,23 @@
         </is>
       </c>
       <c r="C599" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D599" s="5" t="inlineStr">
         <is>
-          <t>2:08:28</t>
+          <t>2:06:35</t>
         </is>
       </c>
       <c r="E599" s="5" t="inlineStr">
         <is>
-          <t>2:24:14</t>
+          <t>2:24:08</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>Zurich Marató de Barcelona</t>
+          <t>Vienna City Marathon</t>
         </is>
       </c>
       <c r="B600" s="3" t="inlineStr">
@@ -15474,16 +15474,16 @@
         </is>
       </c>
       <c r="C600" s="3" t="n">
-        <v>2006</v>
+        <v>2025</v>
       </c>
       <c r="D600" s="3" t="inlineStr">
         <is>
-          <t>2:11:44</t>
+          <t>2:08:28</t>
         </is>
       </c>
       <c r="E600" s="3" t="inlineStr">
         <is>
-          <t>2:36:04</t>
+          <t>2:24:14</t>
         </is>
       </c>
     </row>
@@ -15499,16 +15499,16 @@
         </is>
       </c>
       <c r="C601" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D601" s="5" t="inlineStr">
         <is>
-          <t>2:12:56</t>
+          <t>2:11:44</t>
         </is>
       </c>
       <c r="E601" s="5" t="inlineStr">
         <is>
-          <t>2:37:40</t>
+          <t>2:36:04</t>
         </is>
       </c>
     </row>
@@ -15524,16 +15524,16 @@
         </is>
       </c>
       <c r="C602" s="3" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D602" s="3" t="inlineStr">
         <is>
-          <t>2:10:55</t>
+          <t>2:12:56</t>
         </is>
       </c>
       <c r="E602" s="3" t="inlineStr">
         <is>
-          <t>2:34:03</t>
+          <t>2:37:40</t>
         </is>
       </c>
     </row>
@@ -15549,16 +15549,16 @@
         </is>
       </c>
       <c r="C603" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D603" s="5" t="inlineStr">
         <is>
-          <t>2:10:22</t>
+          <t>2:10:55</t>
         </is>
       </c>
       <c r="E603" s="5" t="inlineStr">
         <is>
-          <t>2:33:19</t>
+          <t>2:34:03</t>
         </is>
       </c>
     </row>
@@ -15574,16 +15574,16 @@
         </is>
       </c>
       <c r="C604" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D604" s="3" t="inlineStr">
         <is>
-          <t>2:07:30</t>
+          <t>2:10:22</t>
         </is>
       </c>
       <c r="E604" s="3" t="inlineStr">
         <is>
-          <t>2:31:51</t>
+          <t>2:33:19</t>
         </is>
       </c>
     </row>
@@ -15599,16 +15599,16 @@
         </is>
       </c>
       <c r="C605" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D605" s="5" t="inlineStr">
         <is>
-          <t>2:07:47</t>
+          <t>2:07:30</t>
         </is>
       </c>
       <c r="E605" s="5" t="inlineStr">
         <is>
-          <t>2:28:47</t>
+          <t>2:31:51</t>
         </is>
       </c>
     </row>
@@ -15624,16 +15624,16 @@
         </is>
       </c>
       <c r="C606" s="3" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D606" s="3" t="inlineStr">
         <is>
-          <t>2:10:06</t>
+          <t>2:07:47</t>
         </is>
       </c>
       <c r="E606" s="3" t="inlineStr">
         <is>
-          <t>2:33:10</t>
+          <t>2:28:47</t>
         </is>
       </c>
     </row>
@@ -15649,16 +15649,16 @@
         </is>
       </c>
       <c r="C607" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D607" s="5" t="inlineStr">
         <is>
-          <t>2:09:36</t>
+          <t>2:10:06</t>
         </is>
       </c>
       <c r="E607" s="5" t="inlineStr">
         <is>
-          <t>2:31:10</t>
+          <t>2:33:10</t>
         </is>
       </c>
     </row>
@@ -15674,16 +15674,16 @@
         </is>
       </c>
       <c r="C608" s="3" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D608" s="3" t="inlineStr">
         <is>
-          <t>2:09:41</t>
+          <t>2:09:36</t>
         </is>
       </c>
       <c r="E608" s="3" t="inlineStr">
         <is>
-          <t>2:29:10</t>
+          <t>2:31:10</t>
         </is>
       </c>
     </row>
@@ -15699,16 +15699,16 @@
         </is>
       </c>
       <c r="C609" s="5" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D609" s="5" t="inlineStr">
         <is>
-          <t>2:05:06</t>
+          <t>2:09:41</t>
         </is>
       </c>
       <c r="E609" s="5" t="inlineStr">
         <is>
-          <t>2:19:44</t>
+          <t>2:29:10</t>
         </is>
       </c>
     </row>
@@ -15724,16 +15724,16 @@
         </is>
       </c>
       <c r="C610" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D610" s="3" t="inlineStr">
         <is>
-          <t>2:05:01</t>
+          <t>2:05:06</t>
         </is>
       </c>
       <c r="E610" s="3" t="inlineStr">
         <is>
-          <t>2:19:52</t>
+          <t>2:19:44</t>
         </is>
       </c>
     </row>
@@ -15749,16 +15749,16 @@
         </is>
       </c>
       <c r="C611" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D611" s="5" t="inlineStr">
         <is>
-          <t>2:04:13</t>
+          <t>2:05:01</t>
         </is>
       </c>
       <c r="E611" s="5" t="inlineStr">
         <is>
-          <t>2:19:33</t>
+          <t>2:19:52</t>
         </is>
       </c>
     </row>
@@ -15774,23 +15774,23 @@
         </is>
       </c>
       <c r="C612" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D612" s="3" t="inlineStr">
         <is>
-          <t>2:04:57</t>
+          <t>2:04:13</t>
         </is>
       </c>
       <c r="E612" s="3" t="inlineStr">
         <is>
-          <t>2:10:53</t>
+          <t>2:19:33</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" s="4" t="inlineStr">
         <is>
-          <t>Zurich Maratón de Sevilla</t>
+          <t>Zurich Marató de Barcelona</t>
         </is>
       </c>
       <c r="B613" s="5" t="inlineStr">
@@ -15799,16 +15799,16 @@
         </is>
       </c>
       <c r="C613" s="5" t="n">
-        <v>2009</v>
+        <v>2026</v>
       </c>
       <c r="D613" s="5" t="inlineStr">
         <is>
-          <t>2:11:51</t>
+          <t>2:04:57</t>
         </is>
       </c>
       <c r="E613" s="5" t="inlineStr">
         <is>
-          <t>2:26:03</t>
+          <t>2:10:53</t>
         </is>
       </c>
     </row>
@@ -15824,16 +15824,16 @@
         </is>
       </c>
       <c r="C614" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D614" s="3" t="inlineStr">
         <is>
-          <t>2:09:53</t>
+          <t>2:11:51</t>
         </is>
       </c>
       <c r="E614" s="3" t="inlineStr">
         <is>
-          <t>2:30:55</t>
+          <t>2:26:03</t>
         </is>
       </c>
     </row>
@@ -15849,16 +15849,16 @@
         </is>
       </c>
       <c r="C615" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D615" s="5" t="inlineStr">
         <is>
-          <t>2:10:26</t>
+          <t>2:09:53</t>
         </is>
       </c>
       <c r="E615" s="5" t="inlineStr">
         <is>
-          <t>2:33:10</t>
+          <t>2:30:55</t>
         </is>
       </c>
     </row>
@@ -15874,16 +15874,16 @@
         </is>
       </c>
       <c r="C616" s="3" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D616" s="3" t="inlineStr">
         <is>
-          <t>2:10:19</t>
+          <t>2:10:26</t>
         </is>
       </c>
       <c r="E616" s="3" t="inlineStr">
         <is>
-          <t>2:33:41</t>
+          <t>2:33:10</t>
         </is>
       </c>
     </row>
@@ -15899,16 +15899,16 @@
         </is>
       </c>
       <c r="C617" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D617" s="5" t="inlineStr">
         <is>
-          <t>2:11:26</t>
+          <t>2:10:19</t>
         </is>
       </c>
       <c r="E617" s="5" t="inlineStr">
         <is>
-          <t>2:33:44</t>
+          <t>2:33:41</t>
         </is>
       </c>
     </row>
@@ -15924,16 +15924,16 @@
         </is>
       </c>
       <c r="C618" s="3" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D618" s="3" t="inlineStr">
         <is>
-          <t>2:08:33</t>
+          <t>2:11:26</t>
         </is>
       </c>
       <c r="E618" s="3" t="inlineStr">
         <is>
-          <t>2:28:39</t>
+          <t>2:33:44</t>
         </is>
       </c>
     </row>
@@ -15949,16 +15949,16 @@
         </is>
       </c>
       <c r="C619" s="5" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D619" s="5" t="inlineStr">
         <is>
-          <t>2:04:59</t>
+          <t>2:08:33</t>
         </is>
       </c>
       <c r="E619" s="5" t="inlineStr">
         <is>
-          <t>2:20:29</t>
+          <t>2:28:39</t>
         </is>
       </c>
     </row>
@@ -15974,16 +15974,16 @@
         </is>
       </c>
       <c r="C620" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D620" s="3" t="inlineStr">
         <is>
-          <t>2:03:27</t>
+          <t>2:04:59</t>
         </is>
       </c>
       <c r="E620" s="3" t="inlineStr">
         <is>
-          <t>2:22:13</t>
+          <t>2:20:29</t>
         </is>
       </c>
     </row>
@@ -15999,16 +15999,16 @@
         </is>
       </c>
       <c r="C621" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D621" s="5" t="inlineStr">
         <is>
-          <t>2:05:15</t>
+          <t>2:03:27</t>
         </is>
       </c>
       <c r="E621" s="5" t="inlineStr">
         <is>
-          <t>2:22:17</t>
+          <t>2:22:13</t>
         </is>
       </c>
     </row>
@@ -16024,23 +16024,23 @@
         </is>
       </c>
       <c r="C622" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D622" s="3" t="inlineStr">
         <is>
-          <t>2:03:59</t>
+          <t>2:05:15</t>
         </is>
       </c>
       <c r="E622" s="3" t="inlineStr">
         <is>
-          <t>2:20:39</t>
+          <t>2:22:17</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
+          <t>Zurich Maratón de Sevilla</t>
         </is>
       </c>
       <c r="B623" s="5" t="inlineStr">
@@ -16049,16 +16049,16 @@
         </is>
       </c>
       <c r="C623" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D623" s="5" t="inlineStr">
         <is>
-          <t>2:10:29</t>
+          <t>2:03:59</t>
         </is>
       </c>
       <c r="E623" s="5" t="inlineStr">
         <is>
-          <t>2:26:31</t>
+          <t>2:20:39</t>
         </is>
       </c>
     </row>
@@ -16074,16 +16074,16 @@
         </is>
       </c>
       <c r="C624" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D624" s="3" t="inlineStr">
         <is>
-          <t>2:08:05</t>
+          <t>2:10:29</t>
         </is>
       </c>
       <c r="E624" s="3" t="inlineStr">
         <is>
-          <t>2:26:19</t>
+          <t>2:26:31</t>
         </is>
       </c>
     </row>
@@ -16099,48 +16099,48 @@
         </is>
       </c>
       <c r="C625" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D625" s="5" t="inlineStr">
+        <is>
+          <t>2:08:05</t>
+        </is>
+      </c>
+      <c r="E625" s="5" t="inlineStr">
+        <is>
+          <t>2:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
+        </is>
+      </c>
+      <c r="B626" s="3" t="inlineStr">
+        <is>
+          <t>42K</t>
+        </is>
+      </c>
+      <c r="C626" s="3" t="n">
         <v>2025</v>
       </c>
-      <c r="D625" s="5" t="inlineStr">
+      <c r="D626" s="3" t="inlineStr">
         <is>
           <t>2:09:11</t>
         </is>
       </c>
-      <c r="E625" s="5" t="inlineStr">
+      <c r="E626" s="3" t="inlineStr">
         <is>
           <t>2:25:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" s="6" t="inlineStr">
-        <is>
-          <t>21K de Montréal</t>
-        </is>
-      </c>
-      <c r="B626" s="7" t="inlineStr">
-        <is>
-          <t>21K</t>
-        </is>
-      </c>
-      <c r="C626" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D626" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E626" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Bristol Run</t>
+          <t>21K de Montréal</t>
         </is>
       </c>
       <c r="B627" s="5" t="inlineStr">
@@ -16149,16 +16149,16 @@
         </is>
       </c>
       <c r="C627" s="5" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D627" s="5" t="inlineStr">
         <is>
-          <t>1:07:50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E627" s="5" t="inlineStr">
         <is>
-          <t>1:18:15</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16174,23 +16174,23 @@
         </is>
       </c>
       <c r="C628" s="7" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D628" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:50</t>
         </is>
       </c>
       <c r="E628" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:18:15</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run</t>
+          <t>AJ Bell Great Bristol Run</t>
         </is>
       </c>
       <c r="B629" s="5" t="inlineStr">
@@ -16199,16 +16199,16 @@
         </is>
       </c>
       <c r="C629" s="5" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D629" s="5" t="inlineStr">
         <is>
-          <t>1:10:25</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E629" s="5" t="inlineStr">
         <is>
-          <t>1:21:56</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16224,23 +16224,23 @@
         </is>
       </c>
       <c r="C630" s="7" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D630" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:25</t>
         </is>
       </c>
       <c r="E630" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:21:56</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great North Run</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B631" s="5" t="inlineStr">
@@ -16249,16 +16249,16 @@
         </is>
       </c>
       <c r="C631" s="5" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D631" s="5" t="inlineStr">
         <is>
-          <t>1:01:57</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E631" s="5" t="inlineStr">
         <is>
-          <t>1:08:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16274,16 +16274,16 @@
         </is>
       </c>
       <c r="C632" s="7" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D632" s="7" t="inlineStr">
         <is>
-          <t>1:00:30</t>
+          <t>1:01:57</t>
         </is>
       </c>
       <c r="E632" s="7" t="inlineStr">
         <is>
-          <t>1:08:40</t>
+          <t>1:08:49</t>
         </is>
       </c>
     </row>
@@ -16299,16 +16299,16 @@
         </is>
       </c>
       <c r="C633" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D633" s="5" t="inlineStr">
         <is>
-          <t>0:59:58</t>
+          <t>1:00:30</t>
         </is>
       </c>
       <c r="E633" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:40</t>
         </is>
       </c>
     </row>
@@ -16324,16 +16324,16 @@
         </is>
       </c>
       <c r="C634" s="7" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D634" s="7" t="inlineStr">
         <is>
-          <t>1:00:01</t>
+          <t>0:59:58</t>
         </is>
       </c>
       <c r="E634" s="7" t="inlineStr">
         <is>
-          <t>1:05:40</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16349,16 +16349,16 @@
         </is>
       </c>
       <c r="C635" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D635" s="5" t="inlineStr">
         <is>
-          <t>0:59:37</t>
+          <t>1:00:01</t>
         </is>
       </c>
       <c r="E635" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:40</t>
         </is>
       </c>
     </row>
@@ -16374,11 +16374,11 @@
         </is>
       </c>
       <c r="C636" s="7" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D636" s="7" t="inlineStr">
         <is>
-          <t>0:59:05</t>
+          <t>0:59:37</t>
         </is>
       </c>
       <c r="E636" s="7" t="inlineStr">
@@ -16399,11 +16399,11 @@
         </is>
       </c>
       <c r="C637" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D637" s="5" t="inlineStr">
         <is>
-          <t>1:01:04</t>
+          <t>0:59:05</t>
         </is>
       </c>
       <c r="E637" s="5" t="inlineStr">
@@ -16424,16 +16424,16 @@
         </is>
       </c>
       <c r="C638" s="7" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D638" s="7" t="inlineStr">
         <is>
-          <t>1:00:08</t>
+          <t>1:01:04</t>
         </is>
       </c>
       <c r="E638" s="7" t="inlineStr">
         <is>
-          <t>1:06:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16449,16 +16449,16 @@
         </is>
       </c>
       <c r="C639" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D639" s="5" t="inlineStr">
         <is>
-          <t>0:59:45</t>
+          <t>1:00:08</t>
         </is>
       </c>
       <c r="E639" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:57</t>
         </is>
       </c>
     </row>
@@ -16474,11 +16474,11 @@
         </is>
       </c>
       <c r="C640" s="7" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D640" s="7" t="inlineStr">
         <is>
-          <t>0:59:32</t>
+          <t>0:59:45</t>
         </is>
       </c>
       <c r="E640" s="7" t="inlineStr">
@@ -16499,11 +16499,11 @@
         </is>
       </c>
       <c r="C641" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D641" s="5" t="inlineStr">
         <is>
-          <t>0:59:33</t>
+          <t>0:59:32</t>
         </is>
       </c>
       <c r="E641" s="5" t="inlineStr">
@@ -16524,11 +16524,11 @@
         </is>
       </c>
       <c r="C642" s="7" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D642" s="7" t="inlineStr">
         <is>
-          <t>0:58:56</t>
+          <t>0:59:33</t>
         </is>
       </c>
       <c r="E642" s="7" t="inlineStr">
@@ -16549,11 +16549,11 @@
         </is>
       </c>
       <c r="C643" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D643" s="5" t="inlineStr">
         <is>
-          <t>0:59:06</t>
+          <t>0:58:56</t>
         </is>
       </c>
       <c r="E643" s="5" t="inlineStr">
@@ -16574,16 +16574,16 @@
         </is>
       </c>
       <c r="C644" s="7" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D644" s="7" t="inlineStr">
         <is>
-          <t>1:00:09</t>
+          <t>0:59:06</t>
         </is>
       </c>
       <c r="E644" s="7" t="inlineStr">
         <is>
-          <t>1:07:29</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16599,16 +16599,16 @@
         </is>
       </c>
       <c r="C645" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D645" s="5" t="inlineStr">
         <is>
-          <t>1:00:00</t>
+          <t>1:00:09</t>
         </is>
       </c>
       <c r="E645" s="5" t="inlineStr">
         <is>
-          <t>1:05:39</t>
+          <t>1:07:29</t>
         </is>
       </c>
     </row>
@@ -16624,16 +16624,16 @@
         </is>
       </c>
       <c r="C646" s="7" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="D646" s="7" t="inlineStr">
         <is>
-          <t>0:58:57</t>
+          <t>1:00:00</t>
         </is>
       </c>
       <c r="E646" s="7" t="inlineStr">
         <is>
-          <t>1:07:41</t>
+          <t>1:05:39</t>
         </is>
       </c>
     </row>
@@ -16649,23 +16649,23 @@
         </is>
       </c>
       <c r="C647" s="5" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D647" s="5" t="inlineStr">
         <is>
-          <t>1:00:52</t>
+          <t>0:58:57</t>
         </is>
       </c>
       <c r="E647" s="5" t="inlineStr">
         <is>
-          <t>1:09:32</t>
+          <t>1:07:41</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" s="6" t="inlineStr">
         <is>
-          <t>Aramco Houston Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B648" s="7" t="inlineStr">
@@ -16674,16 +16674,16 @@
         </is>
       </c>
       <c r="C648" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D648" s="7" t="inlineStr">
         <is>
-          <t>1:00:42</t>
+          <t>1:00:52</t>
         </is>
       </c>
       <c r="E648" s="7" t="inlineStr">
         <is>
-          <t>1:04:37</t>
+          <t>1:09:32</t>
         </is>
       </c>
     </row>
@@ -16699,16 +16699,16 @@
         </is>
       </c>
       <c r="C649" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D649" s="5" t="inlineStr">
         <is>
-          <t>0:59:17</t>
+          <t>1:00:42</t>
         </is>
       </c>
       <c r="E649" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:37</t>
         </is>
       </c>
     </row>
@@ -16724,23 +16724,23 @@
         </is>
       </c>
       <c r="C650" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D650" s="7" t="inlineStr">
         <is>
-          <t>0:59:01</t>
+          <t>0:59:17</t>
         </is>
       </c>
       <c r="E650" s="7" t="inlineStr">
         <is>
-          <t>1:04:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" s="4" t="inlineStr">
         <is>
-          <t>Asics Run Melbourne</t>
+          <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
       <c r="B651" s="5" t="inlineStr">
@@ -16749,23 +16749,23 @@
         </is>
       </c>
       <c r="C651" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D651" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:01</t>
         </is>
       </c>
       <c r="E651" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:49</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" s="6" t="inlineStr">
         <is>
-          <t>Bangsaen21</t>
+          <t>Asics Run Melbourne</t>
         </is>
       </c>
       <c r="B652" s="7" t="inlineStr">
@@ -16774,7 +16774,7 @@
         </is>
       </c>
       <c r="C652" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D652" s="7" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="C653" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D653" s="5" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         </is>
       </c>
       <c r="C654" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D654" s="7" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
     <row r="655">
       <c r="A655" s="4" t="inlineStr">
         <is>
-          <t>Brølløbet - The Bridge Run</t>
+          <t>Bangsaen21</t>
         </is>
       </c>
       <c r="B655" s="5" t="inlineStr">
@@ -16865,7 +16865,7 @@
     <row r="656">
       <c r="A656" s="6" t="inlineStr">
         <is>
-          <t>Burj2Burj Half Marathon</t>
+          <t>Brølløbet - The Bridge Run</t>
         </is>
       </c>
       <c r="B656" s="7" t="inlineStr">
@@ -16874,7 +16874,7 @@
         </is>
       </c>
       <c r="C656" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D656" s="7" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         </is>
       </c>
       <c r="C657" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D657" s="5" t="inlineStr">
         <is>
@@ -16924,23 +16924,23 @@
         </is>
       </c>
       <c r="C658" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D658" s="7" t="inlineStr">
         <is>
-          <t>0:59:26</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E658" s="7" t="inlineStr">
         <is>
-          <t>1:06:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="4" t="inlineStr">
         <is>
-          <t>Cardiff Half Marathon</t>
+          <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
       <c r="B659" s="5" t="inlineStr">
@@ -16949,23 +16949,23 @@
         </is>
       </c>
       <c r="C659" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:26</t>
         </is>
       </c>
       <c r="E659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:57</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" s="6" t="inlineStr">
         <is>
-          <t>Coelmo Napoli City Half Marathon</t>
+          <t>Cardiff Half Marathon</t>
         </is>
       </c>
       <c r="B660" s="7" t="inlineStr">
@@ -16999,7 +16999,7 @@
         </is>
       </c>
       <c r="C661" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D661" s="5" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
     <row r="662">
       <c r="A662" s="6" t="inlineStr">
         <is>
-          <t>Copenhagen Half Marathon</t>
+          <t>Coelmo Napoli City Half Marathon</t>
         </is>
       </c>
       <c r="B662" s="7" t="inlineStr">
@@ -17024,16 +17024,16 @@
         </is>
       </c>
       <c r="C662" s="7" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D662" s="7" t="inlineStr">
         <is>
-          <t>0:59:11</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E662" s="7" t="inlineStr">
         <is>
-          <t>1:05:53</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17049,16 +17049,16 @@
         </is>
       </c>
       <c r="C663" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D663" s="5" t="inlineStr">
         <is>
-          <t>0:58:05</t>
+          <t>0:59:11</t>
         </is>
       </c>
       <c r="E663" s="5" t="inlineStr">
         <is>
-          <t>1:05:11</t>
+          <t>1:05:53</t>
         </is>
       </c>
     </row>
@@ -17074,23 +17074,23 @@
         </is>
       </c>
       <c r="C664" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D664" s="7" t="inlineStr">
         <is>
-          <t>0:58:23</t>
+          <t>0:58:05</t>
         </is>
       </c>
       <c r="E664" s="7" t="inlineStr">
         <is>
-          <t>1:04:44</t>
+          <t>1:05:11</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" s="4" t="inlineStr">
         <is>
-          <t>Disney Princess Half Marathon</t>
+          <t>Copenhagen Half Marathon</t>
         </is>
       </c>
       <c r="B665" s="5" t="inlineStr">
@@ -17103,12 +17103,12 @@
       </c>
       <c r="D665" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:23</t>
         </is>
       </c>
       <c r="E665" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:44</t>
         </is>
       </c>
     </row>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="C666" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D666" s="7" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
     <row r="667">
       <c r="A667" s="4" t="inlineStr">
         <is>
-          <t>EDP Lisboa Meia Maratona</t>
+          <t>Disney Princess Half Marathon</t>
         </is>
       </c>
       <c r="B667" s="5" t="inlineStr">
@@ -17149,11 +17149,11 @@
         </is>
       </c>
       <c r="C667" s="5" t="n">
-        <v>2000</v>
+        <v>2026</v>
       </c>
       <c r="D667" s="5" t="inlineStr">
         <is>
-          <t>0:59:06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E667" s="5" t="inlineStr">
@@ -17174,16 +17174,16 @@
         </is>
       </c>
       <c r="C668" s="7" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D668" s="7" t="inlineStr">
         <is>
-          <t>1:00:26</t>
+          <t>0:59:06</t>
         </is>
       </c>
       <c r="E668" s="7" t="inlineStr">
         <is>
-          <t>1:05:44</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17199,16 +17199,16 @@
         </is>
       </c>
       <c r="C669" s="5" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="D669" s="5" t="inlineStr">
         <is>
-          <t>1:00:10</t>
+          <t>1:00:26</t>
         </is>
       </c>
       <c r="E669" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:44</t>
         </is>
       </c>
     </row>
@@ -17224,16 +17224,16 @@
         </is>
       </c>
       <c r="C670" s="7" t="n">
-        <v>2010</v>
+        <v>2003</v>
       </c>
       <c r="D670" s="7" t="inlineStr">
         <is>
-          <t>0:58:23</t>
+          <t>1:00:10</t>
         </is>
       </c>
       <c r="E670" s="7" t="inlineStr">
         <is>
-          <t>1:08:38</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17249,16 +17249,16 @@
         </is>
       </c>
       <c r="C671" s="5" t="n">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="D671" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:23</t>
         </is>
       </c>
       <c r="E671" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:38</t>
         </is>
       </c>
     </row>
@@ -17274,7 +17274,7 @@
         </is>
       </c>
       <c r="C672" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D672" s="7" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         </is>
       </c>
       <c r="C673" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D673" s="5" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
     <row r="674">
       <c r="A674" s="6" t="inlineStr">
         <is>
-          <t>Eurospin RomaOstia Half Marathon</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B674" s="7" t="inlineStr">
@@ -17324,7 +17324,7 @@
         </is>
       </c>
       <c r="C674" s="7" t="n">
-        <v>2004</v>
+        <v>2026</v>
       </c>
       <c r="D674" s="7" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
       </c>
       <c r="E674" s="7" t="inlineStr">
         <is>
-          <t>1:10:39</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17349,16 +17349,16 @@
         </is>
       </c>
       <c r="C675" s="5" t="n">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="D675" s="5" t="inlineStr">
         <is>
-          <t>0:59:32</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E675" s="5" t="inlineStr">
         <is>
-          <t>1:06:38</t>
+          <t>1:10:39</t>
         </is>
       </c>
     </row>
@@ -17374,16 +17374,16 @@
         </is>
       </c>
       <c r="C676" s="7" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="D676" s="7" t="inlineStr">
         <is>
-          <t>0:59:17</t>
+          <t>0:59:32</t>
         </is>
       </c>
       <c r="E676" s="7" t="inlineStr">
         <is>
-          <t>1:06:21</t>
+          <t>1:06:38</t>
         </is>
       </c>
     </row>
@@ -17399,16 +17399,16 @@
         </is>
       </c>
       <c r="C677" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D677" s="5" t="inlineStr">
         <is>
-          <t>1:01:10</t>
+          <t>0:59:17</t>
         </is>
       </c>
       <c r="E677" s="5" t="inlineStr">
         <is>
-          <t>1:07:38</t>
+          <t>1:06:21</t>
         </is>
       </c>
     </row>
@@ -17424,16 +17424,16 @@
         </is>
       </c>
       <c r="C678" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D678" s="7" t="inlineStr">
         <is>
-          <t>0:58:49</t>
+          <t>1:01:10</t>
         </is>
       </c>
       <c r="E678" s="7" t="inlineStr">
         <is>
-          <t>1:08:20</t>
+          <t>1:07:38</t>
         </is>
       </c>
     </row>
@@ -17449,23 +17449,23 @@
         </is>
       </c>
       <c r="C679" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D679" s="5" t="inlineStr">
         <is>
-          <t>0:58:00</t>
+          <t>0:58:49</t>
         </is>
       </c>
       <c r="E679" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:20</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" s="6" t="inlineStr">
         <is>
-          <t>Generali Berlin Half Marathon</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B680" s="7" t="inlineStr">
@@ -17474,16 +17474,16 @@
         </is>
       </c>
       <c r="C680" s="7" t="n">
-        <v>2006</v>
+        <v>2026</v>
       </c>
       <c r="D680" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:00</t>
         </is>
       </c>
       <c r="E680" s="7" t="inlineStr">
         <is>
-          <t>1:07:16</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17499,16 +17499,16 @@
         </is>
       </c>
       <c r="C681" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D681" s="5" t="inlineStr">
         <is>
-          <t>0:58:56</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E681" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:16</t>
         </is>
       </c>
     </row>
@@ -17524,16 +17524,16 @@
         </is>
       </c>
       <c r="C682" s="7" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="D682" s="7" t="inlineStr">
         <is>
-          <t>1:00:16</t>
+          <t>0:58:56</t>
         </is>
       </c>
       <c r="E682" s="7" t="inlineStr">
         <is>
-          <t>1:09:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17549,16 +17549,16 @@
         </is>
       </c>
       <c r="C683" s="5" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="D683" s="5" t="inlineStr">
         <is>
-          <t>0:59:14</t>
+          <t>1:00:16</t>
         </is>
       </c>
       <c r="E683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:09:43</t>
         </is>
       </c>
     </row>
@@ -17574,16 +17574,16 @@
         </is>
       </c>
       <c r="C684" s="7" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="D684" s="7" t="inlineStr">
         <is>
-          <t>0:59:01</t>
+          <t>0:59:14</t>
         </is>
       </c>
       <c r="E684" s="7" t="inlineStr">
         <is>
-          <t>1:05:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17599,16 +17599,16 @@
         </is>
       </c>
       <c r="C685" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D685" s="5" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>0:59:01</t>
         </is>
       </c>
       <c r="E685" s="5" t="inlineStr">
         <is>
-          <t>1:06:53</t>
+          <t>1:05:43</t>
         </is>
       </c>
     </row>
@@ -17624,23 +17624,23 @@
         </is>
       </c>
       <c r="C686" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D686" s="7" t="inlineStr">
         <is>
-          <t>0:58:43</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E686" s="7" t="inlineStr">
         <is>
-          <t>1:03:35</t>
+          <t>1:06:53</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" s="4" t="inlineStr">
         <is>
-          <t>Generali Prague Half Marathon</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B687" s="5" t="inlineStr">
@@ -17649,16 +17649,16 @@
         </is>
       </c>
       <c r="C687" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D687" s="5" t="inlineStr">
         <is>
-          <t>0:59:43</t>
+          <t>0:58:43</t>
         </is>
       </c>
       <c r="E687" s="5" t="inlineStr">
         <is>
-          <t>1:06:00</t>
+          <t>1:03:35</t>
         </is>
       </c>
     </row>
@@ -17674,16 +17674,16 @@
         </is>
       </c>
       <c r="C688" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D688" s="7" t="inlineStr">
         <is>
-          <t>0:58:24</t>
+          <t>0:59:43</t>
         </is>
       </c>
       <c r="E688" s="7" t="inlineStr">
         <is>
-          <t>1:08:10</t>
+          <t>1:06:00</t>
         </is>
       </c>
     </row>
@@ -17699,23 +17699,23 @@
         </is>
       </c>
       <c r="C689" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D689" s="5" t="inlineStr">
         <is>
-          <t>0:58:54</t>
+          <t>0:58:24</t>
         </is>
       </c>
       <c r="E689" s="5" t="inlineStr">
         <is>
-          <t>1:05:27</t>
+          <t>1:08:10</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" s="6" t="inlineStr">
         <is>
-          <t>GetPro Bath Half</t>
+          <t>Generali Prague Half Marathon</t>
         </is>
       </c>
       <c r="B690" s="7" t="inlineStr">
@@ -17728,12 +17728,12 @@
       </c>
       <c r="D690" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:54</t>
         </is>
       </c>
       <c r="E690" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:27</t>
         </is>
       </c>
     </row>
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="C691" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D691" s="5" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
     <row r="692">
       <c r="A692" s="6" t="inlineStr">
         <is>
-          <t>Göteborgsvarvet</t>
+          <t>GetPro Bath Half</t>
         </is>
       </c>
       <c r="B692" s="7" t="inlineStr">
@@ -17774,16 +17774,16 @@
         </is>
       </c>
       <c r="C692" s="7" t="n">
-        <v>2000</v>
+        <v>2026</v>
       </c>
       <c r="D692" s="7" t="inlineStr">
         <is>
-          <t>1:02:42</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E692" s="7" t="inlineStr">
         <is>
-          <t>1:09:28</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17799,16 +17799,16 @@
         </is>
       </c>
       <c r="C693" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D693" s="5" t="inlineStr">
         <is>
-          <t>1:03:00</t>
+          <t>1:02:42</t>
         </is>
       </c>
       <c r="E693" s="5" t="inlineStr">
         <is>
-          <t>1:11:07</t>
+          <t>1:09:28</t>
         </is>
       </c>
     </row>
@@ -17824,16 +17824,16 @@
         </is>
       </c>
       <c r="C694" s="7" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D694" s="7" t="inlineStr">
         <is>
-          <t>1:03:35</t>
+          <t>1:03:00</t>
         </is>
       </c>
       <c r="E694" s="7" t="inlineStr">
         <is>
-          <t>1:13:03</t>
+          <t>1:11:07</t>
         </is>
       </c>
     </row>
@@ -17849,16 +17849,16 @@
         </is>
       </c>
       <c r="C695" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D695" s="5" t="inlineStr">
         <is>
-          <t>1:03:43</t>
+          <t>1:03:35</t>
         </is>
       </c>
       <c r="E695" s="5" t="inlineStr">
         <is>
-          <t>1:13:27</t>
+          <t>1:13:03</t>
         </is>
       </c>
     </row>
@@ -17874,16 +17874,16 @@
         </is>
       </c>
       <c r="C696" s="7" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D696" s="7" t="inlineStr">
         <is>
-          <t>1:04:03</t>
+          <t>1:03:43</t>
         </is>
       </c>
       <c r="E696" s="7" t="inlineStr">
         <is>
-          <t>1:18:06</t>
+          <t>1:13:27</t>
         </is>
       </c>
     </row>
@@ -17899,16 +17899,16 @@
         </is>
       </c>
       <c r="C697" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D697" s="5" t="inlineStr">
         <is>
-          <t>1:03:19</t>
+          <t>1:04:03</t>
         </is>
       </c>
       <c r="E697" s="5" t="inlineStr">
         <is>
-          <t>1:12:34</t>
+          <t>1:18:06</t>
         </is>
       </c>
     </row>
@@ -17924,11 +17924,11 @@
         </is>
       </c>
       <c r="C698" s="7" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D698" s="7" t="inlineStr">
         <is>
-          <t>1:02:14</t>
+          <t>1:03:19</t>
         </is>
       </c>
       <c r="E698" s="7" t="inlineStr">
@@ -17949,16 +17949,16 @@
         </is>
       </c>
       <c r="C699" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D699" s="5" t="inlineStr">
         <is>
-          <t>1:04:03</t>
+          <t>1:02:14</t>
         </is>
       </c>
       <c r="E699" s="5" t="inlineStr">
         <is>
-          <t>1:12:38</t>
+          <t>1:12:34</t>
         </is>
       </c>
     </row>
@@ -17974,16 +17974,16 @@
         </is>
       </c>
       <c r="C700" s="7" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D700" s="7" t="inlineStr">
         <is>
-          <t>1:01:21</t>
+          <t>1:04:03</t>
         </is>
       </c>
       <c r="E700" s="7" t="inlineStr">
         <is>
-          <t>1:10:19</t>
+          <t>1:12:38</t>
         </is>
       </c>
     </row>
@@ -17999,16 +17999,16 @@
         </is>
       </c>
       <c r="C701" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D701" s="5" t="inlineStr">
         <is>
-          <t>1:01:55</t>
+          <t>1:01:21</t>
         </is>
       </c>
       <c r="E701" s="5" t="inlineStr">
         <is>
-          <t>1:11:27</t>
+          <t>1:10:19</t>
         </is>
       </c>
     </row>
@@ -18024,16 +18024,16 @@
         </is>
       </c>
       <c r="C702" s="7" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D702" s="7" t="inlineStr">
         <is>
-          <t>1:01:10</t>
+          <t>1:01:55</t>
         </is>
       </c>
       <c r="E702" s="7" t="inlineStr">
         <is>
-          <t>1:11:40</t>
+          <t>1:11:27</t>
         </is>
       </c>
     </row>
@@ -18049,16 +18049,16 @@
         </is>
       </c>
       <c r="C703" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D703" s="5" t="inlineStr">
         <is>
-          <t>1:00:52</t>
+          <t>1:01:10</t>
         </is>
       </c>
       <c r="E703" s="5" t="inlineStr">
         <is>
-          <t>1:09:04</t>
+          <t>1:11:40</t>
         </is>
       </c>
     </row>
@@ -18074,16 +18074,16 @@
         </is>
       </c>
       <c r="C704" s="7" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D704" s="7" t="inlineStr">
         <is>
-          <t>1:00:25</t>
+          <t>1:00:52</t>
         </is>
       </c>
       <c r="E704" s="7" t="inlineStr">
         <is>
-          <t>1:09:27</t>
+          <t>1:09:04</t>
         </is>
       </c>
     </row>
@@ -18099,16 +18099,16 @@
         </is>
       </c>
       <c r="C705" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D705" s="5" t="inlineStr">
         <is>
-          <t>1:03:13</t>
+          <t>1:00:25</t>
         </is>
       </c>
       <c r="E705" s="5" t="inlineStr">
         <is>
-          <t>1:11:29</t>
+          <t>1:09:27</t>
         </is>
       </c>
     </row>
@@ -18124,16 +18124,16 @@
         </is>
       </c>
       <c r="C706" s="7" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D706" s="7" t="inlineStr">
         <is>
-          <t>1:00:36</t>
+          <t>1:03:13</t>
         </is>
       </c>
       <c r="E706" s="7" t="inlineStr">
         <is>
-          <t>1:10:12</t>
+          <t>1:11:29</t>
         </is>
       </c>
     </row>
@@ -18149,16 +18149,16 @@
         </is>
       </c>
       <c r="C707" s="5" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="D707" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:36</t>
         </is>
       </c>
       <c r="E707" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:12</t>
         </is>
       </c>
     </row>
@@ -18174,7 +18174,7 @@
         </is>
       </c>
       <c r="C708" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D708" s="7" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
     <row r="709">
       <c r="A709" s="4" t="inlineStr">
         <is>
-          <t>HOKA Semi de Paris</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B709" s="5" t="inlineStr">
@@ -18199,16 +18199,16 @@
         </is>
       </c>
       <c r="C709" s="5" t="n">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="D709" s="5" t="inlineStr">
         <is>
-          <t>1:01:33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E709" s="5" t="inlineStr">
         <is>
-          <t>1:11:07</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -18224,16 +18224,16 @@
         </is>
       </c>
       <c r="C710" s="7" t="n">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="D710" s="7" t="inlineStr">
         <is>
-          <t>0:59:44</t>
+          <t>1:01:33</t>
         </is>
       </c>
       <c r="E710" s="7" t="inlineStr">
         <is>
-          <t>1:07:55</t>
+          <t>1:11:07</t>
         </is>
       </c>
     </row>
@@ -18249,16 +18249,16 @@
         </is>
       </c>
       <c r="C711" s="5" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="D711" s="5" t="inlineStr">
         <is>
-          <t>1:00:08</t>
+          <t>0:59:44</t>
         </is>
       </c>
       <c r="E711" s="5" t="inlineStr">
         <is>
-          <t>1:09:23</t>
+          <t>1:07:55</t>
         </is>
       </c>
     </row>
@@ -18274,16 +18274,16 @@
         </is>
       </c>
       <c r="C712" s="7" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D712" s="7" t="inlineStr">
         <is>
-          <t>0:59:38</t>
+          <t>1:00:08</t>
         </is>
       </c>
       <c r="E712" s="7" t="inlineStr">
         <is>
-          <t>1:06:01</t>
+          <t>1:09:23</t>
         </is>
       </c>
     </row>
@@ -18299,16 +18299,16 @@
         </is>
       </c>
       <c r="C713" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D713" s="5" t="inlineStr">
         <is>
-          <t>1:00:45</t>
+          <t>0:59:38</t>
         </is>
       </c>
       <c r="E713" s="5" t="inlineStr">
         <is>
-          <t>1:06:58</t>
+          <t>1:06:01</t>
         </is>
       </c>
     </row>
@@ -18324,16 +18324,16 @@
         </is>
       </c>
       <c r="C714" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D714" s="7" t="inlineStr">
         <is>
-          <t>1:00:16</t>
+          <t>1:00:45</t>
         </is>
       </c>
       <c r="E714" s="7" t="inlineStr">
         <is>
-          <t>1:07:14</t>
+          <t>1:06:58</t>
         </is>
       </c>
     </row>
@@ -18349,23 +18349,23 @@
         </is>
       </c>
       <c r="C715" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D715" s="5" t="inlineStr">
         <is>
-          <t>1:00:11</t>
+          <t>1:00:16</t>
         </is>
       </c>
       <c r="E715" s="5" t="inlineStr">
         <is>
-          <t>1:05:12</t>
+          <t>1:07:14</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" s="6" t="inlineStr">
         <is>
-          <t>Half Marathon Munchen by Brooks</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B716" s="7" t="inlineStr">
@@ -18374,23 +18374,23 @@
         </is>
       </c>
       <c r="C716" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D716" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:11</t>
         </is>
       </c>
       <c r="E716" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:12</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" s="4" t="inlineStr">
         <is>
-          <t>Hoka Runaway Sydney Half Marathon</t>
+          <t>Half Marathon Munchen by Brooks</t>
         </is>
       </c>
       <c r="B717" s="5" t="inlineStr">
@@ -18415,7 +18415,7 @@
     <row r="718">
       <c r="A718" s="6" t="inlineStr">
         <is>
-          <t>Hyundai Meia Maratona</t>
+          <t>Hoka Runaway Sydney Half Marathon</t>
         </is>
       </c>
       <c r="B718" s="7" t="inlineStr">
@@ -18424,7 +18424,7 @@
         </is>
       </c>
       <c r="C718" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D718" s="7" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         </is>
       </c>
       <c r="C719" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D719" s="5" t="inlineStr">
         <is>
@@ -18474,7 +18474,7 @@
         </is>
       </c>
       <c r="C720" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D720" s="7" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
     <row r="721">
       <c r="A721" s="4" t="inlineStr">
         <is>
-          <t>IU Health 500 Festival Mini-Marathon</t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="B721" s="5" t="inlineStr">
@@ -18515,7 +18515,7 @@
     <row r="722">
       <c r="A722" s="6" t="inlineStr">
         <is>
-          <t>Kagawa Marugame International Half Marathon</t>
+          <t>IU Health 500 Festival Mini-Marathon</t>
         </is>
       </c>
       <c r="B722" s="7" t="inlineStr">
@@ -18524,7 +18524,7 @@
         </is>
       </c>
       <c r="C722" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D722" s="7" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
     <row r="723">
       <c r="A723" s="4" t="inlineStr">
         <is>
-          <t>Life Time Chicago Half Marathon &amp; 5K</t>
+          <t>Kagawa Marugame International Half Marathon</t>
         </is>
       </c>
       <c r="B723" s="5" t="inlineStr">
@@ -18549,7 +18549,7 @@
         </is>
       </c>
       <c r="C723" s="5" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D723" s="5" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         </is>
       </c>
       <c r="C724" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D724" s="7" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
     <row r="725">
       <c r="A725" s="4" t="inlineStr">
         <is>
-          <t>London Landmarks Half Marathon</t>
+          <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
       <c r="B725" s="5" t="inlineStr">
@@ -18599,7 +18599,7 @@
         </is>
       </c>
       <c r="C725" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D725" s="5" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         </is>
       </c>
       <c r="C726" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D726" s="7" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
     <row r="727">
       <c r="A727" s="4" t="inlineStr">
         <is>
-          <t>Manchester Half Marathon</t>
+          <t>London Landmarks Half Marathon</t>
         </is>
       </c>
       <c r="B727" s="5" t="inlineStr">
@@ -18665,7 +18665,7 @@
     <row r="728">
       <c r="A728" s="6" t="inlineStr">
         <is>
-          <t>Media Maraton de Bogota</t>
+          <t>Manchester Half Marathon</t>
         </is>
       </c>
       <c r="B728" s="7" t="inlineStr">
@@ -18690,7 +18690,7 @@
     <row r="729">
       <c r="A729" s="4" t="inlineStr">
         <is>
-          <t>Medio Maraton de Sevilla</t>
+          <t>Media Maraton de Bogota</t>
         </is>
       </c>
       <c r="B729" s="5" t="inlineStr">
@@ -18699,16 +18699,16 @@
         </is>
       </c>
       <c r="C729" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D729" s="5" t="inlineStr">
         <is>
-          <t>0:59:21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E729" s="5" t="inlineStr">
         <is>
-          <t>1:07:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -18724,16 +18724,16 @@
         </is>
       </c>
       <c r="C730" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D730" s="7" t="inlineStr">
         <is>
-          <t>0:59:33</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E730" s="7" t="inlineStr">
         <is>
-          <t>1:07:18</t>
+          <t>1:07:59</t>
         </is>
       </c>
     </row>
@@ -18749,23 +18749,23 @@
         </is>
       </c>
       <c r="C731" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D731" s="5" t="inlineStr">
         <is>
-          <t>1:00:24</t>
+          <t>0:59:33</t>
         </is>
       </c>
       <c r="E731" s="5" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>1:07:18</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" s="6" t="inlineStr">
         <is>
-          <t>Mitja Marato Barcelona by Brooks</t>
+          <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
       <c r="B732" s="7" t="inlineStr">
@@ -18774,16 +18774,16 @@
         </is>
       </c>
       <c r="C732" s="7" t="n">
-        <v>2005</v>
+        <v>2026</v>
       </c>
       <c r="D732" s="7" t="inlineStr">
         <is>
-          <t>1:03:29</t>
+          <t>1:00:24</t>
         </is>
       </c>
       <c r="E732" s="7" t="inlineStr">
         <is>
-          <t>1:09:34</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
@@ -18799,16 +18799,16 @@
         </is>
       </c>
       <c r="C733" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D733" s="5" t="inlineStr">
         <is>
-          <t>1:02:25</t>
+          <t>1:03:29</t>
         </is>
       </c>
       <c r="E733" s="5" t="inlineStr">
         <is>
-          <t>1:09:26</t>
+          <t>1:09:34</t>
         </is>
       </c>
     </row>
@@ -18824,16 +18824,16 @@
         </is>
       </c>
       <c r="C734" s="7" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D734" s="7" t="inlineStr">
         <is>
-          <t>1:03:02</t>
+          <t>1:02:25</t>
         </is>
       </c>
       <c r="E734" s="7" t="inlineStr">
         <is>
-          <t>1:09:05</t>
+          <t>1:09:26</t>
         </is>
       </c>
     </row>
@@ -18849,16 +18849,16 @@
         </is>
       </c>
       <c r="C735" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D735" s="5" t="inlineStr">
         <is>
-          <t>1:02:39</t>
+          <t>1:03:02</t>
         </is>
       </c>
       <c r="E735" s="5" t="inlineStr">
         <is>
-          <t>1:09:15</t>
+          <t>1:09:05</t>
         </is>
       </c>
     </row>
@@ -18874,16 +18874,16 @@
         </is>
       </c>
       <c r="C736" s="7" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D736" s="7" t="inlineStr">
         <is>
-          <t>1:01:45</t>
+          <t>1:02:39</t>
         </is>
       </c>
       <c r="E736" s="7" t="inlineStr">
         <is>
-          <t>1:09:34</t>
+          <t>1:09:15</t>
         </is>
       </c>
     </row>
@@ -18899,16 +18899,16 @@
         </is>
       </c>
       <c r="C737" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D737" s="5" t="inlineStr">
         <is>
-          <t>1:03:00</t>
+          <t>1:01:45</t>
         </is>
       </c>
       <c r="E737" s="5" t="inlineStr">
         <is>
-          <t>1:08:52</t>
+          <t>1:09:34</t>
         </is>
       </c>
     </row>
@@ -18924,16 +18924,16 @@
         </is>
       </c>
       <c r="C738" s="7" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D738" s="7" t="inlineStr">
         <is>
-          <t>1:03:06</t>
+          <t>1:03:00</t>
         </is>
       </c>
       <c r="E738" s="7" t="inlineStr">
         <is>
-          <t>1:08:13</t>
+          <t>1:08:52</t>
         </is>
       </c>
     </row>
@@ -18949,16 +18949,16 @@
         </is>
       </c>
       <c r="C739" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D739" s="5" t="inlineStr">
         <is>
-          <t>1:02:54</t>
+          <t>1:03:06</t>
         </is>
       </c>
       <c r="E739" s="5" t="inlineStr">
         <is>
-          <t>1:10:51</t>
+          <t>1:08:13</t>
         </is>
       </c>
     </row>
@@ -18974,16 +18974,16 @@
         </is>
       </c>
       <c r="C740" s="7" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D740" s="7" t="inlineStr">
         <is>
-          <t>1:01:44</t>
+          <t>1:02:54</t>
         </is>
       </c>
       <c r="E740" s="7" t="inlineStr">
         <is>
-          <t>1:08:28</t>
+          <t>1:10:51</t>
         </is>
       </c>
     </row>
@@ -18999,16 +18999,16 @@
         </is>
       </c>
       <c r="C741" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D741" s="5" t="inlineStr">
         <is>
-          <t>1:02:55</t>
+          <t>1:01:44</t>
         </is>
       </c>
       <c r="E741" s="5" t="inlineStr">
         <is>
-          <t>1:08:35</t>
+          <t>1:08:28</t>
         </is>
       </c>
     </row>
@@ -19024,16 +19024,16 @@
         </is>
       </c>
       <c r="C742" s="7" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D742" s="7" t="inlineStr">
         <is>
-          <t>0:58:53</t>
+          <t>1:02:55</t>
         </is>
       </c>
       <c r="E742" s="7" t="inlineStr">
         <is>
-          <t>1:04:37</t>
+          <t>1:08:35</t>
         </is>
       </c>
     </row>
@@ -19049,16 +19049,16 @@
         </is>
       </c>
       <c r="C743" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D743" s="5" t="inlineStr">
         <is>
-          <t>0:59:21</t>
+          <t>0:58:53</t>
         </is>
       </c>
       <c r="E743" s="5" t="inlineStr">
         <is>
-          <t>1:04:28</t>
+          <t>1:04:37</t>
         </is>
       </c>
     </row>
@@ -19074,16 +19074,16 @@
         </is>
       </c>
       <c r="C744" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D744" s="7" t="inlineStr">
         <is>
-          <t>0:56:42</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E744" s="7" t="inlineStr">
         <is>
-          <t>1:04:11</t>
+          <t>1:04:28</t>
         </is>
       </c>
     </row>
@@ -19099,23 +19099,23 @@
         </is>
       </c>
       <c r="C745" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D745" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:56:42</t>
         </is>
       </c>
       <c r="E745" s="5" t="inlineStr">
         <is>
-          <t>1:04:00</t>
+          <t>1:04:11</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" s="6" t="inlineStr">
         <is>
-          <t>Movistar Madrid Medio Maraton</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B746" s="7" t="inlineStr">
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="C746" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D746" s="7" t="inlineStr">
         <is>
@@ -19133,14 +19133,14 @@
       </c>
       <c r="E746" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:00</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" s="4" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - Half Marathon</t>
+          <t>Movistar Madrid Medio Maraton</t>
         </is>
       </c>
       <c r="B747" s="5" t="inlineStr">
@@ -19178,12 +19178,12 @@
       </c>
       <c r="D748" s="7" t="inlineStr">
         <is>
-          <t>0:59:36</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E748" s="7" t="inlineStr">
         <is>
-          <t>1:08:16</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19199,16 +19199,16 @@
         </is>
       </c>
       <c r="C749" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D749" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:36</t>
         </is>
       </c>
       <c r="E749" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:16</t>
         </is>
       </c>
     </row>
@@ -19228,19 +19228,19 @@
       </c>
       <c r="D750" s="7" t="inlineStr">
         <is>
-          <t>0:59:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E750" s="7" t="inlineStr">
         <is>
-          <t>1:07:34</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" s="4" t="inlineStr">
         <is>
-          <t>NYCRUNS Brooklyn Experience Half Marathon</t>
+          <t>NN CPC Loop Den Haag - Half Marathon</t>
         </is>
       </c>
       <c r="B751" s="5" t="inlineStr">
@@ -19249,23 +19249,23 @@
         </is>
       </c>
       <c r="C751" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D751" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:48</t>
         </is>
       </c>
       <c r="E751" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:34</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" s="6" t="inlineStr">
         <is>
-          <t>NYRR RBC Brooklyn Half</t>
+          <t>NYCRUNS Brooklyn Experience Half Marathon</t>
         </is>
       </c>
       <c r="B752" s="7" t="inlineStr">
@@ -19290,7 +19290,7 @@
     <row r="753">
       <c r="A753" s="4" t="inlineStr">
         <is>
-          <t>Nike Melbourne Marathon Festival</t>
+          <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
       <c r="B753" s="5" t="inlineStr">
@@ -19315,7 +19315,7 @@
     <row r="754">
       <c r="A754" s="6" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>Nike Melbourne Marathon Festival</t>
         </is>
       </c>
       <c r="B754" s="7" t="inlineStr">
@@ -19324,7 +19324,7 @@
         </is>
       </c>
       <c r="C754" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D754" s="7" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         </is>
       </c>
       <c r="C755" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D755" s="5" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         </is>
       </c>
       <c r="C756" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D756" s="7" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         </is>
       </c>
       <c r="C757" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D757" s="5" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
     <row r="758">
       <c r="A758" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B758" s="7" t="inlineStr">
@@ -19424,7 +19424,7 @@
         </is>
       </c>
       <c r="C758" s="7" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D758" s="7" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         </is>
       </c>
       <c r="C759" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D759" s="5" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         </is>
       </c>
       <c r="C760" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D760" s="7" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         </is>
       </c>
       <c r="C761" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D761" s="5" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
     <row r="762">
       <c r="A762" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Mexico City</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B762" s="7" t="inlineStr">
@@ -19524,7 +19524,7 @@
         </is>
       </c>
       <c r="C762" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D762" s="7" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
     <row r="763">
       <c r="A763" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series San Diego</t>
+          <t>Rock 'n' Roll Running Series Mexico City</t>
         </is>
       </c>
       <c r="B763" s="5" t="inlineStr">
@@ -19565,7 +19565,7 @@
     <row r="764">
       <c r="A764" s="6" t="inlineStr">
         <is>
-          <t>Royal Parks Half Marathon</t>
+          <t>Rock 'n' Roll Running Series San Diego</t>
         </is>
       </c>
       <c r="B764" s="7" t="inlineStr">
@@ -19590,7 +19590,7 @@
     <row r="765">
       <c r="A765" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Royal Parks Half Marathon</t>
         </is>
       </c>
       <c r="B765" s="5" t="inlineStr">
@@ -19599,7 +19599,7 @@
         </is>
       </c>
       <c r="C765" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D765" s="5" t="inlineStr">
         <is>
@@ -19624,16 +19624,16 @@
         </is>
       </c>
       <c r="C766" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D766" s="7" t="inlineStr">
         <is>
-          <t>1:05:44</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E766" s="7" t="inlineStr">
         <is>
-          <t>1:18:34</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19649,23 +19649,23 @@
         </is>
       </c>
       <c r="C767" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D767" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:44</t>
         </is>
       </c>
       <c r="E767" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:18:34</t>
         </is>
       </c>
     </row>
     <row r="768">
       <c r="A768" s="6" t="inlineStr">
         <is>
-          <t>Semi-Marathon de Boulogne-Billancourt</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B768" s="7" t="inlineStr">
@@ -19690,7 +19690,7 @@
     <row r="769">
       <c r="A769" s="4" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
+          <t>Semi-Marathon de Boulogne-Billancourt</t>
         </is>
       </c>
       <c r="B769" s="5" t="inlineStr">
@@ -19715,7 +19715,7 @@
     <row r="770">
       <c r="A770" s="6" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Series Nashville</t>
+          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
         </is>
       </c>
       <c r="B770" s="7" t="inlineStr">
@@ -19740,7 +19740,7 @@
     <row r="771">
       <c r="A771" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>St. Jude Rock 'n' Roll Series Nashville</t>
         </is>
       </c>
       <c r="B771" s="5" t="inlineStr">
@@ -19749,16 +19749,16 @@
         </is>
       </c>
       <c r="C771" s="5" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D771" s="5" t="inlineStr">
         <is>
-          <t>1:01:13</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E771" s="5" t="inlineStr">
         <is>
-          <t>1:09:28</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19774,16 +19774,16 @@
         </is>
       </c>
       <c r="C772" s="7" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D772" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:13</t>
         </is>
       </c>
       <c r="E772" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:09:28</t>
         </is>
       </c>
     </row>
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="C773" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D773" s="5" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
     <row r="774">
       <c r="A774" s="6" t="inlineStr">
         <is>
-          <t>Standard Chartered KL Half Marathon</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B774" s="7" t="inlineStr">
@@ -19824,23 +19824,23 @@
         </is>
       </c>
       <c r="C774" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D774" s="7" t="inlineStr">
         <is>
-          <t>1:11:08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E774" s="7" t="inlineStr">
         <is>
-          <t>1:23:55</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Singapore Half Marathon</t>
+          <t>Standard Chartered KL Half Marathon</t>
         </is>
       </c>
       <c r="B775" s="5" t="inlineStr">
@@ -19853,19 +19853,19 @@
       </c>
       <c r="D775" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:11:08</t>
         </is>
       </c>
       <c r="E775" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:23:55</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" s="6" t="inlineStr">
         <is>
-          <t>TCS Mizuno Half Marathon</t>
+          <t>Standard Chartered Singapore Half Marathon</t>
         </is>
       </c>
       <c r="B776" s="7" t="inlineStr">
@@ -19874,16 +19874,16 @@
         </is>
       </c>
       <c r="C776" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D776" s="7" t="inlineStr">
         <is>
-          <t>1:05:23</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E776" s="7" t="inlineStr">
         <is>
-          <t>1:13:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19899,16 +19899,16 @@
         </is>
       </c>
       <c r="C777" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D777" s="5" t="inlineStr">
         <is>
-          <t>1:06:28</t>
+          <t>1:05:23</t>
         </is>
       </c>
       <c r="E777" s="5" t="inlineStr">
         <is>
-          <t>1:17:54</t>
+          <t>1:13:59</t>
         </is>
       </c>
     </row>
@@ -19924,16 +19924,16 @@
         </is>
       </c>
       <c r="C778" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D778" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:28</t>
         </is>
       </c>
       <c r="E778" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:17:54</t>
         </is>
       </c>
     </row>
@@ -19953,19 +19953,19 @@
       </c>
       <c r="D779" s="5" t="inlineStr">
         <is>
-          <t>1:04:21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E779" s="5" t="inlineStr">
         <is>
-          <t>1:10:02</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" s="6" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
       <c r="B780" s="7" t="inlineStr">
@@ -19974,16 +19974,16 @@
         </is>
       </c>
       <c r="C780" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D780" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:21</t>
         </is>
       </c>
       <c r="E780" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:02</t>
         </is>
       </c>
     </row>
@@ -19999,7 +19999,7 @@
         </is>
       </c>
       <c r="C781" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D781" s="5" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         </is>
       </c>
       <c r="C782" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D782" s="7" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
     <row r="783">
       <c r="A783" s="4" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B783" s="5" t="inlineStr">
@@ -20049,7 +20049,7 @@
         </is>
       </c>
       <c r="C783" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D783" s="5" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         </is>
       </c>
       <c r="C784" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D784" s="7" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         </is>
       </c>
       <c r="C785" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D785" s="5" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
     <row r="786">
       <c r="A786" s="6" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon (Half)</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B786" s="7" t="inlineStr">
@@ -20149,7 +20149,7 @@
         </is>
       </c>
       <c r="C787" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D787" s="5" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
     <row r="788">
       <c r="A788" s="6" t="inlineStr">
         <is>
-          <t>The Big Half</t>
+          <t>Tata Mumbai Marathon (Half)</t>
         </is>
       </c>
       <c r="B788" s="7" t="inlineStr">
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="C788" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D788" s="7" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
     <row r="789">
       <c r="A789" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Legacy Half Marathon</t>
+          <t>The Big Half</t>
         </is>
       </c>
       <c r="B789" s="5" t="inlineStr">
@@ -20215,7 +20215,7 @@
     <row r="790">
       <c r="A790" s="6" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>Tokyo Legacy Half Marathon</t>
         </is>
       </c>
       <c r="B790" s="7" t="inlineStr">
@@ -20224,16 +20224,16 @@
         </is>
       </c>
       <c r="C790" s="7" t="n">
-        <v>2006</v>
+        <v>2025</v>
       </c>
       <c r="D790" s="7" t="inlineStr">
         <is>
-          <t>1:01:22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E790" s="7" t="inlineStr">
         <is>
-          <t>1:09:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20249,16 +20249,16 @@
         </is>
       </c>
       <c r="C791" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D791" s="5" t="inlineStr">
         <is>
-          <t>0:59:24</t>
+          <t>1:01:22</t>
         </is>
       </c>
       <c r="E791" s="5" t="inlineStr">
         <is>
-          <t>1:10:32</t>
+          <t>1:09:43</t>
         </is>
       </c>
     </row>
@@ -20274,16 +20274,16 @@
         </is>
       </c>
       <c r="C792" s="7" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D792" s="7" t="inlineStr">
         <is>
-          <t>1:00:58</t>
+          <t>0:59:24</t>
         </is>
       </c>
       <c r="E792" s="7" t="inlineStr">
         <is>
-          <t>1:10:19</t>
+          <t>1:10:32</t>
         </is>
       </c>
     </row>
@@ -20299,16 +20299,16 @@
         </is>
       </c>
       <c r="C793" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D793" s="5" t="inlineStr">
         <is>
-          <t>1:01:06</t>
+          <t>1:00:58</t>
         </is>
       </c>
       <c r="E793" s="5" t="inlineStr">
         <is>
-          <t>1:09:32</t>
+          <t>1:10:19</t>
         </is>
       </c>
     </row>
@@ -20324,16 +20324,16 @@
         </is>
       </c>
       <c r="C794" s="7" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D794" s="7" t="inlineStr">
         <is>
-          <t>0:59:52</t>
+          <t>1:01:06</t>
         </is>
       </c>
       <c r="E794" s="7" t="inlineStr">
         <is>
-          <t>1:09:25</t>
+          <t>1:09:32</t>
         </is>
       </c>
     </row>
@@ -20349,16 +20349,16 @@
         </is>
       </c>
       <c r="C795" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D795" s="5" t="inlineStr">
         <is>
-          <t>1:00:23</t>
+          <t>0:59:52</t>
         </is>
       </c>
       <c r="E795" s="5" t="inlineStr">
         <is>
-          <t>1:08:52</t>
+          <t>1:09:25</t>
         </is>
       </c>
     </row>
@@ -20374,16 +20374,16 @@
         </is>
       </c>
       <c r="C796" s="7" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D796" s="7" t="inlineStr">
         <is>
-          <t>0:59:39</t>
+          <t>1:00:23</t>
         </is>
       </c>
       <c r="E796" s="7" t="inlineStr">
         <is>
-          <t>1:08:35</t>
+          <t>1:08:52</t>
         </is>
       </c>
     </row>
@@ -20399,16 +20399,16 @@
         </is>
       </c>
       <c r="C797" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D797" s="5" t="inlineStr">
         <is>
-          <t>1:01:02</t>
+          <t>0:59:39</t>
         </is>
       </c>
       <c r="E797" s="5" t="inlineStr">
         <is>
-          <t>1:09:09</t>
+          <t>1:08:35</t>
         </is>
       </c>
     </row>
@@ -20424,16 +20424,16 @@
         </is>
       </c>
       <c r="C798" s="7" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D798" s="7" t="inlineStr">
         <is>
-          <t>1:00:50</t>
+          <t>1:01:02</t>
         </is>
       </c>
       <c r="E798" s="7" t="inlineStr">
         <is>
-          <t>1:08:31</t>
+          <t>1:09:09</t>
         </is>
       </c>
     </row>
@@ -20449,16 +20449,16 @@
         </is>
       </c>
       <c r="C799" s="5" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D799" s="5" t="inlineStr">
         <is>
-          <t>1:01:31</t>
+          <t>1:00:50</t>
         </is>
       </c>
       <c r="E799" s="5" t="inlineStr">
         <is>
-          <t>1:07:04</t>
+          <t>1:08:31</t>
         </is>
       </c>
     </row>
@@ -20474,23 +20474,23 @@
         </is>
       </c>
       <c r="C800" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D800" s="7" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>1:01:31</t>
         </is>
       </c>
       <c r="E800" s="7" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>1:07:04</t>
         </is>
       </c>
     </row>
     <row r="801">
       <c r="A801" s="4" t="inlineStr">
         <is>
-          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B801" s="5" t="inlineStr">
@@ -20499,23 +20499,23 @@
         </is>
       </c>
       <c r="C801" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D801" s="5" t="inlineStr">
         <is>
-          <t>0:58:02</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E801" s="5" t="inlineStr">
         <is>
-          <t>1:03:08</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
     <row r="802">
       <c r="A802" s="6" t="inlineStr">
         <is>
-          <t>Vedanta Delhi Half Marathon</t>
+          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B802" s="7" t="inlineStr">
@@ -20528,19 +20528,19 @@
       </c>
       <c r="D802" s="7" t="inlineStr">
         <is>
-          <t>0:59:50</t>
+          <t>0:58:02</t>
         </is>
       </c>
       <c r="E802" s="7" t="inlineStr">
         <is>
-          <t>1:07:20</t>
+          <t>1:03:08</t>
         </is>
       </c>
     </row>
     <row r="803">
       <c r="A803" s="4" t="inlineStr">
         <is>
-          <t>Vienna City Half Marathon</t>
+          <t>Vedanta Delhi Half Marathon</t>
         </is>
       </c>
       <c r="B803" s="5" t="inlineStr">
@@ -20553,19 +20553,19 @@
       </c>
       <c r="D803" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:50</t>
         </is>
       </c>
       <c r="E803" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:20</t>
         </is>
       </c>
     </row>
     <row r="804">
       <c r="A804" s="6" t="inlineStr">
         <is>
-          <t>Walt Disney World Marathon Weekend</t>
+          <t>Vienna City Half Marathon</t>
         </is>
       </c>
       <c r="B804" s="7" t="inlineStr">
@@ -20599,7 +20599,7 @@
         </is>
       </c>
       <c r="C805" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D805" s="5" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
     <row r="806">
       <c r="A806" s="6" t="inlineStr">
         <is>
-          <t>Warsaw Half Marathon</t>
+          <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
       <c r="B806" s="7" t="inlineStr">
@@ -20624,7 +20624,7 @@
         </is>
       </c>
       <c r="C806" s="7" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D806" s="7" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         </is>
       </c>
       <c r="C807" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D807" s="5" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
     <row r="808">
       <c r="A808" s="6" t="inlineStr">
         <is>
-          <t>Wizz Air Rome Half Marathon by Brooks</t>
+          <t>Warsaw Half Marathon</t>
         </is>
       </c>
       <c r="B808" s="7" t="inlineStr">
@@ -20690,7 +20690,7 @@
     <row r="809">
       <c r="A809" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Wizz Air Rome Half Marathon by Brooks</t>
         </is>
       </c>
       <c r="B809" s="5" t="inlineStr">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="C809" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D809" s="5" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         </is>
       </c>
       <c r="C810" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D810" s="7" t="inlineStr">
         <is>
@@ -20749,39 +20749,39 @@
         </is>
       </c>
       <c r="C811" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D811" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E811" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="6" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+        </is>
+      </c>
+      <c r="B812" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C812" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="D811" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E811" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="812">
-      <c r="A812" s="8" t="inlineStr">
-        <is>
-          <t>10K Montmartre</t>
-        </is>
-      </c>
-      <c r="B812" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C812" s="9" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D812" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E812" s="9" t="inlineStr">
+      <c r="D812" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E812" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20790,7 +20790,7 @@
     <row r="813">
       <c r="A813" s="4" t="inlineStr">
         <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
+          <t>10K Montmartre</t>
         </is>
       </c>
       <c r="B813" s="5" t="inlineStr">
@@ -20799,7 +20799,7 @@
         </is>
       </c>
       <c r="C813" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D813" s="5" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="E813" s="5" t="inlineStr">
         <is>
-          <t>0:29:19</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="C814" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D814" s="9" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
       </c>
       <c r="E814" s="9" t="inlineStr">
         <is>
-          <t>0:28:45</t>
+          <t>0:29:19</t>
         </is>
       </c>
     </row>
@@ -20849,7 +20849,7 @@
         </is>
       </c>
       <c r="C815" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D815" s="5" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="E815" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:45</t>
         </is>
       </c>
     </row>
@@ -20874,23 +20874,23 @@
         </is>
       </c>
       <c r="C816" s="9" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D816" s="9" t="inlineStr">
         <is>
-          <t>0:26:45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E816" s="9" t="inlineStr">
         <is>
-          <t>0:29:25</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="817">
       <c r="A817" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Birmingham Run 10K</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B817" s="5" t="inlineStr">
@@ -20899,23 +20899,23 @@
         </is>
       </c>
       <c r="C817" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D817" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:26:45</t>
         </is>
       </c>
       <c r="E817" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:25</t>
         </is>
       </c>
     </row>
     <row r="818">
       <c r="A818" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Bristol Run 10K</t>
+          <t>AJ Bell Great Birmingham Run 10K</t>
         </is>
       </c>
       <c r="B818" s="9" t="inlineStr">
@@ -20940,7 +20940,7 @@
     <row r="819">
       <c r="A819" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run</t>
+          <t>AJ Bell Great Bristol Run 10K</t>
         </is>
       </c>
       <c r="B819" s="5" t="inlineStr">
@@ -20949,16 +20949,16 @@
         </is>
       </c>
       <c r="C819" s="5" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D819" s="5" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E819" s="5" t="inlineStr">
         <is>
-          <t>0:30:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20974,23 +20974,23 @@
         </is>
       </c>
       <c r="C820" s="9" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D820" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E820" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:30:51</t>
         </is>
       </c>
     </row>
     <row r="821">
       <c r="A821" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B821" s="5" t="inlineStr">
@@ -20999,7 +20999,7 @@
         </is>
       </c>
       <c r="C821" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D821" s="5" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         </is>
       </c>
       <c r="C822" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D822" s="9" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
     <row r="823">
       <c r="A823" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great North 10K</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B823" s="5" t="inlineStr">
@@ -21065,7 +21065,7 @@
     <row r="824">
       <c r="A824" s="8" t="inlineStr">
         <is>
-          <t>ASICS LDNX</t>
+          <t>AJ Bell Great North 10K</t>
         </is>
       </c>
       <c r="B824" s="9" t="inlineStr">
@@ -21090,7 +21090,7 @@
     <row r="825">
       <c r="A825" s="4" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>ASICS LDNX</t>
         </is>
       </c>
       <c r="B825" s="5" t="inlineStr">
@@ -21099,7 +21099,7 @@
         </is>
       </c>
       <c r="C825" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D825" s="5" t="inlineStr">
         <is>
@@ -21124,16 +21124,16 @@
         </is>
       </c>
       <c r="C826" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D826" s="9" t="inlineStr">
         <is>
-          <t>0:29:37</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E826" s="9" t="inlineStr">
         <is>
-          <t>0:32:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21149,23 +21149,23 @@
         </is>
       </c>
       <c r="C827" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D827" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:37</t>
         </is>
       </c>
       <c r="E827" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:18</t>
         </is>
       </c>
     </row>
     <row r="828">
       <c r="A828" s="8" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B828" s="9" t="inlineStr">
@@ -21174,16 +21174,16 @@
         </is>
       </c>
       <c r="C828" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D828" s="9" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E828" s="9" t="inlineStr">
         <is>
-          <t>0:30:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21199,16 +21199,16 @@
         </is>
       </c>
       <c r="C829" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D829" s="5" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E829" s="5" t="inlineStr">
         <is>
-          <t>0:31:12</t>
+          <t>0:30:43</t>
         </is>
       </c>
     </row>
@@ -21224,23 +21224,23 @@
         </is>
       </c>
       <c r="C830" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D830" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E830" s="9" t="inlineStr">
         <is>
-          <t>0:31:29</t>
+          <t>0:31:12</t>
         </is>
       </c>
     </row>
     <row r="831">
       <c r="A831" s="4" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B831" s="5" t="inlineStr">
@@ -21249,16 +21249,16 @@
         </is>
       </c>
       <c r="C831" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D831" s="5" t="inlineStr">
         <is>
-          <t>0:29:08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E831" s="5" t="inlineStr">
         <is>
-          <t>0:33:25</t>
+          <t>0:31:29</t>
         </is>
       </c>
     </row>
@@ -21274,16 +21274,16 @@
         </is>
       </c>
       <c r="C832" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D832" s="9" t="inlineStr">
         <is>
-          <t>0:29:13</t>
+          <t>0:29:08</t>
         </is>
       </c>
       <c r="E832" s="9" t="inlineStr">
         <is>
-          <t>0:32:45</t>
+          <t>0:33:25</t>
         </is>
       </c>
     </row>
@@ -21299,16 +21299,16 @@
         </is>
       </c>
       <c r="C833" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D833" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:13</t>
         </is>
       </c>
       <c r="E833" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:45</t>
         </is>
       </c>
     </row>
@@ -21328,19 +21328,19 @@
       </c>
       <c r="D834" s="9" t="inlineStr">
         <is>
-          <t>0:28:36</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E834" s="9" t="inlineStr">
         <is>
-          <t>0:31:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="835">
       <c r="A835" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B835" s="5" t="inlineStr">
@@ -21349,16 +21349,16 @@
         </is>
       </c>
       <c r="C835" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D835" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:36</t>
         </is>
       </c>
       <c r="E835" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:51</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="C836" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D836" s="9" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         </is>
       </c>
       <c r="C837" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D837" s="5" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
     <row r="838">
       <c r="A838" s="8" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B838" s="9" t="inlineStr">
@@ -21424,16 +21424,16 @@
         </is>
       </c>
       <c r="C838" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D838" s="9" t="inlineStr">
         <is>
-          <t>0:28:52</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E838" s="9" t="inlineStr">
         <is>
-          <t>0:31:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21449,16 +21449,16 @@
         </is>
       </c>
       <c r="C839" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D839" s="5" t="inlineStr">
         <is>
-          <t>0:28:46</t>
+          <t>0:28:52</t>
         </is>
       </c>
       <c r="E839" s="5" t="inlineStr">
         <is>
-          <t>0:32:33</t>
+          <t>0:31:59</t>
         </is>
       </c>
     </row>
@@ -21474,16 +21474,16 @@
         </is>
       </c>
       <c r="C840" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D840" s="9" t="inlineStr">
         <is>
-          <t>0:29:22</t>
+          <t>0:28:46</t>
         </is>
       </c>
       <c r="E840" s="9" t="inlineStr">
         <is>
-          <t>0:34:32</t>
+          <t>0:32:33</t>
         </is>
       </c>
     </row>
@@ -21499,23 +21499,23 @@
         </is>
       </c>
       <c r="C841" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D841" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:22</t>
         </is>
       </c>
       <c r="E841" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:34:32</t>
         </is>
       </c>
     </row>
     <row r="842">
       <c r="A842" s="8" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B842" s="9" t="inlineStr">
@@ -21524,7 +21524,7 @@
         </is>
       </c>
       <c r="C842" s="9" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D842" s="9" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         </is>
       </c>
       <c r="C843" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D843" s="5" t="inlineStr">
         <is>
@@ -21574,16 +21574,16 @@
         </is>
       </c>
       <c r="C844" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D844" s="9" t="inlineStr">
         <is>
-          <t>0:28:27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E844" s="9" t="inlineStr">
         <is>
-          <t>0:31:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21603,19 +21603,19 @@
       </c>
       <c r="D845" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:27</t>
         </is>
       </c>
       <c r="E845" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:49</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" s="8" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B846" s="9" t="inlineStr">
@@ -21624,7 +21624,7 @@
         </is>
       </c>
       <c r="C846" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D846" s="9" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         </is>
       </c>
       <c r="C847" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D847" s="5" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         </is>
       </c>
       <c r="C848" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D848" s="9" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         </is>
       </c>
       <c r="C849" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D849" s="5" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
     <row r="850">
       <c r="A850" s="8" t="inlineStr">
         <is>
-          <t>Great Scottish Run 10K</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B850" s="9" t="inlineStr">
@@ -21724,7 +21724,7 @@
         </is>
       </c>
       <c r="C850" s="9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D850" s="9" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
     <row r="851">
       <c r="A851" s="4" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
+          <t>Great Scottish Run 10K</t>
         </is>
       </c>
       <c r="B851" s="5" t="inlineStr">
@@ -21749,7 +21749,7 @@
         </is>
       </c>
       <c r="C851" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D851" s="5" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
     <row r="852">
       <c r="A852" s="8" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
         </is>
       </c>
       <c r="B852" s="9" t="inlineStr">
@@ -21774,7 +21774,7 @@
         </is>
       </c>
       <c r="C852" s="9" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D852" s="9" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         </is>
       </c>
       <c r="C853" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D853" s="5" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
       </c>
       <c r="E853" s="5" t="inlineStr">
         <is>
-          <t>0:31:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21824,23 +21824,23 @@
         </is>
       </c>
       <c r="C854" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D854" s="9" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E854" s="9" t="inlineStr">
         <is>
-          <t>0:31:11</t>
+          <t>0:31:18</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" s="4" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B855" s="5" t="inlineStr">
@@ -21849,16 +21849,16 @@
         </is>
       </c>
       <c r="C855" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D855" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E855" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:11</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
         </is>
       </c>
       <c r="C856" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D856" s="9" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         </is>
       </c>
       <c r="C857" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D857" s="5" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
     <row r="858">
       <c r="A858" s="8" t="inlineStr">
         <is>
-          <t>Run in Lyon</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B858" s="9" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="859">
       <c r="A859" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>Run in Lyon</t>
         </is>
       </c>
       <c r="B859" s="5" t="inlineStr">
@@ -21949,7 +21949,7 @@
         </is>
       </c>
       <c r="C859" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D859" s="5" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         </is>
       </c>
       <c r="C860" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D860" s="9" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         </is>
       </c>
       <c r="C861" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D861" s="5" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
     <row r="862">
       <c r="A862" s="8" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B862" s="9" t="inlineStr">
@@ -22024,7 +22024,7 @@
         </is>
       </c>
       <c r="C862" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D862" s="9" t="inlineStr">
         <is>
@@ -22049,16 +22049,16 @@
         </is>
       </c>
       <c r="C863" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D863" s="5" t="inlineStr">
         <is>
-          <t>0:29:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E863" s="5" t="inlineStr">
         <is>
-          <t>0:32:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22074,23 +22074,23 @@
         </is>
       </c>
       <c r="C864" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D864" s="9" t="inlineStr">
         <is>
-          <t>0:29:33</t>
+          <t>0:29:41</t>
         </is>
       </c>
       <c r="E864" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:51</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered KL 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B865" s="5" t="inlineStr">
@@ -22103,19 +22103,19 @@
       </c>
       <c r="D865" s="5" t="inlineStr">
         <is>
-          <t>0:32:26</t>
+          <t>0:29:33</t>
         </is>
       </c>
       <c r="E865" s="5" t="inlineStr">
         <is>
-          <t>0:39:23</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" s="8" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Standard Chartered KL 10K</t>
         </is>
       </c>
       <c r="B866" s="9" t="inlineStr">
@@ -22124,16 +22124,16 @@
         </is>
       </c>
       <c r="C866" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D866" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:26</t>
         </is>
       </c>
       <c r="E866" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:39:23</t>
         </is>
       </c>
     </row>
@@ -22149,7 +22149,7 @@
         </is>
       </c>
       <c r="C867" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D867" s="5" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         </is>
       </c>
       <c r="C868" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D868" s="9" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
     <row r="869">
       <c r="A869" s="4" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B869" s="5" t="inlineStr">
@@ -22199,7 +22199,7 @@
         </is>
       </c>
       <c r="C869" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D869" s="5" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="C870" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D870" s="9" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
         </is>
       </c>
       <c r="C871" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D871" s="5" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
     <row r="872">
       <c r="A872" s="8" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B872" s="9" t="inlineStr">
@@ -22274,7 +22274,7 @@
         </is>
       </c>
       <c r="C872" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D872" s="9" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         </is>
       </c>
       <c r="C873" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D873" s="5" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         </is>
       </c>
       <c r="C874" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D874" s="9" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
     <row r="875">
       <c r="A875" s="4" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B875" s="5" t="inlineStr">
@@ -22349,7 +22349,7 @@
         </is>
       </c>
       <c r="C875" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D875" s="5" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         </is>
       </c>
       <c r="C876" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D876" s="9" t="inlineStr">
         <is>
@@ -22399,23 +22399,23 @@
         </is>
       </c>
       <c r="C877" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D877" s="5" t="inlineStr">
         <is>
-          <t>0:28:09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E877" s="5" t="inlineStr">
         <is>
-          <t>0:32:54</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" s="8" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Vancouver Sun Run</t>
         </is>
       </c>
       <c r="B878" s="9" t="inlineStr">
@@ -22424,16 +22424,16 @@
         </is>
       </c>
       <c r="C878" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D878" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:09</t>
         </is>
       </c>
       <c r="E878" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:54</t>
         </is>
       </c>
     </row>
@@ -22449,16 +22449,16 @@
         </is>
       </c>
       <c r="C879" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D879" s="5" t="inlineStr">
         <is>
-          <t>0:29:14</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E879" s="5" t="inlineStr">
         <is>
-          <t>0:31:36</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22474,28 +22474,28 @@
         </is>
       </c>
       <c r="C880" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D880" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:14</t>
         </is>
       </c>
       <c r="E880" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:36</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Birmingham Run</t>
+          <t>Vitality London 10,000</t>
         </is>
       </c>
       <c r="B881" s="5" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C881" s="5" t="n">
@@ -22515,25 +22515,25 @@
     <row r="882">
       <c r="A882" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great South Run</t>
+          <t>AJ Bell Great Birmingham Run</t>
         </is>
       </c>
       <c r="B882" s="9" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>SEMI</t>
         </is>
       </c>
       <c r="C882" s="9" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D882" s="9" t="inlineStr">
         <is>
-          <t>0:47:19</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E882" s="9" t="inlineStr">
         <is>
-          <t>0:50:42</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22549,23 +22549,23 @@
         </is>
       </c>
       <c r="C883" s="5" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D883" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:47:19</t>
         </is>
       </c>
       <c r="E883" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:50:42</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" s="8" t="inlineStr">
         <is>
-          <t>Army Ten Miler</t>
+          <t>AJ Bell Great South Run</t>
         </is>
       </c>
       <c r="B884" s="9" t="inlineStr">
@@ -22590,7 +22590,7 @@
     <row r="885">
       <c r="A885" s="4" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>Army Ten Miler</t>
         </is>
       </c>
       <c r="B885" s="5" t="inlineStr">
@@ -22599,7 +22599,7 @@
         </is>
       </c>
       <c r="C885" s="5" t="n">
-        <v>2005</v>
+        <v>2025</v>
       </c>
       <c r="D885" s="5" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
       </c>
       <c r="E885" s="5" t="inlineStr">
         <is>
-          <t>0:38:22</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22624,16 +22624,16 @@
         </is>
       </c>
       <c r="C886" s="9" t="n">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="D886" s="9" t="inlineStr">
         <is>
-          <t>0:33:31</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E886" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:38:22</t>
         </is>
       </c>
     </row>
@@ -22649,16 +22649,16 @@
         </is>
       </c>
       <c r="C887" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D887" s="5" t="inlineStr">
         <is>
-          <t>0:34:15</t>
+          <t>0:33:31</t>
         </is>
       </c>
       <c r="E887" s="5" t="inlineStr">
         <is>
-          <t>0:38:07</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22674,16 +22674,16 @@
         </is>
       </c>
       <c r="C888" s="9" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="D888" s="9" t="inlineStr">
         <is>
-          <t>0:34:40</t>
+          <t>0:34:15</t>
         </is>
       </c>
       <c r="E888" s="9" t="inlineStr">
         <is>
-          <t>0:39:02</t>
+          <t>0:38:07</t>
         </is>
       </c>
     </row>
@@ -22699,16 +22699,16 @@
         </is>
       </c>
       <c r="C889" s="5" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="D889" s="5" t="inlineStr">
         <is>
-          <t>0:35:01</t>
+          <t>0:34:40</t>
         </is>
       </c>
       <c r="E889" s="5" t="inlineStr">
         <is>
-          <t>0:39:28</t>
+          <t>0:39:02</t>
         </is>
       </c>
     </row>
@@ -22724,16 +22724,16 @@
         </is>
       </c>
       <c r="C890" s="9" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D890" s="9" t="inlineStr">
         <is>
-          <t>0:36:10</t>
+          <t>0:35:01</t>
         </is>
       </c>
       <c r="E890" s="9" t="inlineStr">
         <is>
-          <t>0:42:05</t>
+          <t>0:39:28</t>
         </is>
       </c>
     </row>
@@ -22749,23 +22749,23 @@
         </is>
       </c>
       <c r="C891" s="5" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D891" s="5" t="inlineStr">
         <is>
-          <t>0:37:02</t>
+          <t>0:36:10</t>
         </is>
       </c>
       <c r="E891" s="5" t="inlineStr">
         <is>
-          <t>0:43:48</t>
+          <t>0:42:05</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="8" t="inlineStr">
         <is>
-          <t>Boilermaker Road Race</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B892" s="9" t="inlineStr">
@@ -22774,23 +22774,23 @@
         </is>
       </c>
       <c r="C892" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D892" s="9" t="inlineStr">
         <is>
-          <t>0:42:44</t>
+          <t>0:37:02</t>
         </is>
       </c>
       <c r="E892" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:43:48</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" s="4" t="inlineStr">
         <is>
-          <t>Broad Street Run</t>
+          <t>Boilermaker Road Race</t>
         </is>
       </c>
       <c r="B893" s="5" t="inlineStr">
@@ -22803,19 +22803,19 @@
       </c>
       <c r="D893" s="5" t="inlineStr">
         <is>
-          <t>0:46:13</t>
+          <t>0:42:44</t>
         </is>
       </c>
       <c r="E893" s="5" t="inlineStr">
         <is>
-          <t>0:54:01</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="8" t="inlineStr">
         <is>
-          <t>City2Surf</t>
+          <t>Broad Street Run</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
@@ -22824,23 +22824,23 @@
         </is>
       </c>
       <c r="C894" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D894" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:46:13</t>
         </is>
       </c>
       <c r="E894" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:54:01</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>City2Surf</t>
         </is>
       </c>
       <c r="B895" s="5" t="inlineStr">
@@ -22849,7 +22849,7 @@
         </is>
       </c>
       <c r="C895" s="5" t="n">
-        <v>2009</v>
+        <v>2024</v>
       </c>
       <c r="D895" s="5" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
       </c>
       <c r="E895" s="5" t="inlineStr">
         <is>
-          <t>0:50:39</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="C896" s="9" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D896" s="9" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
       </c>
       <c r="E896" s="9" t="inlineStr">
         <is>
-          <t>0:51:30</t>
+          <t>0:50:39</t>
         </is>
       </c>
     </row>
@@ -22899,16 +22899,16 @@
         </is>
       </c>
       <c r="C897" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D897" s="5" t="inlineStr">
         <is>
-          <t>0:44:27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E897" s="5" t="inlineStr">
         <is>
-          <t>0:51:57</t>
+          <t>0:51:30</t>
         </is>
       </c>
     </row>
@@ -22924,16 +22924,16 @@
         </is>
       </c>
       <c r="C898" s="9" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D898" s="9" t="inlineStr">
         <is>
-          <t>0:44:48</t>
+          <t>0:44:27</t>
         </is>
       </c>
       <c r="E898" s="9" t="inlineStr">
         <is>
-          <t>0:51:42</t>
+          <t>0:51:57</t>
         </is>
       </c>
     </row>
@@ -22949,16 +22949,16 @@
         </is>
       </c>
       <c r="C899" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D899" s="5" t="inlineStr">
         <is>
-          <t>0:45:28</t>
+          <t>0:44:48</t>
         </is>
       </c>
       <c r="E899" s="5" t="inlineStr">
         <is>
-          <t>0:51:33</t>
+          <t>0:51:42</t>
         </is>
       </c>
     </row>
@@ -22974,16 +22974,16 @@
         </is>
       </c>
       <c r="C900" s="9" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D900" s="9" t="inlineStr">
         <is>
-          <t>0:45:45</t>
+          <t>0:45:28</t>
         </is>
       </c>
       <c r="E900" s="9" t="inlineStr">
         <is>
-          <t>0:53:09</t>
+          <t>0:51:33</t>
         </is>
       </c>
     </row>
@@ -22999,16 +22999,16 @@
         </is>
       </c>
       <c r="C901" s="5" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D901" s="5" t="inlineStr">
         <is>
-          <t>0:45:15</t>
+          <t>0:45:45</t>
         </is>
       </c>
       <c r="E901" s="5" t="inlineStr">
         <is>
-          <t>0:50:45</t>
+          <t>0:53:09</t>
         </is>
       </c>
     </row>
@@ -23024,16 +23024,16 @@
         </is>
       </c>
       <c r="C902" s="9" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D902" s="9" t="inlineStr">
         <is>
-          <t>0:49:00</t>
+          <t>0:45:15</t>
         </is>
       </c>
       <c r="E902" s="9" t="inlineStr">
         <is>
-          <t>0:55:44</t>
+          <t>0:50:45</t>
         </is>
       </c>
     </row>
@@ -23049,16 +23049,16 @@
         </is>
       </c>
       <c r="C903" s="5" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D903" s="5" t="inlineStr">
         <is>
-          <t>0:44:51</t>
+          <t>0:49:00</t>
         </is>
       </c>
       <c r="E903" s="5" t="inlineStr">
         <is>
-          <t>0:51:15</t>
+          <t>0:55:44</t>
         </is>
       </c>
     </row>
@@ -23074,23 +23074,23 @@
         </is>
       </c>
       <c r="C904" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D904" s="9" t="inlineStr">
         <is>
-          <t>0:46:07</t>
+          <t>0:44:51</t>
         </is>
       </c>
       <c r="E904" s="9" t="inlineStr">
         <is>
-          <t>0:50:51</t>
+          <t>0:51:15</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" s="4" t="inlineStr">
         <is>
-          <t>Falmouth Road Race</t>
+          <t>Dam tot Damloop</t>
         </is>
       </c>
       <c r="B905" s="5" t="inlineStr">
@@ -23103,24 +23103,24 @@
       </c>
       <c r="D905" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:46:07</t>
         </is>
       </c>
       <c r="E905" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:50:51</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" s="8" t="inlineStr">
         <is>
-          <t>Great Scottish Run</t>
+          <t>Falmouth Road Race</t>
         </is>
       </c>
       <c r="B906" s="9" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="C906" s="9" t="n">
@@ -23140,12 +23140,12 @@
     <row r="907">
       <c r="A907" s="4" t="inlineStr">
         <is>
-          <t>Lilac Bloomsday Run</t>
+          <t>Great Scottish Run</t>
         </is>
       </c>
       <c r="B907" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>SEMI</t>
         </is>
       </c>
       <c r="C907" s="5" t="n">
@@ -23165,30 +23165,55 @@
     <row r="908">
       <c r="A908" s="8" t="inlineStr">
         <is>
+          <t>Lilac Bloomsday Run</t>
+        </is>
+      </c>
+      <c r="B908" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C908" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D908" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E908" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="4" t="inlineStr">
+        <is>
           <t>Manchester Road Race</t>
         </is>
       </c>
-      <c r="B908" s="9" t="inlineStr">
+      <c r="B909" s="5" t="inlineStr">
         <is>
           <t>AUTRE</t>
         </is>
       </c>
-      <c r="C908" s="9" t="n">
+      <c r="C909" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="D908" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E908" s="9" t="inlineStr">
+      <c r="D909" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E909" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E908"/>
+  <autoFilter ref="A1:E909"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Chronos_Vainqueurs.xlsx
+++ b/Chronos_Vainqueurs.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$910</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$911</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E910"/>
+  <dimension ref="A1:E911"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -10340,7 +10340,7 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>San Francisco Marathon</t>
+          <t>Run in Lyon</t>
         </is>
       </c>
       <c r="B395" s="5" t="inlineStr">
@@ -10349,16 +10349,16 @@
         </is>
       </c>
       <c r="C395" s="5" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D395" s="5" t="inlineStr">
         <is>
-          <t>2:26:22</t>
+          <t>2:23:24</t>
         </is>
       </c>
       <c r="E395" s="5" t="inlineStr">
         <is>
-          <t>2:49:42</t>
+          <t>2:43:34</t>
         </is>
       </c>
     </row>
@@ -10374,16 +10374,16 @@
         </is>
       </c>
       <c r="C396" s="3" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>2:30:42</t>
+          <t>2:26:22</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>2:49:51</t>
+          <t>2:49:42</t>
         </is>
       </c>
     </row>
@@ -10399,16 +10399,16 @@
         </is>
       </c>
       <c r="C397" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D397" s="5" t="inlineStr">
         <is>
-          <t>2:28:23</t>
+          <t>2:30:42</t>
         </is>
       </c>
       <c r="E397" s="5" t="inlineStr">
         <is>
-          <t>2:52:49</t>
+          <t>2:49:51</t>
         </is>
       </c>
     </row>
@@ -10424,16 +10424,16 @@
         </is>
       </c>
       <c r="C398" s="3" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>2:27:56</t>
+          <t>2:28:23</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>2:54:09</t>
+          <t>2:52:49</t>
         </is>
       </c>
     </row>
@@ -10449,16 +10449,16 @@
         </is>
       </c>
       <c r="C399" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D399" s="5" t="inlineStr">
         <is>
-          <t>2:25:25</t>
+          <t>2:27:56</t>
         </is>
       </c>
       <c r="E399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:54:09</t>
         </is>
       </c>
     </row>
@@ -10474,16 +10474,16 @@
         </is>
       </c>
       <c r="C400" s="3" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>2:20:47</t>
+          <t>2:25:25</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>2:55:20</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -10499,16 +10499,16 @@
         </is>
       </c>
       <c r="C401" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D401" s="5" t="inlineStr">
         <is>
-          <t>2:31:42</t>
+          <t>2:20:47</t>
         </is>
       </c>
       <c r="E401" s="5" t="inlineStr">
         <is>
-          <t>2:44:38</t>
+          <t>2:55:20</t>
         </is>
       </c>
     </row>
@@ -10524,16 +10524,16 @@
         </is>
       </c>
       <c r="C402" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>2:26:17</t>
+          <t>2:31:42</t>
         </is>
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>2:45:59</t>
+          <t>2:44:38</t>
         </is>
       </c>
     </row>
@@ -10549,23 +10549,23 @@
         </is>
       </c>
       <c r="C403" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D403" s="5" t="inlineStr">
         <is>
-          <t>2:22:30</t>
+          <t>2:26:17</t>
         </is>
       </c>
       <c r="E403" s="5" t="inlineStr">
         <is>
-          <t>2:52:10</t>
+          <t>2:45:59</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>Sanlam Cape Town Marathon</t>
+          <t>San Francisco Marathon</t>
         </is>
       </c>
       <c r="B404" s="3" t="inlineStr">
@@ -10574,16 +10574,16 @@
         </is>
       </c>
       <c r="C404" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>2:11:28</t>
+          <t>2:22:30</t>
         </is>
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>2:24:17</t>
+          <t>2:52:10</t>
         </is>
       </c>
     </row>
@@ -10599,16 +10599,16 @@
         </is>
       </c>
       <c r="C405" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D405" s="5" t="inlineStr">
         <is>
-          <t>2:08:16</t>
+          <t>2:11:28</t>
         </is>
       </c>
       <c r="E405" s="5" t="inlineStr">
         <is>
-          <t>2:22:22</t>
+          <t>2:24:17</t>
         </is>
       </c>
     </row>
@@ -10624,23 +10624,23 @@
         </is>
       </c>
       <c r="C406" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>Annulé</t>
+          <t>2:08:16</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>Annulé</t>
+          <t>2:22:22</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>Schneider Electric Marathon de Paris</t>
+          <t>Sanlam Cape Town Marathon</t>
         </is>
       </c>
       <c r="B407" s="5" t="inlineStr">
@@ -10649,16 +10649,16 @@
         </is>
       </c>
       <c r="C407" s="5" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D407" s="5" t="inlineStr">
         <is>
-          <t>2:08:49</t>
+          <t>Annulé</t>
         </is>
       </c>
       <c r="E407" s="5" t="inlineStr">
         <is>
-          <t>2:28:34</t>
+          <t>Annulé</t>
         </is>
       </c>
     </row>
@@ -10674,16 +10674,16 @@
         </is>
       </c>
       <c r="C408" s="3" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>2:09:40</t>
+          <t>2:08:49</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>2:24:33</t>
+          <t>2:28:34</t>
         </is>
       </c>
     </row>
@@ -10699,16 +10699,16 @@
         </is>
       </c>
       <c r="C409" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D409" s="5" t="inlineStr">
         <is>
-          <t>2:08:18</t>
+          <t>2:09:40</t>
         </is>
       </c>
       <c r="E409" s="5" t="inlineStr">
         <is>
-          <t>2:24:34</t>
+          <t>2:24:33</t>
         </is>
       </c>
     </row>
@@ -10724,16 +10724,16 @@
         </is>
       </c>
       <c r="C410" s="3" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>2:06:33</t>
+          <t>2:08:18</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>2:24:03</t>
+          <t>2:24:34</t>
         </is>
       </c>
     </row>
@@ -10749,16 +10749,16 @@
         </is>
       </c>
       <c r="C411" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D411" s="5" t="inlineStr">
         <is>
-          <t>2:08:56</t>
+          <t>2:06:33</t>
         </is>
       </c>
       <c r="E411" s="5" t="inlineStr">
         <is>
-          <t>2:27:01</t>
+          <t>2:24:03</t>
         </is>
       </c>
     </row>
@@ -10774,16 +10774,16 @@
         </is>
       </c>
       <c r="C412" s="3" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>2:08:02</t>
+          <t>2:08:56</t>
         </is>
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>2:24:55</t>
+          <t>2:27:01</t>
         </is>
       </c>
     </row>
@@ -10799,16 +10799,16 @@
         </is>
       </c>
       <c r="C413" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D413" s="5" t="inlineStr">
         <is>
-          <t>2:08:03</t>
+          <t>2:08:02</t>
         </is>
       </c>
       <c r="E413" s="5" t="inlineStr">
         <is>
-          <t>2:29:22</t>
+          <t>2:24:55</t>
         </is>
       </c>
     </row>
@@ -10824,16 +10824,16 @@
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>2:07:17</t>
+          <t>2:08:03</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>2:27:03</t>
+          <t>2:29:22</t>
         </is>
       </c>
     </row>
@@ -10849,16 +10849,16 @@
         </is>
       </c>
       <c r="C415" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D415" s="5" t="inlineStr">
         <is>
-          <t>2:06:40</t>
+          <t>2:07:17</t>
         </is>
       </c>
       <c r="E415" s="5" t="inlineStr">
         <is>
-          <t>2:25:15</t>
+          <t>2:27:03</t>
         </is>
       </c>
     </row>
@@ -10874,16 +10874,16 @@
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>2:05:47</t>
+          <t>2:06:40</t>
         </is>
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>2:25:08</t>
+          <t>2:25:15</t>
         </is>
       </c>
     </row>
@@ -10899,16 +10899,16 @@
         </is>
       </c>
       <c r="C417" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D417" s="5" t="inlineStr">
         <is>
-          <t>2:06:33</t>
+          <t>2:05:47</t>
         </is>
       </c>
       <c r="E417" s="5" t="inlineStr">
         <is>
-          <t>2:22:34</t>
+          <t>2:25:08</t>
         </is>
       </c>
     </row>
@@ -10924,16 +10924,16 @@
         </is>
       </c>
       <c r="C418" s="3" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>2:06:29</t>
+          <t>2:06:33</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>2:22:19</t>
+          <t>2:22:34</t>
         </is>
       </c>
     </row>
@@ -10949,16 +10949,16 @@
         </is>
       </c>
       <c r="C419" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D419" s="5" t="inlineStr">
         <is>
-          <t>2:06:03</t>
+          <t>2:06:29</t>
         </is>
       </c>
       <c r="E419" s="5" t="inlineStr">
         <is>
-          <t>2:22:28</t>
+          <t>2:22:19</t>
         </is>
       </c>
     </row>
@@ -10974,16 +10974,16 @@
         </is>
       </c>
       <c r="C420" s="3" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>2:06:37</t>
+          <t>2:06:03</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>2:25:55</t>
+          <t>2:22:28</t>
         </is>
       </c>
     </row>
@@ -10999,16 +10999,16 @@
         </is>
       </c>
       <c r="C421" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D421" s="5" t="inlineStr">
         <is>
-          <t>2:05:11</t>
+          <t>2:06:37</t>
         </is>
       </c>
       <c r="E421" s="5" t="inlineStr">
         <is>
-          <t>2:22:48</t>
+          <t>2:25:55</t>
         </is>
       </c>
     </row>
@@ -11024,16 +11024,16 @@
         </is>
       </c>
       <c r="C422" s="3" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>2:05:49</t>
+          <t>2:05:11</t>
         </is>
       </c>
       <c r="E422" s="3" t="inlineStr">
         <is>
-          <t>2:25:29</t>
+          <t>2:22:48</t>
         </is>
       </c>
     </row>
@@ -11049,16 +11049,16 @@
         </is>
       </c>
       <c r="C423" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D423" s="5" t="inlineStr">
         <is>
-          <t>2:07:32</t>
+          <t>2:05:49</t>
         </is>
       </c>
       <c r="E423" s="5" t="inlineStr">
         <is>
-          <t>2:25:26</t>
+          <t>2:25:29</t>
         </is>
       </c>
     </row>
@@ -11074,16 +11074,16 @@
         </is>
       </c>
       <c r="C424" s="3" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>2:06:10</t>
+          <t>2:07:32</t>
         </is>
       </c>
       <c r="E424" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:25:26</t>
         </is>
       </c>
     </row>
@@ -11099,16 +11099,16 @@
         </is>
       </c>
       <c r="C425" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D425" s="5" t="inlineStr">
         <is>
-          <t>2:06:25</t>
+          <t>2:06:10</t>
         </is>
       </c>
       <c r="E425" s="5" t="inlineStr">
         <is>
-          <t>2:22:56</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -11124,16 +11124,16 @@
         </is>
       </c>
       <c r="C426" s="3" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>2:07:05</t>
+          <t>2:06:25</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
         <is>
-          <t>2:22:47</t>
+          <t>2:22:56</t>
         </is>
       </c>
     </row>
@@ -11149,16 +11149,16 @@
         </is>
       </c>
       <c r="C427" s="5" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D427" s="5" t="inlineStr">
         <is>
-          <t>2:04:21</t>
+          <t>2:07:05</t>
         </is>
       </c>
       <c r="E427" s="5" t="inlineStr">
         <is>
-          <t>2:26:11</t>
+          <t>2:22:47</t>
         </is>
       </c>
     </row>
@@ -11174,16 +11174,16 @@
         </is>
       </c>
       <c r="C428" s="3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>2:05:07</t>
+          <t>2:04:21</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>2:19:48</t>
+          <t>2:26:11</t>
         </is>
       </c>
     </row>
@@ -11199,16 +11199,16 @@
         </is>
       </c>
       <c r="C429" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D429" s="5" t="inlineStr">
         <is>
-          <t>2:07:15</t>
+          <t>2:05:07</t>
         </is>
       </c>
       <c r="E429" s="5" t="inlineStr">
         <is>
-          <t>2:23:19</t>
+          <t>2:19:48</t>
         </is>
       </c>
     </row>
@@ -11224,16 +11224,16 @@
         </is>
       </c>
       <c r="C430" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>2:05:33</t>
+          <t>2:07:15</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>2:20:45</t>
+          <t>2:23:19</t>
         </is>
       </c>
     </row>
@@ -11249,11 +11249,11 @@
         </is>
       </c>
       <c r="C431" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>2:05:25</t>
+          <t>2:05:33</t>
         </is>
       </c>
       <c r="E431" s="5" t="inlineStr">
@@ -11274,23 +11274,23 @@
         </is>
       </c>
       <c r="C432" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>2:05:18</t>
+          <t>2:05:25</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>2:18:35</t>
+          <t>2:20:45</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>Seoul Marathon</t>
+          <t>Schneider Electric Marathon de Paris</t>
         </is>
       </c>
       <c r="B433" s="5" t="inlineStr">
@@ -11299,16 +11299,16 @@
         </is>
       </c>
       <c r="C433" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D433" s="5" t="inlineStr">
         <is>
-          <t>2:05:27</t>
+          <t>2:05:18</t>
         </is>
       </c>
       <c r="E433" s="5" t="inlineStr">
         <is>
-          <t>2:28:32</t>
+          <t>2:18:35</t>
         </is>
       </c>
     </row>
@@ -11324,16 +11324,16 @@
         </is>
       </c>
       <c r="C434" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D434" s="3" t="inlineStr">
         <is>
-          <t>2:06:08</t>
+          <t>2:05:27</t>
         </is>
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>2:21:32</t>
+          <t>2:28:32</t>
         </is>
       </c>
     </row>
@@ -11349,23 +11349,23 @@
         </is>
       </c>
       <c r="C435" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
-          <t>2:05:42</t>
+          <t>2:06:08</t>
         </is>
       </c>
       <c r="E435" s="5" t="inlineStr">
         <is>
-          <t>2:21:36</t>
+          <t>2:21:32</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>St. Jude Memphis Marathon</t>
+          <t>Seoul Marathon</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
@@ -11374,16 +11374,16 @@
         </is>
       </c>
       <c r="C436" s="3" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D436" s="3" t="inlineStr">
         <is>
-          <t>2:38:23</t>
+          <t>2:05:42</t>
         </is>
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>3:00:20</t>
+          <t>2:21:36</t>
         </is>
       </c>
     </row>
@@ -11399,16 +11399,16 @@
         </is>
       </c>
       <c r="C437" s="5" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
-          <t>2:30:21</t>
+          <t>2:38:23</t>
         </is>
       </c>
       <c r="E437" s="5" t="inlineStr">
         <is>
-          <t>2:56:44</t>
+          <t>3:00:20</t>
         </is>
       </c>
     </row>
@@ -11424,16 +11424,16 @@
         </is>
       </c>
       <c r="C438" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>2:34:18</t>
+          <t>2:30:21</t>
         </is>
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>2:54:45</t>
+          <t>2:56:44</t>
         </is>
       </c>
     </row>
@@ -11449,23 +11449,23 @@
         </is>
       </c>
       <c r="C439" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D439" s="5" t="inlineStr">
         <is>
-          <t>2:28:03</t>
+          <t>2:34:18</t>
         </is>
       </c>
       <c r="E439" s="5" t="inlineStr">
         <is>
-          <t>2:51:12</t>
+          <t>2:54:45</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Marathon</t>
+          <t>St. Jude Memphis Marathon</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
@@ -11474,16 +11474,16 @@
         </is>
       </c>
       <c r="C440" s="3" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>2:09:20</t>
+          <t>2:28:03</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>2:26:13</t>
+          <t>2:51:12</t>
         </is>
       </c>
     </row>
@@ -11499,23 +11499,23 @@
         </is>
       </c>
       <c r="C441" s="5" t="n">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="D441" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:09:20</t>
         </is>
       </c>
       <c r="E441" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:26:13</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>Standard Chartered KL Marathon</t>
+          <t>Standard Chartered Hong Kong Marathon</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
@@ -11524,23 +11524,23 @@
         </is>
       </c>
       <c r="C442" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D442" s="3" t="inlineStr">
         <is>
-          <t>2:17:28</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>2:41:36</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Singapore Marathon</t>
+          <t>Standard Chartered KL Marathon</t>
         </is>
       </c>
       <c r="B443" s="5" t="inlineStr">
@@ -11549,16 +11549,16 @@
         </is>
       </c>
       <c r="C443" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D443" s="5" t="inlineStr">
         <is>
-          <t>2:16:06</t>
+          <t>2:17:28</t>
         </is>
       </c>
       <c r="E443" s="5" t="inlineStr">
         <is>
-          <t>2:39:04</t>
+          <t>2:41:36</t>
         </is>
       </c>
     </row>
@@ -11574,23 +11574,23 @@
         </is>
       </c>
       <c r="C444" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>2:15:40</t>
+          <t>2:16:06</t>
         </is>
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>2:41:24</t>
+          <t>2:39:04</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>Stockholm Marathon</t>
+          <t>Standard Chartered Singapore Marathon</t>
         </is>
       </c>
       <c r="B445" s="5" t="inlineStr">
@@ -11599,16 +11599,16 @@
         </is>
       </c>
       <c r="C445" s="5" t="n">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="D445" s="5" t="inlineStr">
         <is>
-          <t>2:18:22</t>
+          <t>2:15:40</t>
         </is>
       </c>
       <c r="E445" s="5" t="inlineStr">
         <is>
-          <t>2:34:14</t>
+          <t>2:41:24</t>
         </is>
       </c>
     </row>
@@ -11624,16 +11624,16 @@
         </is>
       </c>
       <c r="C446" s="3" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>2:10:58</t>
+          <t>2:18:22</t>
         </is>
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>2:31:46</t>
+          <t>2:34:14</t>
         </is>
       </c>
     </row>
@@ -11649,16 +11649,16 @@
         </is>
       </c>
       <c r="C447" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D447" s="5" t="inlineStr">
         <is>
-          <t>2:11:36</t>
+          <t>2:10:58</t>
         </is>
       </c>
       <c r="E447" s="5" t="inlineStr">
         <is>
-          <t>2:35:45</t>
+          <t>2:31:46</t>
         </is>
       </c>
     </row>
@@ -11674,16 +11674,16 @@
         </is>
       </c>
       <c r="C448" s="3" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>2:13:30</t>
+          <t>2:11:36</t>
         </is>
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>2:40:28</t>
+          <t>2:35:45</t>
         </is>
       </c>
     </row>
@@ -11699,16 +11699,16 @@
         </is>
       </c>
       <c r="C449" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D449" s="5" t="inlineStr">
         <is>
-          <t>2:10:10</t>
+          <t>2:13:30</t>
         </is>
       </c>
       <c r="E449" s="5" t="inlineStr">
         <is>
-          <t>2:33:38</t>
+          <t>2:40:28</t>
         </is>
       </c>
     </row>
@@ -11724,16 +11724,16 @@
         </is>
       </c>
       <c r="C450" s="3" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>2:12:24</t>
+          <t>2:10:10</t>
         </is>
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>2:29:03</t>
+          <t>2:33:38</t>
         </is>
       </c>
     </row>
@@ -11749,16 +11749,16 @@
         </is>
       </c>
       <c r="C451" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D451" s="5" t="inlineStr">
         <is>
-          <t>2:11:08</t>
+          <t>2:12:24</t>
         </is>
       </c>
       <c r="E451" s="5" t="inlineStr">
         <is>
-          <t>2:31:48</t>
+          <t>2:29:03</t>
         </is>
       </c>
     </row>
@@ -11774,16 +11774,16 @@
         </is>
       </c>
       <c r="C452" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D452" s="3" t="inlineStr">
         <is>
-          <t>2:10:32</t>
+          <t>2:11:08</t>
         </is>
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>2:30:44</t>
+          <t>2:31:48</t>
         </is>
       </c>
     </row>
@@ -11799,16 +11799,16 @@
         </is>
       </c>
       <c r="C453" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
-          <t>2:14:17</t>
+          <t>2:10:32</t>
         </is>
       </c>
       <c r="E453" s="5" t="inlineStr">
         <is>
-          <t>2:31:46</t>
+          <t>2:30:44</t>
         </is>
       </c>
     </row>
@@ -11824,23 +11824,23 @@
         </is>
       </c>
       <c r="C454" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D454" s="3" t="inlineStr">
         <is>
-          <t>2:11:34</t>
+          <t>2:14:17</t>
         </is>
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>2:30:38</t>
+          <t>2:31:46</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="4" t="inlineStr">
         <is>
-          <t>TCS Amsterdam Marathon</t>
+          <t>Stockholm Marathon</t>
         </is>
       </c>
       <c r="B455" s="5" t="inlineStr">
@@ -11849,16 +11849,16 @@
         </is>
       </c>
       <c r="C455" s="5" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D455" s="5" t="inlineStr">
         <is>
-          <t>2:08:47</t>
+          <t>2:11:34</t>
         </is>
       </c>
       <c r="E455" s="5" t="inlineStr">
         <is>
-          <t>2:28:42</t>
+          <t>2:30:38</t>
         </is>
       </c>
     </row>
@@ -11874,16 +11874,16 @@
         </is>
       </c>
       <c r="C456" s="3" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D456" s="3" t="inlineStr">
         <is>
-          <t>2:08:22</t>
+          <t>2:08:47</t>
         </is>
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>2:26:04</t>
+          <t>2:28:42</t>
         </is>
       </c>
     </row>
@@ -11899,16 +11899,16 @@
         </is>
       </c>
       <c r="C457" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D457" s="5" t="inlineStr">
         <is>
-          <t>2:07:45</t>
+          <t>2:08:22</t>
         </is>
       </c>
       <c r="E457" s="5" t="inlineStr">
         <is>
-          <t>2:23:54</t>
+          <t>2:26:04</t>
         </is>
       </c>
     </row>
@@ -11924,16 +11924,16 @@
         </is>
       </c>
       <c r="C458" s="3" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D458" s="3" t="inlineStr">
         <is>
-          <t>2:06:38</t>
+          <t>2:07:45</t>
         </is>
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>2:27:08</t>
+          <t>2:23:54</t>
         </is>
       </c>
     </row>
@@ -11949,16 +11949,16 @@
         </is>
       </c>
       <c r="C459" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D459" s="5" t="inlineStr">
         <is>
-          <t>2:06:20</t>
+          <t>2:06:38</t>
         </is>
       </c>
       <c r="E459" s="5" t="inlineStr">
         <is>
-          <t>2:28:39</t>
+          <t>2:27:08</t>
         </is>
       </c>
     </row>
@@ -11974,16 +11974,16 @@
         </is>
       </c>
       <c r="C460" s="3" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D460" s="3" t="inlineStr">
         <is>
-          <t>2:09:27</t>
+          <t>2:06:20</t>
         </is>
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>2:28:18</t>
+          <t>2:28:39</t>
         </is>
       </c>
     </row>
@@ -11999,16 +11999,16 @@
         </is>
       </c>
       <c r="C461" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D461" s="5" t="inlineStr">
         <is>
-          <t>2:08:41</t>
+          <t>2:09:27</t>
         </is>
       </c>
       <c r="E461" s="5" t="inlineStr">
         <is>
-          <t>2:27:37</t>
+          <t>2:28:18</t>
         </is>
       </c>
     </row>
@@ -12024,16 +12024,16 @@
         </is>
       </c>
       <c r="C462" s="3" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D462" s="3" t="inlineStr">
         <is>
-          <t>2:07:57</t>
+          <t>2:08:41</t>
         </is>
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>2:28:41</t>
+          <t>2:27:37</t>
         </is>
       </c>
     </row>
@@ -12049,16 +12049,16 @@
         </is>
       </c>
       <c r="C463" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D463" s="5" t="inlineStr">
         <is>
-          <t>2:06:13</t>
+          <t>2:07:57</t>
         </is>
       </c>
       <c r="E463" s="5" t="inlineStr">
         <is>
-          <t>2:29:02</t>
+          <t>2:28:41</t>
         </is>
       </c>
     </row>
@@ -12074,16 +12074,16 @@
         </is>
       </c>
       <c r="C464" s="3" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D464" s="3" t="inlineStr">
         <is>
-          <t>2:06:00</t>
+          <t>2:06:13</t>
         </is>
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>2:25:46</t>
+          <t>2:29:02</t>
         </is>
       </c>
     </row>
@@ -12099,16 +12099,16 @@
         </is>
       </c>
       <c r="C465" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D465" s="5" t="inlineStr">
         <is>
-          <t>2:05:44</t>
+          <t>2:06:00</t>
         </is>
       </c>
       <c r="E465" s="5" t="inlineStr">
         <is>
-          <t>2:28:28</t>
+          <t>2:25:46</t>
         </is>
       </c>
     </row>
@@ -12124,16 +12124,16 @@
         </is>
       </c>
       <c r="C466" s="3" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D466" s="3" t="inlineStr">
         <is>
-          <t>2:05:16</t>
+          <t>2:05:44</t>
         </is>
       </c>
       <c r="E466" s="3" t="inlineStr">
         <is>
-          <t>2:24:34</t>
+          <t>2:28:28</t>
         </is>
       </c>
     </row>
@@ -12149,16 +12149,16 @@
         </is>
       </c>
       <c r="C467" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D467" s="5" t="inlineStr">
         <is>
-          <t>2:05:36</t>
+          <t>2:05:16</t>
         </is>
       </c>
       <c r="E467" s="5" t="inlineStr">
         <is>
-          <t>2:21:09</t>
+          <t>2:24:34</t>
         </is>
       </c>
     </row>
@@ -12174,7 +12174,7 @@
         </is>
       </c>
       <c r="C468" s="3" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D468" s="3" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E468" s="3" t="inlineStr">
         <is>
-          <t>2:24:27</t>
+          <t>2:21:09</t>
         </is>
       </c>
     </row>
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="C469" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D469" s="5" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="E469" s="5" t="inlineStr">
         <is>
-          <t>2:23:27</t>
+          <t>2:24:27</t>
         </is>
       </c>
     </row>
@@ -12224,16 +12224,16 @@
         </is>
       </c>
       <c r="C470" s="3" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D470" s="3" t="inlineStr">
         <is>
-          <t>2:06:19</t>
+          <t>2:05:36</t>
         </is>
       </c>
       <c r="E470" s="3" t="inlineStr">
         <is>
-          <t>2:24:11</t>
+          <t>2:23:27</t>
         </is>
       </c>
     </row>
@@ -12249,16 +12249,16 @@
         </is>
       </c>
       <c r="C471" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D471" s="5" t="inlineStr">
         <is>
-          <t>2:05:20</t>
+          <t>2:06:19</t>
         </is>
       </c>
       <c r="E471" s="5" t="inlineStr">
         <is>
-          <t>2:23:20</t>
+          <t>2:24:11</t>
         </is>
       </c>
     </row>
@@ -12274,16 +12274,16 @@
         </is>
       </c>
       <c r="C472" s="3" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D472" s="3" t="inlineStr">
         <is>
-          <t>2:05:09</t>
+          <t>2:05:20</t>
         </is>
       </c>
       <c r="E472" s="3" t="inlineStr">
         <is>
-          <t>2:21:53</t>
+          <t>2:23:20</t>
         </is>
       </c>
     </row>
@@ -12299,16 +12299,16 @@
         </is>
       </c>
       <c r="C473" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D473" s="5" t="inlineStr">
         <is>
-          <t>2:04:06</t>
+          <t>2:05:09</t>
         </is>
       </c>
       <c r="E473" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:21:53</t>
         </is>
       </c>
     </row>
@@ -12324,16 +12324,16 @@
         </is>
       </c>
       <c r="C474" s="3" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="D474" s="3" t="inlineStr">
         <is>
-          <t>2:03:38</t>
+          <t>2:04:06</t>
         </is>
       </c>
       <c r="E474" s="3" t="inlineStr">
         <is>
-          <t>2:17:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="D475" s="5" t="inlineStr">
         <is>
-          <t>2:03:36</t>
+          <t>2:03:38</t>
         </is>
       </c>
       <c r="E475" s="5" t="inlineStr">
         <is>
-          <t>2:17:55</t>
+          <t>2:17:57</t>
         </is>
       </c>
     </row>
@@ -12374,16 +12374,16 @@
         </is>
       </c>
       <c r="C476" s="3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D476" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:03:36</t>
         </is>
       </c>
       <c r="E476" s="3" t="inlineStr">
         <is>
-          <t>2:17:20</t>
+          <t>2:17:55</t>
         </is>
       </c>
     </row>
@@ -12403,12 +12403,12 @@
       </c>
       <c r="D477" s="5" t="inlineStr">
         <is>
-          <t>2:04:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E477" s="5" t="inlineStr">
         <is>
-          <t>2:17:18</t>
+          <t>2:17:20</t>
         </is>
       </c>
     </row>
@@ -12424,16 +12424,16 @@
         </is>
       </c>
       <c r="C478" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D478" s="3" t="inlineStr">
         <is>
-          <t>2:04:18</t>
+          <t>2:04:48</t>
         </is>
       </c>
       <c r="E478" s="3" t="inlineStr">
         <is>
-          <t>2:18:21</t>
+          <t>2:17:18</t>
         </is>
       </c>
     </row>
@@ -12474,16 +12474,16 @@
         </is>
       </c>
       <c r="C480" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D480" s="3" t="inlineStr">
         <is>
-          <t>2:05:38</t>
+          <t>2:04:18</t>
         </is>
       </c>
       <c r="E480" s="3" t="inlineStr">
         <is>
-          <t>2:16:52</t>
+          <t>2:18:21</t>
         </is>
       </c>
     </row>
@@ -12503,12 +12503,12 @@
       </c>
       <c r="D481" s="5" t="inlineStr">
         <is>
-          <t>2:05:35</t>
+          <t>2:05:38</t>
         </is>
       </c>
       <c r="E481" s="5" t="inlineStr">
         <is>
-          <t>2:16:50</t>
+          <t>2:16:52</t>
         </is>
       </c>
     </row>
@@ -12524,16 +12524,16 @@
         </is>
       </c>
       <c r="C482" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D482" s="3" t="inlineStr">
         <is>
-          <t>2:03:31</t>
+          <t>2:05:35</t>
         </is>
       </c>
       <c r="E482" s="3" t="inlineStr">
         <is>
-          <t>2:17:37</t>
+          <t>2:16:50</t>
         </is>
       </c>
     </row>
@@ -12553,19 +12553,19 @@
       </c>
       <c r="D483" s="5" t="inlineStr">
         <is>
-          <t>2:07:59</t>
+          <t>2:03:31</t>
         </is>
       </c>
       <c r="E483" s="5" t="inlineStr">
         <is>
-          <t>2:28:27</t>
+          <t>2:17:37</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>TCS London Marathon</t>
+          <t>TCS Amsterdam Marathon</t>
         </is>
       </c>
       <c r="B484" s="3" t="inlineStr">
@@ -12574,16 +12574,16 @@
         </is>
       </c>
       <c r="C484" s="3" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D484" s="3" t="inlineStr">
         <is>
-          <t>2:06:36</t>
+          <t>2:07:59</t>
         </is>
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>2:24:33</t>
+          <t>2:28:27</t>
         </is>
       </c>
     </row>
@@ -12599,16 +12599,16 @@
         </is>
       </c>
       <c r="C485" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D485" s="5" t="inlineStr">
         <is>
-          <t>2:07:11</t>
+          <t>2:06:36</t>
         </is>
       </c>
       <c r="E485" s="5" t="inlineStr">
         <is>
-          <t>2:23:56</t>
+          <t>2:24:33</t>
         </is>
       </c>
     </row>
@@ -12624,16 +12624,16 @@
         </is>
       </c>
       <c r="C486" s="3" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D486" s="3" t="inlineStr">
         <is>
-          <t>2:05:38</t>
+          <t>2:07:11</t>
         </is>
       </c>
       <c r="E486" s="3" t="inlineStr">
         <is>
-          <t>2:18:56</t>
+          <t>2:23:56</t>
         </is>
       </c>
     </row>
@@ -12649,16 +12649,16 @@
         </is>
       </c>
       <c r="C487" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D487" s="5" t="inlineStr">
         <is>
-          <t>2:07:56</t>
+          <t>2:05:38</t>
         </is>
       </c>
       <c r="E487" s="5" t="inlineStr">
         <is>
-          <t>2:15:25</t>
+          <t>2:18:56</t>
         </is>
       </c>
     </row>
@@ -12674,16 +12674,16 @@
         </is>
       </c>
       <c r="C488" s="3" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D488" s="3" t="inlineStr">
         <is>
-          <t>2:06:18</t>
+          <t>2:07:56</t>
         </is>
       </c>
       <c r="E488" s="3" t="inlineStr">
         <is>
-          <t>2:22:35</t>
+          <t>2:15:25</t>
         </is>
       </c>
     </row>
@@ -12699,16 +12699,16 @@
         </is>
       </c>
       <c r="C489" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D489" s="5" t="inlineStr">
         <is>
-          <t>2:07:44</t>
+          <t>2:06:18</t>
         </is>
       </c>
       <c r="E489" s="5" t="inlineStr">
         <is>
-          <t>2:17:42</t>
+          <t>2:22:35</t>
         </is>
       </c>
     </row>
@@ -12724,16 +12724,16 @@
         </is>
       </c>
       <c r="C490" s="3" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D490" s="3" t="inlineStr">
         <is>
-          <t>2:06:39</t>
+          <t>2:07:44</t>
         </is>
       </c>
       <c r="E490" s="3" t="inlineStr">
         <is>
-          <t>2:20:04</t>
+          <t>2:17:42</t>
         </is>
       </c>
     </row>
@@ -12749,16 +12749,16 @@
         </is>
       </c>
       <c r="C491" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D491" s="5" t="inlineStr">
         <is>
-          <t>2:07:41</t>
+          <t>2:06:39</t>
         </is>
       </c>
       <c r="E491" s="5" t="inlineStr">
         <is>
-          <t>2:20:13</t>
+          <t>2:20:04</t>
         </is>
       </c>
     </row>
@@ -12774,16 +12774,16 @@
         </is>
       </c>
       <c r="C492" s="3" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D492" s="3" t="inlineStr">
         <is>
-          <t>2:05:15</t>
+          <t>2:07:41</t>
         </is>
       </c>
       <c r="E492" s="3" t="inlineStr">
         <is>
-          <t>2:24:14</t>
+          <t>2:20:13</t>
         </is>
       </c>
     </row>
@@ -12799,16 +12799,16 @@
         </is>
       </c>
       <c r="C493" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D493" s="5" t="inlineStr">
         <is>
-          <t>2:05:10</t>
+          <t>2:05:15</t>
         </is>
       </c>
       <c r="E493" s="5" t="inlineStr">
         <is>
-          <t>2:23:12</t>
+          <t>2:24:14</t>
         </is>
       </c>
     </row>
@@ -12824,16 +12824,16 @@
         </is>
       </c>
       <c r="C494" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D494" s="3" t="inlineStr">
         <is>
-          <t>2:05:19</t>
+          <t>2:05:10</t>
         </is>
       </c>
       <c r="E494" s="3" t="inlineStr">
         <is>
-          <t>2:22:00</t>
+          <t>2:23:12</t>
         </is>
       </c>
     </row>
@@ -12849,16 +12849,16 @@
         </is>
       </c>
       <c r="C495" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D495" s="5" t="inlineStr">
         <is>
-          <t>2:04:40</t>
+          <t>2:05:19</t>
         </is>
       </c>
       <c r="E495" s="5" t="inlineStr">
         <is>
-          <t>2:19:36</t>
+          <t>2:22:00</t>
         </is>
       </c>
     </row>
@@ -12874,16 +12874,16 @@
         </is>
       </c>
       <c r="C496" s="3" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D496" s="3" t="inlineStr">
         <is>
-          <t>2:04:44</t>
+          <t>2:04:40</t>
         </is>
       </c>
       <c r="E496" s="3" t="inlineStr">
         <is>
-          <t>2:18:37</t>
+          <t>2:19:36</t>
         </is>
       </c>
     </row>
@@ -12899,16 +12899,16 @@
         </is>
       </c>
       <c r="C497" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D497" s="5" t="inlineStr">
         <is>
-          <t>2:04:29</t>
+          <t>2:04:44</t>
         </is>
       </c>
       <c r="E497" s="5" t="inlineStr">
         <is>
-          <t>2:20:15</t>
+          <t>2:18:37</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
         </is>
       </c>
       <c r="C498" s="3" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D498" s="3" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
       </c>
       <c r="E498" s="3" t="inlineStr">
         <is>
-          <t>2:20:21</t>
+          <t>2:20:15</t>
         </is>
       </c>
     </row>
@@ -12949,16 +12949,16 @@
         </is>
       </c>
       <c r="C499" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D499" s="5" t="inlineStr">
         <is>
-          <t>2:04:42</t>
+          <t>2:04:29</t>
         </is>
       </c>
       <c r="E499" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:20:21</t>
         </is>
       </c>
     </row>
@@ -12974,11 +12974,11 @@
         </is>
       </c>
       <c r="C500" s="3" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D500" s="3" t="inlineStr">
         <is>
-          <t>2:03:05</t>
+          <t>2:04:42</t>
         </is>
       </c>
       <c r="E500" s="3" t="inlineStr">
@@ -12999,16 +12999,16 @@
         </is>
       </c>
       <c r="C501" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D501" s="5" t="inlineStr">
         <is>
-          <t>2:05:48</t>
+          <t>2:03:05</t>
         </is>
       </c>
       <c r="E501" s="5" t="inlineStr">
         <is>
-          <t>2:17:01</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -13024,16 +13024,16 @@
         </is>
       </c>
       <c r="C502" s="3" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D502" s="3" t="inlineStr">
         <is>
-          <t>2:04:17</t>
+          <t>2:05:48</t>
         </is>
       </c>
       <c r="E502" s="3" t="inlineStr">
         <is>
-          <t>2:18:31</t>
+          <t>2:17:01</t>
         </is>
       </c>
     </row>
@@ -13049,16 +13049,16 @@
         </is>
       </c>
       <c r="C503" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D503" s="5" t="inlineStr">
         <is>
-          <t>2:02:37</t>
+          <t>2:04:17</t>
         </is>
       </c>
       <c r="E503" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:18:31</t>
         </is>
       </c>
     </row>
@@ -13074,16 +13074,16 @@
         </is>
       </c>
       <c r="C504" s="3" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D504" s="3" t="inlineStr">
         <is>
-          <t>2:05:41</t>
+          <t>2:02:37</t>
         </is>
       </c>
       <c r="E504" s="3" t="inlineStr">
         <is>
-          <t>2:18:58</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -13099,16 +13099,16 @@
         </is>
       </c>
       <c r="C505" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D505" s="5" t="inlineStr">
         <is>
-          <t>2:04:01</t>
+          <t>2:05:41</t>
         </is>
       </c>
       <c r="E505" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:18:58</t>
         </is>
       </c>
     </row>
@@ -13124,16 +13124,16 @@
         </is>
       </c>
       <c r="C506" s="3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D506" s="3" t="inlineStr">
         <is>
-          <t>2:04:39</t>
+          <t>2:04:01</t>
         </is>
       </c>
       <c r="E506" s="3" t="inlineStr">
         <is>
-          <t>2:17:26</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -13149,16 +13149,16 @@
         </is>
       </c>
       <c r="C507" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D507" s="5" t="inlineStr">
         <is>
-          <t>2:01:25</t>
+          <t>2:04:39</t>
         </is>
       </c>
       <c r="E507" s="5" t="inlineStr">
         <is>
-          <t>2:18:33</t>
+          <t>2:17:26</t>
         </is>
       </c>
     </row>
@@ -13174,16 +13174,16 @@
         </is>
       </c>
       <c r="C508" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D508" s="3" t="inlineStr">
         <is>
-          <t>2:04:01</t>
+          <t>2:01:25</t>
         </is>
       </c>
       <c r="E508" s="3" t="inlineStr">
         <is>
-          <t>2:16:16</t>
+          <t>2:18:33</t>
         </is>
       </c>
     </row>
@@ -13199,23 +13199,23 @@
         </is>
       </c>
       <c r="C509" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D509" s="5" t="inlineStr">
         <is>
-          <t>2:02:27</t>
+          <t>2:04:01</t>
         </is>
       </c>
       <c r="E509" s="5" t="inlineStr">
         <is>
-          <t>2:15:50</t>
+          <t>2:16:16</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>TCS New York City Marathon</t>
+          <t>TCS London Marathon</t>
         </is>
       </c>
       <c r="B510" s="3" t="inlineStr">
@@ -13224,16 +13224,16 @@
         </is>
       </c>
       <c r="C510" s="3" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D510" s="3" t="inlineStr">
         <is>
-          <t>2:10:09</t>
+          <t>2:02:27</t>
         </is>
       </c>
       <c r="E510" s="3" t="inlineStr">
         <is>
-          <t>2:25:45</t>
+          <t>2:15:50</t>
         </is>
       </c>
     </row>
@@ -13249,16 +13249,16 @@
         </is>
       </c>
       <c r="C511" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D511" s="5" t="inlineStr">
         <is>
-          <t>2:07:43</t>
+          <t>2:10:09</t>
         </is>
       </c>
       <c r="E511" s="5" t="inlineStr">
         <is>
-          <t>2:24:21</t>
+          <t>2:25:45</t>
         </is>
       </c>
     </row>
@@ -13274,16 +13274,16 @@
         </is>
       </c>
       <c r="C512" s="3" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D512" s="3" t="inlineStr">
         <is>
-          <t>2:08:07</t>
+          <t>2:07:43</t>
         </is>
       </c>
       <c r="E512" s="3" t="inlineStr">
         <is>
-          <t>2:22:31</t>
+          <t>2:24:21</t>
         </is>
       </c>
     </row>
@@ -13299,11 +13299,11 @@
         </is>
       </c>
       <c r="C513" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D513" s="5" t="inlineStr">
         <is>
-          <t>2:10:30</t>
+          <t>2:08:07</t>
         </is>
       </c>
       <c r="E513" s="5" t="inlineStr">
@@ -13324,16 +13324,16 @@
         </is>
       </c>
       <c r="C514" s="3" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D514" s="3" t="inlineStr">
         <is>
-          <t>2:09:28</t>
+          <t>2:10:30</t>
         </is>
       </c>
       <c r="E514" s="3" t="inlineStr">
         <is>
-          <t>2:23:10</t>
+          <t>2:22:31</t>
         </is>
       </c>
     </row>
@@ -13349,16 +13349,16 @@
         </is>
       </c>
       <c r="C515" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D515" s="5" t="inlineStr">
         <is>
-          <t>2:09:30</t>
+          <t>2:09:28</t>
         </is>
       </c>
       <c r="E515" s="5" t="inlineStr">
         <is>
-          <t>2:24:41</t>
+          <t>2:23:10</t>
         </is>
       </c>
     </row>
@@ -13374,16 +13374,16 @@
         </is>
       </c>
       <c r="C516" s="3" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D516" s="3" t="inlineStr">
         <is>
-          <t>2:09:58</t>
+          <t>2:09:30</t>
         </is>
       </c>
       <c r="E516" s="3" t="inlineStr">
         <is>
-          <t>2:25:05</t>
+          <t>2:24:41</t>
         </is>
       </c>
     </row>
@@ -13399,16 +13399,16 @@
         </is>
       </c>
       <c r="C517" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D517" s="5" t="inlineStr">
         <is>
-          <t>2:09:04</t>
+          <t>2:09:58</t>
         </is>
       </c>
       <c r="E517" s="5" t="inlineStr">
         <is>
-          <t>2:23:09</t>
+          <t>2:25:05</t>
         </is>
       </c>
     </row>
@@ -13424,16 +13424,16 @@
         </is>
       </c>
       <c r="C518" s="3" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D518" s="3" t="inlineStr">
         <is>
-          <t>2:08:43</t>
+          <t>2:09:04</t>
         </is>
       </c>
       <c r="E518" s="3" t="inlineStr">
         <is>
-          <t>2:23:56</t>
+          <t>2:23:09</t>
         </is>
       </c>
     </row>
@@ -13449,16 +13449,16 @@
         </is>
       </c>
       <c r="C519" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D519" s="5" t="inlineStr">
         <is>
-          <t>2:09:15</t>
+          <t>2:08:43</t>
         </is>
       </c>
       <c r="E519" s="5" t="inlineStr">
         <is>
-          <t>2:25:53</t>
+          <t>2:23:56</t>
         </is>
       </c>
     </row>
@@ -13474,16 +13474,16 @@
         </is>
       </c>
       <c r="C520" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D520" s="3" t="inlineStr">
         <is>
-          <t>2:08:14</t>
+          <t>2:09:15</t>
         </is>
       </c>
       <c r="E520" s="3" t="inlineStr">
         <is>
-          <t>2:28:20</t>
+          <t>2:25:53</t>
         </is>
       </c>
     </row>
@@ -13499,16 +13499,16 @@
         </is>
       </c>
       <c r="C521" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D521" s="5" t="inlineStr">
         <is>
-          <t>2:05:06</t>
+          <t>2:08:14</t>
         </is>
       </c>
       <c r="E521" s="5" t="inlineStr">
         <is>
-          <t>2:23:15</t>
+          <t>2:28:20</t>
         </is>
       </c>
     </row>
@@ -13524,16 +13524,16 @@
         </is>
       </c>
       <c r="C522" s="3" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="D522" s="3" t="inlineStr">
         <is>
-          <t>2:08:24</t>
+          <t>2:05:06</t>
         </is>
       </c>
       <c r="E522" s="3" t="inlineStr">
         <is>
-          <t>2:25:07</t>
+          <t>2:23:15</t>
         </is>
       </c>
     </row>
@@ -13549,11 +13549,11 @@
         </is>
       </c>
       <c r="C523" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D523" s="5" t="inlineStr">
         <is>
-          <t>2:10:59</t>
+          <t>2:08:24</t>
         </is>
       </c>
       <c r="E523" s="5" t="inlineStr">
@@ -13574,16 +13574,16 @@
         </is>
       </c>
       <c r="C524" s="3" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D524" s="3" t="inlineStr">
         <is>
-          <t>2:10:34</t>
+          <t>2:10:59</t>
         </is>
       </c>
       <c r="E524" s="3" t="inlineStr">
         <is>
-          <t>2:24:25</t>
+          <t>2:25:07</t>
         </is>
       </c>
     </row>
@@ -13599,16 +13599,16 @@
         </is>
       </c>
       <c r="C525" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D525" s="5" t="inlineStr">
         <is>
-          <t>2:07:51</t>
+          <t>2:10:34</t>
         </is>
       </c>
       <c r="E525" s="5" t="inlineStr">
         <is>
-          <t>2:24:26</t>
+          <t>2:24:25</t>
         </is>
       </c>
     </row>
@@ -13624,16 +13624,16 @@
         </is>
       </c>
       <c r="C526" s="3" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D526" s="3" t="inlineStr">
         <is>
-          <t>2:10:53</t>
+          <t>2:07:51</t>
         </is>
       </c>
       <c r="E526" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:24:26</t>
         </is>
       </c>
     </row>
@@ -13649,16 +13649,16 @@
         </is>
       </c>
       <c r="C527" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D527" s="5" t="inlineStr">
         <is>
-          <t>2:05:59</t>
+          <t>2:10:53</t>
         </is>
       </c>
       <c r="E527" s="5" t="inlineStr">
         <is>
-          <t>2:22:48</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -13674,16 +13674,16 @@
         </is>
       </c>
       <c r="C528" s="3" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D528" s="3" t="inlineStr">
         <is>
-          <t>2:08:13</t>
+          <t>2:05:59</t>
         </is>
       </c>
       <c r="E528" s="3" t="inlineStr">
         <is>
-          <t>2:22:38</t>
+          <t>2:22:48</t>
         </is>
       </c>
     </row>
@@ -13699,16 +13699,16 @@
         </is>
       </c>
       <c r="C529" s="5" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
-          <t>2:08:22</t>
+          <t>2:08:13</t>
         </is>
       </c>
       <c r="E529" s="5" t="inlineStr">
         <is>
-          <t>2:22:39</t>
+          <t>2:22:38</t>
         </is>
       </c>
     </row>
@@ -13724,16 +13724,16 @@
         </is>
       </c>
       <c r="C530" s="3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D530" s="3" t="inlineStr">
         <is>
-          <t>2:08:41</t>
+          <t>2:08:22</t>
         </is>
       </c>
       <c r="E530" s="3" t="inlineStr">
         <is>
-          <t>2:23:23</t>
+          <t>2:22:39</t>
         </is>
       </c>
     </row>
@@ -13749,16 +13749,16 @@
         </is>
       </c>
       <c r="C531" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D531" s="5" t="inlineStr">
         <is>
-          <t>2:04:58</t>
+          <t>2:08:41</t>
         </is>
       </c>
       <c r="E531" s="5" t="inlineStr">
         <is>
-          <t>2:27:23</t>
+          <t>2:23:23</t>
         </is>
       </c>
     </row>
@@ -13774,16 +13774,16 @@
         </is>
       </c>
       <c r="C532" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D532" s="3" t="inlineStr">
         <is>
-          <t>2:07:39</t>
+          <t>2:04:58</t>
         </is>
       </c>
       <c r="E532" s="3" t="inlineStr">
         <is>
-          <t>2:24:35</t>
+          <t>2:27:23</t>
         </is>
       </c>
     </row>
@@ -13799,23 +13799,23 @@
         </is>
       </c>
       <c r="C533" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D533" s="5" t="inlineStr">
         <is>
-          <t>2:08:09</t>
+          <t>2:07:39</t>
         </is>
       </c>
       <c r="E533" s="5" t="inlineStr">
         <is>
-          <t>2:19:51</t>
+          <t>2:24:35</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>TCS Sydney Marathon presented by ASICS</t>
+          <t>TCS New York City Marathon</t>
         </is>
       </c>
       <c r="B534" s="3" t="inlineStr">
@@ -13824,16 +13824,16 @@
         </is>
       </c>
       <c r="C534" s="3" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D534" s="3" t="inlineStr">
         <is>
-          <t>2:08:20</t>
+          <t>2:08:09</t>
         </is>
       </c>
       <c r="E534" s="3" t="inlineStr">
         <is>
-          <t>2:26:47</t>
+          <t>2:19:51</t>
         </is>
       </c>
     </row>
@@ -13849,16 +13849,16 @@
         </is>
       </c>
       <c r="C535" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D535" s="5" t="inlineStr">
         <is>
-          <t>2:06:17</t>
+          <t>2:08:20</t>
         </is>
       </c>
       <c r="E535" s="5" t="inlineStr">
         <is>
-          <t>2:21:40</t>
+          <t>2:26:47</t>
         </is>
       </c>
     </row>
@@ -13874,23 +13874,23 @@
         </is>
       </c>
       <c r="C536" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D536" s="3" t="inlineStr">
         <is>
-          <t>2:06:06</t>
+          <t>2:06:17</t>
         </is>
       </c>
       <c r="E536" s="3" t="inlineStr">
         <is>
-          <t>2:18:22</t>
+          <t>2:21:40</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon</t>
+          <t>TCS Sydney Marathon presented by ASICS</t>
         </is>
       </c>
       <c r="B537" s="5" t="inlineStr">
@@ -13899,16 +13899,16 @@
         </is>
       </c>
       <c r="C537" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D537" s="5" t="inlineStr">
         <is>
-          <t>2:09:20</t>
+          <t>2:06:06</t>
         </is>
       </c>
       <c r="E537" s="5" t="inlineStr">
         <is>
-          <t>2:23:11</t>
+          <t>2:18:22</t>
         </is>
       </c>
     </row>
@@ -13924,16 +13924,16 @@
         </is>
       </c>
       <c r="C538" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D538" s="3" t="inlineStr">
         <is>
-          <t>2:07:16</t>
+          <t>2:09:20</t>
         </is>
       </c>
       <c r="E538" s="3" t="inlineStr">
         <is>
-          <t>2:20:44</t>
+          <t>2:23:11</t>
         </is>
       </c>
     </row>
@@ -13949,23 +13949,23 @@
         </is>
       </c>
       <c r="C539" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D539" s="5" t="inlineStr">
         <is>
-          <t>2:08:05</t>
+          <t>2:07:16</t>
         </is>
       </c>
       <c r="E539" s="5" t="inlineStr">
         <is>
-          <t>2:21:04</t>
+          <t>2:20:44</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>Taipei Marathon</t>
+          <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
       <c r="B540" s="3" t="inlineStr">
@@ -13974,16 +13974,16 @@
         </is>
       </c>
       <c r="C540" s="3" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D540" s="3" t="inlineStr">
         <is>
-          <t>2:11:05</t>
+          <t>2:08:05</t>
         </is>
       </c>
       <c r="E540" s="3" t="inlineStr">
         <is>
-          <t>2:27:14</t>
+          <t>2:21:04</t>
         </is>
       </c>
     </row>
@@ -13999,16 +13999,16 @@
         </is>
       </c>
       <c r="C541" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D541" s="5" t="inlineStr">
         <is>
-          <t>2:11:41</t>
+          <t>2:11:05</t>
         </is>
       </c>
       <c r="E541" s="5" t="inlineStr">
         <is>
-          <t>2:32:47</t>
+          <t>2:27:14</t>
         </is>
       </c>
     </row>
@@ -14024,23 +14024,23 @@
         </is>
       </c>
       <c r="C542" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D542" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:11:41</t>
         </is>
       </c>
       <c r="E542" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:32:47</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon</t>
+          <t>Taipei Marathon</t>
         </is>
       </c>
       <c r="B543" s="5" t="inlineStr">
@@ -14049,16 +14049,16 @@
         </is>
       </c>
       <c r="C543" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D543" s="5" t="inlineStr">
         <is>
-          <t>2:07:32</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E543" s="5" t="inlineStr">
         <is>
-          <t>2:24:15</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -14074,16 +14074,16 @@
         </is>
       </c>
       <c r="C544" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D544" s="3" t="inlineStr">
         <is>
-          <t>2:07:50</t>
+          <t>2:07:32</t>
         </is>
       </c>
       <c r="E544" s="3" t="inlineStr">
         <is>
-          <t>2:26:06</t>
+          <t>2:24:15</t>
         </is>
       </c>
     </row>
@@ -14099,16 +14099,16 @@
         </is>
       </c>
       <c r="C545" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D545" s="5" t="inlineStr">
         <is>
-          <t>2:11:44</t>
+          <t>2:07:50</t>
         </is>
       </c>
       <c r="E545" s="5" t="inlineStr">
         <is>
-          <t>2:24:56</t>
+          <t>2:26:06</t>
         </is>
       </c>
     </row>
@@ -14124,23 +14124,23 @@
         </is>
       </c>
       <c r="C546" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D546" s="3" t="inlineStr">
         <is>
-          <t>2:09:55</t>
+          <t>2:11:44</t>
         </is>
       </c>
       <c r="E546" s="3" t="inlineStr">
         <is>
-          <t>2:25:13</t>
+          <t>2:24:56</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Marathon</t>
+          <t>Tata Mumbai Marathon</t>
         </is>
       </c>
       <c r="B547" s="5" t="inlineStr">
@@ -14149,16 +14149,16 @@
         </is>
       </c>
       <c r="C547" s="5" t="n">
-        <v>2007</v>
+        <v>2026</v>
       </c>
       <c r="D547" s="5" t="inlineStr">
         <is>
-          <t>2:09:45</t>
+          <t>2:09:55</t>
         </is>
       </c>
       <c r="E547" s="5" t="inlineStr">
         <is>
-          <t>2:35:28</t>
+          <t>2:25:13</t>
         </is>
       </c>
     </row>
@@ -14174,16 +14174,16 @@
         </is>
       </c>
       <c r="C548" s="3" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D548" s="3" t="inlineStr">
         <is>
-          <t>2:10:57</t>
+          <t>2:09:45</t>
         </is>
       </c>
       <c r="E548" s="3" t="inlineStr">
         <is>
-          <t>2:25:51</t>
+          <t>2:35:28</t>
         </is>
       </c>
     </row>
@@ -14199,16 +14199,16 @@
         </is>
       </c>
       <c r="C549" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D549" s="5" t="inlineStr">
         <is>
-          <t>2:10:25</t>
+          <t>2:10:57</t>
         </is>
       </c>
       <c r="E549" s="5" t="inlineStr">
         <is>
-          <t>2:25:38</t>
+          <t>2:25:51</t>
         </is>
       </c>
     </row>
@@ -14224,16 +14224,16 @@
         </is>
       </c>
       <c r="C550" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D550" s="3" t="inlineStr">
         <is>
-          <t>2:08:12</t>
+          <t>2:10:25</t>
         </is>
       </c>
       <c r="E550" s="3" t="inlineStr">
         <is>
-          <t>2:25:27</t>
+          <t>2:25:38</t>
         </is>
       </c>
     </row>
@@ -14249,16 +14249,16 @@
         </is>
       </c>
       <c r="C551" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D551" s="5" t="inlineStr">
         <is>
-          <t>2:07:32</t>
+          <t>2:08:12</t>
         </is>
       </c>
       <c r="E551" s="5" t="inlineStr">
         <is>
-          <t>2:26:49</t>
+          <t>2:25:27</t>
         </is>
       </c>
     </row>
@@ -14274,16 +14274,16 @@
         </is>
       </c>
       <c r="C552" s="3" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D552" s="3" t="inlineStr">
         <is>
-          <t>2:07:37</t>
+          <t>2:07:32</t>
         </is>
       </c>
       <c r="E552" s="3" t="inlineStr">
         <is>
-          <t>2:25:28</t>
+          <t>2:26:49</t>
         </is>
       </c>
     </row>
@@ -14299,16 +14299,16 @@
         </is>
       </c>
       <c r="C553" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D553" s="5" t="inlineStr">
         <is>
-          <t>2:06:50</t>
+          <t>2:07:37</t>
         </is>
       </c>
       <c r="E553" s="5" t="inlineStr">
         <is>
-          <t>2:25:34</t>
+          <t>2:25:28</t>
         </is>
       </c>
     </row>
@@ -14324,16 +14324,16 @@
         </is>
       </c>
       <c r="C554" s="3" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D554" s="3" t="inlineStr">
         <is>
-          <t>2:05:42</t>
+          <t>2:06:50</t>
         </is>
       </c>
       <c r="E554" s="3" t="inlineStr">
         <is>
-          <t>2:22:23</t>
+          <t>2:25:34</t>
         </is>
       </c>
     </row>
@@ -14349,16 +14349,16 @@
         </is>
       </c>
       <c r="C555" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D555" s="5" t="inlineStr">
         <is>
-          <t>2:06:00</t>
+          <t>2:05:42</t>
         </is>
       </c>
       <c r="E555" s="5" t="inlineStr">
         <is>
-          <t>2:23:15</t>
+          <t>2:22:23</t>
         </is>
       </c>
     </row>
@@ -14374,16 +14374,16 @@
         </is>
       </c>
       <c r="C556" s="3" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D556" s="3" t="inlineStr">
         <is>
-          <t>2:06:56</t>
+          <t>2:06:00</t>
         </is>
       </c>
       <c r="E556" s="3" t="inlineStr">
         <is>
-          <t>2:21:27</t>
+          <t>2:23:15</t>
         </is>
       </c>
     </row>
@@ -14399,16 +14399,16 @@
         </is>
       </c>
       <c r="C557" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D557" s="5" t="inlineStr">
         <is>
-          <t>2:03:58</t>
+          <t>2:06:56</t>
         </is>
       </c>
       <c r="E557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:21:27</t>
         </is>
       </c>
     </row>
@@ -14424,16 +14424,16 @@
         </is>
       </c>
       <c r="C558" s="3" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D558" s="3" t="inlineStr">
         <is>
-          <t>2:05:30</t>
+          <t>2:03:58</t>
         </is>
       </c>
       <c r="E558" s="3" t="inlineStr">
         <is>
-          <t>2:19:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -14449,16 +14449,16 @@
         </is>
       </c>
       <c r="C559" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D559" s="5" t="inlineStr">
         <is>
-          <t>2:04:15</t>
+          <t>2:05:30</t>
         </is>
       </c>
       <c r="E559" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:19:51</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
         </is>
       </c>
       <c r="C560" s="3" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D560" s="3" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="E560" s="3" t="inlineStr">
         <is>
-          <t>2:17:45</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -14499,16 +14499,16 @@
         </is>
       </c>
       <c r="C561" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D561" s="5" t="inlineStr">
         <is>
-          <t>2:02:40</t>
+          <t>2:04:15</t>
         </is>
       </c>
       <c r="E561" s="5" t="inlineStr">
         <is>
-          <t>2:16:02</t>
+          <t>2:17:45</t>
         </is>
       </c>
     </row>
@@ -14524,16 +14524,16 @@
         </is>
       </c>
       <c r="C562" s="3" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D562" s="3" t="inlineStr">
         <is>
-          <t>2:05:22</t>
+          <t>2:02:40</t>
         </is>
       </c>
       <c r="E562" s="3" t="inlineStr">
         <is>
-          <t>2:16:28</t>
+          <t>2:16:02</t>
         </is>
       </c>
     </row>
@@ -14549,16 +14549,16 @@
         </is>
       </c>
       <c r="C563" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D563" s="5" t="inlineStr">
         <is>
-          <t>2:02:16</t>
+          <t>2:05:22</t>
         </is>
       </c>
       <c r="E563" s="5" t="inlineStr">
         <is>
-          <t>2:15:55</t>
+          <t>2:16:28</t>
         </is>
       </c>
     </row>
@@ -14574,16 +14574,16 @@
         </is>
       </c>
       <c r="C564" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D564" s="3" t="inlineStr">
         <is>
-          <t>2:03:23</t>
+          <t>2:02:16</t>
         </is>
       </c>
       <c r="E564" s="3" t="inlineStr">
         <is>
-          <t>2:16:31</t>
+          <t>2:15:55</t>
         </is>
       </c>
     </row>
@@ -14599,23 +14599,23 @@
         </is>
       </c>
       <c r="C565" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D565" s="5" t="inlineStr">
         <is>
-          <t>2:03:37</t>
+          <t>2:03:23</t>
         </is>
       </c>
       <c r="E565" s="5" t="inlineStr">
         <is>
-          <t>2:14:29</t>
+          <t>2:16:31</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
+          <t>Tokyo Marathon</t>
         </is>
       </c>
       <c r="B566" s="3" t="inlineStr">
@@ -14624,16 +14624,16 @@
         </is>
       </c>
       <c r="C566" s="3" t="n">
-        <v>2008</v>
+        <v>2026</v>
       </c>
       <c r="D566" s="3" t="inlineStr">
         <is>
-          <t>2:12:27</t>
+          <t>2:03:37</t>
         </is>
       </c>
       <c r="E566" s="3" t="inlineStr">
         <is>
-          <t>2:36:27</t>
+          <t>2:14:29</t>
         </is>
       </c>
     </row>
@@ -14649,16 +14649,16 @@
         </is>
       </c>
       <c r="C567" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D567" s="5" t="inlineStr">
         <is>
-          <t>2:12:09</t>
+          <t>2:12:27</t>
         </is>
       </c>
       <c r="E567" s="5" t="inlineStr">
         <is>
-          <t>2:35:33</t>
+          <t>2:36:27</t>
         </is>
       </c>
     </row>
@@ -14674,16 +14674,16 @@
         </is>
       </c>
       <c r="C568" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D568" s="3" t="inlineStr">
         <is>
-          <t>2:09:52</t>
+          <t>2:12:09</t>
         </is>
       </c>
       <c r="E568" s="3" t="inlineStr">
         <is>
-          <t>2:33:08</t>
+          <t>2:35:33</t>
         </is>
       </c>
     </row>
@@ -14699,16 +14699,16 @@
         </is>
       </c>
       <c r="C569" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D569" s="5" t="inlineStr">
         <is>
-          <t>2:10:36</t>
+          <t>2:09:52</t>
         </is>
       </c>
       <c r="E569" s="5" t="inlineStr">
         <is>
-          <t>2:35:39</t>
+          <t>2:33:08</t>
         </is>
       </c>
     </row>
@@ -14724,16 +14724,16 @@
         </is>
       </c>
       <c r="C570" s="3" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D570" s="3" t="inlineStr">
         <is>
-          <t>2:09:09</t>
+          <t>2:10:36</t>
         </is>
       </c>
       <c r="E570" s="3" t="inlineStr">
         <is>
-          <t>2:31:35</t>
+          <t>2:35:39</t>
         </is>
       </c>
     </row>
@@ -14749,16 +14749,16 @@
         </is>
       </c>
       <c r="C571" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D571" s="5" t="inlineStr">
         <is>
-          <t>2:09:48</t>
+          <t>2:09:09</t>
         </is>
       </c>
       <c r="E571" s="5" t="inlineStr">
         <is>
-          <t>2:32:47</t>
+          <t>2:31:35</t>
         </is>
       </c>
     </row>
@@ -14774,16 +14774,16 @@
         </is>
       </c>
       <c r="C572" s="3" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D572" s="3" t="inlineStr">
         <is>
-          <t>2:10:42</t>
+          <t>2:09:48</t>
         </is>
       </c>
       <c r="E572" s="3" t="inlineStr">
         <is>
-          <t>2:30:54</t>
+          <t>2:32:47</t>
         </is>
       </c>
     </row>
@@ -14799,16 +14799,16 @@
         </is>
       </c>
       <c r="C573" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D573" s="5" t="inlineStr">
         <is>
-          <t>2:06:13</t>
+          <t>2:10:42</t>
         </is>
       </c>
       <c r="E573" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2:30:54</t>
         </is>
       </c>
     </row>
@@ -14824,11 +14824,11 @@
         </is>
       </c>
       <c r="C574" s="3" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D574" s="3" t="inlineStr">
         <is>
-          <t>2:03:00</t>
+          <t>2:06:13</t>
         </is>
       </c>
       <c r="E574" s="3" t="inlineStr">
@@ -14849,16 +14849,16 @@
         </is>
       </c>
       <c r="C575" s="5" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D575" s="5" t="inlineStr">
         <is>
-          <t>2:01:53</t>
+          <t>2:03:00</t>
         </is>
       </c>
       <c r="E575" s="5" t="inlineStr">
         <is>
-          <t>2:14:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -14874,16 +14874,16 @@
         </is>
       </c>
       <c r="C576" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D576" s="3" t="inlineStr">
         <is>
-          <t>2:01:48</t>
+          <t>2:01:53</t>
         </is>
       </c>
       <c r="E576" s="3" t="inlineStr">
         <is>
-          <t>2:15:51</t>
+          <t>2:14:57</t>
         </is>
       </c>
     </row>
@@ -14899,16 +14899,16 @@
         </is>
       </c>
       <c r="C577" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D577" s="5" t="inlineStr">
         <is>
-          <t>2:02:05</t>
+          <t>2:01:48</t>
         </is>
       </c>
       <c r="E577" s="5" t="inlineStr">
         <is>
-          <t>2:16:49</t>
+          <t>2:15:51</t>
         </is>
       </c>
     </row>
@@ -14924,23 +14924,23 @@
         </is>
       </c>
       <c r="C578" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D578" s="3" t="inlineStr">
         <is>
-          <t>2:02:24</t>
+          <t>2:02:05</t>
         </is>
       </c>
       <c r="E578" s="3" t="inlineStr">
         <is>
-          <t>2:14:00</t>
+          <t>2:16:49</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>Vienna City Marathon</t>
+          <t>Valencia Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B579" s="5" t="inlineStr">
@@ -14949,16 +14949,16 @@
         </is>
       </c>
       <c r="C579" s="5" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D579" s="5" t="inlineStr">
         <is>
-          <t>2:10:24</t>
+          <t>2:02:24</t>
         </is>
       </c>
       <c r="E579" s="5" t="inlineStr">
         <is>
-          <t>2:23:47</t>
+          <t>2:14:00</t>
         </is>
       </c>
     </row>
@@ -14974,16 +14974,16 @@
         </is>
       </c>
       <c r="C580" s="3" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D580" s="3" t="inlineStr">
         <is>
-          <t>2:12:20</t>
+          <t>2:10:24</t>
         </is>
       </c>
       <c r="E580" s="3" t="inlineStr">
         <is>
-          <t>2:31:46</t>
+          <t>2:23:47</t>
         </is>
       </c>
     </row>
@@ -14999,16 +14999,16 @@
         </is>
       </c>
       <c r="C581" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D581" s="5" t="inlineStr">
         <is>
-          <t>2:10:18</t>
+          <t>2:12:20</t>
         </is>
       </c>
       <c r="E581" s="5" t="inlineStr">
         <is>
-          <t>2:30:41</t>
+          <t>2:31:46</t>
         </is>
       </c>
     </row>
@@ -15024,16 +15024,16 @@
         </is>
       </c>
       <c r="C582" s="3" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D582" s="3" t="inlineStr">
         <is>
-          <t>2:10:28</t>
+          <t>2:10:18</t>
         </is>
       </c>
       <c r="E582" s="3" t="inlineStr">
         <is>
-          <t>2:29:31</t>
+          <t>2:30:41</t>
         </is>
       </c>
     </row>
@@ -15049,16 +15049,16 @@
         </is>
       </c>
       <c r="C583" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D583" s="5" t="inlineStr">
         <is>
-          <t>2:10:41</t>
+          <t>2:10:28</t>
         </is>
       </c>
       <c r="E583" s="5" t="inlineStr">
         <is>
-          <t>2:29:24</t>
+          <t>2:29:31</t>
         </is>
       </c>
     </row>
@@ -15074,16 +15074,16 @@
         </is>
       </c>
       <c r="C584" s="3" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D584" s="3" t="inlineStr">
         <is>
-          <t>2:12:22</t>
+          <t>2:10:41</t>
         </is>
       </c>
       <c r="E584" s="3" t="inlineStr">
         <is>
-          <t>2:27:33</t>
+          <t>2:29:24</t>
         </is>
       </c>
     </row>
@@ -15099,16 +15099,16 @@
         </is>
       </c>
       <c r="C585" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D585" s="5" t="inlineStr">
         <is>
-          <t>2:12:09</t>
+          <t>2:12:22</t>
         </is>
       </c>
       <c r="E585" s="5" t="inlineStr">
         <is>
-          <t>2:29:19</t>
+          <t>2:27:33</t>
         </is>
       </c>
     </row>
@@ -15124,16 +15124,16 @@
         </is>
       </c>
       <c r="C586" s="3" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D586" s="3" t="inlineStr">
         <is>
-          <t>2:08:50</t>
+          <t>2:12:09</t>
         </is>
       </c>
       <c r="E586" s="3" t="inlineStr">
         <is>
-          <t>2:30:09</t>
+          <t>2:29:19</t>
         </is>
       </c>
     </row>
@@ -15149,16 +15149,16 @@
         </is>
       </c>
       <c r="C587" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D587" s="5" t="inlineStr">
         <is>
-          <t>2:07:38</t>
+          <t>2:08:50</t>
         </is>
       </c>
       <c r="E587" s="5" t="inlineStr">
         <is>
-          <t>2:25:47</t>
+          <t>2:30:09</t>
         </is>
       </c>
     </row>
@@ -15174,16 +15174,16 @@
         </is>
       </c>
       <c r="C588" s="3" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D588" s="3" t="inlineStr">
         <is>
-          <t>2:08:21</t>
+          <t>2:07:38</t>
         </is>
       </c>
       <c r="E588" s="3" t="inlineStr">
         <is>
-          <t>2:30:43</t>
+          <t>2:25:47</t>
         </is>
       </c>
     </row>
@@ -15199,16 +15199,16 @@
         </is>
       </c>
       <c r="C589" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D589" s="5" t="inlineStr">
         <is>
-          <t>2:08:40</t>
+          <t>2:08:21</t>
         </is>
       </c>
       <c r="E589" s="5" t="inlineStr">
         <is>
-          <t>2:31:08</t>
+          <t>2:30:43</t>
         </is>
       </c>
     </row>
@@ -15224,16 +15224,16 @@
         </is>
       </c>
       <c r="C590" s="3" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D590" s="3" t="inlineStr">
         <is>
-          <t>2:08:29</t>
+          <t>2:08:40</t>
         </is>
       </c>
       <c r="E590" s="3" t="inlineStr">
         <is>
-          <t>2:26:21</t>
+          <t>2:31:08</t>
         </is>
       </c>
     </row>
@@ -15249,16 +15249,16 @@
         </is>
       </c>
       <c r="C591" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D591" s="5" t="inlineStr">
         <is>
-          <t>2:06:58</t>
+          <t>2:08:29</t>
         </is>
       </c>
       <c r="E591" s="5" t="inlineStr">
         <is>
-          <t>2:26:39</t>
+          <t>2:26:21</t>
         </is>
       </c>
     </row>
@@ -15274,16 +15274,16 @@
         </is>
       </c>
       <c r="C592" s="3" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D592" s="3" t="inlineStr">
         <is>
-          <t>2:08:40</t>
+          <t>2:06:58</t>
         </is>
       </c>
       <c r="E592" s="3" t="inlineStr">
         <is>
-          <t>2:31:08</t>
+          <t>2:26:39</t>
         </is>
       </c>
     </row>
@@ -15299,16 +15299,16 @@
         </is>
       </c>
       <c r="C593" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D593" s="5" t="inlineStr">
         <is>
-          <t>2:05:41</t>
+          <t>2:08:40</t>
         </is>
       </c>
       <c r="E593" s="5" t="inlineStr">
         <is>
-          <t>2:28:59</t>
+          <t>2:31:08</t>
         </is>
       </c>
     </row>
@@ -15324,16 +15324,16 @@
         </is>
       </c>
       <c r="C594" s="3" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D594" s="3" t="inlineStr">
         <is>
-          <t>2:07:31</t>
+          <t>2:05:41</t>
         </is>
       </c>
       <c r="E594" s="3" t="inlineStr">
         <is>
-          <t>2:30:09</t>
+          <t>2:28:59</t>
         </is>
       </c>
     </row>
@@ -15349,16 +15349,16 @@
         </is>
       </c>
       <c r="C595" s="5" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="D595" s="5" t="inlineStr">
         <is>
-          <t>2:08:40</t>
+          <t>2:07:31</t>
         </is>
       </c>
       <c r="E595" s="5" t="inlineStr">
         <is>
-          <t>2:24:20</t>
+          <t>2:30:09</t>
         </is>
       </c>
     </row>
@@ -15374,16 +15374,16 @@
         </is>
       </c>
       <c r="C596" s="3" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="D596" s="3" t="inlineStr">
         <is>
-          <t>2:06:56</t>
+          <t>2:08:40</t>
         </is>
       </c>
       <c r="E596" s="3" t="inlineStr">
         <is>
-          <t>2:22:12</t>
+          <t>2:24:20</t>
         </is>
       </c>
     </row>
@@ -15399,16 +15399,16 @@
         </is>
       </c>
       <c r="C597" s="5" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D597" s="5" t="inlineStr">
         <is>
-          <t>2:09:25</t>
+          <t>2:06:56</t>
         </is>
       </c>
       <c r="E597" s="5" t="inlineStr">
         <is>
-          <t>2:24:29</t>
+          <t>2:22:12</t>
         </is>
       </c>
     </row>
@@ -15424,16 +15424,16 @@
         </is>
       </c>
       <c r="C598" s="3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D598" s="3" t="inlineStr">
         <is>
-          <t>2:06:53</t>
+          <t>2:09:25</t>
         </is>
       </c>
       <c r="E598" s="3" t="inlineStr">
         <is>
-          <t>2:20:59</t>
+          <t>2:24:29</t>
         </is>
       </c>
     </row>
@@ -15449,16 +15449,16 @@
         </is>
       </c>
       <c r="C599" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D599" s="5" t="inlineStr">
         <is>
-          <t>2:05:08</t>
+          <t>2:06:53</t>
         </is>
       </c>
       <c r="E599" s="5" t="inlineStr">
         <is>
-          <t>2:24:12</t>
+          <t>2:20:59</t>
         </is>
       </c>
     </row>
@@ -15474,16 +15474,16 @@
         </is>
       </c>
       <c r="C600" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D600" s="3" t="inlineStr">
         <is>
-          <t>2:06:35</t>
+          <t>2:05:08</t>
         </is>
       </c>
       <c r="E600" s="3" t="inlineStr">
         <is>
-          <t>2:24:08</t>
+          <t>2:24:12</t>
         </is>
       </c>
     </row>
@@ -15499,23 +15499,23 @@
         </is>
       </c>
       <c r="C601" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D601" s="5" t="inlineStr">
         <is>
-          <t>2:08:28</t>
+          <t>2:06:35</t>
         </is>
       </c>
       <c r="E601" s="5" t="inlineStr">
         <is>
-          <t>2:24:14</t>
+          <t>2:24:08</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>Zurich Marató de Barcelona</t>
+          <t>Vienna City Marathon</t>
         </is>
       </c>
       <c r="B602" s="3" t="inlineStr">
@@ -15524,16 +15524,16 @@
         </is>
       </c>
       <c r="C602" s="3" t="n">
-        <v>2006</v>
+        <v>2025</v>
       </c>
       <c r="D602" s="3" t="inlineStr">
         <is>
-          <t>2:11:44</t>
+          <t>2:08:28</t>
         </is>
       </c>
       <c r="E602" s="3" t="inlineStr">
         <is>
-          <t>2:36:04</t>
+          <t>2:24:14</t>
         </is>
       </c>
     </row>
@@ -15549,16 +15549,16 @@
         </is>
       </c>
       <c r="C603" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D603" s="5" t="inlineStr">
         <is>
-          <t>2:12:56</t>
+          <t>2:11:44</t>
         </is>
       </c>
       <c r="E603" s="5" t="inlineStr">
         <is>
-          <t>2:37:40</t>
+          <t>2:36:04</t>
         </is>
       </c>
     </row>
@@ -15574,16 +15574,16 @@
         </is>
       </c>
       <c r="C604" s="3" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D604" s="3" t="inlineStr">
         <is>
-          <t>2:10:55</t>
+          <t>2:12:56</t>
         </is>
       </c>
       <c r="E604" s="3" t="inlineStr">
         <is>
-          <t>2:34:03</t>
+          <t>2:37:40</t>
         </is>
       </c>
     </row>
@@ -15599,16 +15599,16 @@
         </is>
       </c>
       <c r="C605" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D605" s="5" t="inlineStr">
         <is>
-          <t>2:10:22</t>
+          <t>2:10:55</t>
         </is>
       </c>
       <c r="E605" s="5" t="inlineStr">
         <is>
-          <t>2:33:19</t>
+          <t>2:34:03</t>
         </is>
       </c>
     </row>
@@ -15624,16 +15624,16 @@
         </is>
       </c>
       <c r="C606" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D606" s="3" t="inlineStr">
         <is>
-          <t>2:07:30</t>
+          <t>2:10:22</t>
         </is>
       </c>
       <c r="E606" s="3" t="inlineStr">
         <is>
-          <t>2:31:51</t>
+          <t>2:33:19</t>
         </is>
       </c>
     </row>
@@ -15649,16 +15649,16 @@
         </is>
       </c>
       <c r="C607" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D607" s="5" t="inlineStr">
         <is>
-          <t>2:07:47</t>
+          <t>2:07:30</t>
         </is>
       </c>
       <c r="E607" s="5" t="inlineStr">
         <is>
-          <t>2:28:47</t>
+          <t>2:31:51</t>
         </is>
       </c>
     </row>
@@ -15674,16 +15674,16 @@
         </is>
       </c>
       <c r="C608" s="3" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D608" s="3" t="inlineStr">
         <is>
-          <t>2:10:06</t>
+          <t>2:07:47</t>
         </is>
       </c>
       <c r="E608" s="3" t="inlineStr">
         <is>
-          <t>2:33:10</t>
+          <t>2:28:47</t>
         </is>
       </c>
     </row>
@@ -15699,16 +15699,16 @@
         </is>
       </c>
       <c r="C609" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D609" s="5" t="inlineStr">
         <is>
-          <t>2:09:36</t>
+          <t>2:10:06</t>
         </is>
       </c>
       <c r="E609" s="5" t="inlineStr">
         <is>
-          <t>2:31:10</t>
+          <t>2:33:10</t>
         </is>
       </c>
     </row>
@@ -15724,16 +15724,16 @@
         </is>
       </c>
       <c r="C610" s="3" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D610" s="3" t="inlineStr">
         <is>
-          <t>2:09:41</t>
+          <t>2:09:36</t>
         </is>
       </c>
       <c r="E610" s="3" t="inlineStr">
         <is>
-          <t>2:29:10</t>
+          <t>2:31:10</t>
         </is>
       </c>
     </row>
@@ -15749,16 +15749,16 @@
         </is>
       </c>
       <c r="C611" s="5" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D611" s="5" t="inlineStr">
         <is>
-          <t>2:05:06</t>
+          <t>2:09:41</t>
         </is>
       </c>
       <c r="E611" s="5" t="inlineStr">
         <is>
-          <t>2:19:44</t>
+          <t>2:29:10</t>
         </is>
       </c>
     </row>
@@ -15774,16 +15774,16 @@
         </is>
       </c>
       <c r="C612" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D612" s="3" t="inlineStr">
         <is>
-          <t>2:05:01</t>
+          <t>2:05:06</t>
         </is>
       </c>
       <c r="E612" s="3" t="inlineStr">
         <is>
-          <t>2:19:52</t>
+          <t>2:19:44</t>
         </is>
       </c>
     </row>
@@ -15799,16 +15799,16 @@
         </is>
       </c>
       <c r="C613" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D613" s="5" t="inlineStr">
         <is>
-          <t>2:04:13</t>
+          <t>2:05:01</t>
         </is>
       </c>
       <c r="E613" s="5" t="inlineStr">
         <is>
-          <t>2:19:33</t>
+          <t>2:19:52</t>
         </is>
       </c>
     </row>
@@ -15824,23 +15824,23 @@
         </is>
       </c>
       <c r="C614" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D614" s="3" t="inlineStr">
         <is>
-          <t>2:04:57</t>
+          <t>2:04:13</t>
         </is>
       </c>
       <c r="E614" s="3" t="inlineStr">
         <is>
-          <t>2:10:53</t>
+          <t>2:19:33</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" s="4" t="inlineStr">
         <is>
-          <t>Zurich Maratón de Sevilla</t>
+          <t>Zurich Marató de Barcelona</t>
         </is>
       </c>
       <c r="B615" s="5" t="inlineStr">
@@ -15849,16 +15849,16 @@
         </is>
       </c>
       <c r="C615" s="5" t="n">
-        <v>2009</v>
+        <v>2026</v>
       </c>
       <c r="D615" s="5" t="inlineStr">
         <is>
-          <t>2:11:51</t>
+          <t>2:04:57</t>
         </is>
       </c>
       <c r="E615" s="5" t="inlineStr">
         <is>
-          <t>2:26:03</t>
+          <t>2:10:53</t>
         </is>
       </c>
     </row>
@@ -15874,16 +15874,16 @@
         </is>
       </c>
       <c r="C616" s="3" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D616" s="3" t="inlineStr">
         <is>
-          <t>2:09:53</t>
+          <t>2:11:51</t>
         </is>
       </c>
       <c r="E616" s="3" t="inlineStr">
         <is>
-          <t>2:30:55</t>
+          <t>2:26:03</t>
         </is>
       </c>
     </row>
@@ -15899,16 +15899,16 @@
         </is>
       </c>
       <c r="C617" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D617" s="5" t="inlineStr">
         <is>
-          <t>2:10:26</t>
+          <t>2:09:53</t>
         </is>
       </c>
       <c r="E617" s="5" t="inlineStr">
         <is>
-          <t>2:33:10</t>
+          <t>2:30:55</t>
         </is>
       </c>
     </row>
@@ -15924,16 +15924,16 @@
         </is>
       </c>
       <c r="C618" s="3" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D618" s="3" t="inlineStr">
         <is>
-          <t>2:10:19</t>
+          <t>2:10:26</t>
         </is>
       </c>
       <c r="E618" s="3" t="inlineStr">
         <is>
-          <t>2:33:41</t>
+          <t>2:33:10</t>
         </is>
       </c>
     </row>
@@ -15949,16 +15949,16 @@
         </is>
       </c>
       <c r="C619" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D619" s="5" t="inlineStr">
         <is>
-          <t>2:11:26</t>
+          <t>2:10:19</t>
         </is>
       </c>
       <c r="E619" s="5" t="inlineStr">
         <is>
-          <t>2:33:44</t>
+          <t>2:33:41</t>
         </is>
       </c>
     </row>
@@ -15974,16 +15974,16 @@
         </is>
       </c>
       <c r="C620" s="3" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D620" s="3" t="inlineStr">
         <is>
-          <t>2:08:33</t>
+          <t>2:11:26</t>
         </is>
       </c>
       <c r="E620" s="3" t="inlineStr">
         <is>
-          <t>2:28:39</t>
+          <t>2:33:44</t>
         </is>
       </c>
     </row>
@@ -15999,16 +15999,16 @@
         </is>
       </c>
       <c r="C621" s="5" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D621" s="5" t="inlineStr">
         <is>
-          <t>2:04:59</t>
+          <t>2:08:33</t>
         </is>
       </c>
       <c r="E621" s="5" t="inlineStr">
         <is>
-          <t>2:20:29</t>
+          <t>2:28:39</t>
         </is>
       </c>
     </row>
@@ -16024,16 +16024,16 @@
         </is>
       </c>
       <c r="C622" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D622" s="3" t="inlineStr">
         <is>
-          <t>2:03:27</t>
+          <t>2:04:59</t>
         </is>
       </c>
       <c r="E622" s="3" t="inlineStr">
         <is>
-          <t>2:22:13</t>
+          <t>2:20:29</t>
         </is>
       </c>
     </row>
@@ -16049,16 +16049,16 @@
         </is>
       </c>
       <c r="C623" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D623" s="5" t="inlineStr">
         <is>
-          <t>2:05:15</t>
+          <t>2:03:27</t>
         </is>
       </c>
       <c r="E623" s="5" t="inlineStr">
         <is>
-          <t>2:22:17</t>
+          <t>2:22:13</t>
         </is>
       </c>
     </row>
@@ -16074,23 +16074,23 @@
         </is>
       </c>
       <c r="C624" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D624" s="3" t="inlineStr">
         <is>
-          <t>2:03:59</t>
+          <t>2:05:15</t>
         </is>
       </c>
       <c r="E624" s="3" t="inlineStr">
         <is>
-          <t>2:20:39</t>
+          <t>2:22:17</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
+          <t>Zurich Maratón de Sevilla</t>
         </is>
       </c>
       <c r="B625" s="5" t="inlineStr">
@@ -16099,16 +16099,16 @@
         </is>
       </c>
       <c r="C625" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D625" s="5" t="inlineStr">
         <is>
-          <t>2:10:29</t>
+          <t>2:03:59</t>
         </is>
       </c>
       <c r="E625" s="5" t="inlineStr">
         <is>
-          <t>2:26:31</t>
+          <t>2:20:39</t>
         </is>
       </c>
     </row>
@@ -16124,16 +16124,16 @@
         </is>
       </c>
       <c r="C626" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D626" s="3" t="inlineStr">
         <is>
-          <t>2:08:05</t>
+          <t>2:10:29</t>
         </is>
       </c>
       <c r="E626" s="3" t="inlineStr">
         <is>
-          <t>2:26:19</t>
+          <t>2:26:31</t>
         </is>
       </c>
     </row>
@@ -16149,48 +16149,48 @@
         </is>
       </c>
       <c r="C627" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D627" s="5" t="inlineStr">
+        <is>
+          <t>2:08:05</t>
+        </is>
+      </c>
+      <c r="E627" s="5" t="inlineStr">
+        <is>
+          <t>2:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid</t>
+        </is>
+      </c>
+      <c r="B628" s="3" t="inlineStr">
+        <is>
+          <t>42K</t>
+        </is>
+      </c>
+      <c r="C628" s="3" t="n">
         <v>2025</v>
       </c>
-      <c r="D627" s="5" t="inlineStr">
+      <c r="D628" s="3" t="inlineStr">
         <is>
           <t>2:09:11</t>
         </is>
       </c>
-      <c r="E627" s="5" t="inlineStr">
+      <c r="E628" s="3" t="inlineStr">
         <is>
           <t>2:25:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" s="6" t="inlineStr">
-        <is>
-          <t>21K de Montréal</t>
-        </is>
-      </c>
-      <c r="B628" s="7" t="inlineStr">
-        <is>
-          <t>21K</t>
-        </is>
-      </c>
-      <c r="C628" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D628" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E628" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Bristol Run</t>
+          <t>21K de Montréal</t>
         </is>
       </c>
       <c r="B629" s="5" t="inlineStr">
@@ -16199,16 +16199,16 @@
         </is>
       </c>
       <c r="C629" s="5" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D629" s="5" t="inlineStr">
         <is>
-          <t>1:07:50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E629" s="5" t="inlineStr">
         <is>
-          <t>1:18:15</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16224,23 +16224,23 @@
         </is>
       </c>
       <c r="C630" s="7" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D630" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:50</t>
         </is>
       </c>
       <c r="E630" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:18:15</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run</t>
+          <t>AJ Bell Great Bristol Run</t>
         </is>
       </c>
       <c r="B631" s="5" t="inlineStr">
@@ -16249,16 +16249,16 @@
         </is>
       </c>
       <c r="C631" s="5" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D631" s="5" t="inlineStr">
         <is>
-          <t>1:10:25</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E631" s="5" t="inlineStr">
         <is>
-          <t>1:21:56</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16274,23 +16274,23 @@
         </is>
       </c>
       <c r="C632" s="7" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D632" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:25</t>
         </is>
       </c>
       <c r="E632" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:21:56</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great North Run</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B633" s="5" t="inlineStr">
@@ -16299,16 +16299,16 @@
         </is>
       </c>
       <c r="C633" s="5" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="D633" s="5" t="inlineStr">
         <is>
-          <t>1:01:57</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E633" s="5" t="inlineStr">
         <is>
-          <t>1:08:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16324,16 +16324,16 @@
         </is>
       </c>
       <c r="C634" s="7" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D634" s="7" t="inlineStr">
         <is>
-          <t>1:00:30</t>
+          <t>1:01:57</t>
         </is>
       </c>
       <c r="E634" s="7" t="inlineStr">
         <is>
-          <t>1:08:40</t>
+          <t>1:08:49</t>
         </is>
       </c>
     </row>
@@ -16349,16 +16349,16 @@
         </is>
       </c>
       <c r="C635" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D635" s="5" t="inlineStr">
         <is>
-          <t>0:59:58</t>
+          <t>1:00:30</t>
         </is>
       </c>
       <c r="E635" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:40</t>
         </is>
       </c>
     </row>
@@ -16374,16 +16374,16 @@
         </is>
       </c>
       <c r="C636" s="7" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D636" s="7" t="inlineStr">
         <is>
-          <t>1:00:01</t>
+          <t>0:59:58</t>
         </is>
       </c>
       <c r="E636" s="7" t="inlineStr">
         <is>
-          <t>1:05:40</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16399,16 +16399,16 @@
         </is>
       </c>
       <c r="C637" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D637" s="5" t="inlineStr">
         <is>
-          <t>0:59:37</t>
+          <t>1:00:01</t>
         </is>
       </c>
       <c r="E637" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:40</t>
         </is>
       </c>
     </row>
@@ -16424,11 +16424,11 @@
         </is>
       </c>
       <c r="C638" s="7" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D638" s="7" t="inlineStr">
         <is>
-          <t>0:59:05</t>
+          <t>0:59:37</t>
         </is>
       </c>
       <c r="E638" s="7" t="inlineStr">
@@ -16449,11 +16449,11 @@
         </is>
       </c>
       <c r="C639" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D639" s="5" t="inlineStr">
         <is>
-          <t>1:01:04</t>
+          <t>0:59:05</t>
         </is>
       </c>
       <c r="E639" s="5" t="inlineStr">
@@ -16474,16 +16474,16 @@
         </is>
       </c>
       <c r="C640" s="7" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D640" s="7" t="inlineStr">
         <is>
-          <t>1:00:08</t>
+          <t>1:01:04</t>
         </is>
       </c>
       <c r="E640" s="7" t="inlineStr">
         <is>
-          <t>1:06:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16499,16 +16499,16 @@
         </is>
       </c>
       <c r="C641" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D641" s="5" t="inlineStr">
         <is>
-          <t>0:59:45</t>
+          <t>1:00:08</t>
         </is>
       </c>
       <c r="E641" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:57</t>
         </is>
       </c>
     </row>
@@ -16524,11 +16524,11 @@
         </is>
       </c>
       <c r="C642" s="7" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D642" s="7" t="inlineStr">
         <is>
-          <t>0:59:32</t>
+          <t>0:59:45</t>
         </is>
       </c>
       <c r="E642" s="7" t="inlineStr">
@@ -16549,11 +16549,11 @@
         </is>
       </c>
       <c r="C643" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D643" s="5" t="inlineStr">
         <is>
-          <t>0:59:33</t>
+          <t>0:59:32</t>
         </is>
       </c>
       <c r="E643" s="5" t="inlineStr">
@@ -16574,11 +16574,11 @@
         </is>
       </c>
       <c r="C644" s="7" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D644" s="7" t="inlineStr">
         <is>
-          <t>0:58:56</t>
+          <t>0:59:33</t>
         </is>
       </c>
       <c r="E644" s="7" t="inlineStr">
@@ -16599,11 +16599,11 @@
         </is>
       </c>
       <c r="C645" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D645" s="5" t="inlineStr">
         <is>
-          <t>0:59:06</t>
+          <t>0:58:56</t>
         </is>
       </c>
       <c r="E645" s="5" t="inlineStr">
@@ -16624,16 +16624,16 @@
         </is>
       </c>
       <c r="C646" s="7" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D646" s="7" t="inlineStr">
         <is>
-          <t>1:00:09</t>
+          <t>0:59:06</t>
         </is>
       </c>
       <c r="E646" s="7" t="inlineStr">
         <is>
-          <t>1:07:29</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -16649,16 +16649,16 @@
         </is>
       </c>
       <c r="C647" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D647" s="5" t="inlineStr">
         <is>
-          <t>1:00:00</t>
+          <t>1:00:09</t>
         </is>
       </c>
       <c r="E647" s="5" t="inlineStr">
         <is>
-          <t>1:05:39</t>
+          <t>1:07:29</t>
         </is>
       </c>
     </row>
@@ -16674,16 +16674,16 @@
         </is>
       </c>
       <c r="C648" s="7" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="D648" s="7" t="inlineStr">
         <is>
-          <t>0:58:57</t>
+          <t>1:00:00</t>
         </is>
       </c>
       <c r="E648" s="7" t="inlineStr">
         <is>
-          <t>1:07:41</t>
+          <t>1:05:39</t>
         </is>
       </c>
     </row>
@@ -16699,23 +16699,23 @@
         </is>
       </c>
       <c r="C649" s="5" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D649" s="5" t="inlineStr">
         <is>
-          <t>1:00:52</t>
+          <t>0:58:57</t>
         </is>
       </c>
       <c r="E649" s="5" t="inlineStr">
         <is>
-          <t>1:09:32</t>
+          <t>1:07:41</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" s="6" t="inlineStr">
         <is>
-          <t>Aramco Houston Half Marathon</t>
+          <t>AJ Bell Great North Run</t>
         </is>
       </c>
       <c r="B650" s="7" t="inlineStr">
@@ -16724,16 +16724,16 @@
         </is>
       </c>
       <c r="C650" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D650" s="7" t="inlineStr">
         <is>
-          <t>1:00:42</t>
+          <t>1:00:52</t>
         </is>
       </c>
       <c r="E650" s="7" t="inlineStr">
         <is>
-          <t>1:04:37</t>
+          <t>1:09:32</t>
         </is>
       </c>
     </row>
@@ -16749,16 +16749,16 @@
         </is>
       </c>
       <c r="C651" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D651" s="5" t="inlineStr">
         <is>
-          <t>0:59:17</t>
+          <t>1:00:42</t>
         </is>
       </c>
       <c r="E651" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:37</t>
         </is>
       </c>
     </row>
@@ -16774,23 +16774,23 @@
         </is>
       </c>
       <c r="C652" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D652" s="7" t="inlineStr">
         <is>
-          <t>0:59:01</t>
+          <t>0:59:17</t>
         </is>
       </c>
       <c r="E652" s="7" t="inlineStr">
         <is>
-          <t>1:04:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="4" t="inlineStr">
         <is>
-          <t>Asics Run Melbourne</t>
+          <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
       <c r="B653" s="5" t="inlineStr">
@@ -16799,23 +16799,23 @@
         </is>
       </c>
       <c r="C653" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:01</t>
         </is>
       </c>
       <c r="E653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:49</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" s="6" t="inlineStr">
         <is>
-          <t>Bangsaen21</t>
+          <t>Asics Run Melbourne</t>
         </is>
       </c>
       <c r="B654" s="7" t="inlineStr">
@@ -16824,7 +16824,7 @@
         </is>
       </c>
       <c r="C654" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D654" s="7" t="inlineStr">
         <is>
@@ -16849,7 +16849,7 @@
         </is>
       </c>
       <c r="C655" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D655" s="5" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         </is>
       </c>
       <c r="C656" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D656" s="7" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
     <row r="657">
       <c r="A657" s="4" t="inlineStr">
         <is>
-          <t>Brølløbet - The Bridge Run</t>
+          <t>Bangsaen21</t>
         </is>
       </c>
       <c r="B657" s="5" t="inlineStr">
@@ -16915,7 +16915,7 @@
     <row r="658">
       <c r="A658" s="6" t="inlineStr">
         <is>
-          <t>Burj2Burj Half Marathon</t>
+          <t>Brølløbet - The Bridge Run</t>
         </is>
       </c>
       <c r="B658" s="7" t="inlineStr">
@@ -16924,7 +16924,7 @@
         </is>
       </c>
       <c r="C658" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D658" s="7" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="C659" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D659" s="5" t="inlineStr">
         <is>
@@ -16974,23 +16974,23 @@
         </is>
       </c>
       <c r="C660" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D660" s="7" t="inlineStr">
         <is>
-          <t>0:59:26</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E660" s="7" t="inlineStr">
         <is>
-          <t>1:06:57</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="4" t="inlineStr">
         <is>
-          <t>Cardiff Half Marathon</t>
+          <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
       <c r="B661" s="5" t="inlineStr">
@@ -16999,23 +16999,23 @@
         </is>
       </c>
       <c r="C661" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D661" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:26</t>
         </is>
       </c>
       <c r="E661" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:57</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" s="6" t="inlineStr">
         <is>
-          <t>Coelmo Napoli City Half Marathon</t>
+          <t>Cardiff Half Marathon</t>
         </is>
       </c>
       <c r="B662" s="7" t="inlineStr">
@@ -17049,7 +17049,7 @@
         </is>
       </c>
       <c r="C663" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D663" s="5" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
     <row r="664">
       <c r="A664" s="6" t="inlineStr">
         <is>
-          <t>Copenhagen Half Marathon</t>
+          <t>Coelmo Napoli City Half Marathon</t>
         </is>
       </c>
       <c r="B664" s="7" t="inlineStr">
@@ -17074,16 +17074,16 @@
         </is>
       </c>
       <c r="C664" s="7" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D664" s="7" t="inlineStr">
         <is>
-          <t>0:59:11</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E664" s="7" t="inlineStr">
         <is>
-          <t>1:05:53</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17099,16 +17099,16 @@
         </is>
       </c>
       <c r="C665" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D665" s="5" t="inlineStr">
         <is>
-          <t>0:58:05</t>
+          <t>0:59:11</t>
         </is>
       </c>
       <c r="E665" s="5" t="inlineStr">
         <is>
-          <t>1:05:11</t>
+          <t>1:05:53</t>
         </is>
       </c>
     </row>
@@ -17124,23 +17124,23 @@
         </is>
       </c>
       <c r="C666" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D666" s="7" t="inlineStr">
         <is>
-          <t>0:58:23</t>
+          <t>0:58:05</t>
         </is>
       </c>
       <c r="E666" s="7" t="inlineStr">
         <is>
-          <t>1:04:44</t>
+          <t>1:05:11</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" s="4" t="inlineStr">
         <is>
-          <t>Disney Princess Half Marathon</t>
+          <t>Copenhagen Half Marathon</t>
         </is>
       </c>
       <c r="B667" s="5" t="inlineStr">
@@ -17153,12 +17153,12 @@
       </c>
       <c r="D667" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:23</t>
         </is>
       </c>
       <c r="E667" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:44</t>
         </is>
       </c>
     </row>
@@ -17174,7 +17174,7 @@
         </is>
       </c>
       <c r="C668" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D668" s="7" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
     <row r="669">
       <c r="A669" s="4" t="inlineStr">
         <is>
-          <t>EDP Lisboa Meia Maratona</t>
+          <t>Disney Princess Half Marathon</t>
         </is>
       </c>
       <c r="B669" s="5" t="inlineStr">
@@ -17199,11 +17199,11 @@
         </is>
       </c>
       <c r="C669" s="5" t="n">
-        <v>2000</v>
+        <v>2026</v>
       </c>
       <c r="D669" s="5" t="inlineStr">
         <is>
-          <t>0:59:06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E669" s="5" t="inlineStr">
@@ -17224,16 +17224,16 @@
         </is>
       </c>
       <c r="C670" s="7" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D670" s="7" t="inlineStr">
         <is>
-          <t>1:00:26</t>
+          <t>0:59:06</t>
         </is>
       </c>
       <c r="E670" s="7" t="inlineStr">
         <is>
-          <t>1:05:44</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17249,16 +17249,16 @@
         </is>
       </c>
       <c r="C671" s="5" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="D671" s="5" t="inlineStr">
         <is>
-          <t>1:00:10</t>
+          <t>1:00:26</t>
         </is>
       </c>
       <c r="E671" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:44</t>
         </is>
       </c>
     </row>
@@ -17274,16 +17274,16 @@
         </is>
       </c>
       <c r="C672" s="7" t="n">
-        <v>2010</v>
+        <v>2003</v>
       </c>
       <c r="D672" s="7" t="inlineStr">
         <is>
-          <t>0:58:23</t>
+          <t>1:00:10</t>
         </is>
       </c>
       <c r="E672" s="7" t="inlineStr">
         <is>
-          <t>1:08:38</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17299,16 +17299,16 @@
         </is>
       </c>
       <c r="C673" s="5" t="n">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="D673" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:23</t>
         </is>
       </c>
       <c r="E673" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:38</t>
         </is>
       </c>
     </row>
@@ -17324,7 +17324,7 @@
         </is>
       </c>
       <c r="C674" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D674" s="7" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         </is>
       </c>
       <c r="C675" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D675" s="5" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
     <row r="676">
       <c r="A676" s="6" t="inlineStr">
         <is>
-          <t>Eurospin RomaOstia Half Marathon</t>
+          <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
       <c r="B676" s="7" t="inlineStr">
@@ -17374,7 +17374,7 @@
         </is>
       </c>
       <c r="C676" s="7" t="n">
-        <v>2004</v>
+        <v>2026</v>
       </c>
       <c r="D676" s="7" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="E676" s="7" t="inlineStr">
         <is>
-          <t>1:10:39</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17399,16 +17399,16 @@
         </is>
       </c>
       <c r="C677" s="5" t="n">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="D677" s="5" t="inlineStr">
         <is>
-          <t>0:59:32</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E677" s="5" t="inlineStr">
         <is>
-          <t>1:06:38</t>
+          <t>1:10:39</t>
         </is>
       </c>
     </row>
@@ -17424,16 +17424,16 @@
         </is>
       </c>
       <c r="C678" s="7" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="D678" s="7" t="inlineStr">
         <is>
-          <t>0:59:17</t>
+          <t>0:59:32</t>
         </is>
       </c>
       <c r="E678" s="7" t="inlineStr">
         <is>
-          <t>1:06:21</t>
+          <t>1:06:38</t>
         </is>
       </c>
     </row>
@@ -17449,16 +17449,16 @@
         </is>
       </c>
       <c r="C679" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D679" s="5" t="inlineStr">
         <is>
-          <t>1:01:10</t>
+          <t>0:59:17</t>
         </is>
       </c>
       <c r="E679" s="5" t="inlineStr">
         <is>
-          <t>1:07:38</t>
+          <t>1:06:21</t>
         </is>
       </c>
     </row>
@@ -17474,16 +17474,16 @@
         </is>
       </c>
       <c r="C680" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D680" s="7" t="inlineStr">
         <is>
-          <t>0:58:49</t>
+          <t>1:01:10</t>
         </is>
       </c>
       <c r="E680" s="7" t="inlineStr">
         <is>
-          <t>1:08:20</t>
+          <t>1:07:38</t>
         </is>
       </c>
     </row>
@@ -17499,23 +17499,23 @@
         </is>
       </c>
       <c r="C681" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D681" s="5" t="inlineStr">
         <is>
-          <t>0:58:00</t>
+          <t>0:58:49</t>
         </is>
       </c>
       <c r="E681" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:20</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" s="6" t="inlineStr">
         <is>
-          <t>Generali Berlin Half Marathon</t>
+          <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
       <c r="B682" s="7" t="inlineStr">
@@ -17524,16 +17524,16 @@
         </is>
       </c>
       <c r="C682" s="7" t="n">
-        <v>2006</v>
+        <v>2026</v>
       </c>
       <c r="D682" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:00</t>
         </is>
       </c>
       <c r="E682" s="7" t="inlineStr">
         <is>
-          <t>1:07:16</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17549,16 +17549,16 @@
         </is>
       </c>
       <c r="C683" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D683" s="5" t="inlineStr">
         <is>
-          <t>0:58:56</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:16</t>
         </is>
       </c>
     </row>
@@ -17574,16 +17574,16 @@
         </is>
       </c>
       <c r="C684" s="7" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="D684" s="7" t="inlineStr">
         <is>
-          <t>1:00:16</t>
+          <t>0:58:56</t>
         </is>
       </c>
       <c r="E684" s="7" t="inlineStr">
         <is>
-          <t>1:09:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17599,16 +17599,16 @@
         </is>
       </c>
       <c r="C685" s="5" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="D685" s="5" t="inlineStr">
         <is>
-          <t>0:59:14</t>
+          <t>1:00:16</t>
         </is>
       </c>
       <c r="E685" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:09:43</t>
         </is>
       </c>
     </row>
@@ -17624,16 +17624,16 @@
         </is>
       </c>
       <c r="C686" s="7" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="D686" s="7" t="inlineStr">
         <is>
-          <t>0:59:01</t>
+          <t>0:59:14</t>
         </is>
       </c>
       <c r="E686" s="7" t="inlineStr">
         <is>
-          <t>1:05:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17649,16 +17649,16 @@
         </is>
       </c>
       <c r="C687" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D687" s="5" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>0:59:01</t>
         </is>
       </c>
       <c r="E687" s="5" t="inlineStr">
         <is>
-          <t>1:06:53</t>
+          <t>1:05:43</t>
         </is>
       </c>
     </row>
@@ -17674,23 +17674,23 @@
         </is>
       </c>
       <c r="C688" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D688" s="7" t="inlineStr">
         <is>
-          <t>0:58:43</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E688" s="7" t="inlineStr">
         <is>
-          <t>1:03:35</t>
+          <t>1:06:53</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" s="4" t="inlineStr">
         <is>
-          <t>Generali Prague Half Marathon</t>
+          <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
       <c r="B689" s="5" t="inlineStr">
@@ -17699,16 +17699,16 @@
         </is>
       </c>
       <c r="C689" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D689" s="5" t="inlineStr">
         <is>
-          <t>0:59:43</t>
+          <t>0:58:43</t>
         </is>
       </c>
       <c r="E689" s="5" t="inlineStr">
         <is>
-          <t>1:06:00</t>
+          <t>1:03:35</t>
         </is>
       </c>
     </row>
@@ -17724,16 +17724,16 @@
         </is>
       </c>
       <c r="C690" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D690" s="7" t="inlineStr">
         <is>
-          <t>0:58:24</t>
+          <t>0:59:43</t>
         </is>
       </c>
       <c r="E690" s="7" t="inlineStr">
         <is>
-          <t>1:08:10</t>
+          <t>1:06:00</t>
         </is>
       </c>
     </row>
@@ -17749,23 +17749,23 @@
         </is>
       </c>
       <c r="C691" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D691" s="5" t="inlineStr">
         <is>
-          <t>0:58:54</t>
+          <t>0:58:24</t>
         </is>
       </c>
       <c r="E691" s="5" t="inlineStr">
         <is>
-          <t>1:05:27</t>
+          <t>1:08:10</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" s="6" t="inlineStr">
         <is>
-          <t>GetPro Bath Half</t>
+          <t>Generali Prague Half Marathon</t>
         </is>
       </c>
       <c r="B692" s="7" t="inlineStr">
@@ -17778,12 +17778,12 @@
       </c>
       <c r="D692" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:54</t>
         </is>
       </c>
       <c r="E692" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:27</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
         </is>
       </c>
       <c r="C693" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D693" s="5" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
     <row r="694">
       <c r="A694" s="6" t="inlineStr">
         <is>
-          <t>Göteborgsvarvet</t>
+          <t>GetPro Bath Half</t>
         </is>
       </c>
       <c r="B694" s="7" t="inlineStr">
@@ -17824,16 +17824,16 @@
         </is>
       </c>
       <c r="C694" s="7" t="n">
-        <v>2000</v>
+        <v>2026</v>
       </c>
       <c r="D694" s="7" t="inlineStr">
         <is>
-          <t>1:02:42</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E694" s="7" t="inlineStr">
         <is>
-          <t>1:09:28</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -17849,16 +17849,16 @@
         </is>
       </c>
       <c r="C695" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D695" s="5" t="inlineStr">
         <is>
-          <t>1:03:00</t>
+          <t>1:02:42</t>
         </is>
       </c>
       <c r="E695" s="5" t="inlineStr">
         <is>
-          <t>1:11:07</t>
+          <t>1:09:28</t>
         </is>
       </c>
     </row>
@@ -17874,16 +17874,16 @@
         </is>
       </c>
       <c r="C696" s="7" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D696" s="7" t="inlineStr">
         <is>
-          <t>1:03:35</t>
+          <t>1:03:00</t>
         </is>
       </c>
       <c r="E696" s="7" t="inlineStr">
         <is>
-          <t>1:13:03</t>
+          <t>1:11:07</t>
         </is>
       </c>
     </row>
@@ -17899,16 +17899,16 @@
         </is>
       </c>
       <c r="C697" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D697" s="5" t="inlineStr">
         <is>
-          <t>1:03:43</t>
+          <t>1:03:35</t>
         </is>
       </c>
       <c r="E697" s="5" t="inlineStr">
         <is>
-          <t>1:13:27</t>
+          <t>1:13:03</t>
         </is>
       </c>
     </row>
@@ -17924,16 +17924,16 @@
         </is>
       </c>
       <c r="C698" s="7" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D698" s="7" t="inlineStr">
         <is>
-          <t>1:04:03</t>
+          <t>1:03:43</t>
         </is>
       </c>
       <c r="E698" s="7" t="inlineStr">
         <is>
-          <t>1:18:06</t>
+          <t>1:13:27</t>
         </is>
       </c>
     </row>
@@ -17949,16 +17949,16 @@
         </is>
       </c>
       <c r="C699" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D699" s="5" t="inlineStr">
         <is>
-          <t>1:03:19</t>
+          <t>1:04:03</t>
         </is>
       </c>
       <c r="E699" s="5" t="inlineStr">
         <is>
-          <t>1:12:34</t>
+          <t>1:18:06</t>
         </is>
       </c>
     </row>
@@ -17974,11 +17974,11 @@
         </is>
       </c>
       <c r="C700" s="7" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D700" s="7" t="inlineStr">
         <is>
-          <t>1:02:14</t>
+          <t>1:03:19</t>
         </is>
       </c>
       <c r="E700" s="7" t="inlineStr">
@@ -17999,16 +17999,16 @@
         </is>
       </c>
       <c r="C701" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D701" s="5" t="inlineStr">
         <is>
-          <t>1:04:03</t>
+          <t>1:02:14</t>
         </is>
       </c>
       <c r="E701" s="5" t="inlineStr">
         <is>
-          <t>1:12:38</t>
+          <t>1:12:34</t>
         </is>
       </c>
     </row>
@@ -18024,16 +18024,16 @@
         </is>
       </c>
       <c r="C702" s="7" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D702" s="7" t="inlineStr">
         <is>
-          <t>1:01:21</t>
+          <t>1:04:03</t>
         </is>
       </c>
       <c r="E702" s="7" t="inlineStr">
         <is>
-          <t>1:10:19</t>
+          <t>1:12:38</t>
         </is>
       </c>
     </row>
@@ -18049,16 +18049,16 @@
         </is>
       </c>
       <c r="C703" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D703" s="5" t="inlineStr">
         <is>
-          <t>1:01:55</t>
+          <t>1:01:21</t>
         </is>
       </c>
       <c r="E703" s="5" t="inlineStr">
         <is>
-          <t>1:11:27</t>
+          <t>1:10:19</t>
         </is>
       </c>
     </row>
@@ -18074,16 +18074,16 @@
         </is>
       </c>
       <c r="C704" s="7" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D704" s="7" t="inlineStr">
         <is>
-          <t>1:01:10</t>
+          <t>1:01:55</t>
         </is>
       </c>
       <c r="E704" s="7" t="inlineStr">
         <is>
-          <t>1:11:40</t>
+          <t>1:11:27</t>
         </is>
       </c>
     </row>
@@ -18099,16 +18099,16 @@
         </is>
       </c>
       <c r="C705" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D705" s="5" t="inlineStr">
         <is>
-          <t>1:00:52</t>
+          <t>1:01:10</t>
         </is>
       </c>
       <c r="E705" s="5" t="inlineStr">
         <is>
-          <t>1:09:04</t>
+          <t>1:11:40</t>
         </is>
       </c>
     </row>
@@ -18124,16 +18124,16 @@
         </is>
       </c>
       <c r="C706" s="7" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D706" s="7" t="inlineStr">
         <is>
-          <t>1:00:25</t>
+          <t>1:00:52</t>
         </is>
       </c>
       <c r="E706" s="7" t="inlineStr">
         <is>
-          <t>1:09:27</t>
+          <t>1:09:04</t>
         </is>
       </c>
     </row>
@@ -18149,16 +18149,16 @@
         </is>
       </c>
       <c r="C707" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D707" s="5" t="inlineStr">
         <is>
-          <t>1:03:13</t>
+          <t>1:00:25</t>
         </is>
       </c>
       <c r="E707" s="5" t="inlineStr">
         <is>
-          <t>1:11:29</t>
+          <t>1:09:27</t>
         </is>
       </c>
     </row>
@@ -18174,16 +18174,16 @@
         </is>
       </c>
       <c r="C708" s="7" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D708" s="7" t="inlineStr">
         <is>
-          <t>1:00:36</t>
+          <t>1:03:13</t>
         </is>
       </c>
       <c r="E708" s="7" t="inlineStr">
         <is>
-          <t>1:10:12</t>
+          <t>1:11:29</t>
         </is>
       </c>
     </row>
@@ -18199,16 +18199,16 @@
         </is>
       </c>
       <c r="C709" s="5" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="D709" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:36</t>
         </is>
       </c>
       <c r="E709" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:12</t>
         </is>
       </c>
     </row>
@@ -18224,7 +18224,7 @@
         </is>
       </c>
       <c r="C710" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D710" s="7" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
     <row r="711">
       <c r="A711" s="4" t="inlineStr">
         <is>
-          <t>HOKA Semi de Paris</t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="B711" s="5" t="inlineStr">
@@ -18249,16 +18249,16 @@
         </is>
       </c>
       <c r="C711" s="5" t="n">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="D711" s="5" t="inlineStr">
         <is>
-          <t>1:01:33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E711" s="5" t="inlineStr">
         <is>
-          <t>1:11:07</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -18274,16 +18274,16 @@
         </is>
       </c>
       <c r="C712" s="7" t="n">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="D712" s="7" t="inlineStr">
         <is>
-          <t>0:59:44</t>
+          <t>1:01:33</t>
         </is>
       </c>
       <c r="E712" s="7" t="inlineStr">
         <is>
-          <t>1:07:55</t>
+          <t>1:11:07</t>
         </is>
       </c>
     </row>
@@ -18299,16 +18299,16 @@
         </is>
       </c>
       <c r="C713" s="5" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="D713" s="5" t="inlineStr">
         <is>
-          <t>1:00:08</t>
+          <t>0:59:44</t>
         </is>
       </c>
       <c r="E713" s="5" t="inlineStr">
         <is>
-          <t>1:09:23</t>
+          <t>1:07:55</t>
         </is>
       </c>
     </row>
@@ -18324,16 +18324,16 @@
         </is>
       </c>
       <c r="C714" s="7" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D714" s="7" t="inlineStr">
         <is>
-          <t>0:59:38</t>
+          <t>1:00:08</t>
         </is>
       </c>
       <c r="E714" s="7" t="inlineStr">
         <is>
-          <t>1:06:01</t>
+          <t>1:09:23</t>
         </is>
       </c>
     </row>
@@ -18349,16 +18349,16 @@
         </is>
       </c>
       <c r="C715" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D715" s="5" t="inlineStr">
         <is>
-          <t>1:00:45</t>
+          <t>0:59:38</t>
         </is>
       </c>
       <c r="E715" s="5" t="inlineStr">
         <is>
-          <t>1:06:58</t>
+          <t>1:06:01</t>
         </is>
       </c>
     </row>
@@ -18374,16 +18374,16 @@
         </is>
       </c>
       <c r="C716" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D716" s="7" t="inlineStr">
         <is>
-          <t>1:00:16</t>
+          <t>1:00:45</t>
         </is>
       </c>
       <c r="E716" s="7" t="inlineStr">
         <is>
-          <t>1:07:14</t>
+          <t>1:06:58</t>
         </is>
       </c>
     </row>
@@ -18399,23 +18399,23 @@
         </is>
       </c>
       <c r="C717" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D717" s="5" t="inlineStr">
         <is>
-          <t>1:00:11</t>
+          <t>1:00:16</t>
         </is>
       </c>
       <c r="E717" s="5" t="inlineStr">
         <is>
-          <t>1:05:12</t>
+          <t>1:07:14</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" s="6" t="inlineStr">
         <is>
-          <t>Half Marathon Munchen by Brooks</t>
+          <t>HOKA Semi de Paris</t>
         </is>
       </c>
       <c r="B718" s="7" t="inlineStr">
@@ -18424,23 +18424,23 @@
         </is>
       </c>
       <c r="C718" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D718" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:11</t>
         </is>
       </c>
       <c r="E718" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:12</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" s="4" t="inlineStr">
         <is>
-          <t>Hoka Runaway Sydney Half Marathon</t>
+          <t>Half Marathon Munchen by Brooks</t>
         </is>
       </c>
       <c r="B719" s="5" t="inlineStr">
@@ -18465,7 +18465,7 @@
     <row r="720">
       <c r="A720" s="6" t="inlineStr">
         <is>
-          <t>Hyundai Meia Maratona</t>
+          <t>Hoka Runaway Sydney Half Marathon</t>
         </is>
       </c>
       <c r="B720" s="7" t="inlineStr">
@@ -18474,7 +18474,7 @@
         </is>
       </c>
       <c r="C720" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D720" s="7" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         </is>
       </c>
       <c r="C721" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D721" s="5" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         </is>
       </c>
       <c r="C722" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D722" s="7" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
     <row r="723">
       <c r="A723" s="4" t="inlineStr">
         <is>
-          <t>IU Health 500 Festival Mini-Marathon</t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="B723" s="5" t="inlineStr">
@@ -18565,7 +18565,7 @@
     <row r="724">
       <c r="A724" s="6" t="inlineStr">
         <is>
-          <t>Kagawa Marugame International Half Marathon</t>
+          <t>IU Health 500 Festival Mini-Marathon</t>
         </is>
       </c>
       <c r="B724" s="7" t="inlineStr">
@@ -18574,7 +18574,7 @@
         </is>
       </c>
       <c r="C724" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D724" s="7" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
     <row r="725">
       <c r="A725" s="4" t="inlineStr">
         <is>
-          <t>Life Time Chicago Half Marathon &amp; 5K</t>
+          <t>Kagawa Marugame International Half Marathon</t>
         </is>
       </c>
       <c r="B725" s="5" t="inlineStr">
@@ -18599,7 +18599,7 @@
         </is>
       </c>
       <c r="C725" s="5" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D725" s="5" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         </is>
       </c>
       <c r="C726" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D726" s="7" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
     <row r="727">
       <c r="A727" s="4" t="inlineStr">
         <is>
-          <t>London Landmarks Half Marathon</t>
+          <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
       <c r="B727" s="5" t="inlineStr">
@@ -18649,7 +18649,7 @@
         </is>
       </c>
       <c r="C727" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D727" s="5" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         </is>
       </c>
       <c r="C728" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D728" s="7" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
     <row r="729">
       <c r="A729" s="4" t="inlineStr">
         <is>
-          <t>Manchester Half Marathon</t>
+          <t>London Landmarks Half Marathon</t>
         </is>
       </c>
       <c r="B729" s="5" t="inlineStr">
@@ -18715,7 +18715,7 @@
     <row r="730">
       <c r="A730" s="6" t="inlineStr">
         <is>
-          <t>Media Maraton de Bogota</t>
+          <t>Manchester Half Marathon</t>
         </is>
       </c>
       <c r="B730" s="7" t="inlineStr">
@@ -18740,7 +18740,7 @@
     <row r="731">
       <c r="A731" s="4" t="inlineStr">
         <is>
-          <t>Medio Maraton de Sevilla</t>
+          <t>Media Maraton de Bogota</t>
         </is>
       </c>
       <c r="B731" s="5" t="inlineStr">
@@ -18749,16 +18749,16 @@
         </is>
       </c>
       <c r="C731" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D731" s="5" t="inlineStr">
         <is>
-          <t>0:59:21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E731" s="5" t="inlineStr">
         <is>
-          <t>1:07:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -18774,16 +18774,16 @@
         </is>
       </c>
       <c r="C732" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D732" s="7" t="inlineStr">
         <is>
-          <t>0:59:33</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E732" s="7" t="inlineStr">
         <is>
-          <t>1:07:18</t>
+          <t>1:07:59</t>
         </is>
       </c>
     </row>
@@ -18799,23 +18799,23 @@
         </is>
       </c>
       <c r="C733" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D733" s="5" t="inlineStr">
         <is>
-          <t>1:00:24</t>
+          <t>0:59:33</t>
         </is>
       </c>
       <c r="E733" s="5" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>1:07:18</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" s="6" t="inlineStr">
         <is>
-          <t>Mitja Marato Barcelona by Brooks</t>
+          <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
       <c r="B734" s="7" t="inlineStr">
@@ -18824,16 +18824,16 @@
         </is>
       </c>
       <c r="C734" s="7" t="n">
-        <v>2005</v>
+        <v>2026</v>
       </c>
       <c r="D734" s="7" t="inlineStr">
         <is>
-          <t>1:03:29</t>
+          <t>1:00:24</t>
         </is>
       </c>
       <c r="E734" s="7" t="inlineStr">
         <is>
-          <t>1:09:34</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
@@ -18849,16 +18849,16 @@
         </is>
       </c>
       <c r="C735" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D735" s="5" t="inlineStr">
         <is>
-          <t>1:02:25</t>
+          <t>1:03:29</t>
         </is>
       </c>
       <c r="E735" s="5" t="inlineStr">
         <is>
-          <t>1:09:26</t>
+          <t>1:09:34</t>
         </is>
       </c>
     </row>
@@ -18874,16 +18874,16 @@
         </is>
       </c>
       <c r="C736" s="7" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D736" s="7" t="inlineStr">
         <is>
-          <t>1:03:02</t>
+          <t>1:02:25</t>
         </is>
       </c>
       <c r="E736" s="7" t="inlineStr">
         <is>
-          <t>1:09:05</t>
+          <t>1:09:26</t>
         </is>
       </c>
     </row>
@@ -18899,16 +18899,16 @@
         </is>
       </c>
       <c r="C737" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D737" s="5" t="inlineStr">
         <is>
-          <t>1:02:39</t>
+          <t>1:03:02</t>
         </is>
       </c>
       <c r="E737" s="5" t="inlineStr">
         <is>
-          <t>1:09:15</t>
+          <t>1:09:05</t>
         </is>
       </c>
     </row>
@@ -18924,16 +18924,16 @@
         </is>
       </c>
       <c r="C738" s="7" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D738" s="7" t="inlineStr">
         <is>
-          <t>1:01:45</t>
+          <t>1:02:39</t>
         </is>
       </c>
       <c r="E738" s="7" t="inlineStr">
         <is>
-          <t>1:09:34</t>
+          <t>1:09:15</t>
         </is>
       </c>
     </row>
@@ -18949,16 +18949,16 @@
         </is>
       </c>
       <c r="C739" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D739" s="5" t="inlineStr">
         <is>
-          <t>1:03:00</t>
+          <t>1:01:45</t>
         </is>
       </c>
       <c r="E739" s="5" t="inlineStr">
         <is>
-          <t>1:08:52</t>
+          <t>1:09:34</t>
         </is>
       </c>
     </row>
@@ -18974,16 +18974,16 @@
         </is>
       </c>
       <c r="C740" s="7" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D740" s="7" t="inlineStr">
         <is>
-          <t>1:03:06</t>
+          <t>1:03:00</t>
         </is>
       </c>
       <c r="E740" s="7" t="inlineStr">
         <is>
-          <t>1:08:13</t>
+          <t>1:08:52</t>
         </is>
       </c>
     </row>
@@ -18999,16 +18999,16 @@
         </is>
       </c>
       <c r="C741" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D741" s="5" t="inlineStr">
         <is>
-          <t>1:02:54</t>
+          <t>1:03:06</t>
         </is>
       </c>
       <c r="E741" s="5" t="inlineStr">
         <is>
-          <t>1:10:51</t>
+          <t>1:08:13</t>
         </is>
       </c>
     </row>
@@ -19024,16 +19024,16 @@
         </is>
       </c>
       <c r="C742" s="7" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D742" s="7" t="inlineStr">
         <is>
-          <t>1:01:44</t>
+          <t>1:02:54</t>
         </is>
       </c>
       <c r="E742" s="7" t="inlineStr">
         <is>
-          <t>1:08:28</t>
+          <t>1:10:51</t>
         </is>
       </c>
     </row>
@@ -19049,16 +19049,16 @@
         </is>
       </c>
       <c r="C743" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D743" s="5" t="inlineStr">
         <is>
-          <t>1:02:55</t>
+          <t>1:01:44</t>
         </is>
       </c>
       <c r="E743" s="5" t="inlineStr">
         <is>
-          <t>1:08:35</t>
+          <t>1:08:28</t>
         </is>
       </c>
     </row>
@@ -19074,16 +19074,16 @@
         </is>
       </c>
       <c r="C744" s="7" t="n">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="D744" s="7" t="inlineStr">
         <is>
-          <t>0:58:53</t>
+          <t>1:02:55</t>
         </is>
       </c>
       <c r="E744" s="7" t="inlineStr">
         <is>
-          <t>1:04:37</t>
+          <t>1:08:35</t>
         </is>
       </c>
     </row>
@@ -19099,16 +19099,16 @@
         </is>
       </c>
       <c r="C745" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D745" s="5" t="inlineStr">
         <is>
-          <t>0:59:21</t>
+          <t>0:58:53</t>
         </is>
       </c>
       <c r="E745" s="5" t="inlineStr">
         <is>
-          <t>1:04:28</t>
+          <t>1:04:37</t>
         </is>
       </c>
     </row>
@@ -19124,16 +19124,16 @@
         </is>
       </c>
       <c r="C746" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D746" s="7" t="inlineStr">
         <is>
-          <t>0:56:42</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E746" s="7" t="inlineStr">
         <is>
-          <t>1:04:11</t>
+          <t>1:04:28</t>
         </is>
       </c>
     </row>
@@ -19149,23 +19149,23 @@
         </is>
       </c>
       <c r="C747" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D747" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:56:42</t>
         </is>
       </c>
       <c r="E747" s="5" t="inlineStr">
         <is>
-          <t>1:04:00</t>
+          <t>1:04:11</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" s="6" t="inlineStr">
         <is>
-          <t>Movistar Madrid Medio Maraton</t>
+          <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
       <c r="B748" s="7" t="inlineStr">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="C748" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D748" s="7" t="inlineStr">
         <is>
@@ -19183,14 +19183,14 @@
       </c>
       <c r="E748" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:00</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" s="4" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - Half Marathon</t>
+          <t>Movistar Madrid Medio Maraton</t>
         </is>
       </c>
       <c r="B749" s="5" t="inlineStr">
@@ -19228,12 +19228,12 @@
       </c>
       <c r="D750" s="7" t="inlineStr">
         <is>
-          <t>0:59:36</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E750" s="7" t="inlineStr">
         <is>
-          <t>1:08:16</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19249,16 +19249,16 @@
         </is>
       </c>
       <c r="C751" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D751" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:36</t>
         </is>
       </c>
       <c r="E751" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:08:16</t>
         </is>
       </c>
     </row>
@@ -19278,19 +19278,19 @@
       </c>
       <c r="D752" s="7" t="inlineStr">
         <is>
-          <t>0:59:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E752" s="7" t="inlineStr">
         <is>
-          <t>1:07:34</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" s="4" t="inlineStr">
         <is>
-          <t>NYCRUNS Brooklyn Experience Half Marathon</t>
+          <t>NN CPC Loop Den Haag - Half Marathon</t>
         </is>
       </c>
       <c r="B753" s="5" t="inlineStr">
@@ -19299,23 +19299,23 @@
         </is>
       </c>
       <c r="C753" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D753" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:48</t>
         </is>
       </c>
       <c r="E753" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:34</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" s="6" t="inlineStr">
         <is>
-          <t>NYRR RBC Brooklyn Half</t>
+          <t>NYCRUNS Brooklyn Experience Half Marathon</t>
         </is>
       </c>
       <c r="B754" s="7" t="inlineStr">
@@ -19340,7 +19340,7 @@
     <row r="755">
       <c r="A755" s="4" t="inlineStr">
         <is>
-          <t>Nike Melbourne Marathon Festival</t>
+          <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
       <c r="B755" s="5" t="inlineStr">
@@ -19365,7 +19365,7 @@
     <row r="756">
       <c r="A756" s="6" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>Nike Melbourne Marathon Festival</t>
         </is>
       </c>
       <c r="B756" s="7" t="inlineStr">
@@ -19374,7 +19374,7 @@
         </is>
       </c>
       <c r="C756" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D756" s="7" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         </is>
       </c>
       <c r="C757" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D757" s="5" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         </is>
       </c>
       <c r="C758" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D758" s="7" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         </is>
       </c>
       <c r="C759" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D759" s="5" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
     <row r="760">
       <c r="A760" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B760" s="7" t="inlineStr">
@@ -19474,7 +19474,7 @@
         </is>
       </c>
       <c r="C760" s="7" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D760" s="7" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         </is>
       </c>
       <c r="C761" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D761" s="5" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         </is>
       </c>
       <c r="C762" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D762" s="7" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         </is>
       </c>
       <c r="C763" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D763" s="5" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
     <row r="764">
       <c r="A764" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Mexico City</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B764" s="7" t="inlineStr">
@@ -19574,7 +19574,7 @@
         </is>
       </c>
       <c r="C764" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D764" s="7" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
     <row r="765">
       <c r="A765" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series San Diego</t>
+          <t>Rock 'n' Roll Running Series Mexico City</t>
         </is>
       </c>
       <c r="B765" s="5" t="inlineStr">
@@ -19615,7 +19615,7 @@
     <row r="766">
       <c r="A766" s="6" t="inlineStr">
         <is>
-          <t>Royal Parks Half Marathon</t>
+          <t>Rock 'n' Roll Running Series San Diego</t>
         </is>
       </c>
       <c r="B766" s="7" t="inlineStr">
@@ -19640,7 +19640,7 @@
     <row r="767">
       <c r="A767" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Royal Parks Half Marathon</t>
         </is>
       </c>
       <c r="B767" s="5" t="inlineStr">
@@ -19649,7 +19649,7 @@
         </is>
       </c>
       <c r="C767" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D767" s="5" t="inlineStr">
         <is>
@@ -19674,16 +19674,16 @@
         </is>
       </c>
       <c r="C768" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D768" s="7" t="inlineStr">
         <is>
-          <t>1:05:44</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E768" s="7" t="inlineStr">
         <is>
-          <t>1:18:34</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19699,23 +19699,23 @@
         </is>
       </c>
       <c r="C769" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D769" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:44</t>
         </is>
       </c>
       <c r="E769" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:18:34</t>
         </is>
       </c>
     </row>
     <row r="770">
       <c r="A770" s="6" t="inlineStr">
         <is>
-          <t>Semi-Marathon de Boulogne-Billancourt</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B770" s="7" t="inlineStr">
@@ -19740,7 +19740,7 @@
     <row r="771">
       <c r="A771" s="4" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
+          <t>Semi-Marathon de Boulogne-Billancourt</t>
         </is>
       </c>
       <c r="B771" s="5" t="inlineStr">
@@ -19765,7 +19765,7 @@
     <row r="772">
       <c r="A772" s="6" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Series Nashville</t>
+          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
         </is>
       </c>
       <c r="B772" s="7" t="inlineStr">
@@ -19790,7 +19790,7 @@
     <row r="773">
       <c r="A773" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>St. Jude Rock 'n' Roll Series Nashville</t>
         </is>
       </c>
       <c r="B773" s="5" t="inlineStr">
@@ -19799,16 +19799,16 @@
         </is>
       </c>
       <c r="C773" s="5" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D773" s="5" t="inlineStr">
         <is>
-          <t>1:01:13</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E773" s="5" t="inlineStr">
         <is>
-          <t>1:09:28</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19824,16 +19824,16 @@
         </is>
       </c>
       <c r="C774" s="7" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D774" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:13</t>
         </is>
       </c>
       <c r="E774" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:09:28</t>
         </is>
       </c>
     </row>
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="C775" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D775" s="5" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
     <row r="776">
       <c r="A776" s="6" t="inlineStr">
         <is>
-          <t>Standard Chartered KL Half Marathon</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B776" s="7" t="inlineStr">
@@ -19874,23 +19874,23 @@
         </is>
       </c>
       <c r="C776" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D776" s="7" t="inlineStr">
         <is>
-          <t>1:11:08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E776" s="7" t="inlineStr">
         <is>
-          <t>1:23:55</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Singapore Half Marathon</t>
+          <t>Standard Chartered KL Half Marathon</t>
         </is>
       </c>
       <c r="B777" s="5" t="inlineStr">
@@ -19903,19 +19903,19 @@
       </c>
       <c r="D777" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:11:08</t>
         </is>
       </c>
       <c r="E777" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:23:55</t>
         </is>
       </c>
     </row>
     <row r="778">
       <c r="A778" s="6" t="inlineStr">
         <is>
-          <t>TCS Mizuno Half Marathon</t>
+          <t>Standard Chartered Singapore Half Marathon</t>
         </is>
       </c>
       <c r="B778" s="7" t="inlineStr">
@@ -19924,16 +19924,16 @@
         </is>
       </c>
       <c r="C778" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D778" s="7" t="inlineStr">
         <is>
-          <t>1:05:23</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E778" s="7" t="inlineStr">
         <is>
-          <t>1:13:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -19949,16 +19949,16 @@
         </is>
       </c>
       <c r="C779" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D779" s="5" t="inlineStr">
         <is>
-          <t>1:06:28</t>
+          <t>1:05:23</t>
         </is>
       </c>
       <c r="E779" s="5" t="inlineStr">
         <is>
-          <t>1:17:54</t>
+          <t>1:13:59</t>
         </is>
       </c>
     </row>
@@ -19974,16 +19974,16 @@
         </is>
       </c>
       <c r="C780" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D780" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:28</t>
         </is>
       </c>
       <c r="E780" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:17:54</t>
         </is>
       </c>
     </row>
@@ -20003,19 +20003,19 @@
       </c>
       <c r="D781" s="5" t="inlineStr">
         <is>
-          <t>1:04:21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E781" s="5" t="inlineStr">
         <is>
-          <t>1:10:02</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" s="6" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
       <c r="B782" s="7" t="inlineStr">
@@ -20024,16 +20024,16 @@
         </is>
       </c>
       <c r="C782" s="7" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D782" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:21</t>
         </is>
       </c>
       <c r="E782" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:02</t>
         </is>
       </c>
     </row>
@@ -20049,7 +20049,7 @@
         </is>
       </c>
       <c r="C783" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D783" s="5" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         </is>
       </c>
       <c r="C784" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D784" s="7" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
     <row r="785">
       <c r="A785" s="4" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B785" s="5" t="inlineStr">
@@ -20099,7 +20099,7 @@
         </is>
       </c>
       <c r="C785" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D785" s="5" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         </is>
       </c>
       <c r="C786" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D786" s="7" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         </is>
       </c>
       <c r="C787" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D787" s="5" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
     <row r="788">
       <c r="A788" s="6" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon (Half)</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B788" s="7" t="inlineStr">
@@ -20199,7 +20199,7 @@
         </is>
       </c>
       <c r="C789" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D789" s="5" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
     <row r="790">
       <c r="A790" s="6" t="inlineStr">
         <is>
-          <t>The Big Half</t>
+          <t>Tata Mumbai Marathon (Half)</t>
         </is>
       </c>
       <c r="B790" s="7" t="inlineStr">
@@ -20224,7 +20224,7 @@
         </is>
       </c>
       <c r="C790" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D790" s="7" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
     <row r="791">
       <c r="A791" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Legacy Half Marathon</t>
+          <t>The Big Half</t>
         </is>
       </c>
       <c r="B791" s="5" t="inlineStr">
@@ -20265,7 +20265,7 @@
     <row r="792">
       <c r="A792" s="6" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>Tokyo Legacy Half Marathon</t>
         </is>
       </c>
       <c r="B792" s="7" t="inlineStr">
@@ -20274,16 +20274,16 @@
         </is>
       </c>
       <c r="C792" s="7" t="n">
-        <v>2006</v>
+        <v>2025</v>
       </c>
       <c r="D792" s="7" t="inlineStr">
         <is>
-          <t>1:01:22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E792" s="7" t="inlineStr">
         <is>
-          <t>1:09:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20299,16 +20299,16 @@
         </is>
       </c>
       <c r="C793" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D793" s="5" t="inlineStr">
         <is>
-          <t>0:59:24</t>
+          <t>1:01:22</t>
         </is>
       </c>
       <c r="E793" s="5" t="inlineStr">
         <is>
-          <t>1:10:32</t>
+          <t>1:09:43</t>
         </is>
       </c>
     </row>
@@ -20324,16 +20324,16 @@
         </is>
       </c>
       <c r="C794" s="7" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D794" s="7" t="inlineStr">
         <is>
-          <t>1:00:58</t>
+          <t>0:59:24</t>
         </is>
       </c>
       <c r="E794" s="7" t="inlineStr">
         <is>
-          <t>1:10:19</t>
+          <t>1:10:32</t>
         </is>
       </c>
     </row>
@@ -20349,16 +20349,16 @@
         </is>
       </c>
       <c r="C795" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D795" s="5" t="inlineStr">
         <is>
-          <t>1:01:06</t>
+          <t>1:00:58</t>
         </is>
       </c>
       <c r="E795" s="5" t="inlineStr">
         <is>
-          <t>1:09:32</t>
+          <t>1:10:19</t>
         </is>
       </c>
     </row>
@@ -20374,16 +20374,16 @@
         </is>
       </c>
       <c r="C796" s="7" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D796" s="7" t="inlineStr">
         <is>
-          <t>0:59:52</t>
+          <t>1:01:06</t>
         </is>
       </c>
       <c r="E796" s="7" t="inlineStr">
         <is>
-          <t>1:09:25</t>
+          <t>1:09:32</t>
         </is>
       </c>
     </row>
@@ -20399,16 +20399,16 @@
         </is>
       </c>
       <c r="C797" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D797" s="5" t="inlineStr">
         <is>
-          <t>1:00:23</t>
+          <t>0:59:52</t>
         </is>
       </c>
       <c r="E797" s="5" t="inlineStr">
         <is>
-          <t>1:08:52</t>
+          <t>1:09:25</t>
         </is>
       </c>
     </row>
@@ -20424,16 +20424,16 @@
         </is>
       </c>
       <c r="C798" s="7" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D798" s="7" t="inlineStr">
         <is>
-          <t>0:59:39</t>
+          <t>1:00:23</t>
         </is>
       </c>
       <c r="E798" s="7" t="inlineStr">
         <is>
-          <t>1:08:35</t>
+          <t>1:08:52</t>
         </is>
       </c>
     </row>
@@ -20449,16 +20449,16 @@
         </is>
       </c>
       <c r="C799" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D799" s="5" t="inlineStr">
         <is>
-          <t>1:01:02</t>
+          <t>0:59:39</t>
         </is>
       </c>
       <c r="E799" s="5" t="inlineStr">
         <is>
-          <t>1:09:09</t>
+          <t>1:08:35</t>
         </is>
       </c>
     </row>
@@ -20474,16 +20474,16 @@
         </is>
       </c>
       <c r="C800" s="7" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D800" s="7" t="inlineStr">
         <is>
-          <t>1:00:50</t>
+          <t>1:01:02</t>
         </is>
       </c>
       <c r="E800" s="7" t="inlineStr">
         <is>
-          <t>1:08:31</t>
+          <t>1:09:09</t>
         </is>
       </c>
     </row>
@@ -20499,16 +20499,16 @@
         </is>
       </c>
       <c r="C801" s="5" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D801" s="5" t="inlineStr">
         <is>
-          <t>1:01:31</t>
+          <t>1:00:50</t>
         </is>
       </c>
       <c r="E801" s="5" t="inlineStr">
         <is>
-          <t>1:07:04</t>
+          <t>1:08:31</t>
         </is>
       </c>
     </row>
@@ -20524,23 +20524,23 @@
         </is>
       </c>
       <c r="C802" s="7" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D802" s="7" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>1:01:31</t>
         </is>
       </c>
       <c r="E802" s="7" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>1:07:04</t>
         </is>
       </c>
     </row>
     <row r="803">
       <c r="A803" s="4" t="inlineStr">
         <is>
-          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B803" s="5" t="inlineStr">
@@ -20549,23 +20549,23 @@
         </is>
       </c>
       <c r="C803" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D803" s="5" t="inlineStr">
         <is>
-          <t>0:58:02</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E803" s="5" t="inlineStr">
         <is>
-          <t>1:03:08</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
     <row r="804">
       <c r="A804" s="6" t="inlineStr">
         <is>
-          <t>Vedanta Delhi Half Marathon</t>
+          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B804" s="7" t="inlineStr">
@@ -20578,19 +20578,19 @@
       </c>
       <c r="D804" s="7" t="inlineStr">
         <is>
-          <t>0:59:50</t>
+          <t>0:58:02</t>
         </is>
       </c>
       <c r="E804" s="7" t="inlineStr">
         <is>
-          <t>1:07:20</t>
+          <t>1:03:08</t>
         </is>
       </c>
     </row>
     <row r="805">
       <c r="A805" s="4" t="inlineStr">
         <is>
-          <t>Vienna City Half Marathon</t>
+          <t>Vedanta Delhi Half Marathon</t>
         </is>
       </c>
       <c r="B805" s="5" t="inlineStr">
@@ -20603,19 +20603,19 @@
       </c>
       <c r="D805" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:50</t>
         </is>
       </c>
       <c r="E805" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:20</t>
         </is>
       </c>
     </row>
     <row r="806">
       <c r="A806" s="6" t="inlineStr">
         <is>
-          <t>Walt Disney World Marathon Weekend</t>
+          <t>Vienna City Half Marathon</t>
         </is>
       </c>
       <c r="B806" s="7" t="inlineStr">
@@ -20649,7 +20649,7 @@
         </is>
       </c>
       <c r="C807" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D807" s="5" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
     <row r="808">
       <c r="A808" s="6" t="inlineStr">
         <is>
-          <t>Warsaw Half Marathon</t>
+          <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
       <c r="B808" s="7" t="inlineStr">
@@ -20674,7 +20674,7 @@
         </is>
       </c>
       <c r="C808" s="7" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D808" s="7" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="C809" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D809" s="5" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
     <row r="810">
       <c r="A810" s="6" t="inlineStr">
         <is>
-          <t>Wizz Air Rome Half Marathon by Brooks</t>
+          <t>Warsaw Half Marathon</t>
         </is>
       </c>
       <c r="B810" s="7" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="811">
       <c r="A811" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Wizz Air Rome Half Marathon by Brooks</t>
         </is>
       </c>
       <c r="B811" s="5" t="inlineStr">
@@ -20749,7 +20749,7 @@
         </is>
       </c>
       <c r="C811" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D811" s="5" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         </is>
       </c>
       <c r="C812" s="7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D812" s="7" t="inlineStr">
         <is>
@@ -20799,39 +20799,39 @@
         </is>
       </c>
       <c r="C813" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D813" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E813" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="6" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+        </is>
+      </c>
+      <c r="B814" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C814" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="D813" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E813" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="814">
-      <c r="A814" s="8" t="inlineStr">
-        <is>
-          <t>10K Montmartre</t>
-        </is>
-      </c>
-      <c r="B814" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C814" s="9" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D814" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E814" s="9" t="inlineStr">
+      <c r="D814" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E814" s="7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -20840,7 +20840,7 @@
     <row r="815">
       <c r="A815" s="4" t="inlineStr">
         <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
+          <t>10K Montmartre</t>
         </is>
       </c>
       <c r="B815" s="5" t="inlineStr">
@@ -20849,7 +20849,7 @@
         </is>
       </c>
       <c r="C815" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D815" s="5" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="E815" s="5" t="inlineStr">
         <is>
-          <t>0:29:19</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20874,7 +20874,7 @@
         </is>
       </c>
       <c r="C816" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D816" s="9" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="E816" s="9" t="inlineStr">
         <is>
-          <t>0:28:45</t>
+          <t>0:29:19</t>
         </is>
       </c>
     </row>
@@ -20899,7 +20899,7 @@
         </is>
       </c>
       <c r="C817" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D817" s="5" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="E817" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:45</t>
         </is>
       </c>
     </row>
@@ -20924,23 +20924,23 @@
         </is>
       </c>
       <c r="C818" s="9" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D818" s="9" t="inlineStr">
         <is>
-          <t>0:26:45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E818" s="9" t="inlineStr">
         <is>
-          <t>0:29:25</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="819">
       <c r="A819" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Birmingham Run 10K</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B819" s="5" t="inlineStr">
@@ -20949,23 +20949,23 @@
         </is>
       </c>
       <c r="C819" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D819" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:26:45</t>
         </is>
       </c>
       <c r="E819" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:25</t>
         </is>
       </c>
     </row>
     <row r="820">
       <c r="A820" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Bristol Run 10K</t>
+          <t>AJ Bell Great Birmingham Run 10K</t>
         </is>
       </c>
       <c r="B820" s="9" t="inlineStr">
@@ -20990,7 +20990,7 @@
     <row r="821">
       <c r="A821" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run</t>
+          <t>AJ Bell Great Bristol Run 10K</t>
         </is>
       </c>
       <c r="B821" s="5" t="inlineStr">
@@ -20999,16 +20999,16 @@
         </is>
       </c>
       <c r="C821" s="5" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D821" s="5" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E821" s="5" t="inlineStr">
         <is>
-          <t>0:30:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21024,23 +21024,23 @@
         </is>
       </c>
       <c r="C822" s="9" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D822" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E822" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:30:51</t>
         </is>
       </c>
     </row>
     <row r="823">
       <c r="A823" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B823" s="5" t="inlineStr">
@@ -21049,7 +21049,7 @@
         </is>
       </c>
       <c r="C823" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D823" s="5" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         </is>
       </c>
       <c r="C824" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D824" s="9" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
     <row r="825">
       <c r="A825" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great North 10K</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B825" s="5" t="inlineStr">
@@ -21115,7 +21115,7 @@
     <row r="826">
       <c r="A826" s="8" t="inlineStr">
         <is>
-          <t>ASICS LDNX</t>
+          <t>AJ Bell Great North 10K</t>
         </is>
       </c>
       <c r="B826" s="9" t="inlineStr">
@@ -21140,7 +21140,7 @@
     <row r="827">
       <c r="A827" s="4" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>ASICS LDNX</t>
         </is>
       </c>
       <c r="B827" s="5" t="inlineStr">
@@ -21149,7 +21149,7 @@
         </is>
       </c>
       <c r="C827" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D827" s="5" t="inlineStr">
         <is>
@@ -21174,16 +21174,16 @@
         </is>
       </c>
       <c r="C828" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D828" s="9" t="inlineStr">
         <is>
-          <t>0:29:37</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E828" s="9" t="inlineStr">
         <is>
-          <t>0:32:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21199,23 +21199,23 @@
         </is>
       </c>
       <c r="C829" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D829" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:37</t>
         </is>
       </c>
       <c r="E829" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:18</t>
         </is>
       </c>
     </row>
     <row r="830">
       <c r="A830" s="8" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B830" s="9" t="inlineStr">
@@ -21224,16 +21224,16 @@
         </is>
       </c>
       <c r="C830" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D830" s="9" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E830" s="9" t="inlineStr">
         <is>
-          <t>0:30:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21249,16 +21249,16 @@
         </is>
       </c>
       <c r="C831" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D831" s="5" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E831" s="5" t="inlineStr">
         <is>
-          <t>0:31:12</t>
+          <t>0:30:43</t>
         </is>
       </c>
     </row>
@@ -21274,23 +21274,23 @@
         </is>
       </c>
       <c r="C832" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D832" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E832" s="9" t="inlineStr">
         <is>
-          <t>0:31:29</t>
+          <t>0:31:12</t>
         </is>
       </c>
     </row>
     <row r="833">
       <c r="A833" s="4" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B833" s="5" t="inlineStr">
@@ -21299,16 +21299,16 @@
         </is>
       </c>
       <c r="C833" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D833" s="5" t="inlineStr">
         <is>
-          <t>0:29:08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E833" s="5" t="inlineStr">
         <is>
-          <t>0:33:25</t>
+          <t>0:31:29</t>
         </is>
       </c>
     </row>
@@ -21324,16 +21324,16 @@
         </is>
       </c>
       <c r="C834" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D834" s="9" t="inlineStr">
         <is>
-          <t>0:29:13</t>
+          <t>0:29:08</t>
         </is>
       </c>
       <c r="E834" s="9" t="inlineStr">
         <is>
-          <t>0:32:45</t>
+          <t>0:33:25</t>
         </is>
       </c>
     </row>
@@ -21349,16 +21349,16 @@
         </is>
       </c>
       <c r="C835" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D835" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:13</t>
         </is>
       </c>
       <c r="E835" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:45</t>
         </is>
       </c>
     </row>
@@ -21378,19 +21378,19 @@
       </c>
       <c r="D836" s="9" t="inlineStr">
         <is>
-          <t>0:28:36</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E836" s="9" t="inlineStr">
         <is>
-          <t>0:31:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B837" s="5" t="inlineStr">
@@ -21399,16 +21399,16 @@
         </is>
       </c>
       <c r="C837" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D837" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:36</t>
         </is>
       </c>
       <c r="E837" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:51</t>
         </is>
       </c>
     </row>
@@ -21424,7 +21424,7 @@
         </is>
       </c>
       <c r="C838" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D838" s="9" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         </is>
       </c>
       <c r="C839" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D839" s="5" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
     <row r="840">
       <c r="A840" s="8" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B840" s="9" t="inlineStr">
@@ -21474,16 +21474,16 @@
         </is>
       </c>
       <c r="C840" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D840" s="9" t="inlineStr">
         <is>
-          <t>0:28:52</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E840" s="9" t="inlineStr">
         <is>
-          <t>0:31:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21499,16 +21499,16 @@
         </is>
       </c>
       <c r="C841" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D841" s="5" t="inlineStr">
         <is>
-          <t>0:28:46</t>
+          <t>0:28:52</t>
         </is>
       </c>
       <c r="E841" s="5" t="inlineStr">
         <is>
-          <t>0:32:33</t>
+          <t>0:31:59</t>
         </is>
       </c>
     </row>
@@ -21524,16 +21524,16 @@
         </is>
       </c>
       <c r="C842" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D842" s="9" t="inlineStr">
         <is>
-          <t>0:29:22</t>
+          <t>0:28:46</t>
         </is>
       </c>
       <c r="E842" s="9" t="inlineStr">
         <is>
-          <t>0:34:32</t>
+          <t>0:32:33</t>
         </is>
       </c>
     </row>
@@ -21549,23 +21549,23 @@
         </is>
       </c>
       <c r="C843" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D843" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:22</t>
         </is>
       </c>
       <c r="E843" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:34:32</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" s="8" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B844" s="9" t="inlineStr">
@@ -21574,7 +21574,7 @@
         </is>
       </c>
       <c r="C844" s="9" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D844" s="9" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         </is>
       </c>
       <c r="C845" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D845" s="5" t="inlineStr">
         <is>
@@ -21624,16 +21624,16 @@
         </is>
       </c>
       <c r="C846" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D846" s="9" t="inlineStr">
         <is>
-          <t>0:28:27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E846" s="9" t="inlineStr">
         <is>
-          <t>0:31:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21653,19 +21653,19 @@
       </c>
       <c r="D847" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:27</t>
         </is>
       </c>
       <c r="E847" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:49</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" s="8" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B848" s="9" t="inlineStr">
@@ -21674,7 +21674,7 @@
         </is>
       </c>
       <c r="C848" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D848" s="9" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         </is>
       </c>
       <c r="C849" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D849" s="5" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         </is>
       </c>
       <c r="C850" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D850" s="9" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         </is>
       </c>
       <c r="C851" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D851" s="5" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
     <row r="852">
       <c r="A852" s="8" t="inlineStr">
         <is>
-          <t>Great Scottish Run 10K</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B852" s="9" t="inlineStr">
@@ -21774,7 +21774,7 @@
         </is>
       </c>
       <c r="C852" s="9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D852" s="9" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
     <row r="853">
       <c r="A853" s="4" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
+          <t>Great Scottish Run 10K</t>
         </is>
       </c>
       <c r="B853" s="5" t="inlineStr">
@@ -21799,7 +21799,7 @@
         </is>
       </c>
       <c r="C853" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D853" s="5" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
     <row r="854">
       <c r="A854" s="8" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
         </is>
       </c>
       <c r="B854" s="9" t="inlineStr">
@@ -21824,7 +21824,7 @@
         </is>
       </c>
       <c r="C854" s="9" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D854" s="9" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="C855" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D855" s="5" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
       </c>
       <c r="E855" s="5" t="inlineStr">
         <is>
-          <t>0:31:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21874,23 +21874,23 @@
         </is>
       </c>
       <c r="C856" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D856" s="9" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E856" s="9" t="inlineStr">
         <is>
-          <t>0:31:11</t>
+          <t>0:31:18</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" s="4" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B857" s="5" t="inlineStr">
@@ -21899,16 +21899,16 @@
         </is>
       </c>
       <c r="C857" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D857" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E857" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:11</t>
         </is>
       </c>
     </row>
@@ -21924,7 +21924,7 @@
         </is>
       </c>
       <c r="C858" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D858" s="9" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         </is>
       </c>
       <c r="C859" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D859" s="5" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
     <row r="860">
       <c r="A860" s="8" t="inlineStr">
         <is>
-          <t>Run in Lyon</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B860" s="9" t="inlineStr">
@@ -21990,7 +21990,7 @@
     <row r="861">
       <c r="A861" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>Run in Lyon</t>
         </is>
       </c>
       <c r="B861" s="5" t="inlineStr">
@@ -21999,7 +21999,7 @@
         </is>
       </c>
       <c r="C861" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D861" s="5" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         </is>
       </c>
       <c r="C862" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D862" s="9" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="C863" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D863" s="5" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
     <row r="864">
       <c r="A864" s="8" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B864" s="9" t="inlineStr">
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="C864" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D864" s="9" t="inlineStr">
         <is>
@@ -22099,16 +22099,16 @@
         </is>
       </c>
       <c r="C865" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D865" s="5" t="inlineStr">
         <is>
-          <t>0:29:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E865" s="5" t="inlineStr">
         <is>
-          <t>0:32:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22124,23 +22124,23 @@
         </is>
       </c>
       <c r="C866" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D866" s="9" t="inlineStr">
         <is>
-          <t>0:29:33</t>
+          <t>0:29:41</t>
         </is>
       </c>
       <c r="E866" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:51</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered KL 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B867" s="5" t="inlineStr">
@@ -22153,19 +22153,19 @@
       </c>
       <c r="D867" s="5" t="inlineStr">
         <is>
-          <t>0:32:26</t>
+          <t>0:29:33</t>
         </is>
       </c>
       <c r="E867" s="5" t="inlineStr">
         <is>
-          <t>0:39:23</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" s="8" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Standard Chartered KL 10K</t>
         </is>
       </c>
       <c r="B868" s="9" t="inlineStr">
@@ -22174,16 +22174,16 @@
         </is>
       </c>
       <c r="C868" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D868" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:26</t>
         </is>
       </c>
       <c r="E868" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:39:23</t>
         </is>
       </c>
     </row>
@@ -22199,7 +22199,7 @@
         </is>
       </c>
       <c r="C869" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D869" s="5" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="C870" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D870" s="9" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
     <row r="871">
       <c r="A871" s="4" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B871" s="5" t="inlineStr">
@@ -22249,7 +22249,7 @@
         </is>
       </c>
       <c r="C871" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D871" s="5" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         </is>
       </c>
       <c r="C872" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D872" s="9" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         </is>
       </c>
       <c r="C873" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D873" s="5" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
     <row r="874">
       <c r="A874" s="8" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B874" s="9" t="inlineStr">
@@ -22324,7 +22324,7 @@
         </is>
       </c>
       <c r="C874" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D874" s="9" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         </is>
       </c>
       <c r="C875" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D875" s="5" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         </is>
       </c>
       <c r="C876" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D876" s="9" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
     <row r="877">
       <c r="A877" s="4" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B877" s="5" t="inlineStr">
@@ -22399,7 +22399,7 @@
         </is>
       </c>
       <c r="C877" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D877" s="5" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         </is>
       </c>
       <c r="C878" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D878" s="9" t="inlineStr">
         <is>
@@ -22449,23 +22449,23 @@
         </is>
       </c>
       <c r="C879" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D879" s="5" t="inlineStr">
         <is>
-          <t>0:28:09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E879" s="5" t="inlineStr">
         <is>
-          <t>0:32:54</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" s="8" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Vancouver Sun Run</t>
         </is>
       </c>
       <c r="B880" s="9" t="inlineStr">
@@ -22474,16 +22474,16 @@
         </is>
       </c>
       <c r="C880" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D880" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:09</t>
         </is>
       </c>
       <c r="E880" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:54</t>
         </is>
       </c>
     </row>
@@ -22499,16 +22499,16 @@
         </is>
       </c>
       <c r="C881" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D881" s="5" t="inlineStr">
         <is>
-          <t>0:29:14</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E881" s="5" t="inlineStr">
         <is>
-          <t>0:31:36</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22524,28 +22524,28 @@
         </is>
       </c>
       <c r="C882" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D882" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:14</t>
         </is>
       </c>
       <c r="E882" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:36</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Birmingham Run</t>
+          <t>Vitality London 10,000</t>
         </is>
       </c>
       <c r="B883" s="5" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C883" s="5" t="n">
@@ -22565,25 +22565,25 @@
     <row r="884">
       <c r="A884" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great South Run</t>
+          <t>AJ Bell Great Birmingham Run</t>
         </is>
       </c>
       <c r="B884" s="9" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>SEMI</t>
         </is>
       </c>
       <c r="C884" s="9" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D884" s="9" t="inlineStr">
         <is>
-          <t>0:47:19</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E884" s="9" t="inlineStr">
         <is>
-          <t>0:50:42</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22599,23 +22599,23 @@
         </is>
       </c>
       <c r="C885" s="5" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D885" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:47:19</t>
         </is>
       </c>
       <c r="E885" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:50:42</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" s="8" t="inlineStr">
         <is>
-          <t>Army Ten Miler</t>
+          <t>AJ Bell Great South Run</t>
         </is>
       </c>
       <c r="B886" s="9" t="inlineStr">
@@ -22640,7 +22640,7 @@
     <row r="887">
       <c r="A887" s="4" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>Army Ten Miler</t>
         </is>
       </c>
       <c r="B887" s="5" t="inlineStr">
@@ -22649,7 +22649,7 @@
         </is>
       </c>
       <c r="C887" s="5" t="n">
-        <v>2005</v>
+        <v>2025</v>
       </c>
       <c r="D887" s="5" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
       </c>
       <c r="E887" s="5" t="inlineStr">
         <is>
-          <t>0:38:22</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22674,16 +22674,16 @@
         </is>
       </c>
       <c r="C888" s="9" t="n">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="D888" s="9" t="inlineStr">
         <is>
-          <t>0:33:31</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E888" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:38:22</t>
         </is>
       </c>
     </row>
@@ -22699,16 +22699,16 @@
         </is>
       </c>
       <c r="C889" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D889" s="5" t="inlineStr">
         <is>
-          <t>0:34:15</t>
+          <t>0:33:31</t>
         </is>
       </c>
       <c r="E889" s="5" t="inlineStr">
         <is>
-          <t>0:38:07</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22724,16 +22724,16 @@
         </is>
       </c>
       <c r="C890" s="9" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="D890" s="9" t="inlineStr">
         <is>
-          <t>0:34:40</t>
+          <t>0:34:15</t>
         </is>
       </c>
       <c r="E890" s="9" t="inlineStr">
         <is>
-          <t>0:39:02</t>
+          <t>0:38:07</t>
         </is>
       </c>
     </row>
@@ -22749,16 +22749,16 @@
         </is>
       </c>
       <c r="C891" s="5" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="D891" s="5" t="inlineStr">
         <is>
-          <t>0:35:01</t>
+          <t>0:34:40</t>
         </is>
       </c>
       <c r="E891" s="5" t="inlineStr">
         <is>
-          <t>0:39:28</t>
+          <t>0:39:02</t>
         </is>
       </c>
     </row>
@@ -22774,16 +22774,16 @@
         </is>
       </c>
       <c r="C892" s="9" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D892" s="9" t="inlineStr">
         <is>
-          <t>0:36:10</t>
+          <t>0:35:01</t>
         </is>
       </c>
       <c r="E892" s="9" t="inlineStr">
         <is>
-          <t>0:42:05</t>
+          <t>0:39:28</t>
         </is>
       </c>
     </row>
@@ -22799,23 +22799,23 @@
         </is>
       </c>
       <c r="C893" s="5" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D893" s="5" t="inlineStr">
         <is>
-          <t>0:37:02</t>
+          <t>0:36:10</t>
         </is>
       </c>
       <c r="E893" s="5" t="inlineStr">
         <is>
-          <t>0:43:48</t>
+          <t>0:42:05</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="8" t="inlineStr">
         <is>
-          <t>Boilermaker Road Race</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
@@ -22824,23 +22824,23 @@
         </is>
       </c>
       <c r="C894" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D894" s="9" t="inlineStr">
         <is>
-          <t>0:42:44</t>
+          <t>0:37:02</t>
         </is>
       </c>
       <c r="E894" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:43:48</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="4" t="inlineStr">
         <is>
-          <t>Broad Street Run</t>
+          <t>Boilermaker Road Race</t>
         </is>
       </c>
       <c r="B895" s="5" t="inlineStr">
@@ -22853,19 +22853,19 @@
       </c>
       <c r="D895" s="5" t="inlineStr">
         <is>
-          <t>0:46:13</t>
+          <t>0:42:44</t>
         </is>
       </c>
       <c r="E895" s="5" t="inlineStr">
         <is>
-          <t>0:54:01</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="8" t="inlineStr">
         <is>
-          <t>City2Surf</t>
+          <t>Broad Street Run</t>
         </is>
       </c>
       <c r="B896" s="9" t="inlineStr">
@@ -22874,23 +22874,23 @@
         </is>
       </c>
       <c r="C896" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D896" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:46:13</t>
         </is>
       </c>
       <c r="E896" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:54:01</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>City2Surf</t>
         </is>
       </c>
       <c r="B897" s="5" t="inlineStr">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="C897" s="5" t="n">
-        <v>2009</v>
+        <v>2024</v>
       </c>
       <c r="D897" s="5" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="E897" s="5" t="inlineStr">
         <is>
-          <t>0:50:39</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22924,7 +22924,7 @@
         </is>
       </c>
       <c r="C898" s="9" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D898" s="9" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
       </c>
       <c r="E898" s="9" t="inlineStr">
         <is>
-          <t>0:51:30</t>
+          <t>0:50:39</t>
         </is>
       </c>
     </row>
@@ -22949,16 +22949,16 @@
         </is>
       </c>
       <c r="C899" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D899" s="5" t="inlineStr">
         <is>
-          <t>0:44:27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E899" s="5" t="inlineStr">
         <is>
-          <t>0:51:57</t>
+          <t>0:51:30</t>
         </is>
       </c>
     </row>
@@ -22974,16 +22974,16 @@
         </is>
       </c>
       <c r="C900" s="9" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D900" s="9" t="inlineStr">
         <is>
-          <t>0:44:48</t>
+          <t>0:44:27</t>
         </is>
       </c>
       <c r="E900" s="9" t="inlineStr">
         <is>
-          <t>0:51:42</t>
+          <t>0:51:57</t>
         </is>
       </c>
     </row>
@@ -22999,16 +22999,16 @@
         </is>
       </c>
       <c r="C901" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="D901" s="5" t="inlineStr">
         <is>
-          <t>0:45:28</t>
+          <t>0:44:48</t>
         </is>
       </c>
       <c r="E901" s="5" t="inlineStr">
         <is>
-          <t>0:51:33</t>
+          <t>0:51:42</t>
         </is>
       </c>
     </row>
@@ -23024,16 +23024,16 @@
         </is>
       </c>
       <c r="C902" s="9" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D902" s="9" t="inlineStr">
         <is>
-          <t>0:45:45</t>
+          <t>0:45:28</t>
         </is>
       </c>
       <c r="E902" s="9" t="inlineStr">
         <is>
-          <t>0:53:09</t>
+          <t>0:51:33</t>
         </is>
       </c>
     </row>
@@ -23049,16 +23049,16 @@
         </is>
       </c>
       <c r="C903" s="5" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D903" s="5" t="inlineStr">
         <is>
-          <t>0:45:15</t>
+          <t>0:45:45</t>
         </is>
       </c>
       <c r="E903" s="5" t="inlineStr">
         <is>
-          <t>0:50:45</t>
+          <t>0:53:09</t>
         </is>
       </c>
     </row>
@@ -23074,16 +23074,16 @@
         </is>
       </c>
       <c r="C904" s="9" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D904" s="9" t="inlineStr">
         <is>
-          <t>0:49:00</t>
+          <t>0:45:15</t>
         </is>
       </c>
       <c r="E904" s="9" t="inlineStr">
         <is>
-          <t>0:55:44</t>
+          <t>0:50:45</t>
         </is>
       </c>
     </row>
@@ -23099,16 +23099,16 @@
         </is>
       </c>
       <c r="C905" s="5" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D905" s="5" t="inlineStr">
         <is>
-          <t>0:44:51</t>
+          <t>0:49:00</t>
         </is>
       </c>
       <c r="E905" s="5" t="inlineStr">
         <is>
-          <t>0:51:15</t>
+          <t>0:55:44</t>
         </is>
       </c>
     </row>
@@ -23124,23 +23124,23 @@
         </is>
       </c>
       <c r="C906" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D906" s="9" t="inlineStr">
         <is>
-          <t>0:46:07</t>
+          <t>0:44:51</t>
         </is>
       </c>
       <c r="E906" s="9" t="inlineStr">
         <is>
-          <t>0:50:51</t>
+          <t>0:51:15</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" s="4" t="inlineStr">
         <is>
-          <t>Falmouth Road Race</t>
+          <t>Dam tot Damloop</t>
         </is>
       </c>
       <c r="B907" s="5" t="inlineStr">
@@ -23153,24 +23153,24 @@
       </c>
       <c r="D907" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:46:07</t>
         </is>
       </c>
       <c r="E907" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:50:51</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="8" t="inlineStr">
         <is>
-          <t>Great Scottish Run</t>
+          <t>Falmouth Road Race</t>
         </is>
       </c>
       <c r="B908" s="9" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="C908" s="9" t="n">
@@ -23190,12 +23190,12 @@
     <row r="909">
       <c r="A909" s="4" t="inlineStr">
         <is>
-          <t>Lilac Bloomsday Run</t>
+          <t>Great Scottish Run</t>
         </is>
       </c>
       <c r="B909" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>SEMI</t>
         </is>
       </c>
       <c r="C909" s="5" t="n">
@@ -23215,30 +23215,55 @@
     <row r="910">
       <c r="A910" s="8" t="inlineStr">
         <is>
+          <t>Lilac Bloomsday Run</t>
+        </is>
+      </c>
+      <c r="B910" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C910" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D910" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E910" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="4" t="inlineStr">
+        <is>
           <t>Manchester Road Race</t>
         </is>
       </c>
-      <c r="B910" s="9" t="inlineStr">
+      <c r="B911" s="5" t="inlineStr">
         <is>
           <t>AUTRE</t>
         </is>
       </c>
-      <c r="C910" s="9" t="n">
+      <c r="C911" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="D910" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E910" s="9" t="inlineStr">
+      <c r="D911" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E911" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E910"/>
+  <autoFilter ref="A1:E911"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Chronos_Vainqueurs.xlsx
+++ b/Chronos_Vainqueurs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$915</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$923</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E915"/>
+  <dimension ref="A1:E923"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -19424,23 +19424,23 @@
         </is>
       </c>
       <c r="C758" s="7" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D758" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:58</t>
         </is>
       </c>
       <c r="E758" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:12:54</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" s="4" t="inlineStr">
         <is>
-          <t>Nike Melbourne Marathon Festival</t>
+          <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
       <c r="B759" s="5" t="inlineStr">
@@ -19449,23 +19449,23 @@
         </is>
       </c>
       <c r="C759" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D759" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:05</t>
         </is>
       </c>
       <c r="E759" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:11:38</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" s="6" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
       <c r="B760" s="7" t="inlineStr">
@@ -19474,23 +19474,23 @@
         </is>
       </c>
       <c r="C760" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D760" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:08</t>
         </is>
       </c>
       <c r="E760" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:12:41</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" s="4" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
       <c r="B761" s="5" t="inlineStr">
@@ -19499,7 +19499,7 @@
         </is>
       </c>
       <c r="C761" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D761" s="5" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
     <row r="762">
       <c r="A762" s="6" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>Nike Melbourne Marathon Festival</t>
         </is>
       </c>
       <c r="B762" s="7" t="inlineStr">
@@ -19549,7 +19549,7 @@
         </is>
       </c>
       <c r="C763" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D763" s="5" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
     <row r="764">
       <c r="A764" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B764" s="7" t="inlineStr">
@@ -19574,7 +19574,7 @@
         </is>
       </c>
       <c r="C764" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D764" s="7" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
     <row r="765">
       <c r="A765" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B765" s="5" t="inlineStr">
@@ -19599,7 +19599,7 @@
         </is>
       </c>
       <c r="C765" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D765" s="5" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
     <row r="766">
       <c r="A766" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B766" s="7" t="inlineStr">
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="C766" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D766" s="7" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         </is>
       </c>
       <c r="C767" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D767" s="5" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
     <row r="768">
       <c r="A768" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Mexico City</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B768" s="7" t="inlineStr">
@@ -19674,7 +19674,7 @@
         </is>
       </c>
       <c r="C768" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D768" s="7" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
     <row r="769">
       <c r="A769" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series San Diego</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B769" s="5" t="inlineStr">
@@ -19715,7 +19715,7 @@
     <row r="770">
       <c r="A770" s="6" t="inlineStr">
         <is>
-          <t>Royal Parks Half Marathon</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B770" s="7" t="inlineStr">
@@ -19724,7 +19724,7 @@
         </is>
       </c>
       <c r="C770" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D770" s="7" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
     <row r="771">
       <c r="A771" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Rock 'n' Roll Running Series Mexico City</t>
         </is>
       </c>
       <c r="B771" s="5" t="inlineStr">
@@ -19749,7 +19749,7 @@
         </is>
       </c>
       <c r="C771" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D771" s="5" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
     <row r="772">
       <c r="A772" s="6" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Rock 'n' Roll Running Series San Diego</t>
         </is>
       </c>
       <c r="B772" s="7" t="inlineStr">
@@ -19774,23 +19774,23 @@
         </is>
       </c>
       <c r="C772" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D772" s="7" t="inlineStr">
         <is>
-          <t>1:05:44</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E772" s="7" t="inlineStr">
         <is>
-          <t>1:18:34</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Royal Parks Half Marathon</t>
         </is>
       </c>
       <c r="B773" s="5" t="inlineStr">
@@ -19815,7 +19815,7 @@
     <row r="774">
       <c r="A774" s="6" t="inlineStr">
         <is>
-          <t>Semi-Marathon de Boulogne-Billancourt</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B774" s="7" t="inlineStr">
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="C774" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D774" s="7" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
     <row r="775">
       <c r="A775" s="4" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B775" s="5" t="inlineStr">
@@ -19849,23 +19849,23 @@
         </is>
       </c>
       <c r="C775" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D775" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:44</t>
         </is>
       </c>
       <c r="E775" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:18:34</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" s="6" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Series Nashville</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B776" s="7" t="inlineStr">
@@ -19890,7 +19890,7 @@
     <row r="777">
       <c r="A777" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>Semi-Marathon de Boulogne-Billancourt</t>
         </is>
       </c>
       <c r="B777" s="5" t="inlineStr">
@@ -19899,23 +19899,23 @@
         </is>
       </c>
       <c r="C777" s="5" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D777" s="5" t="inlineStr">
         <is>
-          <t>1:01:13</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E777" s="5" t="inlineStr">
         <is>
-          <t>1:09:28</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="778">
       <c r="A778" s="6" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
         </is>
       </c>
       <c r="B778" s="7" t="inlineStr">
@@ -19940,7 +19940,7 @@
     <row r="779">
       <c r="A779" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>St. Jude Rock 'n' Roll Series Nashville</t>
         </is>
       </c>
       <c r="B779" s="5" t="inlineStr">
@@ -19949,7 +19949,7 @@
         </is>
       </c>
       <c r="C779" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D779" s="5" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
     <row r="780">
       <c r="A780" s="6" t="inlineStr">
         <is>
-          <t>Standard Chartered KL Half Marathon</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B780" s="7" t="inlineStr">
@@ -19974,23 +19974,23 @@
         </is>
       </c>
       <c r="C780" s="7" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D780" s="7" t="inlineStr">
         <is>
-          <t>1:11:08</t>
+          <t>1:01:13</t>
         </is>
       </c>
       <c r="E780" s="7" t="inlineStr">
         <is>
-          <t>1:23:55</t>
+          <t>1:09:28</t>
         </is>
       </c>
     </row>
     <row r="781">
       <c r="A781" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Singapore Half Marathon</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B781" s="5" t="inlineStr">
@@ -20015,7 +20015,7 @@
     <row r="782">
       <c r="A782" s="6" t="inlineStr">
         <is>
-          <t>TCS Mizuno Half Marathon</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B782" s="7" t="inlineStr">
@@ -20024,23 +20024,23 @@
         </is>
       </c>
       <c r="C782" s="7" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D782" s="7" t="inlineStr">
         <is>
-          <t>1:05:23</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E782" s="7" t="inlineStr">
         <is>
-          <t>1:13:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" s="4" t="inlineStr">
         <is>
-          <t>TCS Mizuno Half Marathon</t>
+          <t>Standard Chartered KL Half Marathon</t>
         </is>
       </c>
       <c r="B783" s="5" t="inlineStr">
@@ -20049,23 +20049,23 @@
         </is>
       </c>
       <c r="C783" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D783" s="5" t="inlineStr">
         <is>
-          <t>1:06:28</t>
+          <t>1:11:08</t>
         </is>
       </c>
       <c r="E783" s="5" t="inlineStr">
         <is>
-          <t>1:17:54</t>
+          <t>1:23:55</t>
         </is>
       </c>
     </row>
     <row r="784">
       <c r="A784" s="6" t="inlineStr">
         <is>
-          <t>TCS Mizuno Half Marathon</t>
+          <t>Standard Chartered Singapore Half Marathon</t>
         </is>
       </c>
       <c r="B784" s="7" t="inlineStr">
@@ -20099,23 +20099,23 @@
         </is>
       </c>
       <c r="C785" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D785" s="5" t="inlineStr">
         <is>
-          <t>1:04:21</t>
+          <t>1:05:23</t>
         </is>
       </c>
       <c r="E785" s="5" t="inlineStr">
         <is>
-          <t>1:10:02</t>
+          <t>1:13:59</t>
         </is>
       </c>
     </row>
     <row r="786">
       <c r="A786" s="6" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
       <c r="B786" s="7" t="inlineStr">
@@ -20124,23 +20124,23 @@
         </is>
       </c>
       <c r="C786" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D786" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:28</t>
         </is>
       </c>
       <c r="E786" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:17:54</t>
         </is>
       </c>
     </row>
     <row r="787">
       <c r="A787" s="4" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
       <c r="B787" s="5" t="inlineStr">
@@ -20149,7 +20149,7 @@
         </is>
       </c>
       <c r="C787" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D787" s="5" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
     <row r="788">
       <c r="A788" s="6" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
       <c r="B788" s="7" t="inlineStr">
@@ -20178,19 +20178,19 @@
       </c>
       <c r="D788" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:21</t>
         </is>
       </c>
       <c r="E788" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:02</t>
         </is>
       </c>
     </row>
     <row r="789">
       <c r="A789" s="4" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B789" s="5" t="inlineStr">
@@ -20215,7 +20215,7 @@
     <row r="790">
       <c r="A790" s="6" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B790" s="7" t="inlineStr">
@@ -20240,7 +20240,7 @@
     <row r="791">
       <c r="A791" s="4" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B791" s="5" t="inlineStr">
@@ -20265,7 +20265,7 @@
     <row r="792">
       <c r="A792" s="6" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon (Half)</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B792" s="7" t="inlineStr">
@@ -20274,7 +20274,7 @@
         </is>
       </c>
       <c r="C792" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D792" s="7" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
     <row r="793">
       <c r="A793" s="4" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon (Half)</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B793" s="5" t="inlineStr">
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="C793" s="5" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D793" s="5" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
     <row r="794">
       <c r="A794" s="6" t="inlineStr">
         <is>
-          <t>The Big Half</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B794" s="7" t="inlineStr">
@@ -20340,7 +20340,7 @@
     <row r="795">
       <c r="A795" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Legacy Half Marathon</t>
+          <t>Tata Mumbai Marathon (Half)</t>
         </is>
       </c>
       <c r="B795" s="5" t="inlineStr">
@@ -20365,7 +20365,7 @@
     <row r="796">
       <c r="A796" s="6" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>Tata Mumbai Marathon (Half)</t>
         </is>
       </c>
       <c r="B796" s="7" t="inlineStr">
@@ -20374,23 +20374,23 @@
         </is>
       </c>
       <c r="C796" s="7" t="n">
-        <v>2006</v>
+        <v>2026</v>
       </c>
       <c r="D796" s="7" t="inlineStr">
         <is>
-          <t>1:01:22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E796" s="7" t="inlineStr">
         <is>
-          <t>1:09:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="797">
       <c r="A797" s="4" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>The Big Half</t>
         </is>
       </c>
       <c r="B797" s="5" t="inlineStr">
@@ -20399,23 +20399,23 @@
         </is>
       </c>
       <c r="C797" s="5" t="n">
-        <v>2007</v>
+        <v>2025</v>
       </c>
       <c r="D797" s="5" t="inlineStr">
         <is>
-          <t>0:59:24</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E797" s="5" t="inlineStr">
         <is>
-          <t>1:10:32</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="798">
       <c r="A798" s="6" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>Tokyo Legacy Half Marathon</t>
         </is>
       </c>
       <c r="B798" s="7" t="inlineStr">
@@ -20424,16 +20424,16 @@
         </is>
       </c>
       <c r="C798" s="7" t="n">
-        <v>2008</v>
+        <v>2025</v>
       </c>
       <c r="D798" s="7" t="inlineStr">
         <is>
-          <t>1:00:58</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E798" s="7" t="inlineStr">
         <is>
-          <t>1:10:19</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20449,16 +20449,16 @@
         </is>
       </c>
       <c r="C799" s="5" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="D799" s="5" t="inlineStr">
         <is>
-          <t>1:01:06</t>
+          <t>1:01:22</t>
         </is>
       </c>
       <c r="E799" s="5" t="inlineStr">
         <is>
-          <t>1:09:32</t>
+          <t>1:09:43</t>
         </is>
       </c>
     </row>
@@ -20474,16 +20474,16 @@
         </is>
       </c>
       <c r="C800" s="7" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="D800" s="7" t="inlineStr">
         <is>
-          <t>0:59:52</t>
+          <t>0:59:24</t>
         </is>
       </c>
       <c r="E800" s="7" t="inlineStr">
         <is>
-          <t>1:09:25</t>
+          <t>1:10:32</t>
         </is>
       </c>
     </row>
@@ -20499,16 +20499,16 @@
         </is>
       </c>
       <c r="C801" s="5" t="n">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="D801" s="5" t="inlineStr">
         <is>
-          <t>1:00:23</t>
+          <t>1:00:58</t>
         </is>
       </c>
       <c r="E801" s="5" t="inlineStr">
         <is>
-          <t>1:08:52</t>
+          <t>1:10:19</t>
         </is>
       </c>
     </row>
@@ -20524,16 +20524,16 @@
         </is>
       </c>
       <c r="C802" s="7" t="n">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="D802" s="7" t="inlineStr">
         <is>
-          <t>0:59:39</t>
+          <t>1:01:06</t>
         </is>
       </c>
       <c r="E802" s="7" t="inlineStr">
         <is>
-          <t>1:08:35</t>
+          <t>1:09:32</t>
         </is>
       </c>
     </row>
@@ -20549,16 +20549,16 @@
         </is>
       </c>
       <c r="C803" s="5" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="D803" s="5" t="inlineStr">
         <is>
-          <t>1:01:02</t>
+          <t>0:59:52</t>
         </is>
       </c>
       <c r="E803" s="5" t="inlineStr">
         <is>
-          <t>1:09:09</t>
+          <t>1:09:25</t>
         </is>
       </c>
     </row>
@@ -20574,16 +20574,16 @@
         </is>
       </c>
       <c r="C804" s="7" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="D804" s="7" t="inlineStr">
         <is>
-          <t>1:00:50</t>
+          <t>1:00:23</t>
         </is>
       </c>
       <c r="E804" s="7" t="inlineStr">
         <is>
-          <t>1:08:31</t>
+          <t>1:08:52</t>
         </is>
       </c>
     </row>
@@ -20599,16 +20599,16 @@
         </is>
       </c>
       <c r="C805" s="5" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="D805" s="5" t="inlineStr">
         <is>
-          <t>1:01:31</t>
+          <t>0:59:39</t>
         </is>
       </c>
       <c r="E805" s="5" t="inlineStr">
         <is>
-          <t>1:07:04</t>
+          <t>1:08:35</t>
         </is>
       </c>
     </row>
@@ -20624,23 +20624,23 @@
         </is>
       </c>
       <c r="C806" s="7" t="n">
-        <v>2026</v>
+        <v>2013</v>
       </c>
       <c r="D806" s="7" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>1:01:02</t>
         </is>
       </c>
       <c r="E806" s="7" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>1:09:09</t>
         </is>
       </c>
     </row>
     <row r="807">
       <c r="A807" s="4" t="inlineStr">
         <is>
-          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B807" s="5" t="inlineStr">
@@ -20649,23 +20649,23 @@
         </is>
       </c>
       <c r="C807" s="5" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D807" s="5" t="inlineStr">
         <is>
-          <t>0:58:02</t>
+          <t>1:00:50</t>
         </is>
       </c>
       <c r="E807" s="5" t="inlineStr">
         <is>
-          <t>1:03:08</t>
+          <t>1:08:31</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="A808" s="6" t="inlineStr">
         <is>
-          <t>Vedanta Delhi Half Marathon</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B808" s="7" t="inlineStr">
@@ -20678,19 +20678,19 @@
       </c>
       <c r="D808" s="7" t="inlineStr">
         <is>
-          <t>0:59:50</t>
+          <t>1:01:31</t>
         </is>
       </c>
       <c r="E808" s="7" t="inlineStr">
         <is>
-          <t>1:07:20</t>
+          <t>1:07:04</t>
         </is>
       </c>
     </row>
     <row r="809">
       <c r="A809" s="4" t="inlineStr">
         <is>
-          <t>Vienna City Half Marathon</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B809" s="5" t="inlineStr">
@@ -20699,23 +20699,23 @@
         </is>
       </c>
       <c r="C809" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D809" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E809" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
     <row r="810">
       <c r="A810" s="6" t="inlineStr">
         <is>
-          <t>Walt Disney World Marathon Weekend</t>
+          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B810" s="7" t="inlineStr">
@@ -20728,19 +20728,19 @@
       </c>
       <c r="D810" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:02</t>
         </is>
       </c>
       <c r="E810" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:08</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" s="4" t="inlineStr">
         <is>
-          <t>Walt Disney World Marathon Weekend</t>
+          <t>Vedanta Delhi Half Marathon</t>
         </is>
       </c>
       <c r="B811" s="5" t="inlineStr">
@@ -20749,23 +20749,23 @@
         </is>
       </c>
       <c r="C811" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D811" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:50</t>
         </is>
       </c>
       <c r="E811" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:20</t>
         </is>
       </c>
     </row>
     <row r="812">
       <c r="A812" s="6" t="inlineStr">
         <is>
-          <t>Warsaw Half Marathon</t>
+          <t>Vienna City Half Marathon</t>
         </is>
       </c>
       <c r="B812" s="7" t="inlineStr">
@@ -20774,7 +20774,7 @@
         </is>
       </c>
       <c r="C812" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D812" s="7" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
     <row r="813">
       <c r="A813" s="4" t="inlineStr">
         <is>
-          <t>Warsaw Half Marathon</t>
+          <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
       <c r="B813" s="5" t="inlineStr">
@@ -20815,7 +20815,7 @@
     <row r="814">
       <c r="A814" s="6" t="inlineStr">
         <is>
-          <t>Wizz Air Rome Half Marathon by Brooks</t>
+          <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
       <c r="B814" s="7" t="inlineStr">
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="C814" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D814" s="7" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
     <row r="815">
       <c r="A815" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Warsaw Half Marathon</t>
         </is>
       </c>
       <c r="B815" s="5" t="inlineStr">
@@ -20849,7 +20849,7 @@
         </is>
       </c>
       <c r="C815" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D815" s="5" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
     <row r="816">
       <c r="A816" s="6" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Warsaw Half Marathon</t>
         </is>
       </c>
       <c r="B816" s="7" t="inlineStr">
@@ -20874,7 +20874,7 @@
         </is>
       </c>
       <c r="C816" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D816" s="7" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
     <row r="817">
       <c r="A817" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Wizz Air Rome Half Marathon by Brooks</t>
         </is>
       </c>
       <c r="B817" s="5" t="inlineStr">
@@ -20913,43 +20913,43 @@
       </c>
     </row>
     <row r="818">
-      <c r="A818" s="8" t="inlineStr">
-        <is>
-          <t>10K Montmartre</t>
-        </is>
-      </c>
-      <c r="B818" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C818" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D818" s="9" t="inlineStr">
-        <is>
-          <t>0:31:14</t>
-        </is>
-      </c>
-      <c r="E818" s="9" t="inlineStr">
-        <is>
-          <t>0:35:46</t>
+      <c r="A818" s="6" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+        </is>
+      </c>
+      <c r="B818" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C818" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D818" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E818" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="819">
       <c r="A819" s="4" t="inlineStr">
         <is>
-          <t>10K Montmartre</t>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
         </is>
       </c>
       <c r="B819" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C819" s="5" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D819" s="5" t="inlineStr">
         <is>
@@ -20963,34 +20963,34 @@
       </c>
     </row>
     <row r="820">
-      <c r="A820" s="8" t="inlineStr">
-        <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
-        </is>
-      </c>
-      <c r="B820" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C820" s="9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D820" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E820" s="9" t="inlineStr">
-        <is>
-          <t>0:29:19</t>
+      <c r="A820" s="6" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+        </is>
+      </c>
+      <c r="B820" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C820" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D820" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E820" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="821">
       <c r="A821" s="4" t="inlineStr">
         <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
+          <t>10K Montmartre</t>
         </is>
       </c>
       <c r="B821" s="5" t="inlineStr">
@@ -20999,23 +20999,23 @@
         </is>
       </c>
       <c r="C821" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D821" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:14</t>
         </is>
       </c>
       <c r="E821" s="5" t="inlineStr">
         <is>
-          <t>0:28:45</t>
+          <t>0:35:46</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" s="8" t="inlineStr">
         <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
+          <t>10K Montmartre</t>
         </is>
       </c>
       <c r="B822" s="9" t="inlineStr">
@@ -21024,7 +21024,7 @@
         </is>
       </c>
       <c r="C822" s="9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D822" s="9" t="inlineStr">
         <is>
@@ -21049,23 +21049,23 @@
         </is>
       </c>
       <c r="C823" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D823" s="5" t="inlineStr">
         <is>
-          <t>0:26:45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E823" s="5" t="inlineStr">
         <is>
-          <t>0:29:25</t>
+          <t>0:29:19</t>
         </is>
       </c>
     </row>
     <row r="824">
       <c r="A824" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Birmingham Run 10K</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B824" s="9" t="inlineStr">
@@ -21074,7 +21074,7 @@
         </is>
       </c>
       <c r="C824" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D824" s="9" t="inlineStr">
         <is>
@@ -21083,14 +21083,14 @@
       </c>
       <c r="E824" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:45</t>
         </is>
       </c>
     </row>
     <row r="825">
       <c r="A825" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Bristol Run 10K</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B825" s="5" t="inlineStr">
@@ -21115,7 +21115,7 @@
     <row r="826">
       <c r="A826" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B826" s="9" t="inlineStr">
@@ -21124,23 +21124,23 @@
         </is>
       </c>
       <c r="C826" s="9" t="n">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="D826" s="9" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>0:26:45</t>
         </is>
       </c>
       <c r="E826" s="9" t="inlineStr">
         <is>
-          <t>0:30:51</t>
+          <t>0:29:25</t>
         </is>
       </c>
     </row>
     <row r="827">
       <c r="A827" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run</t>
+          <t>AJ Bell Great Birmingham Run 10K</t>
         </is>
       </c>
       <c r="B827" s="5" t="inlineStr">
@@ -21165,7 +21165,7 @@
     <row r="828">
       <c r="A828" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>AJ Bell Great Bristol Run 10K</t>
         </is>
       </c>
       <c r="B828" s="9" t="inlineStr">
@@ -21174,7 +21174,7 @@
         </is>
       </c>
       <c r="C828" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D828" s="9" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
     <row r="829">
       <c r="A829" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B829" s="5" t="inlineStr">
@@ -21199,23 +21199,23 @@
         </is>
       </c>
       <c r="C829" s="5" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D829" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E829" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:30:51</t>
         </is>
       </c>
     </row>
     <row r="830">
       <c r="A830" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great North 10K</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B830" s="9" t="inlineStr">
@@ -21240,7 +21240,7 @@
     <row r="831">
       <c r="A831" s="4" t="inlineStr">
         <is>
-          <t>ASICS LDNX</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B831" s="5" t="inlineStr">
@@ -21249,7 +21249,7 @@
         </is>
       </c>
       <c r="C831" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D831" s="5" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
     <row r="832">
       <c r="A832" s="8" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B832" s="9" t="inlineStr">
@@ -21274,7 +21274,7 @@
         </is>
       </c>
       <c r="C832" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D832" s="9" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
     <row r="833">
       <c r="A833" s="4" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>AJ Bell Great North 10K</t>
         </is>
       </c>
       <c r="B833" s="5" t="inlineStr">
@@ -21299,23 +21299,23 @@
         </is>
       </c>
       <c r="C833" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D833" s="5" t="inlineStr">
         <is>
-          <t>0:29:37</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E833" s="5" t="inlineStr">
         <is>
-          <t>0:32:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" s="8" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>ASICS LDNX</t>
         </is>
       </c>
       <c r="B834" s="9" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="835">
       <c r="A835" s="4" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B835" s="5" t="inlineStr">
@@ -21353,19 +21353,19 @@
       </c>
       <c r="D835" s="5" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E835" s="5" t="inlineStr">
         <is>
-          <t>0:30:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="836">
       <c r="A836" s="8" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B836" s="9" t="inlineStr">
@@ -21378,19 +21378,19 @@
       </c>
       <c r="D836" s="9" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>0:29:37</t>
         </is>
       </c>
       <c r="E836" s="9" t="inlineStr">
         <is>
-          <t>0:31:12</t>
+          <t>0:32:18</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" s="4" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B837" s="5" t="inlineStr">
@@ -21408,14 +21408,14 @@
       </c>
       <c r="E837" s="5" t="inlineStr">
         <is>
-          <t>0:31:29</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" s="8" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B838" s="9" t="inlineStr">
@@ -21428,19 +21428,19 @@
       </c>
       <c r="D838" s="9" t="inlineStr">
         <is>
-          <t>0:29:08</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E838" s="9" t="inlineStr">
         <is>
-          <t>0:33:25</t>
+          <t>0:30:43</t>
         </is>
       </c>
     </row>
     <row r="839">
       <c r="A839" s="4" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B839" s="5" t="inlineStr">
@@ -21453,19 +21453,19 @@
       </c>
       <c r="D839" s="5" t="inlineStr">
         <is>
-          <t>0:29:13</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E839" s="5" t="inlineStr">
         <is>
-          <t>0:32:45</t>
+          <t>0:31:12</t>
         </is>
       </c>
     </row>
     <row r="840">
       <c r="A840" s="8" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B840" s="9" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="E840" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:29</t>
         </is>
       </c>
     </row>
@@ -21499,23 +21499,23 @@
         </is>
       </c>
       <c r="C841" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D841" s="5" t="inlineStr">
         <is>
-          <t>0:28:36</t>
+          <t>0:29:08</t>
         </is>
       </c>
       <c r="E841" s="5" t="inlineStr">
         <is>
-          <t>0:31:51</t>
+          <t>0:33:25</t>
         </is>
       </c>
     </row>
     <row r="842">
       <c r="A842" s="8" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B842" s="9" t="inlineStr">
@@ -21524,23 +21524,23 @@
         </is>
       </c>
       <c r="C842" s="9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D842" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:13</t>
         </is>
       </c>
       <c r="E842" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:45</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B843" s="5" t="inlineStr">
@@ -21549,7 +21549,7 @@
         </is>
       </c>
       <c r="C843" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D843" s="5" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
     <row r="844">
       <c r="A844" s="8" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B844" s="9" t="inlineStr">
@@ -21578,19 +21578,19 @@
       </c>
       <c r="D844" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:36</t>
         </is>
       </c>
       <c r="E844" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:51</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" s="4" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B845" s="5" t="inlineStr">
@@ -21603,19 +21603,19 @@
       </c>
       <c r="D845" s="5" t="inlineStr">
         <is>
-          <t>0:28:52</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E845" s="5" t="inlineStr">
         <is>
-          <t>0:31:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" s="8" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B846" s="9" t="inlineStr">
@@ -21628,19 +21628,19 @@
       </c>
       <c r="D846" s="9" t="inlineStr">
         <is>
-          <t>0:28:46</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E846" s="9" t="inlineStr">
         <is>
-          <t>0:32:33</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" s="4" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B847" s="5" t="inlineStr">
@@ -21653,12 +21653,12 @@
       </c>
       <c r="D847" s="5" t="inlineStr">
         <is>
-          <t>0:29:22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E847" s="5" t="inlineStr">
         <is>
-          <t>0:34:32</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21674,23 +21674,23 @@
         </is>
       </c>
       <c r="C848" s="9" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D848" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:52</t>
         </is>
       </c>
       <c r="E848" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:59</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" s="4" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B849" s="5" t="inlineStr">
@@ -21699,23 +21699,23 @@
         </is>
       </c>
       <c r="C849" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D849" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:46</t>
         </is>
       </c>
       <c r="E849" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:33</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" s="8" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B850" s="9" t="inlineStr">
@@ -21724,23 +21724,23 @@
         </is>
       </c>
       <c r="C850" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D850" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:22</t>
         </is>
       </c>
       <c r="E850" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:34:32</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" s="4" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B851" s="5" t="inlineStr">
@@ -21749,16 +21749,16 @@
         </is>
       </c>
       <c r="C851" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D851" s="5" t="inlineStr">
         <is>
-          <t>0:28:27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E851" s="5" t="inlineStr">
         <is>
-          <t>0:31:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21774,7 +21774,7 @@
         </is>
       </c>
       <c r="C852" s="9" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D852" s="9" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
     <row r="853">
       <c r="A853" s="4" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B853" s="5" t="inlineStr">
@@ -21799,7 +21799,7 @@
         </is>
       </c>
       <c r="C853" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D853" s="5" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
     <row r="854">
       <c r="A854" s="8" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B854" s="9" t="inlineStr">
@@ -21824,23 +21824,23 @@
         </is>
       </c>
       <c r="C854" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D854" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:27</t>
         </is>
       </c>
       <c r="E854" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:49</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" s="4" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B855" s="5" t="inlineStr">
@@ -21874,7 +21874,7 @@
         </is>
       </c>
       <c r="C856" s="9" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D856" s="9" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
     <row r="857">
       <c r="A857" s="4" t="inlineStr">
         <is>
-          <t>Great Scottish Run 10K</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B857" s="5" t="inlineStr">
@@ -21899,7 +21899,7 @@
         </is>
       </c>
       <c r="C857" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D857" s="5" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
     <row r="858">
       <c r="A858" s="8" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B858" s="9" t="inlineStr">
@@ -21924,7 +21924,7 @@
         </is>
       </c>
       <c r="C858" s="9" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D858" s="9" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
     <row r="859">
       <c r="A859" s="4" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B859" s="5" t="inlineStr">
@@ -21949,7 +21949,7 @@
         </is>
       </c>
       <c r="C859" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D859" s="5" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
     <row r="860">
       <c r="A860" s="8" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>Great Scottish Run 10K</t>
         </is>
       </c>
       <c r="B860" s="9" t="inlineStr">
@@ -21974,7 +21974,7 @@
         </is>
       </c>
       <c r="C860" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D860" s="9" t="inlineStr">
         <is>
@@ -21983,14 +21983,14 @@
       </c>
       <c r="E860" s="9" t="inlineStr">
         <is>
-          <t>0:31:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" s="4" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
         </is>
       </c>
       <c r="B861" s="5" t="inlineStr">
@@ -21999,23 +21999,23 @@
         </is>
       </c>
       <c r="C861" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D861" s="5" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E861" s="5" t="inlineStr">
         <is>
-          <t>0:31:11</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" s="8" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B862" s="9" t="inlineStr">
@@ -22040,7 +22040,7 @@
     <row r="863">
       <c r="A863" s="4" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B863" s="5" t="inlineStr">
@@ -22058,14 +22058,14 @@
       </c>
       <c r="E863" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:18</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" s="8" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B864" s="9" t="inlineStr">
@@ -22078,19 +22078,19 @@
       </c>
       <c r="D864" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E864" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:11</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B865" s="5" t="inlineStr">
@@ -22099,7 +22099,7 @@
         </is>
       </c>
       <c r="C865" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D865" s="5" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
     <row r="866">
       <c r="A866" s="8" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B866" s="9" t="inlineStr">
@@ -22124,7 +22124,7 @@
         </is>
       </c>
       <c r="C866" s="9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D866" s="9" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
     <row r="867">
       <c r="A867" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B867" s="5" t="inlineStr">
@@ -22149,7 +22149,7 @@
         </is>
       </c>
       <c r="C867" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D867" s="5" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
     <row r="868">
       <c r="A868" s="8" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>Run in Lyon</t>
         </is>
       </c>
       <c r="B868" s="9" t="inlineStr">
@@ -22190,7 +22190,7 @@
     <row r="869">
       <c r="A869" s="4" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B869" s="5" t="inlineStr">
@@ -22215,7 +22215,7 @@
     <row r="870">
       <c r="A870" s="8" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B870" s="9" t="inlineStr">
@@ -22228,19 +22228,19 @@
       </c>
       <c r="D870" s="9" t="inlineStr">
         <is>
-          <t>0:29:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E870" s="9" t="inlineStr">
         <is>
-          <t>0:32:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" s="4" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B871" s="5" t="inlineStr">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="D871" s="5" t="inlineStr">
         <is>
-          <t>0:29:33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E871" s="5" t="inlineStr">
@@ -22265,7 +22265,7 @@
     <row r="872">
       <c r="A872" s="8" t="inlineStr">
         <is>
-          <t>Standard Chartered KL 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B872" s="9" t="inlineStr">
@@ -22274,23 +22274,23 @@
         </is>
       </c>
       <c r="C872" s="9" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D872" s="9" t="inlineStr">
         <is>
-          <t>0:32:26</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E872" s="9" t="inlineStr">
         <is>
-          <t>0:39:23</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" s="4" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B873" s="5" t="inlineStr">
@@ -22299,23 +22299,23 @@
         </is>
       </c>
       <c r="C873" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D873" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:41</t>
         </is>
       </c>
       <c r="E873" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:51</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" s="8" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B874" s="9" t="inlineStr">
@@ -22324,11 +22324,11 @@
         </is>
       </c>
       <c r="C874" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D874" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:33</t>
         </is>
       </c>
       <c r="E874" s="9" t="inlineStr">
@@ -22340,7 +22340,7 @@
     <row r="875">
       <c r="A875" s="4" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Standard Chartered KL 10K</t>
         </is>
       </c>
       <c r="B875" s="5" t="inlineStr">
@@ -22353,19 +22353,19 @@
       </c>
       <c r="D875" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:26</t>
         </is>
       </c>
       <c r="E875" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:39:23</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" s="8" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B876" s="9" t="inlineStr">
@@ -22390,7 +22390,7 @@
     <row r="877">
       <c r="A877" s="4" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B877" s="5" t="inlineStr">
@@ -22415,7 +22415,7 @@
     <row r="878">
       <c r="A878" s="8" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B878" s="9" t="inlineStr">
@@ -22440,7 +22440,7 @@
     <row r="879">
       <c r="A879" s="4" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B879" s="5" t="inlineStr">
@@ -22465,7 +22465,7 @@
     <row r="880">
       <c r="A880" s="8" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B880" s="9" t="inlineStr">
@@ -22490,7 +22490,7 @@
     <row r="881">
       <c r="A881" s="4" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B881" s="5" t="inlineStr">
@@ -22515,7 +22515,7 @@
     <row r="882">
       <c r="A882" s="8" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B882" s="9" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="883">
       <c r="A883" s="4" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B883" s="5" t="inlineStr">
@@ -22565,7 +22565,7 @@
     <row r="884">
       <c r="A884" s="8" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B884" s="9" t="inlineStr">
@@ -22578,19 +22578,19 @@
       </c>
       <c r="D884" s="9" t="inlineStr">
         <is>
-          <t>0:28:09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E884" s="9" t="inlineStr">
         <is>
-          <t>0:32:54</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" s="4" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Vancouver Sun Run</t>
         </is>
       </c>
       <c r="B885" s="5" t="inlineStr">
@@ -22615,7 +22615,7 @@
     <row r="886">
       <c r="A886" s="8" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Vancouver Sun Run</t>
         </is>
       </c>
       <c r="B886" s="9" t="inlineStr">
@@ -22628,19 +22628,19 @@
       </c>
       <c r="D886" s="9" t="inlineStr">
         <is>
-          <t>0:29:14</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E886" s="9" t="inlineStr">
         <is>
-          <t>0:31:36</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" s="4" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Vancouver Sun Run</t>
         </is>
       </c>
       <c r="B887" s="5" t="inlineStr">
@@ -22653,28 +22653,28 @@
       </c>
       <c r="D887" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:09</t>
         </is>
       </c>
       <c r="E887" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:54</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Birmingham Run</t>
+          <t>Vitality London 10,000</t>
         </is>
       </c>
       <c r="B888" s="9" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C888" s="9" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D888" s="9" t="inlineStr">
         <is>
@@ -22690,37 +22690,37 @@
     <row r="889">
       <c r="A889" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great South Run</t>
+          <t>Vitality London 10,000</t>
         </is>
       </c>
       <c r="B889" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C889" s="5" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D889" s="5" t="inlineStr">
         <is>
-          <t>0:47:19</t>
+          <t>0:29:14</t>
         </is>
       </c>
       <c r="E889" s="5" t="inlineStr">
         <is>
-          <t>0:50:42</t>
+          <t>0:31:36</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great South Run</t>
+          <t>Vitality London 10,000</t>
         </is>
       </c>
       <c r="B890" s="9" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C890" s="9" t="n">
@@ -22740,7 +22740,7 @@
     <row r="891">
       <c r="A891" s="4" t="inlineStr">
         <is>
-          <t>Army Ten Miler</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B891" s="5" t="inlineStr">
@@ -22749,23 +22749,23 @@
         </is>
       </c>
       <c r="C891" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D891" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:15</t>
         </is>
       </c>
       <c r="E891" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:44</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B892" s="9" t="inlineStr">
@@ -22774,36 +22774,36 @@
         </is>
       </c>
       <c r="C892" s="9" t="n">
-        <v>2005</v>
+        <v>2024</v>
       </c>
       <c r="D892" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:57</t>
         </is>
       </c>
       <c r="E892" s="9" t="inlineStr">
         <is>
-          <t>0:38:22</t>
+          <t>1:10:56</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" s="4" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>AJ Bell Great Birmingham Run</t>
         </is>
       </c>
       <c r="B893" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>SEMI</t>
         </is>
       </c>
       <c r="C893" s="5" t="n">
-        <v>2009</v>
+        <v>2025</v>
       </c>
       <c r="D893" s="5" t="inlineStr">
         <is>
-          <t>0:33:31</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E893" s="5" t="inlineStr">
@@ -22815,7 +22815,7 @@
     <row r="894">
       <c r="A894" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>AJ Bell Great South Run</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
@@ -22824,23 +22824,23 @@
         </is>
       </c>
       <c r="C894" s="9" t="n">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="D894" s="9" t="inlineStr">
         <is>
-          <t>0:34:15</t>
+          <t>0:47:19</t>
         </is>
       </c>
       <c r="E894" s="9" t="inlineStr">
         <is>
-          <t>0:38:07</t>
+          <t>0:50:42</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="4" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>AJ Bell Great South Run</t>
         </is>
       </c>
       <c r="B895" s="5" t="inlineStr">
@@ -22849,23 +22849,23 @@
         </is>
       </c>
       <c r="C895" s="5" t="n">
-        <v>2012</v>
+        <v>2025</v>
       </c>
       <c r="D895" s="5" t="inlineStr">
         <is>
-          <t>0:34:40</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E895" s="5" t="inlineStr">
         <is>
-          <t>0:39:02</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>Army Ten Miler</t>
         </is>
       </c>
       <c r="B896" s="9" t="inlineStr">
@@ -22874,23 +22874,23 @@
         </is>
       </c>
       <c r="C896" s="9" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D896" s="9" t="inlineStr">
         <is>
-          <t>0:35:01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E896" s="9" t="inlineStr">
         <is>
-          <t>0:39:28</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" s="4" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>Baloise Antwerp 10 miles</t>
         </is>
       </c>
       <c r="B897" s="5" t="inlineStr">
@@ -22903,19 +22903,19 @@
       </c>
       <c r="D897" s="5" t="inlineStr">
         <is>
-          <t>0:36:10</t>
+          <t>0:48:48</t>
         </is>
       </c>
       <c r="E897" s="5" t="inlineStr">
         <is>
-          <t>0:42:05</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>Baloise Antwerp 10 miles</t>
         </is>
       </c>
       <c r="B898" s="9" t="inlineStr">
@@ -22924,23 +22924,23 @@
         </is>
       </c>
       <c r="C898" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D898" s="9" t="inlineStr">
         <is>
-          <t>0:37:02</t>
+          <t>0:47:50</t>
         </is>
       </c>
       <c r="E898" s="9" t="inlineStr">
         <is>
-          <t>0:43:48</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" s="4" t="inlineStr">
         <is>
-          <t>Boilermaker Road Race</t>
+          <t>Baloise Antwerp 10 miles</t>
         </is>
       </c>
       <c r="B899" s="5" t="inlineStr">
@@ -22949,11 +22949,11 @@
         </is>
       </c>
       <c r="C899" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D899" s="5" t="inlineStr">
         <is>
-          <t>0:42:44</t>
+          <t>0:47:21</t>
         </is>
       </c>
       <c r="E899" s="5" t="inlineStr">
@@ -22965,7 +22965,7 @@
     <row r="900">
       <c r="A900" s="8" t="inlineStr">
         <is>
-          <t>Broad Street Run</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B900" s="9" t="inlineStr">
@@ -22974,23 +22974,23 @@
         </is>
       </c>
       <c r="C900" s="9" t="n">
-        <v>2025</v>
+        <v>2005</v>
       </c>
       <c r="D900" s="9" t="inlineStr">
         <is>
-          <t>0:46:13</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E900" s="9" t="inlineStr">
         <is>
-          <t>0:54:01</t>
+          <t>0:38:22</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" s="4" t="inlineStr">
         <is>
-          <t>City2Surf</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B901" s="5" t="inlineStr">
@@ -22999,11 +22999,11 @@
         </is>
       </c>
       <c r="C901" s="5" t="n">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="D901" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:33:31</t>
         </is>
       </c>
       <c r="E901" s="5" t="inlineStr">
@@ -23015,7 +23015,7 @@
     <row r="902">
       <c r="A902" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B902" s="9" t="inlineStr">
@@ -23024,23 +23024,23 @@
         </is>
       </c>
       <c r="C902" s="9" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="D902" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:34:15</t>
         </is>
       </c>
       <c r="E902" s="9" t="inlineStr">
         <is>
-          <t>0:50:39</t>
+          <t>0:38:07</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B903" s="5" t="inlineStr">
@@ -23049,23 +23049,23 @@
         </is>
       </c>
       <c r="C903" s="5" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="D903" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:34:40</t>
         </is>
       </c>
       <c r="E903" s="5" t="inlineStr">
         <is>
-          <t>0:51:30</t>
+          <t>0:39:02</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B904" s="9" t="inlineStr">
@@ -23074,23 +23074,23 @@
         </is>
       </c>
       <c r="C904" s="9" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="D904" s="9" t="inlineStr">
         <is>
-          <t>0:44:27</t>
+          <t>0:35:01</t>
         </is>
       </c>
       <c r="E904" s="9" t="inlineStr">
         <is>
-          <t>0:51:57</t>
+          <t>0:39:28</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B905" s="5" t="inlineStr">
@@ -23099,23 +23099,23 @@
         </is>
       </c>
       <c r="C905" s="5" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="D905" s="5" t="inlineStr">
         <is>
-          <t>0:44:48</t>
+          <t>0:36:10</t>
         </is>
       </c>
       <c r="E905" s="5" t="inlineStr">
         <is>
-          <t>0:51:42</t>
+          <t>0:42:05</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B906" s="9" t="inlineStr">
@@ -23124,23 +23124,23 @@
         </is>
       </c>
       <c r="C906" s="9" t="n">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="D906" s="9" t="inlineStr">
         <is>
-          <t>0:45:28</t>
+          <t>0:37:02</t>
         </is>
       </c>
       <c r="E906" s="9" t="inlineStr">
         <is>
-          <t>0:51:33</t>
+          <t>0:43:48</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Boilermaker Road Race</t>
         </is>
       </c>
       <c r="B907" s="5" t="inlineStr">
@@ -23149,23 +23149,23 @@
         </is>
       </c>
       <c r="C907" s="5" t="n">
-        <v>2014</v>
+        <v>2025</v>
       </c>
       <c r="D907" s="5" t="inlineStr">
         <is>
-          <t>0:45:45</t>
+          <t>0:42:44</t>
         </is>
       </c>
       <c r="E907" s="5" t="inlineStr">
         <is>
-          <t>0:53:09</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Broad Street Run</t>
         </is>
       </c>
       <c r="B908" s="9" t="inlineStr">
@@ -23174,23 +23174,23 @@
         </is>
       </c>
       <c r="C908" s="9" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D908" s="9" t="inlineStr">
         <is>
-          <t>0:45:15</t>
+          <t>0:46:13</t>
         </is>
       </c>
       <c r="E908" s="9" t="inlineStr">
         <is>
-          <t>0:50:45</t>
+          <t>0:54:01</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>City2Surf</t>
         </is>
       </c>
       <c r="B909" s="5" t="inlineStr">
@@ -23199,16 +23199,16 @@
         </is>
       </c>
       <c r="C909" s="5" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D909" s="5" t="inlineStr">
         <is>
-          <t>0:49:00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E909" s="5" t="inlineStr">
         <is>
-          <t>0:55:44</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -23224,16 +23224,16 @@
         </is>
       </c>
       <c r="C910" s="9" t="n">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="D910" s="9" t="inlineStr">
         <is>
-          <t>0:44:51</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E910" s="9" t="inlineStr">
         <is>
-          <t>0:51:15</t>
+          <t>0:50:39</t>
         </is>
       </c>
     </row>
@@ -23249,23 +23249,23 @@
         </is>
       </c>
       <c r="C911" s="5" t="n">
-        <v>2025</v>
+        <v>2010</v>
       </c>
       <c r="D911" s="5" t="inlineStr">
         <is>
-          <t>0:46:07</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E911" s="5" t="inlineStr">
         <is>
-          <t>0:50:51</t>
+          <t>0:51:30</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" s="8" t="inlineStr">
         <is>
-          <t>Falmouth Road Race</t>
+          <t>Dam tot Damloop</t>
         </is>
       </c>
       <c r="B912" s="9" t="inlineStr">
@@ -23274,48 +23274,48 @@
         </is>
       </c>
       <c r="C912" s="9" t="n">
-        <v>2025</v>
+        <v>2011</v>
       </c>
       <c r="D912" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:44:27</t>
         </is>
       </c>
       <c r="E912" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:51:57</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" s="4" t="inlineStr">
         <is>
-          <t>Great Scottish Run</t>
+          <t>Dam tot Damloop</t>
         </is>
       </c>
       <c r="B913" s="5" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="C913" s="5" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="D913" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:44:48</t>
         </is>
       </c>
       <c r="E913" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:51:42</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" s="8" t="inlineStr">
         <is>
-          <t>Lilac Bloomsday Run</t>
+          <t>Dam tot Damloop</t>
         </is>
       </c>
       <c r="B914" s="9" t="inlineStr">
@@ -23324,46 +23324,246 @@
         </is>
       </c>
       <c r="C914" s="9" t="n">
-        <v>2025</v>
+        <v>2013</v>
       </c>
       <c r="D914" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:45:28</t>
         </is>
       </c>
       <c r="E914" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:51:33</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" s="4" t="inlineStr">
         <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B915" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C915" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D915" s="5" t="inlineStr">
+        <is>
+          <t>0:45:45</t>
+        </is>
+      </c>
+      <c r="E915" s="5" t="inlineStr">
+        <is>
+          <t>0:53:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B916" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C916" s="9" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D916" s="9" t="inlineStr">
+        <is>
+          <t>0:45:15</t>
+        </is>
+      </c>
+      <c r="E916" s="9" t="inlineStr">
+        <is>
+          <t>0:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B917" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C917" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D917" s="5" t="inlineStr">
+        <is>
+          <t>0:49:00</t>
+        </is>
+      </c>
+      <c r="E917" s="5" t="inlineStr">
+        <is>
+          <t>0:55:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B918" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C918" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D918" s="9" t="inlineStr">
+        <is>
+          <t>0:44:51</t>
+        </is>
+      </c>
+      <c r="E918" s="9" t="inlineStr">
+        <is>
+          <t>0:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B919" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C919" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D919" s="5" t="inlineStr">
+        <is>
+          <t>0:46:07</t>
+        </is>
+      </c>
+      <c r="E919" s="5" t="inlineStr">
+        <is>
+          <t>0:50:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="8" t="inlineStr">
+        <is>
+          <t>Falmouth Road Race</t>
+        </is>
+      </c>
+      <c r="B920" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C920" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D920" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E920" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="4" t="inlineStr">
+        <is>
+          <t>Great Scottish Run</t>
+        </is>
+      </c>
+      <c r="B921" s="5" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="C921" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D921" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E921" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="8" t="inlineStr">
+        <is>
+          <t>Lilac Bloomsday Run</t>
+        </is>
+      </c>
+      <c r="B922" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C922" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D922" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E922" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="4" t="inlineStr">
+        <is>
           <t>Manchester Road Race</t>
         </is>
       </c>
-      <c r="B915" s="5" t="inlineStr">
+      <c r="B923" s="5" t="inlineStr">
         <is>
           <t>AUTRE</t>
         </is>
       </c>
-      <c r="C915" s="5" t="n">
+      <c r="C923" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="D915" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E915" s="5" t="inlineStr">
+      <c r="D923" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E923" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E915"/>
+  <autoFilter ref="A1:E923"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Chronos_Vainqueurs.xlsx
+++ b/Chronos_Vainqueurs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$923</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$933</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E923"/>
+  <dimension ref="A1:E933"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -22749,16 +22749,16 @@
         </is>
       </c>
       <c r="C891" s="5" t="n">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="D891" s="5" t="inlineStr">
         <is>
-          <t>1:00:15</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E891" s="5" t="inlineStr">
         <is>
-          <t>1:10:44</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22774,36 +22774,36 @@
         </is>
       </c>
       <c r="C892" s="9" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="D892" s="9" t="inlineStr">
         <is>
-          <t>0:59:57</t>
+          <t>0:59:05</t>
         </is>
       </c>
       <c r="E892" s="9" t="inlineStr">
         <is>
-          <t>1:10:56</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Birmingham Run</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B893" s="5" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="C893" s="5" t="n">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="D893" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:01:47</t>
         </is>
       </c>
       <c r="E893" s="5" t="inlineStr">
@@ -22815,7 +22815,7 @@
     <row r="894">
       <c r="A894" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great South Run</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
@@ -22824,23 +22824,23 @@
         </is>
       </c>
       <c r="C894" s="9" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="D894" s="9" t="inlineStr">
         <is>
-          <t>0:47:19</t>
+          <t>1:02:07</t>
         </is>
       </c>
       <c r="E894" s="9" t="inlineStr">
         <is>
-          <t>0:50:42</t>
+          <t>1:13:51</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great South Run</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B895" s="5" t="inlineStr">
@@ -22849,23 +22849,23 @@
         </is>
       </c>
       <c r="C895" s="5" t="n">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="D895" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:37</t>
         </is>
       </c>
       <c r="E895" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:13:42</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="8" t="inlineStr">
         <is>
-          <t>Army Ten Miler</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B896" s="9" t="inlineStr">
@@ -22874,23 +22874,23 @@
         </is>
       </c>
       <c r="C896" s="9" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="D896" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:02:56</t>
         </is>
       </c>
       <c r="E896" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:14:38</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" s="4" t="inlineStr">
         <is>
-          <t>Baloise Antwerp 10 miles</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B897" s="5" t="inlineStr">
@@ -22899,23 +22899,23 @@
         </is>
       </c>
       <c r="C897" s="5" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D897" s="5" t="inlineStr">
         <is>
-          <t>0:48:48</t>
+          <t>1:00:34</t>
         </is>
       </c>
       <c r="E897" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:13:04</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" s="8" t="inlineStr">
         <is>
-          <t>Baloise Antwerp 10 miles</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B898" s="9" t="inlineStr">
@@ -22924,23 +22924,23 @@
         </is>
       </c>
       <c r="C898" s="9" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D898" s="9" t="inlineStr">
         <is>
-          <t>0:47:50</t>
+          <t>0:59:31</t>
         </is>
       </c>
       <c r="E898" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:09:50</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" s="4" t="inlineStr">
         <is>
-          <t>Baloise Antwerp 10 miles</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B899" s="5" t="inlineStr">
@@ -22949,23 +22949,23 @@
         </is>
       </c>
       <c r="C899" s="5" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D899" s="5" t="inlineStr">
         <is>
-          <t>0:47:21</t>
+          <t>1:00:01</t>
         </is>
       </c>
       <c r="E899" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:11:11</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B900" s="9" t="inlineStr">
@@ -22974,23 +22974,23 @@
         </is>
       </c>
       <c r="C900" s="9" t="n">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="D900" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:00:15</t>
         </is>
       </c>
       <c r="E900" s="9" t="inlineStr">
         <is>
-          <t>0:38:22</t>
+          <t>1:10:44</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" s="4" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B901" s="5" t="inlineStr">
@@ -22999,23 +22999,23 @@
         </is>
       </c>
       <c r="C901" s="5" t="n">
-        <v>2009</v>
+        <v>2024</v>
       </c>
       <c r="D901" s="5" t="inlineStr">
         <is>
-          <t>0:33:31</t>
+          <t>0:59:57</t>
         </is>
       </c>
       <c r="E901" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:56</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B902" s="9" t="inlineStr">
@@ -23024,48 +23024,48 @@
         </is>
       </c>
       <c r="C902" s="9" t="n">
-        <v>2010</v>
+        <v>2025</v>
       </c>
       <c r="D902" s="9" t="inlineStr">
         <is>
-          <t>0:34:15</t>
+          <t>0:59:26</t>
         </is>
       </c>
       <c r="E902" s="9" t="inlineStr">
         <is>
-          <t>0:38:07</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" s="4" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>AJ Bell Great Birmingham Run</t>
         </is>
       </c>
       <c r="B903" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>SEMI</t>
         </is>
       </c>
       <c r="C903" s="5" t="n">
-        <v>2012</v>
+        <v>2025</v>
       </c>
       <c r="D903" s="5" t="inlineStr">
         <is>
-          <t>0:34:40</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E903" s="5" t="inlineStr">
         <is>
-          <t>0:39:02</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>AJ Bell Great South Run</t>
         </is>
       </c>
       <c r="B904" s="9" t="inlineStr">
@@ -23074,23 +23074,23 @@
         </is>
       </c>
       <c r="C904" s="9" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D904" s="9" t="inlineStr">
         <is>
-          <t>0:35:01</t>
+          <t>0:47:19</t>
         </is>
       </c>
       <c r="E904" s="9" t="inlineStr">
         <is>
-          <t>0:39:28</t>
+          <t>0:50:42</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" s="4" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>AJ Bell Great South Run</t>
         </is>
       </c>
       <c r="B905" s="5" t="inlineStr">
@@ -23099,23 +23099,23 @@
         </is>
       </c>
       <c r="C905" s="5" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D905" s="5" t="inlineStr">
         <is>
-          <t>0:36:10</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E905" s="5" t="inlineStr">
         <is>
-          <t>0:42:05</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>Army Ten Miler</t>
         </is>
       </c>
       <c r="B906" s="9" t="inlineStr">
@@ -23124,23 +23124,23 @@
         </is>
       </c>
       <c r="C906" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D906" s="9" t="inlineStr">
         <is>
-          <t>0:37:02</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E906" s="9" t="inlineStr">
         <is>
-          <t>0:43:48</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" s="4" t="inlineStr">
         <is>
-          <t>Boilermaker Road Race</t>
+          <t>Baloise Antwerp 10 miles</t>
         </is>
       </c>
       <c r="B907" s="5" t="inlineStr">
@@ -23149,11 +23149,11 @@
         </is>
       </c>
       <c r="C907" s="5" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D907" s="5" t="inlineStr">
         <is>
-          <t>0:42:44</t>
+          <t>0:48:48</t>
         </is>
       </c>
       <c r="E907" s="5" t="inlineStr">
@@ -23165,7 +23165,7 @@
     <row r="908">
       <c r="A908" s="8" t="inlineStr">
         <is>
-          <t>Broad Street Run</t>
+          <t>Baloise Antwerp 10 miles</t>
         </is>
       </c>
       <c r="B908" s="9" t="inlineStr">
@@ -23174,23 +23174,23 @@
         </is>
       </c>
       <c r="C908" s="9" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D908" s="9" t="inlineStr">
         <is>
-          <t>0:46:13</t>
+          <t>0:47:50</t>
         </is>
       </c>
       <c r="E908" s="9" t="inlineStr">
         <is>
-          <t>0:54:01</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" s="4" t="inlineStr">
         <is>
-          <t>City2Surf</t>
+          <t>Baloise Antwerp 10 miles</t>
         </is>
       </c>
       <c r="B909" s="5" t="inlineStr">
@@ -23203,7 +23203,7 @@
       </c>
       <c r="D909" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:47:21</t>
         </is>
       </c>
       <c r="E909" s="5" t="inlineStr">
@@ -23215,7 +23215,7 @@
     <row r="910">
       <c r="A910" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B910" s="9" t="inlineStr">
@@ -23224,7 +23224,7 @@
         </is>
       </c>
       <c r="C910" s="9" t="n">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="D910" s="9" t="inlineStr">
         <is>
@@ -23233,14 +23233,14 @@
       </c>
       <c r="E910" s="9" t="inlineStr">
         <is>
-          <t>0:50:39</t>
+          <t>0:38:22</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B911" s="5" t="inlineStr">
@@ -23249,23 +23249,23 @@
         </is>
       </c>
       <c r="C911" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D911" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:33:31</t>
         </is>
       </c>
       <c r="E911" s="5" t="inlineStr">
         <is>
-          <t>0:51:30</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B912" s="9" t="inlineStr">
@@ -23274,23 +23274,23 @@
         </is>
       </c>
       <c r="C912" s="9" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D912" s="9" t="inlineStr">
         <is>
-          <t>0:44:27</t>
+          <t>0:34:15</t>
         </is>
       </c>
       <c r="E912" s="9" t="inlineStr">
         <is>
-          <t>0:51:57</t>
+          <t>0:38:07</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B913" s="5" t="inlineStr">
@@ -23303,19 +23303,19 @@
       </c>
       <c r="D913" s="5" t="inlineStr">
         <is>
-          <t>0:44:48</t>
+          <t>0:34:40</t>
         </is>
       </c>
       <c r="E913" s="5" t="inlineStr">
         <is>
-          <t>0:51:42</t>
+          <t>0:39:02</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B914" s="9" t="inlineStr">
@@ -23324,23 +23324,23 @@
         </is>
       </c>
       <c r="C914" s="9" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="D914" s="9" t="inlineStr">
         <is>
-          <t>0:45:28</t>
+          <t>0:35:01</t>
         </is>
       </c>
       <c r="E914" s="9" t="inlineStr">
         <is>
-          <t>0:51:33</t>
+          <t>0:39:28</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B915" s="5" t="inlineStr">
@@ -23349,23 +23349,23 @@
         </is>
       </c>
       <c r="C915" s="5" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="D915" s="5" t="inlineStr">
         <is>
-          <t>0:45:45</t>
+          <t>0:36:10</t>
         </is>
       </c>
       <c r="E915" s="5" t="inlineStr">
         <is>
-          <t>0:53:09</t>
+          <t>0:42:05</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B916" s="9" t="inlineStr">
@@ -23374,23 +23374,23 @@
         </is>
       </c>
       <c r="C916" s="9" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="D916" s="9" t="inlineStr">
         <is>
-          <t>0:45:15</t>
+          <t>0:37:02</t>
         </is>
       </c>
       <c r="E916" s="9" t="inlineStr">
         <is>
-          <t>0:50:45</t>
+          <t>0:43:48</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Boilermaker Road Race</t>
         </is>
       </c>
       <c r="B917" s="5" t="inlineStr">
@@ -23399,23 +23399,23 @@
         </is>
       </c>
       <c r="C917" s="5" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D917" s="5" t="inlineStr">
         <is>
-          <t>0:49:00</t>
+          <t>0:42:44</t>
         </is>
       </c>
       <c r="E917" s="5" t="inlineStr">
         <is>
-          <t>0:55:44</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Broad Street Run</t>
         </is>
       </c>
       <c r="B918" s="9" t="inlineStr">
@@ -23424,23 +23424,23 @@
         </is>
       </c>
       <c r="C918" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D918" s="9" t="inlineStr">
         <is>
-          <t>0:44:51</t>
+          <t>0:46:13</t>
         </is>
       </c>
       <c r="E918" s="9" t="inlineStr">
         <is>
-          <t>0:51:15</t>
+          <t>0:54:01</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>City2Surf</t>
         </is>
       </c>
       <c r="B919" s="5" t="inlineStr">
@@ -23449,23 +23449,23 @@
         </is>
       </c>
       <c r="C919" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D919" s="5" t="inlineStr">
         <is>
-          <t>0:46:07</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E919" s="5" t="inlineStr">
         <is>
-          <t>0:50:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" s="8" t="inlineStr">
         <is>
-          <t>Falmouth Road Race</t>
+          <t>Dam tot Damloop</t>
         </is>
       </c>
       <c r="B920" s="9" t="inlineStr">
@@ -23474,7 +23474,7 @@
         </is>
       </c>
       <c r="C920" s="9" t="n">
-        <v>2025</v>
+        <v>2009</v>
       </c>
       <c r="D920" s="9" t="inlineStr">
         <is>
@@ -23483,23 +23483,23 @@
       </c>
       <c r="E920" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:50:39</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" s="4" t="inlineStr">
         <is>
-          <t>Great Scottish Run</t>
+          <t>Dam tot Damloop</t>
         </is>
       </c>
       <c r="B921" s="5" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="C921" s="5" t="n">
-        <v>2025</v>
+        <v>2010</v>
       </c>
       <c r="D921" s="5" t="inlineStr">
         <is>
@@ -23508,14 +23508,14 @@
       </c>
       <c r="E921" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:51:30</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" s="8" t="inlineStr">
         <is>
-          <t>Lilac Bloomsday Run</t>
+          <t>Dam tot Damloop</t>
         </is>
       </c>
       <c r="B922" s="9" t="inlineStr">
@@ -23524,46 +23524,296 @@
         </is>
       </c>
       <c r="C922" s="9" t="n">
-        <v>2025</v>
+        <v>2011</v>
       </c>
       <c r="D922" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:44:27</t>
         </is>
       </c>
       <c r="E922" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:51:57</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" s="4" t="inlineStr">
         <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B923" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C923" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D923" s="5" t="inlineStr">
+        <is>
+          <t>0:44:48</t>
+        </is>
+      </c>
+      <c r="E923" s="5" t="inlineStr">
+        <is>
+          <t>0:51:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B924" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C924" s="9" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D924" s="9" t="inlineStr">
+        <is>
+          <t>0:45:28</t>
+        </is>
+      </c>
+      <c r="E924" s="9" t="inlineStr">
+        <is>
+          <t>0:51:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B925" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C925" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D925" s="5" t="inlineStr">
+        <is>
+          <t>0:45:45</t>
+        </is>
+      </c>
+      <c r="E925" s="5" t="inlineStr">
+        <is>
+          <t>0:53:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B926" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C926" s="9" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D926" s="9" t="inlineStr">
+        <is>
+          <t>0:45:15</t>
+        </is>
+      </c>
+      <c r="E926" s="9" t="inlineStr">
+        <is>
+          <t>0:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B927" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C927" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D927" s="5" t="inlineStr">
+        <is>
+          <t>0:49:00</t>
+        </is>
+      </c>
+      <c r="E927" s="5" t="inlineStr">
+        <is>
+          <t>0:55:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B928" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C928" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D928" s="9" t="inlineStr">
+        <is>
+          <t>0:44:51</t>
+        </is>
+      </c>
+      <c r="E928" s="9" t="inlineStr">
+        <is>
+          <t>0:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B929" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C929" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D929" s="5" t="inlineStr">
+        <is>
+          <t>0:46:07</t>
+        </is>
+      </c>
+      <c r="E929" s="5" t="inlineStr">
+        <is>
+          <t>0:50:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="8" t="inlineStr">
+        <is>
+          <t>Falmouth Road Race</t>
+        </is>
+      </c>
+      <c r="B930" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C930" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D930" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E930" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="4" t="inlineStr">
+        <is>
+          <t>Great Scottish Run</t>
+        </is>
+      </c>
+      <c r="B931" s="5" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="C931" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D931" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E931" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="8" t="inlineStr">
+        <is>
+          <t>Lilac Bloomsday Run</t>
+        </is>
+      </c>
+      <c r="B932" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C932" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D932" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E932" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="4" t="inlineStr">
+        <is>
           <t>Manchester Road Race</t>
         </is>
       </c>
-      <c r="B923" s="5" t="inlineStr">
+      <c r="B933" s="5" t="inlineStr">
         <is>
           <t>AUTRE</t>
         </is>
       </c>
-      <c r="C923" s="5" t="n">
+      <c r="C933" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="D923" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E923" s="5" t="inlineStr">
+      <c r="D933" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E933" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E923"/>
+  <autoFilter ref="A1:E933"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Chronos_Vainqueurs.xlsx
+++ b/Chronos_Vainqueurs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chronos Vainqueurs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$919</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chronos Vainqueurs'!$A$1:$E$937</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E919"/>
+  <dimension ref="A1:E937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -19524,23 +19524,23 @@
         </is>
       </c>
       <c r="C762" s="7" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D762" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:58</t>
         </is>
       </c>
       <c r="E762" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:12:54</t>
         </is>
       </c>
     </row>
     <row r="763">
       <c r="A763" s="4" t="inlineStr">
         <is>
-          <t>Nike Melbourne Marathon Festival</t>
+          <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
       <c r="B763" s="5" t="inlineStr">
@@ -19549,23 +19549,23 @@
         </is>
       </c>
       <c r="C763" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D763" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:05</t>
         </is>
       </c>
       <c r="E763" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:11:38</t>
         </is>
       </c>
     </row>
     <row r="764">
       <c r="A764" s="6" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
       <c r="B764" s="7" t="inlineStr">
@@ -19574,23 +19574,23 @@
         </is>
       </c>
       <c r="C764" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D764" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:08</t>
         </is>
       </c>
       <c r="E764" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:12:41</t>
         </is>
       </c>
     </row>
     <row r="765">
       <c r="A765" s="4" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
       <c r="B765" s="5" t="inlineStr">
@@ -19599,7 +19599,7 @@
         </is>
       </c>
       <c r="C765" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D765" s="5" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
     <row r="766">
       <c r="A766" s="6" t="inlineStr">
         <is>
-          <t>Riyadh Marathon (Half)</t>
+          <t>Nike Melbourne Marathon Festival</t>
         </is>
       </c>
       <c r="B766" s="7" t="inlineStr">
@@ -19649,7 +19649,7 @@
         </is>
       </c>
       <c r="C767" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D767" s="5" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
     <row r="768">
       <c r="A768" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B768" s="7" t="inlineStr">
@@ -19674,7 +19674,7 @@
         </is>
       </c>
       <c r="C768" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D768" s="7" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
     <row r="769">
       <c r="A769" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B769" s="5" t="inlineStr">
@@ -19699,7 +19699,7 @@
         </is>
       </c>
       <c r="C769" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D769" s="5" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
     <row r="770">
       <c r="A770" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Las Vegas</t>
+          <t>Riyadh Marathon (Half)</t>
         </is>
       </c>
       <c r="B770" s="7" t="inlineStr">
@@ -19724,7 +19724,7 @@
         </is>
       </c>
       <c r="C770" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D770" s="7" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         </is>
       </c>
       <c r="C771" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D771" s="5" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
     <row r="772">
       <c r="A772" s="6" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series Mexico City</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B772" s="7" t="inlineStr">
@@ -19774,7 +19774,7 @@
         </is>
       </c>
       <c r="C772" s="7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D772" s="7" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
     <row r="773">
       <c r="A773" s="4" t="inlineStr">
         <is>
-          <t>Rock 'n' Roll Running Series San Diego</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B773" s="5" t="inlineStr">
@@ -19815,7 +19815,7 @@
     <row r="774">
       <c r="A774" s="6" t="inlineStr">
         <is>
-          <t>Royal Parks Half Marathon</t>
+          <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
       <c r="B774" s="7" t="inlineStr">
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="C774" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D774" s="7" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
     <row r="775">
       <c r="A775" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Rock 'n' Roll Running Series Mexico City</t>
         </is>
       </c>
       <c r="B775" s="5" t="inlineStr">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="C775" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D775" s="5" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
     <row r="776">
       <c r="A776" s="6" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Rock 'n' Roll Running Series San Diego</t>
         </is>
       </c>
       <c r="B776" s="7" t="inlineStr">
@@ -19874,23 +19874,23 @@
         </is>
       </c>
       <c r="C776" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D776" s="7" t="inlineStr">
         <is>
-          <t>1:05:44</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E776" s="7" t="inlineStr">
         <is>
-          <t>1:18:34</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (Semi)</t>
+          <t>Royal Parks Half Marathon</t>
         </is>
       </c>
       <c r="B777" s="5" t="inlineStr">
@@ -19915,7 +19915,7 @@
     <row r="778">
       <c r="A778" s="6" t="inlineStr">
         <is>
-          <t>Semi-Marathon de Boulogne-Billancourt</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B778" s="7" t="inlineStr">
@@ -19924,7 +19924,7 @@
         </is>
       </c>
       <c r="C778" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D778" s="7" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
     <row r="779">
       <c r="A779" s="4" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B779" s="5" t="inlineStr">
@@ -19949,23 +19949,23 @@
         </is>
       </c>
       <c r="C779" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D779" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:05:44</t>
         </is>
       </c>
       <c r="E779" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:18:34</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" s="6" t="inlineStr">
         <is>
-          <t>St. Jude Rock 'n' Roll Series Nashville</t>
+          <t>Run in Lyon (Semi)</t>
         </is>
       </c>
       <c r="B780" s="7" t="inlineStr">
@@ -19990,7 +19990,7 @@
     <row r="781">
       <c r="A781" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>Semi-Marathon de Boulogne-Billancourt</t>
         </is>
       </c>
       <c r="B781" s="5" t="inlineStr">
@@ -19999,23 +19999,23 @@
         </is>
       </c>
       <c r="C781" s="5" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="D781" s="5" t="inlineStr">
         <is>
-          <t>1:01:13</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E781" s="5" t="inlineStr">
         <is>
-          <t>1:09:28</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" s="6" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
         </is>
       </c>
       <c r="B782" s="7" t="inlineStr">
@@ -20040,7 +20040,7 @@
     <row r="783">
       <c r="A783" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Hong Kong Half Marathon</t>
+          <t>St. Jude Rock 'n' Roll Series Nashville</t>
         </is>
       </c>
       <c r="B783" s="5" t="inlineStr">
@@ -20049,7 +20049,7 @@
         </is>
       </c>
       <c r="C783" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D783" s="5" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
     <row r="784">
       <c r="A784" s="6" t="inlineStr">
         <is>
-          <t>Standard Chartered KL Half Marathon</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B784" s="7" t="inlineStr">
@@ -20074,23 +20074,23 @@
         </is>
       </c>
       <c r="C784" s="7" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D784" s="7" t="inlineStr">
         <is>
-          <t>1:11:08</t>
+          <t>1:01:13</t>
         </is>
       </c>
       <c r="E784" s="7" t="inlineStr">
         <is>
-          <t>1:23:55</t>
+          <t>1:09:28</t>
         </is>
       </c>
     </row>
     <row r="785">
       <c r="A785" s="4" t="inlineStr">
         <is>
-          <t>Standard Chartered Singapore Half Marathon</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B785" s="5" t="inlineStr">
@@ -20115,7 +20115,7 @@
     <row r="786">
       <c r="A786" s="6" t="inlineStr">
         <is>
-          <t>TCS Mizuno Half Marathon</t>
+          <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
       <c r="B786" s="7" t="inlineStr">
@@ -20124,23 +20124,23 @@
         </is>
       </c>
       <c r="C786" s="7" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D786" s="7" t="inlineStr">
         <is>
-          <t>1:05:23</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E786" s="7" t="inlineStr">
         <is>
-          <t>1:13:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="787">
       <c r="A787" s="4" t="inlineStr">
         <is>
-          <t>TCS Mizuno Half Marathon</t>
+          <t>Standard Chartered KL Half Marathon</t>
         </is>
       </c>
       <c r="B787" s="5" t="inlineStr">
@@ -20149,23 +20149,23 @@
         </is>
       </c>
       <c r="C787" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D787" s="5" t="inlineStr">
         <is>
-          <t>1:06:28</t>
+          <t>1:11:08</t>
         </is>
       </c>
       <c r="E787" s="5" t="inlineStr">
         <is>
-          <t>1:17:54</t>
+          <t>1:23:55</t>
         </is>
       </c>
     </row>
     <row r="788">
       <c r="A788" s="6" t="inlineStr">
         <is>
-          <t>TCS Mizuno Half Marathon</t>
+          <t>Standard Chartered Singapore Half Marathon</t>
         </is>
       </c>
       <c r="B788" s="7" t="inlineStr">
@@ -20199,23 +20199,23 @@
         </is>
       </c>
       <c r="C789" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D789" s="5" t="inlineStr">
         <is>
-          <t>1:04:21</t>
+          <t>1:05:23</t>
         </is>
       </c>
       <c r="E789" s="5" t="inlineStr">
         <is>
-          <t>1:10:02</t>
+          <t>1:13:59</t>
         </is>
       </c>
     </row>
     <row r="790">
       <c r="A790" s="6" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
       <c r="B790" s="7" t="inlineStr">
@@ -20224,23 +20224,23 @@
         </is>
       </c>
       <c r="C790" s="7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D790" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:28</t>
         </is>
       </c>
       <c r="E790" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:17:54</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" s="4" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
       <c r="B791" s="5" t="inlineStr">
@@ -20249,7 +20249,7 @@
         </is>
       </c>
       <c r="C791" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D791" s="5" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
     <row r="792">
       <c r="A792" s="6" t="inlineStr">
         <is>
-          <t>TCS Toronto Waterfront Marathon (Half)</t>
+          <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
       <c r="B792" s="7" t="inlineStr">
@@ -20278,19 +20278,19 @@
       </c>
       <c r="D792" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:04:21</t>
         </is>
       </c>
       <c r="E792" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:02</t>
         </is>
       </c>
     </row>
     <row r="793">
       <c r="A793" s="4" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B793" s="5" t="inlineStr">
@@ -20315,7 +20315,7 @@
     <row r="794">
       <c r="A794" s="6" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B794" s="7" t="inlineStr">
@@ -20340,7 +20340,7 @@
     <row r="795">
       <c r="A795" s="4" t="inlineStr">
         <is>
-          <t>Taipei Half Marathon</t>
+          <t>TCS Toronto Waterfront Marathon (Half)</t>
         </is>
       </c>
       <c r="B795" s="5" t="inlineStr">
@@ -20365,7 +20365,7 @@
     <row r="796">
       <c r="A796" s="6" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon (Half)</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B796" s="7" t="inlineStr">
@@ -20374,7 +20374,7 @@
         </is>
       </c>
       <c r="C796" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D796" s="7" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
     <row r="797">
       <c r="A797" s="4" t="inlineStr">
         <is>
-          <t>Tata Mumbai Marathon (Half)</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B797" s="5" t="inlineStr">
@@ -20399,7 +20399,7 @@
         </is>
       </c>
       <c r="C797" s="5" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D797" s="5" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
     <row r="798">
       <c r="A798" s="6" t="inlineStr">
         <is>
-          <t>The Big Half</t>
+          <t>Taipei Half Marathon</t>
         </is>
       </c>
       <c r="B798" s="7" t="inlineStr">
@@ -20440,7 +20440,7 @@
     <row r="799">
       <c r="A799" s="4" t="inlineStr">
         <is>
-          <t>Tokyo Legacy Half Marathon</t>
+          <t>Tata Mumbai Marathon (Half)</t>
         </is>
       </c>
       <c r="B799" s="5" t="inlineStr">
@@ -20465,7 +20465,7 @@
     <row r="800">
       <c r="A800" s="6" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>Tata Mumbai Marathon (Half)</t>
         </is>
       </c>
       <c r="B800" s="7" t="inlineStr">
@@ -20474,23 +20474,23 @@
         </is>
       </c>
       <c r="C800" s="7" t="n">
-        <v>2006</v>
+        <v>2026</v>
       </c>
       <c r="D800" s="7" t="inlineStr">
         <is>
-          <t>1:01:22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E800" s="7" t="inlineStr">
         <is>
-          <t>1:09:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="801">
       <c r="A801" s="4" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>The Big Half</t>
         </is>
       </c>
       <c r="B801" s="5" t="inlineStr">
@@ -20499,23 +20499,23 @@
         </is>
       </c>
       <c r="C801" s="5" t="n">
-        <v>2007</v>
+        <v>2025</v>
       </c>
       <c r="D801" s="5" t="inlineStr">
         <is>
-          <t>0:59:24</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E801" s="5" t="inlineStr">
         <is>
-          <t>1:10:32</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="802">
       <c r="A802" s="6" t="inlineStr">
         <is>
-          <t>United Airlines NYC Half</t>
+          <t>Tokyo Legacy Half Marathon</t>
         </is>
       </c>
       <c r="B802" s="7" t="inlineStr">
@@ -20524,16 +20524,16 @@
         </is>
       </c>
       <c r="C802" s="7" t="n">
-        <v>2008</v>
+        <v>2025</v>
       </c>
       <c r="D802" s="7" t="inlineStr">
         <is>
-          <t>1:00:58</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E802" s="7" t="inlineStr">
         <is>
-          <t>1:10:19</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -20549,16 +20549,16 @@
         </is>
       </c>
       <c r="C803" s="5" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="D803" s="5" t="inlineStr">
         <is>
-          <t>1:01:06</t>
+          <t>1:01:22</t>
         </is>
       </c>
       <c r="E803" s="5" t="inlineStr">
         <is>
-          <t>1:09:32</t>
+          <t>1:09:43</t>
         </is>
       </c>
     </row>
@@ -20574,16 +20574,16 @@
         </is>
       </c>
       <c r="C804" s="7" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="D804" s="7" t="inlineStr">
         <is>
-          <t>0:59:52</t>
+          <t>0:59:24</t>
         </is>
       </c>
       <c r="E804" s="7" t="inlineStr">
         <is>
-          <t>1:09:25</t>
+          <t>1:10:32</t>
         </is>
       </c>
     </row>
@@ -20599,16 +20599,16 @@
         </is>
       </c>
       <c r="C805" s="5" t="n">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="D805" s="5" t="inlineStr">
         <is>
-          <t>1:00:23</t>
+          <t>1:00:58</t>
         </is>
       </c>
       <c r="E805" s="5" t="inlineStr">
         <is>
-          <t>1:08:52</t>
+          <t>1:10:19</t>
         </is>
       </c>
     </row>
@@ -20624,16 +20624,16 @@
         </is>
       </c>
       <c r="C806" s="7" t="n">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="D806" s="7" t="inlineStr">
         <is>
-          <t>0:59:39</t>
+          <t>1:01:06</t>
         </is>
       </c>
       <c r="E806" s="7" t="inlineStr">
         <is>
-          <t>1:08:35</t>
+          <t>1:09:32</t>
         </is>
       </c>
     </row>
@@ -20649,16 +20649,16 @@
         </is>
       </c>
       <c r="C807" s="5" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="D807" s="5" t="inlineStr">
         <is>
-          <t>1:01:02</t>
+          <t>0:59:52</t>
         </is>
       </c>
       <c r="E807" s="5" t="inlineStr">
         <is>
-          <t>1:09:09</t>
+          <t>1:09:25</t>
         </is>
       </c>
     </row>
@@ -20674,16 +20674,16 @@
         </is>
       </c>
       <c r="C808" s="7" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="D808" s="7" t="inlineStr">
         <is>
-          <t>1:00:50</t>
+          <t>1:00:23</t>
         </is>
       </c>
       <c r="E808" s="7" t="inlineStr">
         <is>
-          <t>1:08:31</t>
+          <t>1:08:52</t>
         </is>
       </c>
     </row>
@@ -20699,16 +20699,16 @@
         </is>
       </c>
       <c r="C809" s="5" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="D809" s="5" t="inlineStr">
         <is>
-          <t>1:01:31</t>
+          <t>0:59:39</t>
         </is>
       </c>
       <c r="E809" s="5" t="inlineStr">
         <is>
-          <t>1:07:04</t>
+          <t>1:08:35</t>
         </is>
       </c>
     </row>
@@ -20724,23 +20724,23 @@
         </is>
       </c>
       <c r="C810" s="7" t="n">
-        <v>2026</v>
+        <v>2013</v>
       </c>
       <c r="D810" s="7" t="inlineStr">
         <is>
-          <t>0:59:30</t>
+          <t>1:01:02</t>
         </is>
       </c>
       <c r="E810" s="7" t="inlineStr">
         <is>
-          <t>1:06:33</t>
+          <t>1:09:09</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" s="4" t="inlineStr">
         <is>
-          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B811" s="5" t="inlineStr">
@@ -20749,23 +20749,23 @@
         </is>
       </c>
       <c r="C811" s="5" t="n">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D811" s="5" t="inlineStr">
         <is>
-          <t>0:58:02</t>
+          <t>1:00:50</t>
         </is>
       </c>
       <c r="E811" s="5" t="inlineStr">
         <is>
-          <t>1:03:08</t>
+          <t>1:08:31</t>
         </is>
       </c>
     </row>
     <row r="812">
       <c r="A812" s="6" t="inlineStr">
         <is>
-          <t>Vedanta Delhi Half Marathon</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B812" s="7" t="inlineStr">
@@ -20778,19 +20778,19 @@
       </c>
       <c r="D812" s="7" t="inlineStr">
         <is>
-          <t>0:59:50</t>
+          <t>1:01:31</t>
         </is>
       </c>
       <c r="E812" s="7" t="inlineStr">
         <is>
-          <t>1:07:20</t>
+          <t>1:07:04</t>
         </is>
       </c>
     </row>
     <row r="813">
       <c r="A813" s="4" t="inlineStr">
         <is>
-          <t>Vienna City Half Marathon</t>
+          <t>United Airlines NYC Half</t>
         </is>
       </c>
       <c r="B813" s="5" t="inlineStr">
@@ -20799,23 +20799,23 @@
         </is>
       </c>
       <c r="C813" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D813" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:30</t>
         </is>
       </c>
       <c r="E813" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:06:33</t>
         </is>
       </c>
     </row>
     <row r="814">
       <c r="A814" s="6" t="inlineStr">
         <is>
-          <t>Walt Disney World Marathon Weekend</t>
+          <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
       <c r="B814" s="7" t="inlineStr">
@@ -20828,19 +20828,19 @@
       </c>
       <c r="D814" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:58:02</t>
         </is>
       </c>
       <c r="E814" s="7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:03:08</t>
         </is>
       </c>
     </row>
     <row r="815">
       <c r="A815" s="4" t="inlineStr">
         <is>
-          <t>Walt Disney World Marathon Weekend</t>
+          <t>Vedanta Delhi Half Marathon</t>
         </is>
       </c>
       <c r="B815" s="5" t="inlineStr">
@@ -20849,23 +20849,23 @@
         </is>
       </c>
       <c r="C815" s="5" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D815" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:50</t>
         </is>
       </c>
       <c r="E815" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:07:20</t>
         </is>
       </c>
     </row>
     <row r="816">
       <c r="A816" s="6" t="inlineStr">
         <is>
-          <t>Warsaw Half Marathon</t>
+          <t>Vienna City Half Marathon</t>
         </is>
       </c>
       <c r="B816" s="7" t="inlineStr">
@@ -20874,7 +20874,7 @@
         </is>
       </c>
       <c r="C816" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D816" s="7" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
     <row r="817">
       <c r="A817" s="4" t="inlineStr">
         <is>
-          <t>Warsaw Half Marathon</t>
+          <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
       <c r="B817" s="5" t="inlineStr">
@@ -20915,7 +20915,7 @@
     <row r="818">
       <c r="A818" s="6" t="inlineStr">
         <is>
-          <t>Wizz Air Rome Half Marathon by Brooks</t>
+          <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
       <c r="B818" s="7" t="inlineStr">
@@ -20924,7 +20924,7 @@
         </is>
       </c>
       <c r="C818" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D818" s="7" t="inlineStr">
         <is>
@@ -20940,7 +20940,7 @@
     <row r="819">
       <c r="A819" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Warsaw Half Marathon</t>
         </is>
       </c>
       <c r="B819" s="5" t="inlineStr">
@@ -20949,7 +20949,7 @@
         </is>
       </c>
       <c r="C819" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D819" s="5" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
     <row r="820">
       <c r="A820" s="6" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Warsaw Half Marathon</t>
         </is>
       </c>
       <c r="B820" s="7" t="inlineStr">
@@ -20974,7 +20974,7 @@
         </is>
       </c>
       <c r="C820" s="7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D820" s="7" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
     <row r="821">
       <c r="A821" s="4" t="inlineStr">
         <is>
-          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+          <t>Wizz Air Rome Half Marathon by Brooks</t>
         </is>
       </c>
       <c r="B821" s="5" t="inlineStr">
@@ -21013,43 +21013,43 @@
       </c>
     </row>
     <row r="822">
-      <c r="A822" s="8" t="inlineStr">
-        <is>
-          <t>10K Montmartre</t>
-        </is>
-      </c>
-      <c r="B822" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C822" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D822" s="9" t="inlineStr">
-        <is>
-          <t>0:31:14</t>
-        </is>
-      </c>
-      <c r="E822" s="9" t="inlineStr">
-        <is>
-          <t>0:35:46</t>
+      <c r="A822" s="6" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+        </is>
+      </c>
+      <c r="B822" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C822" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D822" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E822" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="823">
       <c r="A823" s="4" t="inlineStr">
         <is>
-          <t>10K Montmartre</t>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
         </is>
       </c>
       <c r="B823" s="5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>21K</t>
         </is>
       </c>
       <c r="C823" s="5" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D823" s="5" t="inlineStr">
         <is>
@@ -21063,34 +21063,34 @@
       </c>
     </row>
     <row r="824">
-      <c r="A824" s="8" t="inlineStr">
-        <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
-        </is>
-      </c>
-      <c r="B824" s="9" t="inlineStr">
-        <is>
-          <t>10K</t>
-        </is>
-      </c>
-      <c r="C824" s="9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D824" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E824" s="9" t="inlineStr">
-        <is>
-          <t>0:29:19</t>
+      <c r="A824" s="6" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid (Half)</t>
+        </is>
+      </c>
+      <c r="B824" s="7" t="inlineStr">
+        <is>
+          <t>21K</t>
+        </is>
+      </c>
+      <c r="C824" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D824" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E824" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="825">
       <c r="A825" s="4" t="inlineStr">
         <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
+          <t>10K Montmartre</t>
         </is>
       </c>
       <c r="B825" s="5" t="inlineStr">
@@ -21099,23 +21099,23 @@
         </is>
       </c>
       <c r="C825" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D825" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:14</t>
         </is>
       </c>
       <c r="E825" s="5" t="inlineStr">
         <is>
-          <t>0:28:45</t>
+          <t>0:35:46</t>
         </is>
       </c>
     </row>
     <row r="826">
       <c r="A826" s="8" t="inlineStr">
         <is>
-          <t>10K Valencia Ibercaja by Kiprun</t>
+          <t>10K Montmartre</t>
         </is>
       </c>
       <c r="B826" s="9" t="inlineStr">
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="C826" s="9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D826" s="9" t="inlineStr">
         <is>
@@ -21149,23 +21149,23 @@
         </is>
       </c>
       <c r="C827" s="5" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D827" s="5" t="inlineStr">
         <is>
-          <t>0:26:45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E827" s="5" t="inlineStr">
         <is>
-          <t>0:29:25</t>
+          <t>0:29:19</t>
         </is>
       </c>
     </row>
     <row r="828">
       <c r="A828" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Birmingham Run 10K</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B828" s="9" t="inlineStr">
@@ -21174,7 +21174,7 @@
         </is>
       </c>
       <c r="C828" s="9" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D828" s="9" t="inlineStr">
         <is>
@@ -21183,14 +21183,14 @@
       </c>
       <c r="E828" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:45</t>
         </is>
       </c>
     </row>
     <row r="829">
       <c r="A829" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Bristol Run 10K</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B829" s="5" t="inlineStr">
@@ -21215,7 +21215,7 @@
     <row r="830">
       <c r="A830" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run</t>
+          <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
       <c r="B830" s="9" t="inlineStr">
@@ -21224,23 +21224,23 @@
         </is>
       </c>
       <c r="C830" s="9" t="n">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="D830" s="9" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>0:26:45</t>
         </is>
       </c>
       <c r="E830" s="9" t="inlineStr">
         <is>
-          <t>0:30:51</t>
+          <t>0:29:25</t>
         </is>
       </c>
     </row>
     <row r="831">
       <c r="A831" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run</t>
+          <t>AJ Bell Great Birmingham Run 10K</t>
         </is>
       </c>
       <c r="B831" s="5" t="inlineStr">
@@ -21265,7 +21265,7 @@
     <row r="832">
       <c r="A832" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>AJ Bell Great Bristol Run 10K</t>
         </is>
       </c>
       <c r="B832" s="9" t="inlineStr">
@@ -21274,7 +21274,7 @@
         </is>
       </c>
       <c r="C832" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D832" s="9" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
     <row r="833">
       <c r="A833" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great Manchester Run (10K)</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B833" s="5" t="inlineStr">
@@ -21299,23 +21299,23 @@
         </is>
       </c>
       <c r="C833" s="5" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D833" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E833" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:30:51</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great North 10K</t>
+          <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
       <c r="B834" s="9" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="835">
       <c r="A835" s="4" t="inlineStr">
         <is>
-          <t>ASICS LDNX</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B835" s="5" t="inlineStr">
@@ -21349,7 +21349,7 @@
         </is>
       </c>
       <c r="C835" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D835" s="5" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
     <row r="836">
       <c r="A836" s="8" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>AJ Bell Great Manchester Run (10K)</t>
         </is>
       </c>
       <c r="B836" s="9" t="inlineStr">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="C836" s="9" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D836" s="9" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
     <row r="837">
       <c r="A837" s="4" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>AJ Bell Great North 10K</t>
         </is>
       </c>
       <c r="B837" s="5" t="inlineStr">
@@ -21399,23 +21399,23 @@
         </is>
       </c>
       <c r="C837" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D837" s="5" t="inlineStr">
         <is>
-          <t>0:29:37</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E837" s="5" t="inlineStr">
         <is>
-          <t>0:32:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" s="8" t="inlineStr">
         <is>
-          <t>Adidas 10K Paris</t>
+          <t>ASICS LDNX</t>
         </is>
       </c>
       <c r="B838" s="9" t="inlineStr">
@@ -21440,7 +21440,7 @@
     <row r="839">
       <c r="A839" s="4" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B839" s="5" t="inlineStr">
@@ -21453,19 +21453,19 @@
       </c>
       <c r="D839" s="5" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E839" s="5" t="inlineStr">
         <is>
-          <t>0:30:43</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="840">
       <c r="A840" s="8" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B840" s="9" t="inlineStr">
@@ -21478,19 +21478,19 @@
       </c>
       <c r="D840" s="9" t="inlineStr">
         <is>
-          <t>0:28:03</t>
+          <t>0:29:37</t>
         </is>
       </c>
       <c r="E840" s="9" t="inlineStr">
         <is>
-          <t>0:31:12</t>
+          <t>0:32:18</t>
         </is>
       </c>
     </row>
     <row r="841">
       <c r="A841" s="4" t="inlineStr">
         <is>
-          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
+          <t>Adidas 10K Paris</t>
         </is>
       </c>
       <c r="B841" s="5" t="inlineStr">
@@ -21508,14 +21508,14 @@
       </c>
       <c r="E841" s="5" t="inlineStr">
         <is>
-          <t>0:31:29</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="842">
       <c r="A842" s="8" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B842" s="9" t="inlineStr">
@@ -21528,19 +21528,19 @@
       </c>
       <c r="D842" s="9" t="inlineStr">
         <is>
-          <t>0:29:08</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E842" s="9" t="inlineStr">
         <is>
-          <t>0:33:25</t>
+          <t>0:30:43</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" s="4" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B843" s="5" t="inlineStr">
@@ -21553,19 +21553,19 @@
       </c>
       <c r="D843" s="5" t="inlineStr">
         <is>
-          <t>0:29:13</t>
+          <t>0:28:03</t>
         </is>
       </c>
       <c r="E843" s="5" t="inlineStr">
         <is>
-          <t>0:32:45</t>
+          <t>0:31:12</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" s="8" t="inlineStr">
         <is>
-          <t>BOLDERBoulder 10K</t>
+          <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
       <c r="B844" s="9" t="inlineStr">
@@ -21583,7 +21583,7 @@
       </c>
       <c r="E844" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:29</t>
         </is>
       </c>
     </row>
@@ -21599,23 +21599,23 @@
         </is>
       </c>
       <c r="C845" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D845" s="5" t="inlineStr">
         <is>
-          <t>0:28:36</t>
+          <t>0:29:08</t>
         </is>
       </c>
       <c r="E845" s="5" t="inlineStr">
         <is>
-          <t>0:31:51</t>
+          <t>0:33:25</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" s="8" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B846" s="9" t="inlineStr">
@@ -21624,23 +21624,23 @@
         </is>
       </c>
       <c r="C846" s="9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D846" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:13</t>
         </is>
       </c>
       <c r="E846" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:45</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" s="4" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B847" s="5" t="inlineStr">
@@ -21649,7 +21649,7 @@
         </is>
       </c>
       <c r="C847" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D847" s="5" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
     <row r="848">
       <c r="A848" s="8" t="inlineStr">
         <is>
-          <t>Bangsaen10</t>
+          <t>BOLDERBoulder 10K</t>
         </is>
       </c>
       <c r="B848" s="9" t="inlineStr">
@@ -21678,19 +21678,19 @@
       </c>
       <c r="D848" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:36</t>
         </is>
       </c>
       <c r="E848" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:51</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" s="4" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B849" s="5" t="inlineStr">
@@ -21703,19 +21703,19 @@
       </c>
       <c r="D849" s="5" t="inlineStr">
         <is>
-          <t>0:28:52</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E849" s="5" t="inlineStr">
         <is>
-          <t>0:31:59</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" s="8" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B850" s="9" t="inlineStr">
@@ -21728,19 +21728,19 @@
       </c>
       <c r="D850" s="9" t="inlineStr">
         <is>
-          <t>0:28:46</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E850" s="9" t="inlineStr">
         <is>
-          <t>0:32:33</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" s="4" t="inlineStr">
         <is>
-          <t>Cancer Research UK London Winter Run</t>
+          <t>Bangsaen10</t>
         </is>
       </c>
       <c r="B851" s="5" t="inlineStr">
@@ -21753,12 +21753,12 @@
       </c>
       <c r="D851" s="5" t="inlineStr">
         <is>
-          <t>0:29:22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E851" s="5" t="inlineStr">
         <is>
-          <t>0:34:32</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21774,23 +21774,23 @@
         </is>
       </c>
       <c r="C852" s="9" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D852" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:52</t>
         </is>
       </c>
       <c r="E852" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:59</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" s="4" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B853" s="5" t="inlineStr">
@@ -21799,23 +21799,23 @@
         </is>
       </c>
       <c r="C853" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D853" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:46</t>
         </is>
       </c>
       <c r="E853" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:33</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" s="8" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B854" s="9" t="inlineStr">
@@ -21824,23 +21824,23 @@
         </is>
       </c>
       <c r="C854" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D854" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:22</t>
         </is>
       </c>
       <c r="E854" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:34:32</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" s="4" t="inlineStr">
         <is>
-          <t>Cooper River Bridge Run</t>
+          <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
       <c r="B855" s="5" t="inlineStr">
@@ -21849,16 +21849,16 @@
         </is>
       </c>
       <c r="C855" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D855" s="5" t="inlineStr">
         <is>
-          <t>0:28:27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E855" s="5" t="inlineStr">
         <is>
-          <t>0:31:49</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
         </is>
       </c>
       <c r="C856" s="9" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D856" s="9" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
     <row r="857">
       <c r="A857" s="4" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B857" s="5" t="inlineStr">
@@ -21899,7 +21899,7 @@
         </is>
       </c>
       <c r="C857" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D857" s="5" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
     <row r="858">
       <c r="A858" s="8" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B858" s="9" t="inlineStr">
@@ -21924,23 +21924,23 @@
         </is>
       </c>
       <c r="C858" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D858" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:27</t>
         </is>
       </c>
       <c r="E858" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:49</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" s="4" t="inlineStr">
         <is>
-          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
+          <t>Cooper River Bridge Run</t>
         </is>
       </c>
       <c r="B859" s="5" t="inlineStr">
@@ -21974,7 +21974,7 @@
         </is>
       </c>
       <c r="C860" s="9" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D860" s="9" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
     <row r="861">
       <c r="A861" s="4" t="inlineStr">
         <is>
-          <t>Great Scottish Run 10K</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B861" s="5" t="inlineStr">
@@ -21999,7 +21999,7 @@
         </is>
       </c>
       <c r="C861" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D861" s="5" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
     <row r="862">
       <c r="A862" s="8" t="inlineStr">
         <is>
-          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B862" s="9" t="inlineStr">
@@ -22024,7 +22024,7 @@
         </is>
       </c>
       <c r="C862" s="9" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D862" s="9" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
     <row r="863">
       <c r="A863" s="4" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
       <c r="B863" s="5" t="inlineStr">
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="C863" s="5" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D863" s="5" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
     <row r="864">
       <c r="A864" s="8" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>Great Scottish Run 10K</t>
         </is>
       </c>
       <c r="B864" s="9" t="inlineStr">
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="C864" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D864" s="9" t="inlineStr">
         <is>
@@ -22083,14 +22083,14 @@
       </c>
       <c r="E864" s="9" t="inlineStr">
         <is>
-          <t>0:31:18</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" s="4" t="inlineStr">
         <is>
-          <t>NN San Silvestre Vallecana</t>
+          <t>NN CPC Loop Den Haag - 10 KM Loop</t>
         </is>
       </c>
       <c r="B865" s="5" t="inlineStr">
@@ -22099,23 +22099,23 @@
         </is>
       </c>
       <c r="C865" s="5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D865" s="5" t="inlineStr">
         <is>
-          <t>0:27:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E865" s="5" t="inlineStr">
         <is>
-          <t>0:31:11</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" s="8" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B866" s="9" t="inlineStr">
@@ -22140,7 +22140,7 @@
     <row r="867">
       <c r="A867" s="4" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B867" s="5" t="inlineStr">
@@ -22158,14 +22158,14 @@
       </c>
       <c r="E867" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:18</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" s="8" t="inlineStr">
         <is>
-          <t>Royal Run</t>
+          <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
       <c r="B868" s="9" t="inlineStr">
@@ -22178,19 +22178,19 @@
       </c>
       <c r="D868" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:27:41</t>
         </is>
       </c>
       <c r="E868" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:31:11</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B869" s="5" t="inlineStr">
@@ -22199,7 +22199,7 @@
         </is>
       </c>
       <c r="C869" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D869" s="5" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
     <row r="870">
       <c r="A870" s="8" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B870" s="9" t="inlineStr">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="C870" s="9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D870" s="9" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
     <row r="871">
       <c r="A871" s="4" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>Royal Run</t>
         </is>
       </c>
       <c r="B871" s="5" t="inlineStr">
@@ -22249,7 +22249,7 @@
         </is>
       </c>
       <c r="C871" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D871" s="5" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
     <row r="872">
       <c r="A872" s="8" t="inlineStr">
         <is>
-          <t>Run in Lyon (10K)</t>
+          <t>Run in Lyon</t>
         </is>
       </c>
       <c r="B872" s="9" t="inlineStr">
@@ -22290,7 +22290,7 @@
     <row r="873">
       <c r="A873" s="4" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B873" s="5" t="inlineStr">
@@ -22315,7 +22315,7 @@
     <row r="874">
       <c r="A874" s="8" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B874" s="9" t="inlineStr">
@@ -22328,19 +22328,19 @@
       </c>
       <c r="D874" s="9" t="inlineStr">
         <is>
-          <t>0:29:41</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E874" s="9" t="inlineStr">
         <is>
-          <t>0:32:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" s="4" t="inlineStr">
         <is>
-          <t>Saucony London 10K</t>
+          <t>Run in Lyon (10K)</t>
         </is>
       </c>
       <c r="B875" s="5" t="inlineStr">
@@ -22353,7 +22353,7 @@
       </c>
       <c r="D875" s="5" t="inlineStr">
         <is>
-          <t>0:29:33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E875" s="5" t="inlineStr">
@@ -22365,7 +22365,7 @@
     <row r="876">
       <c r="A876" s="8" t="inlineStr">
         <is>
-          <t>Standard Chartered KL 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B876" s="9" t="inlineStr">
@@ -22374,23 +22374,23 @@
         </is>
       </c>
       <c r="C876" s="9" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D876" s="9" t="inlineStr">
         <is>
-          <t>0:32:26</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E876" s="9" t="inlineStr">
         <is>
-          <t>0:39:23</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" s="4" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B877" s="5" t="inlineStr">
@@ -22399,23 +22399,23 @@
         </is>
       </c>
       <c r="C877" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D877" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:41</t>
         </is>
       </c>
       <c r="E877" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:51</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" s="8" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Saucony London 10K</t>
         </is>
       </c>
       <c r="B878" s="9" t="inlineStr">
@@ -22424,11 +22424,11 @@
         </is>
       </c>
       <c r="C878" s="9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D878" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:29:33</t>
         </is>
       </c>
       <c r="E878" s="9" t="inlineStr">
@@ -22440,7 +22440,7 @@
     <row r="879">
       <c r="A879" s="4" t="inlineStr">
         <is>
-          <t>Statesman Capitol 10K</t>
+          <t>Standard Chartered KL 10K</t>
         </is>
       </c>
       <c r="B879" s="5" t="inlineStr">
@@ -22453,19 +22453,19 @@
       </c>
       <c r="D879" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:26</t>
         </is>
       </c>
       <c r="E879" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:39:23</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" s="8" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B880" s="9" t="inlineStr">
@@ -22490,7 +22490,7 @@
     <row r="881">
       <c r="A881" s="4" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B881" s="5" t="inlineStr">
@@ -22515,7 +22515,7 @@
     <row r="882">
       <c r="A882" s="8" t="inlineStr">
         <is>
-          <t>Transurban Bridge to Brisbane</t>
+          <t>Statesman Capitol 10K</t>
         </is>
       </c>
       <c r="B882" s="9" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="883">
       <c r="A883" s="4" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B883" s="5" t="inlineStr">
@@ -22565,7 +22565,7 @@
     <row r="884">
       <c r="A884" s="8" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B884" s="9" t="inlineStr">
@@ -22590,7 +22590,7 @@
     <row r="885">
       <c r="A885" s="4" t="inlineStr">
         <is>
-          <t>Ukrop's Monument Avenue 10K</t>
+          <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
       <c r="B885" s="5" t="inlineStr">
@@ -22615,7 +22615,7 @@
     <row r="886">
       <c r="A886" s="8" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B886" s="9" t="inlineStr">
@@ -22640,7 +22640,7 @@
     <row r="887">
       <c r="A887" s="4" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B887" s="5" t="inlineStr">
@@ -22665,7 +22665,7 @@
     <row r="888">
       <c r="A888" s="8" t="inlineStr">
         <is>
-          <t>Vancouver Sun Run</t>
+          <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
       <c r="B888" s="9" t="inlineStr">
@@ -22678,19 +22678,19 @@
       </c>
       <c r="D888" s="9" t="inlineStr">
         <is>
-          <t>0:28:09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E888" s="9" t="inlineStr">
         <is>
-          <t>0:32:54</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" s="4" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Vancouver Sun Run</t>
         </is>
       </c>
       <c r="B889" s="5" t="inlineStr">
@@ -22715,7 +22715,7 @@
     <row r="890">
       <c r="A890" s="8" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Vancouver Sun Run</t>
         </is>
       </c>
       <c r="B890" s="9" t="inlineStr">
@@ -22728,19 +22728,19 @@
       </c>
       <c r="D890" s="9" t="inlineStr">
         <is>
-          <t>0:29:14</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E890" s="9" t="inlineStr">
         <is>
-          <t>0:31:36</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" s="4" t="inlineStr">
         <is>
-          <t>Vitality London 10,000</t>
+          <t>Vancouver Sun Run</t>
         </is>
       </c>
       <c r="B891" s="5" t="inlineStr">
@@ -22753,28 +22753,28 @@
       </c>
       <c r="D891" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:28:09</t>
         </is>
       </c>
       <c r="E891" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:32:54</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great Birmingham Run</t>
+          <t>Vitality London 10,000</t>
         </is>
       </c>
       <c r="B892" s="9" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C892" s="9" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D892" s="9" t="inlineStr">
         <is>
@@ -22790,37 +22790,37 @@
     <row r="893">
       <c r="A893" s="4" t="inlineStr">
         <is>
-          <t>AJ Bell Great South Run</t>
+          <t>Vitality London 10,000</t>
         </is>
       </c>
       <c r="B893" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C893" s="5" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D893" s="5" t="inlineStr">
         <is>
-          <t>0:47:19</t>
+          <t>0:29:14</t>
         </is>
       </c>
       <c r="E893" s="5" t="inlineStr">
         <is>
-          <t>0:50:42</t>
+          <t>0:31:36</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="8" t="inlineStr">
         <is>
-          <t>AJ Bell Great South Run</t>
+          <t>Vitality London 10,000</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C894" s="9" t="n">
@@ -22840,7 +22840,7 @@
     <row r="895">
       <c r="A895" s="4" t="inlineStr">
         <is>
-          <t>Army Ten Miler</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B895" s="5" t="inlineStr">
@@ -22849,11 +22849,11 @@
         </is>
       </c>
       <c r="C895" s="5" t="n">
-        <v>2025</v>
+        <v>2013</v>
       </c>
       <c r="D895" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:21</t>
         </is>
       </c>
       <c r="E895" s="5" t="inlineStr">
@@ -22865,7 +22865,7 @@
     <row r="896">
       <c r="A896" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B896" s="9" t="inlineStr">
@@ -22874,23 +22874,23 @@
         </is>
       </c>
       <c r="C896" s="9" t="n">
-        <v>2005</v>
+        <v>2014</v>
       </c>
       <c r="D896" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:05</t>
         </is>
       </c>
       <c r="E896" s="9" t="inlineStr">
         <is>
-          <t>0:38:22</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" s="4" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B897" s="5" t="inlineStr">
@@ -22899,11 +22899,11 @@
         </is>
       </c>
       <c r="C897" s="5" t="n">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="D897" s="5" t="inlineStr">
         <is>
-          <t>0:33:31</t>
+          <t>1:01:47</t>
         </is>
       </c>
       <c r="E897" s="5" t="inlineStr">
@@ -22915,7 +22915,7 @@
     <row r="898">
       <c r="A898" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B898" s="9" t="inlineStr">
@@ -22924,23 +22924,23 @@
         </is>
       </c>
       <c r="C898" s="9" t="n">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="D898" s="9" t="inlineStr">
         <is>
-          <t>0:34:15</t>
+          <t>1:02:07</t>
         </is>
       </c>
       <c r="E898" s="9" t="inlineStr">
         <is>
-          <t>0:38:07</t>
+          <t>1:13:51</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" s="4" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B899" s="5" t="inlineStr">
@@ -22949,23 +22949,23 @@
         </is>
       </c>
       <c r="C899" s="5" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="D899" s="5" t="inlineStr">
         <is>
-          <t>0:34:40</t>
+          <t>1:00:37</t>
         </is>
       </c>
       <c r="E899" s="5" t="inlineStr">
         <is>
-          <t>0:39:02</t>
+          <t>1:13:42</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B900" s="9" t="inlineStr">
@@ -22974,23 +22974,23 @@
         </is>
       </c>
       <c r="C900" s="9" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D900" s="9" t="inlineStr">
         <is>
-          <t>0:35:01</t>
+          <t>1:02:56</t>
         </is>
       </c>
       <c r="E900" s="9" t="inlineStr">
         <is>
-          <t>0:39:28</t>
+          <t>1:14:38</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" s="4" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B901" s="5" t="inlineStr">
@@ -22999,23 +22999,23 @@
         </is>
       </c>
       <c r="C901" s="5" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D901" s="5" t="inlineStr">
         <is>
-          <t>0:36:10</t>
+          <t>1:00:34</t>
         </is>
       </c>
       <c r="E901" s="5" t="inlineStr">
         <is>
-          <t>0:42:05</t>
+          <t>1:13:04</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" s="8" t="inlineStr">
         <is>
-          <t>Bay to Breakers</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B902" s="9" t="inlineStr">
@@ -23024,23 +23024,23 @@
         </is>
       </c>
       <c r="C902" s="9" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D902" s="9" t="inlineStr">
         <is>
-          <t>0:37:02</t>
+          <t>0:59:31</t>
         </is>
       </c>
       <c r="E902" s="9" t="inlineStr">
         <is>
-          <t>0:43:48</t>
+          <t>1:09:50</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" s="4" t="inlineStr">
         <is>
-          <t>Boilermaker Road Race</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B903" s="5" t="inlineStr">
@@ -23049,23 +23049,23 @@
         </is>
       </c>
       <c r="C903" s="5" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D903" s="5" t="inlineStr">
         <is>
-          <t>0:42:44</t>
+          <t>1:00:01</t>
         </is>
       </c>
       <c r="E903" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:11:11</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" s="8" t="inlineStr">
         <is>
-          <t>Broad Street Run</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B904" s="9" t="inlineStr">
@@ -23074,23 +23074,23 @@
         </is>
       </c>
       <c r="C904" s="9" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D904" s="9" t="inlineStr">
         <is>
-          <t>0:46:13</t>
+          <t>1:00:15</t>
         </is>
       </c>
       <c r="E904" s="9" t="inlineStr">
         <is>
-          <t>0:54:01</t>
+          <t>1:10:44</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" s="4" t="inlineStr">
         <is>
-          <t>City2Surf</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B905" s="5" t="inlineStr">
@@ -23103,19 +23103,19 @@
       </c>
       <c r="D905" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:57</t>
         </is>
       </c>
       <c r="E905" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1:10:56</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>20KM de Bruxelles</t>
         </is>
       </c>
       <c r="B906" s="9" t="inlineStr">
@@ -23124,32 +23124,32 @@
         </is>
       </c>
       <c r="C906" s="9" t="n">
-        <v>2009</v>
+        <v>2025</v>
       </c>
       <c r="D906" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:59:26</t>
         </is>
       </c>
       <c r="E906" s="9" t="inlineStr">
         <is>
-          <t>0:50:39</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>AJ Bell Great Birmingham Run</t>
         </is>
       </c>
       <c r="B907" s="5" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>SEMI</t>
         </is>
       </c>
       <c r="C907" s="5" t="n">
-        <v>2010</v>
+        <v>2025</v>
       </c>
       <c r="D907" s="5" t="inlineStr">
         <is>
@@ -23158,14 +23158,14 @@
       </c>
       <c r="E907" s="5" t="inlineStr">
         <is>
-          <t>0:51:30</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>AJ Bell Great South Run</t>
         </is>
       </c>
       <c r="B908" s="9" t="inlineStr">
@@ -23174,23 +23174,23 @@
         </is>
       </c>
       <c r="C908" s="9" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="D908" s="9" t="inlineStr">
         <is>
-          <t>0:44:27</t>
+          <t>0:47:19</t>
         </is>
       </c>
       <c r="E908" s="9" t="inlineStr">
         <is>
-          <t>0:51:57</t>
+          <t>0:50:42</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>AJ Bell Great South Run</t>
         </is>
       </c>
       <c r="B909" s="5" t="inlineStr">
@@ -23199,23 +23199,23 @@
         </is>
       </c>
       <c r="C909" s="5" t="n">
-        <v>2012</v>
+        <v>2025</v>
       </c>
       <c r="D909" s="5" t="inlineStr">
         <is>
-          <t>0:44:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E909" s="5" t="inlineStr">
         <is>
-          <t>0:51:42</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Army Ten Miler</t>
         </is>
       </c>
       <c r="B910" s="9" t="inlineStr">
@@ -23224,23 +23224,23 @@
         </is>
       </c>
       <c r="C910" s="9" t="n">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="D910" s="9" t="inlineStr">
         <is>
-          <t>0:45:28</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E910" s="9" t="inlineStr">
         <is>
-          <t>0:51:33</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Baloise Antwerp 10 miles</t>
         </is>
       </c>
       <c r="B911" s="5" t="inlineStr">
@@ -23249,23 +23249,23 @@
         </is>
       </c>
       <c r="C911" s="5" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="D911" s="5" t="inlineStr">
         <is>
-          <t>0:45:45</t>
+          <t>0:48:48</t>
         </is>
       </c>
       <c r="E911" s="5" t="inlineStr">
         <is>
-          <t>0:53:09</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Baloise Antwerp 10 miles</t>
         </is>
       </c>
       <c r="B912" s="9" t="inlineStr">
@@ -23274,23 +23274,23 @@
         </is>
       </c>
       <c r="C912" s="9" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="D912" s="9" t="inlineStr">
         <is>
-          <t>0:45:15</t>
+          <t>0:47:50</t>
         </is>
       </c>
       <c r="E912" s="9" t="inlineStr">
         <is>
-          <t>0:50:45</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Baloise Antwerp 10 miles</t>
         </is>
       </c>
       <c r="B913" s="5" t="inlineStr">
@@ -23299,23 +23299,23 @@
         </is>
       </c>
       <c r="C913" s="5" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D913" s="5" t="inlineStr">
         <is>
-          <t>0:49:00</t>
+          <t>0:47:21</t>
         </is>
       </c>
       <c r="E913" s="5" t="inlineStr">
         <is>
-          <t>0:55:44</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" s="8" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B914" s="9" t="inlineStr">
@@ -23324,23 +23324,23 @@
         </is>
       </c>
       <c r="C914" s="9" t="n">
-        <v>2024</v>
+        <v>2005</v>
       </c>
       <c r="D914" s="9" t="inlineStr">
         <is>
-          <t>0:44:51</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E914" s="9" t="inlineStr">
         <is>
-          <t>0:51:15</t>
+          <t>0:38:22</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" s="4" t="inlineStr">
         <is>
-          <t>Dam tot Damloop</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B915" s="5" t="inlineStr">
@@ -23349,23 +23349,23 @@
         </is>
       </c>
       <c r="C915" s="5" t="n">
-        <v>2025</v>
+        <v>2009</v>
       </c>
       <c r="D915" s="5" t="inlineStr">
         <is>
-          <t>0:46:07</t>
+          <t>0:33:31</t>
         </is>
       </c>
       <c r="E915" s="5" t="inlineStr">
         <is>
-          <t>0:50:51</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" s="8" t="inlineStr">
         <is>
-          <t>Falmouth Road Race</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B916" s="9" t="inlineStr">
@@ -23374,48 +23374,48 @@
         </is>
       </c>
       <c r="C916" s="9" t="n">
-        <v>2025</v>
+        <v>2010</v>
       </c>
       <c r="D916" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:34:15</t>
         </is>
       </c>
       <c r="E916" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:38:07</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" s="4" t="inlineStr">
         <is>
-          <t>Great Scottish Run</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B917" s="5" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="C917" s="5" t="n">
-        <v>2025</v>
+        <v>2012</v>
       </c>
       <c r="D917" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:34:40</t>
         </is>
       </c>
       <c r="E917" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:39:02</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="8" t="inlineStr">
         <is>
-          <t>Lilac Bloomsday Run</t>
+          <t>Bay to Breakers</t>
         </is>
       </c>
       <c r="B918" s="9" t="inlineStr">
@@ -23424,46 +23424,496 @@
         </is>
       </c>
       <c r="C918" s="9" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D918" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:35:01</t>
         </is>
       </c>
       <c r="E918" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0:39:28</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" s="4" t="inlineStr">
         <is>
+          <t>Bay to Breakers</t>
+        </is>
+      </c>
+      <c r="B919" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C919" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D919" s="5" t="inlineStr">
+        <is>
+          <t>0:36:10</t>
+        </is>
+      </c>
+      <c r="E919" s="5" t="inlineStr">
+        <is>
+          <t>0:42:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="8" t="inlineStr">
+        <is>
+          <t>Bay to Breakers</t>
+        </is>
+      </c>
+      <c r="B920" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C920" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D920" s="9" t="inlineStr">
+        <is>
+          <t>0:37:02</t>
+        </is>
+      </c>
+      <c r="E920" s="9" t="inlineStr">
+        <is>
+          <t>0:43:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="4" t="inlineStr">
+        <is>
+          <t>Boilermaker Road Race</t>
+        </is>
+      </c>
+      <c r="B921" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C921" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D921" s="5" t="inlineStr">
+        <is>
+          <t>0:42:44</t>
+        </is>
+      </c>
+      <c r="E921" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="8" t="inlineStr">
+        <is>
+          <t>Broad Street Run</t>
+        </is>
+      </c>
+      <c r="B922" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C922" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D922" s="9" t="inlineStr">
+        <is>
+          <t>0:46:13</t>
+        </is>
+      </c>
+      <c r="E922" s="9" t="inlineStr">
+        <is>
+          <t>0:54:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="4" t="inlineStr">
+        <is>
+          <t>City2Surf</t>
+        </is>
+      </c>
+      <c r="B923" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C923" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D923" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E923" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B924" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C924" s="9" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D924" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E924" s="9" t="inlineStr">
+        <is>
+          <t>0:50:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B925" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C925" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D925" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E925" s="5" t="inlineStr">
+        <is>
+          <t>0:51:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B926" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C926" s="9" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D926" s="9" t="inlineStr">
+        <is>
+          <t>0:44:27</t>
+        </is>
+      </c>
+      <c r="E926" s="9" t="inlineStr">
+        <is>
+          <t>0:51:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B927" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C927" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D927" s="5" t="inlineStr">
+        <is>
+          <t>0:44:48</t>
+        </is>
+      </c>
+      <c r="E927" s="5" t="inlineStr">
+        <is>
+          <t>0:51:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B928" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C928" s="9" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D928" s="9" t="inlineStr">
+        <is>
+          <t>0:45:28</t>
+        </is>
+      </c>
+      <c r="E928" s="9" t="inlineStr">
+        <is>
+          <t>0:51:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B929" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C929" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D929" s="5" t="inlineStr">
+        <is>
+          <t>0:45:45</t>
+        </is>
+      </c>
+      <c r="E929" s="5" t="inlineStr">
+        <is>
+          <t>0:53:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B930" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C930" s="9" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D930" s="9" t="inlineStr">
+        <is>
+          <t>0:45:15</t>
+        </is>
+      </c>
+      <c r="E930" s="9" t="inlineStr">
+        <is>
+          <t>0:50:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B931" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C931" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D931" s="5" t="inlineStr">
+        <is>
+          <t>0:49:00</t>
+        </is>
+      </c>
+      <c r="E931" s="5" t="inlineStr">
+        <is>
+          <t>0:55:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="8" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B932" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C932" s="9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D932" s="9" t="inlineStr">
+        <is>
+          <t>0:44:51</t>
+        </is>
+      </c>
+      <c r="E932" s="9" t="inlineStr">
+        <is>
+          <t>0:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="4" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="B933" s="5" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C933" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D933" s="5" t="inlineStr">
+        <is>
+          <t>0:46:07</t>
+        </is>
+      </c>
+      <c r="E933" s="5" t="inlineStr">
+        <is>
+          <t>0:50:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="8" t="inlineStr">
+        <is>
+          <t>Falmouth Road Race</t>
+        </is>
+      </c>
+      <c r="B934" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C934" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D934" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E934" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="4" t="inlineStr">
+        <is>
+          <t>Great Scottish Run</t>
+        </is>
+      </c>
+      <c r="B935" s="5" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="C935" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D935" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E935" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="8" t="inlineStr">
+        <is>
+          <t>Lilac Bloomsday Run</t>
+        </is>
+      </c>
+      <c r="B936" s="9" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="C936" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D936" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E936" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="4" t="inlineStr">
+        <is>
           <t>Manchester Road Race</t>
         </is>
       </c>
-      <c r="B919" s="5" t="inlineStr">
+      <c r="B937" s="5" t="inlineStr">
         <is>
           <t>AUTRE</t>
         </is>
       </c>
-      <c r="C919" s="5" t="n">
+      <c r="C937" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="D919" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E919" s="5" t="inlineStr">
+      <c r="D937" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E937" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E919"/>
+  <autoFilter ref="A1:E937"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>